--- a/API데이터_경기_득점_및_도움_기록.xlsx
+++ b/API데이터_경기_득점_및_도움_기록.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,310 +452,310 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-19 16:32:52</t>
+          <t>2026-09-20 11:27:42</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(2골), 스페인전도사_866235522(2골), 여수가스_861215732(1골)</t>
+          <t>호야국2인_851216409(1골), 호야국2인_848232293(1골), 개포동덕배_845190048(1골), 개포동덕배_856202126(3골), 개포동덕배_848206113(1골)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-19 16:20:51</t>
+          <t>2026-09-20 11:16:23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1_4</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(1골), 여수가스_861162895(1골), 여수가스_861215732(3골)</t>
+          <t>호야국2인_851216409(1골), 호야국2인_848232293(1골), 호야국2인_846192505(1골), 호야국2인_845198219(1골), 개포동덕배_845168473(1골), 개포동덕배_845190048(1골), 개포동덕배_856202126(2골)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-19 15:34:28</t>
+          <t>2026-09-20 10:36:38</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3_8</t>
+          <t>6_0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_867166676(2골), Voor_845247090(1골), Voor_852233700(2골), Voor_845009676(1골), Voor_858020775(2골), Voor_851238616(1골), Voor_845001620(1골)</t>
+          <t>호야국2인_845198219(1골), 호야국2인_848232293(3골), 호야국2인_848216435(2골)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-19 15:21:21</t>
+          <t>2026-09-20 10:25:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), Voor_845247090(1골), Voor_845009676(2골)</t>
+          <t>호야국2인_848232293(1골), 호야국2인_848216435(1골)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-19 15:17:09</t>
+          <t>2026-09-20 10:10:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(1골), 스페인전도사_845224574(1골), 콩콩콩룔_866223710(3골), 콩콩콩룔_867220502(1골), 콩콩콩룔_867223848(1골)</t>
+          <t>여수가스_861215732(4골), 겐지간지_814231747(1골), 겐지간지_826247635(1골), 겐지간지_856237679(1골)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-19 15:08:18</t>
+          <t>2026-09-20 09:58:44</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>은안_866241236(1골), 은안_856246420(1골), Voor_845009676(1골), Voor_858020775(1골)</t>
+          <t>여수가스_861162895(1골), 여수가스_861215732(2골), 여수가스_846001551(1골), 겐지간지_814231747(1골)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-19 15:05:47</t>
+          <t>2026-09-20 08:25:43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>스페인전도사</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>콩콩콩룔</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>6_3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(1골), 콩콩콩룔_848189505(1골), 콩콩콩룔_866223710(1골)</t>
+          <t>개포동덕배_845208722(1골), 개포동덕배_856202126(2골), 개포동덕배_845190048(3골), 스페인전도사_845224574(1골), 스페인전도사_867192629(2골)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-19 14:56:37</t>
+          <t>2026-09-20 08:14:10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2_8</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>은안_866241236(1골), 은안_856246420(1골), Voor_845009676(2골), Voor_852233700(4골), Voor_858020775(2골)</t>
+          <t>개포동덕배_856202126(1골), 개포동덕배_863212622(1골), 개포동덕배_845190048(4골), 개포동덕배_863234396(1골), 스페인전도사_867192629(1골), 스페인전도사_866235522(1골)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-19 14:24:16</t>
+          <t>2026-09-20 08:13:05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골)</t>
+          <t>suma수마_861190046(1골), suma수마_861221162(1골), 셀래스틴_863251854(1골), 셀래스틴_856277179(1골)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-19 14:13:53</t>
+          <t>2026-09-20 08:02:06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5_5</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -765,29 +765,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(2골), 앙쿠_851194765(3골), UNIT_867166676(1골), UNIT_848180930(4골)</t>
+          <t>suma수마_861190046(2골), suma수마_861221162(2골), 셀래스틴_861026709(1골), 셀래스틴_852241461(1골), 셀래스틴_836158023(1골)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-19 13:54:08</t>
+          <t>2026-09-20 07:39:16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -797,147 +797,147 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 앙쿠_848176580(3골), UNIT_867166676(4골)</t>
+          <t>A지냐크_861167134(2골), A지냐크_855213648(1골), 겐지간지_856237679(1골), 겐지간지_814231747(1골)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-19 13:36:20</t>
+          <t>2026-09-20 07:25:46</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>앙쿠_866266039(1골), 앙쿠_848176580(1골)</t>
+          <t>겐지간지_856237679(1골)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-19 13:25:57</t>
+          <t>2026-09-20 07:08:13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>앙쿠_863232488(1골), 앙쿠_848176580(1골), UNIT_848180930(1골), UNIT_840228251(1골), UNIT_840192883(1골)</t>
+          <t>Legend독수리_836054050(1골), Legend독수리_848140601(1골), Legend독수리_864039943(2골), 겐지간지_852231443(1골)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-19 12:33:16</t>
+          <t>2026-09-20 06:55:35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), UNIT_848180930(2골), 셀래스틴_868222481(1골), 셀래스틴_852241461(2골)</t>
+          <t>Legend독수리_840192505(1골), 겐지간지_848170890(1골), 겐지간지_814231747(1골), 겐지간지_856237679(1골)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-19 12:20:50</t>
+          <t>2026-09-20 06:18:57</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>0_2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), UNIT_840228251(1골), 셀래스틴_863277643(1골)</t>
+          <t>suma수마_861221162(2골)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-19 12:10:22</t>
+          <t>2026-09-20 06:05:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -947,71 +947,71 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>2_10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(3골), 앙쿠_866266039(1골), suma수마_861013383(1골), suma수마_861221162(1골)</t>
+          <t>A지냐크_848031432(1골), A지냐크_861167134(1골), suma수마_861221162(10골)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-19 12:06:46</t>
+          <t>2026-09-20 05:45:06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2골), 셀래스틴_863277643(1골), 셀래스틴_845158023(2골), 셀래스틴_863251854(1골)</t>
+          <t>suma수마_861013383(1골), suma수마_861190046(1골), suma수마_861221162(3골), ShangHaiPortFC_861051412(1골), ShangHaiPortFC_845231138(1골)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-19 11:59:22</t>
+          <t>2026-09-20 05:33:58</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1021,29 +1021,29 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2골), 앙쿠_863246191(2골), 앙쿠_866266039(1골), suma수마_840001114(1골), suma수마_861190046(1골)</t>
+          <t>suma수마_861190046(2골), suma수마_861221162(2골), ShangHaiPortFC_864191910(1골), ShangHaiPortFC_848031432(2골)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-19 11:55:57</t>
+          <t>2026-09-20 05:20:20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1053,51 +1053,51 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(1골), ZD장인지참치_852213331(1골), 셀래스틴_846199564(1골), 셀래스틴_863277643(1골), 셀래스틴_856277179(1골)</t>
+          <t>앙쿠_848176580(2골), 앙쿠_851194765(2골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_827143001(1골)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-19 11:38:35</t>
+          <t>2026-09-20 05:09:38</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ZD장인지참치_839200104(1골), 경남FC가즈아_853221467(1골), 경남FC가즈아_225238224(1골)</t>
+          <t>앙쿠_846193747(1골), 앙쿠_814226161(1골), 앙쿠_863246191(2골)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-19 11:35:15</t>
+          <t>2026-09-20 03:47:49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1107,39 +1107,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>suma수마_861221162(2골), 셀래스틴_852241461(2골)</t>
+          <t>Legend독수리_840192505(2골), Legend독수리_861007518(1골), 셀래스틴_863277643(1골), 셀래스틴_852241461(2골), 셀래스틴_856277179(1골)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-19 11:32:23</t>
+          <t>2026-09-20 03:44:09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>8_3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1149,29 +1149,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(3골), 개포동덕배_845208722(1골), 개포동덕배_848206113(1골), UNIT_848180930(1골), UNIT_851236403(1골)</t>
+          <t>앙쿠_848176580(3골), 앙쿠_863246191(2골), 앙쿠_851194765(3골), ShangHaiPortFC_848031432(2골), ShangHaiPortFC_864191910(1골)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-19 11:27:23</t>
+          <t>2026-09-20 03:36:07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1181,93 +1181,93 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ZD장인지참치_861182521(1골), ZD장인지참치_851240740(1골), ZD장인지참치_840256630(1골), 경남FC가즈아_518200601(1골)</t>
+          <t>Legend독수리_840192505(1골), Legend독수리_861230025(1골), Legend독수리_839226764(1골), 셀래스틴_856277179(2골)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-19 11:23:35</t>
+          <t>2026-09-20 03:31:53</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>suma수마_861221162(2골), 셀래스틴_845158023(1골), 셀래스틴_856277179(1골), 셀래스틴_852241461(1골), 셀래스틴_863277643(1골)</t>
+          <t>앙쿠_848176580(2골), 앙쿠_863246191(2골), 앙쿠_863232488(1골), 앙쿠_866266039(1골), ShangHaiPortFC_864191910(1골)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-19 11:21:04</t>
+          <t>2026-09-20 03:17:22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(2골), UNIT_840210736(1골), UNIT_867166676(2골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_848176580(2골), 셀래스틴_852241461(1골), 셀래스틴_845158023(1골)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-19 11:06:32</t>
+          <t>2026-09-20 03:17:01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1277,121 +1277,125 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>A지냐크_848031432(1골), A지냐크_863241496(1골), 경남FC가즈아_864139443(1골), 경남FC가즈아_225238224(1골), 경남FC가즈아_277205156(1골)</t>
+          <t>Legend독수리_861007518(1골), Legend독수리_821143001(1골), ShangHaiPortFC_864191910(4골)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-19 10:53:44</t>
+          <t>2026-09-20 03:05:59</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>8_3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Legend독수리_840192505(4골), Legend독수리_866259399(2골), Legend독수리_839226764(1골), Legend독수리_861230025(1골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_284190813(1골), ShangHaiPortFC_861051412(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-19 10:46:09</t>
+          <t>2026-09-19 16:32:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4_5</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>A지냐크_848031432(1골), A지냐크_861167134(1골), A지냐크_840236496(1골), A지냐크_863241496(1골), 스페인전도사_858008348(1골), 스페인전도사_867192629(3골), 스페인전도사_866235522(1골)</t>
+          <t>스페인전도사_867192629(2골), 스페인전도사_866235522(2골), 여수가스_861215732(1골)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-19 10:33:32</t>
+          <t>2026-09-19 16:20:51</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>A지냐크_848031432(3골), 스페인전도사_866235522(1골), 스페인전도사_861001668(1골)</t>
+          <t>스페인전도사_867192629(1골), 여수가스_861162895(1골), 여수가스_861215732(3골)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-19 10:19:19</t>
+          <t>2026-09-19 15:34:28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0_4</t>
+          <t>3_8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1401,157 +1405,157 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(2골), 앙쿠_848176580(2골)</t>
+          <t>UNIT_848180930(1골), UNIT_867166676(2골), Voor_845247090(1골), Voor_852233700(2골), Voor_845009676(1골), Voor_858020775(2골), Voor_851238616(1골), Voor_845001620(1골)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-19 10:06:31</t>
+          <t>2026-09-19 15:21:21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>A지냐크_848031432(1골), A지냐크_861167134(1골), A지냐크_867214101(1골), 앙쿠_863246191(2골), 앙쿠_848176580(1골)</t>
+          <t>UNIT_867166676(2골), Voor_845247090(1골), Voor_845009676(2골)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-19 09:48:12</t>
+          <t>2026-09-19 15:17:09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1골), UNIT_848265695(1골), UNIT_848180930(3골), 검정소_868013128(4골)</t>
+          <t>스페인전도사_867192629(1골), 스페인전도사_845224574(1골), 콩콩콩룔_866223710(3골), 콩콩콩룔_867220502(1골), 콩콩콩룔_867223848(1골)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-19 09:36:18</t>
+          <t>2026-09-19 15:08:18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>검정소_868192181(1골)</t>
+          <t>은안_866241236(1골), 은안_856246420(1골), Voor_845009676(1골), Voor_858020775(1골)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-19 09:21:02</t>
+          <t>2026-09-19 15:05:47</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(2골), 검정소_868013128(2골)</t>
+          <t>스페인전도사_867192629(1골), 콩콩콩룔_848189505(1골), 콩콩콩룔_866223710(1골)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-19 09:14:49</t>
+          <t>2026-09-19 14:56:37</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3_5</t>
+          <t>2_8</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1561,14 +1565,14 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>오스트리아_864182152(2골), 오스트리아_851236636(1골), ZD장인지참치_840256630(1골), ZD장인지참치_839200104(3골), ZD장인지참치_840191208(1골)</t>
+          <t>은안_866241236(1골), 은안_856246420(1골), Voor_845009676(2골), Voor_852233700(4골), Voor_858020775(2골)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-19 09:10:07</t>
+          <t>2026-09-19 14:24:16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1578,44 +1582,44 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2골), 앙쿠_851194765(1골), 검정소_867241096(1골)</t>
+          <t>UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-19 09:03:03</t>
+          <t>2026-09-19 14:13:53</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>5_5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1625,29 +1629,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>오스트리아_862140057(1골), 오스트리아_864199266(2골), ZD장인지참치_840256630(1골)</t>
+          <t>앙쿠_863246191(2골), 앙쿠_851194765(3골), UNIT_867166676(1골), UNIT_848180930(4골)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-19 08:47:53</t>
+          <t>2026-09-19 13:54:08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>오스트리아</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1657,121 +1661,125 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UNIT_840192883(2골), UNIT_867166676(3골), 오스트리아_864182152(1골), 오스트리아_864199266(1골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_848176580(3골), UNIT_867166676(4골)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-19 08:36:31</t>
+          <t>2026-09-19 13:36:20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>오스트리아</t>
-        </is>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>앙쿠_866266039(1골), 앙쿠_848176580(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-19 08:35:13</t>
+          <t>2026-09-19 13:25:57</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>오스트리아</t>
-        </is>
-      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), UNIT_848180930(1골), 오스트리아_864199266(2골)</t>
+          <t>앙쿠_863232488(1골), 앙쿠_848176580(1골), UNIT_848180930(1골), UNIT_840228251(1골), UNIT_840192883(1골)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-19 08:24:13</t>
+          <t>2026-09-19 12:33:16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4_8</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(4골), ZD장인지참치_840247263(2골), ZD장인지참치_839200104(4골), ZD장인지참치_840191208(2골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(2골), 셀래스틴_868222481(1골), 셀래스틴_852241461(2골)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-19 08:15:28</t>
+          <t>2026-09-19 12:20:50</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1781,56 +1789,56 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>오스트리아_826204497(1골), 오스트리아_864182152(1골), suma수마_861221162(1골)</t>
+          <t>UNIT_848180930(2골), UNIT_840228251(1골), 셀래스틴_863277643(1골)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-19 08:12:24</t>
+          <t>2026-09-19 12:10:22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ZD장인지참치_861182521(1골)</t>
+          <t>앙쿠_848176580(3골), 앙쿠_866266039(1골), suma수마_861013383(1골), suma수마_861221162(1골)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-19 08:09:08</t>
+          <t>2026-09-19 12:06:46</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1845,19 +1853,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(2골), ZD장인지참치_839200104(1골), ZD장인지참치_848199503(1골), ZD장인지참치_851240740(1골), ZD장인지참치_840191208(1골)</t>
+          <t>ZD장인지참치_840191208(2골), 셀래스틴_863277643(1골), 셀래스틴_845158023(2골), 셀래스틴_863251854(1골)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-19 08:03:54</t>
+          <t>2026-09-19 11:59:22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1877,189 +1885,189 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>오스트리아_862140057(1골), 오스트리아_864182152(1골), 오스트리아_851236636(1골), 오스트리아_864199266(2골), suma수마_861221162(1골), suma수마_861190046(1골)</t>
+          <t>앙쿠_848176580(2골), 앙쿠_863246191(2골), 앙쿠_866266039(1골), suma수마_840001114(1골), suma수마_861190046(1골)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-19 05:58:58</t>
+          <t>2026-09-19 11:55:57</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), 비주류중독_840052241(1골)</t>
+          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(1골), ZD장인지참치_852213331(1골), 셀래스틴_846199564(1골), 셀래스틴_863277643(1골), 셀래스틴_856277179(1골)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-19 05:47:10</t>
+          <t>2026-09-19 11:38:35</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), UNIT_848180930(2골), 비주류중독_862180283(1골)</t>
+          <t>ZD장인지참치_839200104(1골), 경남FC가즈아_853221467(1골), 경남FC가즈아_225238224(1골)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-19 05:24:55</t>
+          <t>2026-09-19 11:35:15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Legend독수리_848140601(1골), 경남FC가즈아_225238224(1골), 경남FC가즈아_805267825(1골)</t>
+          <t>suma수마_861221162(2골), 셀래스틴_852241461(2골)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-19 05:13:36</t>
+          <t>2026-09-19 11:32:23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Legend독수리_821143001(1골), 경남FC가즈아_853221467(1골)</t>
+          <t>개포동덕배_845190048(3골), 개포동덕배_845208722(1골), 개포동덕배_848206113(1골), UNIT_848180930(1골), UNIT_851236403(1골)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-19 05:00:44</t>
+          <t>2026-09-19 11:27:23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Legend독수리_840192505(1골), Legend독수리_839226764(1골), 비주류중독_839247699(2골), 비주류중독_840052241(2골)</t>
+          <t>ZD장인지참치_861182521(1골), ZD장인지참치_851240740(1골), ZD장인지참치_840256630(1골), 경남FC가즈아_518200601(1골)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-19 04:48:52</t>
+          <t>2026-09-19 11:23:35</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2069,24 +2077,24 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Legend독수리_821143001(2골), 비주류중독_848006975(1골), 비주류중독_862180283(1골), 비주류중독_839247699(1골)</t>
+          <t>suma수마_861221162(2골), 셀래스틴_845158023(1골), 셀래스틴_856277179(1골), 셀래스틴_852241461(1골), 셀래스틴_863277643(1골)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-19 04:11:38</t>
+          <t>2026-09-19 11:21:04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2101,61 +2109,61 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Legend독수리_840192505(2골), 셀래스틴_852241461(1골), 셀래스틴_845158023(1골), 셀래스틴_863277643(1골)</t>
+          <t>개포동덕배_845190048(2골), UNIT_840210736(1골), UNIT_867166676(2골)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:02</t>
+          <t>2026-09-19 11:06:32</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Legend독수리_821143001(3골), Legend독수리_836054050(1골), Legend독수리_861000246(1골), 셀래스틴_863277643(1골)</t>
+          <t>A지냐크_848031432(1골), A지냐크_863241496(1골), 경남FC가즈아_864139443(1골), 경남FC가즈아_225238224(1골), 경남FC가즈아_277205156(1골)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-19 03:15:22</t>
+          <t>2026-09-19 10:53:44</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2_6</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2163,63 +2171,59 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>여수가스_846001551(1골), 여수가스_861215732(1골), ZD장인지참치_840256630(1골), ZD장인지참치_839200104(3골), ZD장인지참치_840191208(1골), ZD장인지참치_840247263(1골)</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-19 03:03:53</t>
+          <t>2026-09-19 10:46:09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>여수가스_861215732(1골), 여수가스_861162895(2골), ZD장인지참치_840191208(2골)</t>
+          <t>A지냐크_848031432(1골), A지냐크_861167134(1골), A지냐크_840236496(1골), A지냐크_863241496(1골), 스페인전도사_858008348(1골), 스페인전도사_867192629(3골), 스페인전도사_866235522(1골)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-19 01:33:00</t>
+          <t>2026-09-19 10:33:32</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2229,29 +2233,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>겐지간지_852231443(1골), 겐지간지_814231747(3골), Gucci와퍼_839200104(2골), Gucci와퍼_852010264(1골)</t>
+          <t>A지냐크_848031432(3골), 스페인전도사_866235522(1골), 스페인전도사_861001668(1골)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-19 01:18:46</t>
+          <t>2026-09-19 10:19:19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>0_4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2261,89 +2265,93 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>겐지간지_814231747(1골), Gucci와퍼_852168473(1골), Gucci와퍼_839200104(1골)</t>
+          <t>앙쿠_863246191(2골), 앙쿠_848176580(2골)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-19 01:06:48</t>
+          <t>2026-09-19 10:06:31</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>A지냐크_848031432(1골), A지냐크_861167134(1골), A지냐크_867214101(1골), 앙쿠_863246191(2골), 앙쿠_848176580(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-19 00:56:16</t>
+          <t>2026-09-19 09:48:12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2_7</t>
+          <t>5_4</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>겐지간지_861001668(1골), 겐지간지_818179813(1골), ZD장인지참치_861182521(1골), ZD장인지참치_840191208(3골), ZD장인지참치_839200104(3골)</t>
+          <t>UNIT_840192883(1골), UNIT_848265695(1골), UNIT_848180930(3골), 검정소_868013128(4골)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-19 00:43:56</t>
+          <t>2026-09-19 09:36:18</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0_5</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2353,37 +2361,893 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(3골), ZD장인지참치_839200104(2골)</t>
+          <t>검정소_868192181(1골)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>2026-09-19 09:21:02</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>검정소</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(2골), 검정소_868013128(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-19 09:14:49</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3_5</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>오스트리아_864182152(2골), 오스트리아_851236636(1골), ZD장인지참치_840256630(1골), ZD장인지참치_839200104(3골), ZD장인지참치_840191208(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-19 09:10:07</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>검정소</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(2골), 앙쿠_851194765(1골), 검정소_867241096(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-19 09:03:03</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>오스트리아_862140057(1골), 오스트리아_864199266(2골), ZD장인지참치_840256630(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:47:53</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(2골), UNIT_867166676(3골), 오스트리아_864182152(1골), 오스트리아_864199266(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:36:31</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>0_0</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:35:13</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), UNIT_848180930(1골), 오스트리아_864199266(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:24:13</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>스페인전도사</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>4_8</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>스페인전도사_867192629(4골), ZD장인지참치_840247263(2골), ZD장인지참치_839200104(4골), ZD장인지참치_840191208(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:15:28</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>오스트리아_826204497(1골), 오스트리아_864182152(1골), suma수마_861221162(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:12:24</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>스페인전도사</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>0_1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_861182521(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:09:08</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>스페인전도사</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>스페인전도사_867192629(2골), ZD장인지참치_839200104(1골), ZD장인지참치_848199503(1골), ZD장인지참치_851240740(1골), ZD장인지참치_840191208(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:03:54</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>오스트리아_862140057(1골), 오스트리아_864182152(1골), 오스트리아_851236636(1골), 오스트리아_864199266(2골), suma수마_861221162(1골), suma수마_861190046(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:58:58</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1골), 비주류중독_840052241(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:47:10</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>4_1</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), UNIT_848180930(2골), 비주류중독_862180283(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:24:55</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Legend독수리_848140601(1골), 경남FC가즈아_225238224(1골), 경남FC가즈아_805267825(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:13:36</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Legend독수리_821143001(1골), 경남FC가즈아_853221467(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:00:44</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Legend독수리_840192505(1골), Legend독수리_839226764(1골), 비주류중독_839247699(2골), 비주류중독_840052241(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:48:52</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Legend독수리_821143001(2골), 비주류중독_848006975(1골), 비주류중독_862180283(1골), 비주류중독_839247699(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:11:38</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Legend독수리_840192505(2골), 셀래스틴_852241461(1골), 셀래스틴_845158023(1골), 셀래스틴_863277643(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:00:02</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Legend독수리_821143001(3골), Legend독수리_836054050(1골), Legend독수리_861000246(1골), 셀래스틴_863277643(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:15:22</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2_6</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>여수가스_846001551(1골), 여수가스_861215732(1골), ZD장인지참치_840256630(1골), ZD장인지참치_839200104(3골), ZD장인지참치_840191208(1골), ZD장인지참치_840247263(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:03:53</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>여수가스_861215732(1골), 여수가스_861162895(2골), ZD장인지참치_840191208(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:33:00</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>겐지간지_852231443(1골), 겐지간지_814231747(3골), Gucci와퍼_839200104(2골), Gucci와퍼_852010264(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:18:46</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>겐지간지_814231747(1골), Gucci와퍼_852168473(1골), Gucci와퍼_839200104(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:06:48</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>0_0</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:56:16</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2_7</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>겐지간지_861001668(1골), 겐지간지_818179813(1골), ZD장인지참치_861182521(1골), ZD장인지참치_840191208(3골), ZD장인지참치_839200104(3골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:43:56</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>0_5</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(3골), ZD장인지참치_839200104(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>2026-09-18 17:47:34</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>스페인전도사</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>여수가스</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>2_2</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>무</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>스페인전도사_867192629(1골), 스페인전도사_866235522(1골), 여수가스_861162895(1골), 여수가스_861215732(1골)</t>
         </is>
@@ -2400,7 +3264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2438,310 +3302,310 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-19 16:32:52</t>
+          <t>2026-09-20 11:27:42</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(2도움), 스페인전도사_866235522(1도움), 스페인전도사_851224415(1도움), 여수가스_101001625(1도움)</t>
+          <t>호야국2인_851216409(1도움), 호야국2인_846192505(1도움), 개포동덕배_845190048(1도움), 개포동덕배_845168473(1도움), 개포동덕배_845208722(2도움)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-19 16:20:51</t>
+          <t>2026-09-20 11:16:23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1_4</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>스페인전도사_866235522(1도움), 여수가스_861162895(1도움), 여수가스_861215732(1도움), 여수가스_852274967(2도움)</t>
+          <t>호야국2인_851216409(1도움), 호야국2인_848227236(1도움), 호야국2인_848232293(1도움), 호야국2인_846192505(1도움), 개포동덕배_852225375(1도움), 개포동덕배_845168473(1도움), 개포동덕배_845190048(2도움)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-19 15:34:28</t>
+          <t>2026-09-20 10:36:38</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3_8</t>
+          <t>6_0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UNIT_840225782(1도움), UNIT_829274967(1도움), UNIT_840216150(1도움), Voor_852233700(1도움), Voor_845009676(5도움)</t>
+          <t>호야국2인_846192505(2도움), 호야국2인_848232293(1도움), 호야국2인_851216409(2도움), 호야국2인_848216435(1도움)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-19 15:21:21</t>
+          <t>2026-09-20 10:25:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_848180930(1도움), Voor_852001201(1도움), Voor_852233700(1도움), Voor_845001620(1도움)</t>
+          <t>호야국2인_851216409(1도움), 호야국2인_848216435(1도움)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-19 15:17:09</t>
+          <t>2026-09-20 10:10:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>스페인전도사_845224574(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(2도움), 콩콩콩룔_851236496(1도움)</t>
+          <t>여수가스_861162895(2도움), 여수가스_852216393(1도움), 여수가스_828231747(1도움), 겐지간지_863243780(1도움), 겐지간지_845158023(2도움)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-19 15:08:18</t>
+          <t>2026-09-20 09:58:44</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>은안_866241236(1도움), 은안_848239818(1도움), Voor_845247090(1도움), Voor_852233700(1도움)</t>
+          <t>여수가스_861162895(2도움), 여수가스_846001551(1도움), 여수가스_852216393(1도움), 겐지간지_848170890(1도움)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-19 15:05:47</t>
+          <t>2026-09-20 08:25:43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>스페인전도사</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>콩콩콩룔</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>6_3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>스페인전도사_858008348(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_851236496(1도움)</t>
+          <t>개포동덕배_852225375(1도움), 개포동덕배_845208722(2도움), 개포동덕배_856202126(2도움), 개포동덕배_848206113(1도움), 스페인전도사_851236295(1도움), 스페인전도사_866235522(1도움)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-19 14:56:37</t>
+          <t>2026-09-20 08:14:10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2_8</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>은안_866241236(1도움), 은안_848143001(1도움), Voor_845247090(2도움), Voor_845009676(1도움), Voor_852233700(1도움), Voor_845001620(2도움), Voor_858020775(2도움)</t>
+          <t>개포동덕배_856202126(3도움), 개포동덕배_845208722(4도움), 스페인전도사_851216435(1도움), 스페인전도사_851224415(1도움)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-19 14:24:16</t>
+          <t>2026-09-20 08:13:05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움)</t>
+          <t>suma수마_861013383(1도움), suma수마_861190046(1도움), 셀래스틴_863277643(2도움)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-19 14:13:53</t>
+          <t>2026-09-20 08:02:06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5_5</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2751,29 +3615,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(1도움), 앙쿠_848176580(2도움), 앙쿠_846193747(1도움), UNIT_867166676(1도움), UNIT_840225782(3도움), UNIT_840228251(1도움)</t>
+          <t>suma수마_840001114(1도움), suma수마_861221162(1도움), suma수마_848225439(2도움), 셀래스틴_846199564(1도움), 셀래스틴_856277179(1도움)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-19 13:54:08</t>
+          <t>2026-09-20 07:39:16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2783,147 +3647,147 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_814226161(1도움), 앙쿠_863246191(1도움), 앙쿠_846193747(1도움), UNIT_840210736(1도움), UNIT_863250723(1도움), UNIT_840228251(1도움), UNIT_840192883(1도움)</t>
+          <t>A지냐크_863241496(1도움), A지냐크_867214101(1도움), 겐지간지_856237679(1도움), 겐지간지_845158023(1도움)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-19 13:36:20</t>
+          <t>2026-09-20 07:25:46</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>앙쿠_846186345(1도움), 앙쿠_863246191(1도움)</t>
+          <t>겐지간지_814231747(1도움)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-19 13:25:57</t>
+          <t>2026-09-20 07:08:13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), UNIT_840225782(1도움), UNIT_840228251(1도움), UNIT_840210736(1도움)</t>
+          <t>Legend독수리_840205988(1도움), Legend독수리_836054050(1도움), Legend독수리_861000246(1도움), 겐지간지_826247635(1도움)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-19 12:33:16</t>
+          <t>2026-09-20 06:55:35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_840210736(1도움), 셀래스틴_846199564(1도움), 셀래스틴_845158023(1도움), 셀래스틴_856277179(1도움)</t>
+          <t>겐지간지_845158023(1도움), 겐지간지_814231747(1도움), 겐지간지_856237679(1도움)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-19 12:20:50</t>
+          <t>2026-09-20 06:18:57</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>0_2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UNIT_863250723(1도움), UNIT_840192883(1도움), UNIT_840228251(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>suma수마_861013383(1도움), suma수마_861190046(1도움)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-19 12:10:22</t>
+          <t>2026-09-20 06:05:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2933,71 +3797,71 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>2_10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(3도움), 앙쿠_856247103(1도움), suma수마_840001114(1도움)</t>
+          <t>A지냐크_848031432(1도움), A지냐크_861167134(1도움), suma수마_861190046(3도움), suma수마_840001114(3도움), suma수마_848225439(1도움), suma수마_861013383(1도움)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-19 12:06:46</t>
+          <t>2026-09-20 05:45:06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840256630(1도움), ZD장인지참치_839200104(1도움), 셀래스틴_855239231(3도움), 셀래스틴_856277179(1도움)</t>
+          <t>suma수마_848225439(1도움), suma수마_826223697(1도움), suma수마_861190046(1도움), suma수마_851234112(1도움), suma수마_840001114(1도움), ShangHaiPortFC_256164959(1도움)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-19 11:59:22</t>
+          <t>2026-09-20 05:33:58</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3007,29 +3871,29 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_863233084(1도움), 앙쿠_848176580(2도움), 앙쿠_814226161(1도움), suma수마_826223697(1도움), suma수마_861221162(1도움)</t>
+          <t>suma수마_861013383(1도움), suma수마_845192190(1도움), suma수마_861190046(1도움), ShangHaiPortFC_861051412(2도움), ShangHaiPortFC_848031432(1도움)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-19 11:55:57</t>
+          <t>2026-09-20 05:20:20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3039,51 +3903,51 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ZD장인지참치_861182521(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), 셀래스틴_863277643(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>앙쿠_848176580(1도움), 앙쿠_863246191(3도움), ShangHaiPortFC_861051412(2도움)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-19 11:38:35</t>
+          <t>2026-09-20 05:09:38</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840256630(1도움), 경남FC가즈아_805207730(1도움), 경남FC가즈아_225238224(1도움)</t>
+          <t>앙쿠_848176580(1도움), 앙쿠_851194765(1도움), 앙쿠_856247103(1도움), 앙쿠_814226161(1도움)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-19 11:35:15</t>
+          <t>2026-09-20 03:47:49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3093,39 +3957,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>suma수마_848225439(1도움), 셀래스틴_863251854(1도움), 셀래스틴_863277643(1도움)</t>
+          <t>Legend독수리_840205988(1도움), 셀래스틴_852241461(1도움), 셀래스틴_856277179(1도움), 셀래스틴_846199564(1도움)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-19 11:32:23</t>
+          <t>2026-09-20 03:44:09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>8_3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3135,29 +3999,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(1도움), 개포동덕배_863212622(1도움), 개포동덕배_856202126(2도움), UNIT_840192883(1도움), UNIT_840228251(1도움)</t>
+          <t>앙쿠_848176580(2도움), 앙쿠_814226161(1도움), 앙쿠_863246191(2도움), 앙쿠_851194765(2도움), ShangHaiPortFC_845231138(1도움), ShangHaiPortFC_827143001(1도움)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-19 11:27:23</t>
+          <t>2026-09-20 03:36:07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3167,93 +4031,93 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(1도움), 경남FC가즈아_277205156(1도움)</t>
+          <t>Legend독수리_829200145(2도움), Legend독수리_839226764(1도움), 셀래스틴_852241461(1도움), 셀래스틴_863251854(1도움)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-19 11:23:35</t>
+          <t>2026-09-20 03:31:53</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>suma수마_861190046(1도움), suma수마_845192190(1도움), 셀래스틴_845158023(1도움), 셀래스틴_848230938(1도움), 셀래스틴_855239231(1도움), 셀래스틴_863251854(1도움)</t>
+          <t>앙쿠_848176580(1도움), 앙쿠_863246191(1도움), 앙쿠_846186345(1도움), 앙쿠_856247103(1도움), ShangHaiPortFC_845231138(1도움)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-19 11:21:04</t>
+          <t>2026-09-20 03:17:22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>개포동덕배_848206113(1도움), 개포동덕배_856202126(1도움), UNIT_845207439(1도움), UNIT_840210736(1도움), UNIT_867166676(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), 셀래스틴_856277179(1도움), 셀래스틴_848230938(1도움)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-19 11:06:32</t>
+          <t>2026-09-20 03:17:01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3263,121 +4127,125 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>A지냐크_848226851(1도움), A지냐크_863241496(1도움), 경남FC가즈아_830228007(1도움), 경남FC가즈아_805207730(1도움), 경남FC가즈아_853221467(1도움)</t>
+          <t>Legend독수리_864039943(1도움), Legend독수리_852229880(1도움), ShangHaiPortFC_827143001(2도움), ShangHaiPortFC_284190813(1도움), ShangHaiPortFC_845231138(1도움)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-19 10:53:44</t>
+          <t>2026-09-20 03:05:59</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>8_3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Legend독수리_866259399(1도움), Legend독수리_839226764(4도움), Legend독수리_861230025(1도움), ShangHaiPortFC_845231138(1도움), ShangHaiPortFC_848031432(1도움), ShangHaiPortFC_284190813(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-19 10:46:09</t>
+          <t>2026-09-19 16:32:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4_5</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>A지냐크_834271400(1도움), A지냐크_848226851(1도움), A지냐크_863241496(1도움), 스페인전도사_867192629(1도움), 스페인전도사_866235522(1도움), 스페인전도사_861001668(1도움), 스페인전도사_851216435(1도움)</t>
+          <t>스페인전도사_867192629(2도움), 스페인전도사_866235522(1도움), 스페인전도사_851224415(1도움), 여수가스_101001625(1도움)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-19 10:33:32</t>
+          <t>2026-09-19 16:20:51</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>A지냐크_855213648(3도움), 스페인전도사_851216435(1도움)</t>
+          <t>스페인전도사_866235522(1도움), 여수가스_861162895(1도움), 여수가스_861215732(1도움), 여수가스_852274967(2도움)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-19 10:19:19</t>
+          <t>2026-09-19 15:34:28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0_4</t>
+          <t>3_8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3387,157 +4255,157 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움), 앙쿠_848176580(1도움)</t>
+          <t>UNIT_840225782(1도움), UNIT_829274967(1도움), UNIT_840216150(1도움), Voor_852233700(1도움), Voor_845009676(5도움)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-19 10:06:31</t>
+          <t>2026-09-19 15:21:21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>A지냐크_848226851(1도움), A지냐크_863241496(2도움), 앙쿠_851194765(2도움), 앙쿠_863246191(1도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_848180930(1도움), Voor_852001201(1도움), Voor_852233700(1도움), Voor_845001620(1도움)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-19 09:48:12</t>
+          <t>2026-09-19 15:17:09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UNIT_840225782(2도움), UNIT_840192883(1도움), UNIT_867166676(1도움), UNIT_848180930(1도움), 검정소_868192181(1도움), 검정소_861005003(1도움), 검정소_851241721(1도움)</t>
+          <t>스페인전도사_845224574(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(2도움), 콩콩콩룔_851236496(1도움)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-19 09:36:18</t>
+          <t>2026-09-19 15:08:18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>검정소_868013128(1도움)</t>
+          <t>은안_866241236(1도움), 은안_848239818(1도움), Voor_845247090(1도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-19 09:21:02</t>
+          <t>2026-09-19 15:05:47</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>앙쿠_856216460(1도움), 앙쿠_848176580(1도움), 검정소_861005003(2도움)</t>
+          <t>스페인전도사_858008348(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_851236496(1도움)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-19 09:14:49</t>
+          <t>2026-09-19 14:56:37</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3_5</t>
+          <t>2_8</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3547,14 +4415,14 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>오스트리아_851216275(1도움), 오스트리아_864199266(1도움), 오스트리아_291223790(1도움), ZD장인지참치_851240740(1도움), ZD장인지참치_861182521(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(1도움)</t>
+          <t>은안_866241236(1도움), 은안_848143001(1도움), Voor_845247090(2도움), Voor_845009676(1도움), Voor_852233700(1도움), Voor_845001620(2도움), Voor_858020775(2도움)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-19 09:10:07</t>
+          <t>2026-09-19 14:24:16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3564,44 +4432,44 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(2도움), 검정소_868192181(1도움)</t>
+          <t>UNIT_840192883(1도움)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-19 09:03:03</t>
+          <t>2026-09-19 14:13:53</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>5_5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3611,29 +4479,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>오스트리아_851216275(1도움), 오스트리아_862140057(1도움), 오스트리아_864199266(1도움), ZD장인지참치_839200104(1도움)</t>
+          <t>앙쿠_863246191(1도움), 앙쿠_848176580(2도움), 앙쿠_846193747(1도움), UNIT_867166676(1도움), UNIT_840225782(3도움), UNIT_840228251(1도움)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-19 08:47:53</t>
+          <t>2026-09-19 13:54:08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>오스트리아</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3643,121 +4511,125 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UNIT_840216150(1도움), UNIT_867166676(1도움), UNIT_848180930(1도움), UNIT_829274967(1도움), 오스트리아_864191566(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_814226161(1도움), 앙쿠_863246191(1도움), 앙쿠_846193747(1도움), UNIT_840210736(1도움), UNIT_863250723(1도움), UNIT_840228251(1도움), UNIT_840192883(1도움)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-19 08:36:31</t>
+          <t>2026-09-19 13:36:20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>오스트리아</t>
-        </is>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>앙쿠_846186345(1도움), 앙쿠_863246191(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-19 08:35:13</t>
+          <t>2026-09-19 13:25:57</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>오스트리아</t>
-        </is>
-      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UNIT_840225782(1도움), UNIT_840228251(2도움), 오스트리아_851221671(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), UNIT_840225782(1도움), UNIT_840228251(1도움), UNIT_840210736(1도움)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-19 08:24:13</t>
+          <t>2026-09-19 12:33:16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4_8</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>스페인전도사_866235522(1도움), 스페인전도사_845224574(1도움), ZD장인지참치_848199503(3도움), ZD장인지참치_851240740(1도움), ZD장인지참치_861182521(3도움), ZD장인지참치_840191208(1도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_840210736(1도움), 셀래스틴_846199564(1도움), 셀래스틴_845158023(1도움), 셀래스틴_856277179(1도움)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-19 08:15:28</t>
+          <t>2026-09-19 12:20:50</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3767,56 +4639,56 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>오스트리아_862140057(1도움), 오스트리아_856245253(1도움), suma수마_861190046(1도움)</t>
+          <t>UNIT_863250723(1도움), UNIT_840192883(1도움), UNIT_840228251(1도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-19 08:12:24</t>
+          <t>2026-09-19 12:10:22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(1도움)</t>
+          <t>앙쿠_851194765(3도움), 앙쿠_856247103(1도움), suma수마_840001114(1도움)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-19 08:09:08</t>
+          <t>2026-09-19 12:06:46</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3831,19 +4703,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>스페인전도사_866235522(2도움), ZD장인지참치_861182521(1도움), ZD장인지참치_839200104(2도움), ZD장인지참치_840191208(1도움)</t>
+          <t>ZD장인지참치_840256630(1도움), ZD장인지참치_839200104(1도움), 셀래스틴_855239231(3도움), 셀래스틴_856277179(1도움)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-19 08:03:54</t>
+          <t>2026-09-19 11:59:22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3863,189 +4735,189 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>오스트리아_851216275(3도움), suma수마_861190046(1도움), suma수마_848225439(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_863233084(1도움), 앙쿠_848176580(2도움), 앙쿠_814226161(1도움), suma수마_826223697(1도움), suma수마_861221162(1도움)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-19 05:58:58</t>
+          <t>2026-09-19 11:55:57</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), 비주류중독_848006975(1도움)</t>
+          <t>ZD장인지참치_861182521(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), 셀래스틴_863277643(1도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-19 05:47:10</t>
+          <t>2026-09-19 11:38:35</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_848265695(1도움), UNIT_840228251(1도움), UNIT_829274967(1도움), 비주류중독_840052241(1도움)</t>
+          <t>ZD장인지참치_840256630(1도움), 경남FC가즈아_805207730(1도움), 경남FC가즈아_225238224(1도움)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-19 05:24:55</t>
+          <t>2026-09-19 11:35:15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Legend독수리_840205988(1도움), 경남FC가즈아_853221467(1도움), 경남FC가즈아_805267825(1도움)</t>
+          <t>suma수마_848225439(1도움), 셀래스틴_863251854(1도움), 셀래스틴_863277643(1도움)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-19 05:13:36</t>
+          <t>2026-09-19 11:32:23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>경남FC가즈아_518251161(1도움)</t>
+          <t>개포동덕배_845190048(1도움), 개포동덕배_863212622(1도움), 개포동덕배_856202126(2도움), UNIT_840192883(1도움), UNIT_840228251(1도움)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-19 05:00:44</t>
+          <t>2026-09-19 11:27:23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Legend독수리_861230025(1도움), Legend독수리_866259399(1도움), 비주류중독_834239977(3도움), 비주류중독_839247699(1도움)</t>
+          <t>ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(1도움), 경남FC가즈아_277205156(1도움)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-19 04:48:52</t>
+          <t>2026-09-19 11:23:35</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4055,24 +4927,24 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Legend독수리_836054050(1도움), Legend독수리_840205988(1도움), 비주류중독_848006975(1도움), 비주류중독_829203376(1도움), 비주류중독_839247699(1도움)</t>
+          <t>suma수마_861190046(1도움), suma수마_845192190(1도움), 셀래스틴_845158023(1도움), 셀래스틴_848230938(1도움), 셀래스틴_855239231(1도움), 셀래스틴_863251854(1도움)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-19 04:11:38</t>
+          <t>2026-09-19 11:21:04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4087,61 +4959,61 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Legend독수리_852229880(1도움), Legend독수리_861230025(1도움), 셀래스틴_856277179(1도움)</t>
+          <t>개포동덕배_848206113(1도움), 개포동덕배_856202126(1도움), UNIT_845207439(1도움), UNIT_840210736(1도움), UNIT_867166676(1도움)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:02</t>
+          <t>2026-09-19 11:06:32</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Legend독수리_861007518(1도움), Legend독수리_852229880(1도움), Legend독수리_836054050(1도움), Legend독수리_840205988(1도움), 셀래스틴_845158023(1도움)</t>
+          <t>A지냐크_848226851(1도움), A지냐크_863241496(1도움), 경남FC가즈아_830228007(1도움), 경남FC가즈아_805207730(1도움), 경남FC가즈아_853221467(1도움)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-19 03:15:22</t>
+          <t>2026-09-19 10:53:44</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2_6</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4149,63 +5021,59 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>여수가스_861215732(1도움), 여수가스_101001625(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(2도움), ZD장인지참치_848210035(1도움), ZD장인지참치_840247263(1도움)</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-19 03:03:53</t>
+          <t>2026-09-19 10:46:09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>여수가스_828231747(1도움), 여수가스_861215732(1도움), 여수가스_846001551(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
+          <t>A지냐크_834271400(1도움), A지냐크_848226851(1도움), A지냐크_863241496(1도움), 스페인전도사_867192629(1도움), 스페인전도사_866235522(1도움), 스페인전도사_861001668(1도움), 스페인전도사_851216435(1도움)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-19 01:33:00</t>
+          <t>2026-09-19 10:33:32</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4215,29 +5083,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>겐지간지_826247635(1도움), 겐지간지_852231443(2도움), 겐지간지_814231747(1도움), Gucci와퍼_852168473(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_851210697(1도움)</t>
+          <t>A지냐크_855213648(3도움), 스페인전도사_851216435(1도움)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-19 01:18:46</t>
+          <t>2026-09-19 10:19:19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>0_4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4247,89 +5115,93 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>겐지간지_826247635(1도움), Gucci와퍼_852168473(1도움), Gucci와퍼_840208574(1도움)</t>
+          <t>앙쿠_856247103(1도움), 앙쿠_848176580(1도움)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-19 01:06:48</t>
+          <t>2026-09-19 10:06:31</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>A지냐크_848226851(1도움), A지냐크_863241496(2도움), 앙쿠_851194765(2도움), 앙쿠_863246191(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-19 00:56:16</t>
+          <t>2026-09-19 09:48:12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2_7</t>
+          <t>5_4</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>겐지간지_863252145(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_840191208(3도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움)</t>
+          <t>UNIT_840225782(2도움), UNIT_840192883(1도움), UNIT_867166676(1도움), UNIT_848180930(1도움), 검정소_868192181(1도움), 검정소_861005003(1도움), 검정소_851241721(1도움)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-19 00:43:56</t>
+          <t>2026-09-19 09:36:18</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0_5</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4339,37 +5211,893 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840256630(1도움), ZD장인지참치_839200104(2도움), ZD장인지참치_848199503(1도움)</t>
+          <t>검정소_868013128(1도움)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>2026-09-19 09:21:02</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>검정소</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>앙쿠_856216460(1도움), 앙쿠_848176580(1도움), 검정소_861005003(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-19 09:14:49</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3_5</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>오스트리아_851216275(1도움), 오스트리아_864199266(1도움), 오스트리아_291223790(1도움), ZD장인지참치_851240740(1도움), ZD장인지참치_861182521(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-19 09:10:07</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>검정소</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(2도움), 검정소_868192181(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-19 09:03:03</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>오스트리아_851216275(1도움), 오스트리아_862140057(1도움), 오스트리아_864199266(1도움), ZD장인지참치_839200104(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:47:53</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>UNIT_840216150(1도움), UNIT_867166676(1도움), UNIT_848180930(1도움), UNIT_829274967(1도움), 오스트리아_864191566(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:36:31</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>0_0</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:35:13</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>UNIT_840225782(1도움), UNIT_840228251(2도움), 오스트리아_851221671(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:24:13</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>스페인전도사</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>4_8</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>스페인전도사_866235522(1도움), 스페인전도사_845224574(1도움), ZD장인지참치_848199503(3도움), ZD장인지참치_851240740(1도움), ZD장인지참치_861182521(3도움), ZD장인지참치_840191208(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:15:28</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>오스트리아_862140057(1도움), 오스트리아_856245253(1도움), suma수마_861190046(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:12:24</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>스페인전도사</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>0_1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:09:08</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>스페인전도사</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>스페인전도사_866235522(2도움), ZD장인지참치_861182521(1도움), ZD장인지참치_839200104(2도움), ZD장인지참치_840191208(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:03:54</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>오스트리아_851216275(3도움), suma수마_861190046(1도움), suma수마_848225439(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:58:58</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1도움), 비주류중독_848006975(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:47:10</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>4_1</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1도움), UNIT_848265695(1도움), UNIT_840228251(1도움), UNIT_829274967(1도움), 비주류중독_840052241(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:24:55</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Legend독수리_840205988(1도움), 경남FC가즈아_853221467(1도움), 경남FC가즈아_805267825(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:13:36</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_518251161(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:00:44</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Legend독수리_861230025(1도움), Legend독수리_866259399(1도움), 비주류중독_834239977(3도움), 비주류중독_839247699(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:48:52</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Legend독수리_836054050(1도움), Legend독수리_840205988(1도움), 비주류중독_848006975(1도움), 비주류중독_829203376(1도움), 비주류중독_839247699(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:11:38</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Legend독수리_852229880(1도움), Legend독수리_861230025(1도움), 셀래스틴_856277179(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:00:02</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Legend독수리_861007518(1도움), Legend독수리_852229880(1도움), Legend독수리_836054050(1도움), Legend독수리_840205988(1도움), 셀래스틴_845158023(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:15:22</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2_6</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>여수가스_861215732(1도움), 여수가스_101001625(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(2도움), ZD장인지참치_848210035(1도움), ZD장인지참치_840247263(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:03:53</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>여수가스_828231747(1도움), 여수가스_861215732(1도움), 여수가스_846001551(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:33:00</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>겐지간지_826247635(1도움), 겐지간지_852231443(2도움), 겐지간지_814231747(1도움), Gucci와퍼_852168473(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_851210697(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:18:46</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>겐지간지_826247635(1도움), Gucci와퍼_852168473(1도움), Gucci와퍼_840208574(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:06:48</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>0_0</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:56:16</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2_7</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>겐지간지_863252145(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_840191208(3도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:43:56</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>0_5</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840256630(1도움), ZD장인지참치_839200104(2도움), ZD장인지참치_848199503(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>2026-09-18 17:47:34</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>스페인전도사</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>여수가스</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>2_2</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>무</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>스페인전도사_867192629(1도움), 스페인전도사_861001668(1도움), 여수가스_846001551(1도움), 여수가스_828231747(1도움)</t>
         </is>

--- a/API데이터_경기_득점_및_도움_기록.xlsx
+++ b/API데이터_경기_득점_및_도움_기록.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,22 +452,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:27:42</t>
+          <t>2026-09-20 15:26:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -477,248 +477,244 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>호야국2인_851216409(1골), 호야국2인_848232293(1골), 개포동덕배_845190048(1골), 개포동덕배_856202126(3골), 개포동덕배_848206113(1골)</t>
+          <t>0708ManUtd_851226161(2골), 0708ManUtd_868001397(1골), 0708ManUtd_848037576(1골), 은안_866241236(2골), 은안_848143001(1골), 은안_852237692(1골), 은안_856246420(1골)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20 11:16:23</t>
+          <t>2026-09-20 15:15:36</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>호야국2인_851216409(1골), 호야국2인_848232293(1골), 호야국2인_846192505(1골), 호야국2인_845198219(1골), 개포동덕배_845168473(1골), 개포동덕배_845190048(1골), 개포동덕배_856202126(2골)</t>
+          <t>0708ManUtd_851226161(1골), 0708ManUtd_848037576(1골), 0708ManUtd_834239053(2골), 은안_852237692(1골), 은안_848143001(1골)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20 10:36:38</t>
+          <t>2026-09-20 14:55:27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6_0</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>호야국2인_845198219(1골), 호야국2인_848232293(3골), 호야국2인_848216435(2골)</t>
+          <t>0708ManUtd_848037576(1골), 0708ManUtd_848238794(1골), 비주류중독_840052241(1골), 비주류중독_848006975(1골), 비주류중독_839247699(1골)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20 10:25:22</t>
+          <t>2026-09-20 14:43:23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(1골), 호야국2인_848216435(1골)</t>
+          <t>0708ManUtd_848037576(1골), 0708ManUtd_834239053(1골), 0708ManUtd_848238794(1골), UNIT_848180930(3골)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20 10:10:07</t>
+          <t>2026-09-20 14:31:41</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>여수가스_861215732(4골), 겐지간지_814231747(1골), 겐지간지_826247635(1골), 겐지간지_856237679(1골)</t>
+          <t>Gucci차붐_853272992(2골), 비주류중독_839247699(2골), 비주류중독_863224258(1골)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20 09:58:44</t>
+          <t>2026-09-20 14:20:24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>여수가스_861162895(1골), 여수가스_861215732(2골), 여수가스_846001551(1골), 겐지간지_814231747(1골)</t>
+          <t>Gucci차붐_853272733(1골), 비주류중독_840052241(1골), 비주류중독_825000240(1골), 비주류중독_839247699(1골)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20 08:25:43</t>
+          <t>2026-09-20 14:16:35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6_3</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>개포동덕배_845208722(1골), 개포동덕배_856202126(2골), 개포동덕배_845190048(3골), 스페인전도사_845224574(1골), 스페인전도사_867192629(2골)</t>
+          <t>0708ManUtd_848037576(1골), Legend독수리_866259399(1골)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20 08:14:10</t>
+          <t>2026-09-20 14:05:22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>개포동덕배_856202126(1골), 개포동덕배_863212622(1골), 개포동덕배_845190048(4골), 개포동덕배_863234396(1골), 스페인전도사_867192629(1골), 스페인전도사_866235522(1골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20 08:13:05</t>
+          <t>2026-09-20 14:01:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -733,29 +729,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>suma수마_861190046(1골), suma수마_861221162(1골), 셀래스틴_863251854(1골), 셀래스틴_856277179(1골)</t>
+          <t>0708ManUtd_851226161(1골), 0708ManUtd_868001397(1골), Legend독수리_861000246(1골), Legend독수리_861007518(1골)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20 08:02:06</t>
+          <t>2026-09-20 13:12:16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -765,51 +761,51 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>suma수마_861190046(2골), suma수마_861221162(2골), 셀래스틴_861026709(1골), 셀래스틴_852241461(1골), 셀래스틴_836158023(1골)</t>
+          <t>은안_852237692(1골), 은안_856246420(1골), 은안_851242641(1골), 은안_866241236(2골), 겐지간지_863243780(1골)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20 07:39:16</t>
+          <t>2026-09-20 13:12:13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>킹왕두</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>A지냐크_861167134(2골), A지냐크_855213648(1골), 겐지간지_856237679(1골), 겐지간지_814231747(1골)</t>
+          <t>킹왕두_856209331(1골), UNIT_848180930(1골), UNIT_851236403(1골)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-20 07:25:46</t>
+          <t>2026-09-20 12:59:17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -819,93 +815,93 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>겐지간지_856237679(1골)</t>
+          <t>은안_848143001(2골), 은안_866241236(2골), 은안_856251517(1골), 겐지간지_852231443(1골)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20 07:08:13</t>
+          <t>2026-09-20 12:56:53</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>킹왕두</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Legend독수리_836054050(1골), Legend독수리_848140601(1골), Legend독수리_864039943(2골), 겐지간지_852231443(1골)</t>
+          <t>킹왕두_861049369(1골), 킹왕두_846181291(1골), UNIT_848265695(1골), UNIT_867166676(3골), UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-20 06:55:35</t>
+          <t>2026-09-20 12:46:14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Legend독수리_840192505(1골), 겐지간지_848170890(1골), 겐지간지_814231747(1골), 겐지간지_856237679(1골)</t>
+          <t>은안_852237692(1골), 은안_866241236(2골), 은안_848143001(2골), 은안_856246420(1골), suma수마_861221162(1골)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-20 06:18:57</t>
+          <t>2026-09-20 12:34:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -915,98 +911,98 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0_2</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>suma수마_861221162(2골)</t>
+          <t>은안_866241236(2골), 은안_848143001(1골), 은안_852237692(1골), suma수마_840001114(1골), suma수마_861221162(1골), suma수마_848225439(1골)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-20 06:05:40</t>
+          <t>2026-09-20 12:31:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2_10</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>A지냐크_848031432(1골), A지냐크_861167134(1골), suma수마_861221162(10골)</t>
+          <t>개포동덕배_856202126(2골), 개포동덕배_845190048(4골), 개포동덕배_845208722(1골), ZD장인지참치_840191208(2골)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-20 05:45:06</t>
+          <t>2026-09-20 12:24:08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>suma수마_861013383(1골), suma수마_861190046(1골), suma수마_861221162(3골), ShangHaiPortFC_861051412(1골), ShangHaiPortFC_845231138(1골)</t>
+          <t>셀래스틴_855239231(1골)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-20 05:33:58</t>
+          <t>2026-09-20 12:20:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1021,125 +1017,125 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>suma수마_861190046(2골), suma수마_861221162(2골), ShangHaiPortFC_864191910(1골), ShangHaiPortFC_848031432(2골)</t>
+          <t>개포동덕배_845190048(2골), 개포동덕배_845208722(1골), 개포동덕배_856202126(1골), ZD장인지참치_848199503(2골), ZD장인지참치_840191208(1골)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-20 05:20:20</t>
+          <t>2026-09-20 12:13:37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2골), 앙쿠_851194765(2골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_827143001(1골)</t>
+          <t>방덕_856228093(1골), 셀래스틴_863277643(2골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-20 05:09:38</t>
+          <t>2026-09-20 11:27:42</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4_0</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>앙쿠_846193747(1골), 앙쿠_814226161(1골), 앙쿠_863246191(2골)</t>
+          <t>호야국2인_848232293(1골), 호야국2인_851216409(1골), 개포동덕배_845190048(1골), 개포동덕배_856202126(3골), 개포동덕배_848206113(1골)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-20 03:47:49</t>
+          <t>2026-09-20 11:16:23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Legend독수리_840192505(2골), Legend독수리_861007518(1골), 셀래스틴_863277643(1골), 셀래스틴_852241461(2골), 셀래스틴_856277179(1골)</t>
+          <t>호야국2인_846192505(1골), 호야국2인_845198219(1골), 호야국2인_851216409(1골), 호야국2인_848232293(1골), 개포동덕배_845168473(1골), 개포동덕배_845190048(1골), 개포동덕배_856202126(2골)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-20 03:44:09</t>
+          <t>2026-09-20 10:36:38</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8_3</t>
+          <t>6_0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1149,29 +1145,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(3골), 앙쿠_863246191(2골), 앙쿠_851194765(3골), ShangHaiPortFC_848031432(2골), ShangHaiPortFC_864191910(1골)</t>
+          <t>호야국2인_848232293(3골), 호야국2인_845198219(1골), 호야국2인_848216435(2골)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-20 03:36:07</t>
+          <t>2026-09-20 10:25:22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1181,29 +1177,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Legend독수리_840192505(1골), Legend독수리_861230025(1골), Legend독수리_839226764(1골), 셀래스틴_856277179(2골)</t>
+          <t>호야국2인_848216435(1골), 호야국2인_848232293(1골)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-20 03:31:53</t>
+          <t>2026-09-20 10:10:07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6_1</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1213,29 +1209,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2골), 앙쿠_863246191(2골), 앙쿠_863232488(1골), 앙쿠_866266039(1골), ShangHaiPortFC_864191910(1골)</t>
+          <t>여수가스_861215732(4골), 겐지간지_856237679(1골), 겐지간지_814231747(1골), 겐지간지_826247635(1골)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-20 03:17:22</t>
+          <t>2026-09-20 09:58:44</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1245,61 +1241,61 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 앙쿠_848176580(2골), 셀래스틴_852241461(1골), 셀래스틴_845158023(1골)</t>
+          <t>여수가스_861162895(1골), 여수가스_861215732(2골), 여수가스_846001551(1골), 겐지간지_814231747(1골)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-20 03:17:01</t>
+          <t>2026-09-20 08:25:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>6_3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Legend독수리_861007518(1골), Legend독수리_821143001(1골), ShangHaiPortFC_864191910(4골)</t>
+          <t>개포동덕배_845208722(1골), 개포동덕배_856202126(2골), 개포동덕배_845190048(3골), 스페인전도사_845224574(1골), 스페인전도사_867192629(2골)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-20 03:05:59</t>
+          <t>2026-09-20 08:14:10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8_3</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1309,125 +1305,125 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Legend독수리_840192505(4골), Legend독수리_866259399(2골), Legend독수리_839226764(1골), Legend독수리_861230025(1골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_284190813(1골), ShangHaiPortFC_861051412(1골)</t>
+          <t>개포동덕배_856202126(1골), 개포동덕배_863212622(1골), 개포동덕배_845190048(4골), 개포동덕배_863234396(1골), 스페인전도사_867192629(1골), 스페인전도사_866235522(1골)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-19 16:32:52</t>
+          <t>2026-09-20 08:13:05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(2골), 스페인전도사_866235522(2골), 여수가스_861215732(1골)</t>
+          <t>suma수마_861190046(1골), suma수마_861221162(1골), 셀래스틴_863251854(1골), 셀래스틴_856277179(1골)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-19 16:20:51</t>
+          <t>2026-09-20 08:02:06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1_4</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(1골), 여수가스_861162895(1골), 여수가스_861215732(3골)</t>
+          <t>suma수마_861190046(2골), suma수마_861221162(2골), 셀래스틴_861026709(1골), 셀래스틴_852241461(1골), 셀래스틴_836158023(1골)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-19 15:34:28</t>
+          <t>2026-09-20 07:39:16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3_8</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_867166676(2골), Voor_845247090(1골), Voor_852233700(2골), Voor_845009676(1골), Voor_858020775(2골), Voor_851238616(1골), Voor_845001620(1골)</t>
+          <t>A지냐크_861167134(2골), A지냐크_855213648(1골), 겐지간지_856237679(1골), 겐지간지_814231747(1골)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-19 15:21:21</t>
+          <t>2026-09-20 07:25:46</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1437,93 +1433,93 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), Voor_845247090(1골), Voor_845009676(2골)</t>
+          <t>겐지간지_856237679(1골)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-19 15:17:09</t>
+          <t>2026-09-20 07:08:13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(1골), 스페인전도사_845224574(1골), 콩콩콩룔_866223710(3골), 콩콩콩룔_867220502(1골), 콩콩콩룔_867223848(1골)</t>
+          <t>Legend독수리_836054050(1골), Legend독수리_848140601(1골), Legend독수리_864039943(2골), 겐지간지_852231443(1골)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-19 15:08:18</t>
+          <t>2026-09-20 06:55:35</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>은안_866241236(1골), 은안_856246420(1골), Voor_845009676(1골), Voor_858020775(1골)</t>
+          <t>Legend독수리_840192505(1골), 겐지간지_848170890(1골), 겐지간지_814231747(1골), 겐지간지_856237679(1골)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-19 15:05:47</t>
+          <t>2026-09-20 06:18:57</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>0_2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1533,29 +1529,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(1골), 콩콩콩룔_848189505(1골), 콩콩콩룔_866223710(1골)</t>
+          <t>suma수마_861221162(2골)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-19 14:56:37</t>
+          <t>2026-09-20 06:05:40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2_8</t>
+          <t>2_10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1565,61 +1561,61 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>은안_866241236(1골), 은안_856246420(1골), Voor_845009676(2골), Voor_852233700(4골), Voor_858020775(2골)</t>
+          <t>A지냐크_848031432(1골), A지냐크_861167134(1골), suma수마_861221162(10골)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-19 14:24:16</t>
+          <t>2026-09-20 05:45:06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골)</t>
+          <t>suma수마_861013383(1골), suma수마_861190046(1골), suma수마_861221162(3골), ShangHaiPortFC_861051412(1골), ShangHaiPortFC_845231138(1골)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-19 14:13:53</t>
+          <t>2026-09-20 05:33:58</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5_5</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1629,14 +1625,14 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(2골), 앙쿠_851194765(3골), UNIT_867166676(1골), UNIT_848180930(4골)</t>
+          <t>suma수마_861190046(2골), suma수마_861221162(2골), ShangHaiPortFC_864191910(1골), ShangHaiPortFC_848031432(2골)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-19 13:54:08</t>
+          <t>2026-09-20 05:20:20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1646,12 +1642,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1661,14 +1657,14 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 앙쿠_848176580(3골), UNIT_867166676(4골)</t>
+          <t>앙쿠_848176580(2골), 앙쿠_851194765(2골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_827143001(1골)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-19 13:36:20</t>
+          <t>2026-09-20 05:09:38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1678,12 +1674,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1693,29 +1689,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>앙쿠_866266039(1골), 앙쿠_848176580(1골)</t>
+          <t>앙쿠_846193747(1골), 앙쿠_814226161(1골), 앙쿠_863246191(2골)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-19 13:25:57</t>
+          <t>2026-09-20 03:47:49</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1725,51 +1721,51 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>앙쿠_863232488(1골), 앙쿠_848176580(1골), UNIT_848180930(1골), UNIT_840228251(1골), UNIT_840192883(1골)</t>
+          <t>Legend독수리_840192505(2골), Legend독수리_861007518(1골), 셀래스틴_863277643(1골), 셀래스틴_852241461(2골), 셀래스틴_856277179(1골)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-19 12:33:16</t>
+          <t>2026-09-20 03:44:09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>8_3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), UNIT_848180930(2골), 셀래스틴_868222481(1골), 셀래스틴_852241461(2골)</t>
+          <t>앙쿠_848176580(3골), 앙쿠_863246191(2골), 앙쿠_851194765(3골), ShangHaiPortFC_848031432(2골), ShangHaiPortFC_864191910(1골)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-19 12:20:50</t>
+          <t>2026-09-20 03:36:07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1779,7 +1775,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1789,14 +1785,14 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), UNIT_840228251(1골), 셀래스틴_863277643(1골)</t>
+          <t>Legend독수리_840192505(1골), Legend독수리_861230025(1골), Legend독수리_839226764(1골), 셀래스틴_856277179(2골)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-19 12:10:22</t>
+          <t>2026-09-20 03:31:53</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1806,12 +1802,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1821,19 +1817,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(3골), 앙쿠_866266039(1골), suma수마_861013383(1골), suma수마_861221162(1골)</t>
+          <t>앙쿠_848176580(2골), 앙쿠_863246191(2골), 앙쿠_863232488(1골), 앙쿠_866266039(1골), ShangHaiPortFC_864191910(1골)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-19 12:06:46</t>
+          <t>2026-09-20 03:17:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1843,71 +1839,71 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2골), 셀래스틴_863277643(1골), 셀래스틴_845158023(2골), 셀래스틴_863251854(1골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_848176580(2골), 셀래스틴_852241461(1골), 셀래스틴_845158023(1골)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-19 11:59:22</t>
+          <t>2026-09-20 03:17:01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2골), 앙쿠_863246191(2골), 앙쿠_866266039(1골), suma수마_840001114(1골), suma수마_861190046(1골)</t>
+          <t>Legend독수리_861007518(1골), Legend독수리_821143001(1골), ShangHaiPortFC_864191910(4골)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-19 11:55:57</t>
+          <t>2026-09-20 03:05:59</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>8_3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1917,157 +1913,157 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(1골), ZD장인지참치_852213331(1골), 셀래스틴_846199564(1골), 셀래스틴_863277643(1골), 셀래스틴_856277179(1골)</t>
+          <t>Legend독수리_840192505(4골), Legend독수리_866259399(2골), Legend독수리_839226764(1골), Legend독수리_861230025(1골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_284190813(1골), ShangHaiPortFC_861051412(1골)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-19 11:38:35</t>
+          <t>2026-09-19 16:32:52</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ZD장인지참치_839200104(1골), 경남FC가즈아_853221467(1골), 경남FC가즈아_225238224(1골)</t>
+          <t>스페인전도사_867192629(2골), 스페인전도사_866235522(2골), 여수가스_861215732(1골)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-19 11:35:15</t>
+          <t>2026-09-19 16:20:51</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>suma수마_861221162(2골), 셀래스틴_852241461(2골)</t>
+          <t>스페인전도사_867192629(1골), 여수가스_861162895(1골), 여수가스_861215732(3골)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-19 11:32:23</t>
+          <t>2026-09-19 15:34:28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_8</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(3골), 개포동덕배_845208722(1골), 개포동덕배_848206113(1골), UNIT_848180930(1골), UNIT_851236403(1골)</t>
+          <t>UNIT_848180930(1골), UNIT_867166676(2골), Voor_845247090(1골), Voor_852233700(2골), Voor_845009676(1골), Voor_858020775(2골), Voor_851238616(1골), Voor_845001620(1골)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-19 11:27:23</t>
+          <t>2026-09-19 15:21:21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ZD장인지참치_861182521(1골), ZD장인지참치_851240740(1골), ZD장인지참치_840256630(1골), 경남FC가즈아_518200601(1골)</t>
+          <t>UNIT_867166676(2골), Voor_845247090(1골), Voor_845009676(2골)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-19 11:23:35</t>
+          <t>2026-09-19 15:17:09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2077,61 +2073,61 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>suma수마_861221162(2골), 셀래스틴_845158023(1골), 셀래스틴_856277179(1골), 셀래스틴_852241461(1골), 셀래스틴_863277643(1골)</t>
+          <t>스페인전도사_867192629(1골), 스페인전도사_845224574(1골), 콩콩콩룔_866223710(3골), 콩콩콩룔_867220502(1골), 콩콩콩룔_867223848(1골)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-19 11:21:04</t>
+          <t>2026-09-19 15:08:18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(2골), UNIT_840210736(1골), UNIT_867166676(2골)</t>
+          <t>은안_866241236(1골), 은안_856246420(1골), Voor_845009676(1골), Voor_858020775(1골)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-19 11:06:32</t>
+          <t>2026-09-19 15:05:47</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2141,29 +2137,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>A지냐크_848031432(1골), A지냐크_863241496(1골), 경남FC가즈아_864139443(1골), 경남FC가즈아_225238224(1골), 경남FC가즈아_277205156(1골)</t>
+          <t>스페인전도사_867192629(1골), 콩콩콩룔_848189505(1골), 콩콩콩룔_866223710(1골)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-19 10:53:44</t>
+          <t>2026-09-19 14:56:37</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_8</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2171,27 +2167,31 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>은안_866241236(1골), 은안_856246420(1골), Voor_845009676(2골), Voor_852233700(4골), Voor_858020775(2골)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-19 10:46:09</t>
+          <t>2026-09-19 14:24:16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4_5</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2201,29 +2201,29 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>A지냐크_848031432(1골), A지냐크_861167134(1골), A지냐크_840236496(1골), A지냐크_863241496(1골), 스페인전도사_858008348(1골), 스페인전도사_867192629(3골), 스페인전도사_866235522(1골)</t>
+          <t>UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-19 10:33:32</t>
+          <t>2026-09-19 14:13:53</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>5_5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2233,110 +2233,110 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>A지냐크_848031432(3골), 스페인전도사_866235522(1골), 스페인전도사_861001668(1골)</t>
+          <t>앙쿠_863246191(2골), 앙쿠_851194765(3골), UNIT_867166676(1골), UNIT_848180930(4골)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-19 10:19:19</t>
+          <t>2026-09-19 13:54:08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0_4</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(2골), 앙쿠_848176580(2골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_848176580(3골), UNIT_867166676(4골)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-19 10:06:31</t>
+          <t>2026-09-19 13:36:20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>A지냐크_848031432(1골), A지냐크_861167134(1골), A지냐크_867214101(1골), 앙쿠_863246191(2골), 앙쿠_848176580(1골)</t>
+          <t>앙쿠_866266039(1골), 앙쿠_848176580(1골)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-19 09:48:12</t>
+          <t>2026-09-19 13:25:57</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>검정소</t>
-        </is>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1골), UNIT_848265695(1골), UNIT_848180930(3골), 검정소_868013128(4골)</t>
+          <t>앙쿠_863232488(1골), 앙쿠_848176580(1골), UNIT_848180930(1골), UNIT_840228251(1골), UNIT_840192883(1골)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-19 09:36:18</t>
+          <t>2026-09-19 12:33:16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2346,140 +2346,140 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>검정소_868192181(1골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(2골), 셀래스틴_868222481(1골), 셀래스틴_852241461(2골)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-19 09:21:02</t>
+          <t>2026-09-19 12:20:50</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(2골), 검정소_868013128(2골)</t>
+          <t>UNIT_848180930(2골), UNIT_840228251(1골), 셀래스틴_863277643(1골)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-19 09:14:49</t>
+          <t>2026-09-19 12:10:22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3_5</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>오스트리아_864182152(2골), 오스트리아_851236636(1골), ZD장인지참치_840256630(1골), ZD장인지참치_839200104(3골), ZD장인지참치_840191208(1골)</t>
+          <t>앙쿠_848176580(3골), 앙쿠_866266039(1골), suma수마_861013383(1골), suma수마_861221162(1골)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-19 09:10:07</t>
+          <t>2026-09-19 12:06:46</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2골), 앙쿠_851194765(1골), 검정소_867241096(1골)</t>
+          <t>ZD장인지참치_840191208(2골), 셀래스틴_863277643(1골), 셀래스틴_845158023(2골), 셀래스틴_863251854(1골)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-19 09:03:03</t>
+          <t>2026-09-19 11:59:22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2489,29 +2489,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>오스트리아_862140057(1골), 오스트리아_864199266(2골), ZD장인지참치_840256630(1골)</t>
+          <t>앙쿠_848176580(2골), 앙쿠_863246191(2골), 앙쿠_866266039(1골), suma수마_840001114(1골), suma수마_861190046(1골)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-19 08:47:53</t>
+          <t>2026-09-19 11:55:57</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2521,29 +2521,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UNIT_840192883(2골), UNIT_867166676(3골), 오스트리아_864182152(1골), 오스트리아_864199266(1골)</t>
+          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(1골), ZD장인지참치_852213331(1골), 셀래스틴_846199564(1골), 셀래스틴_863277643(1골), 셀래스틴_856277179(1골)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-19 08:36:31</t>
+          <t>2026-09-19 11:38:35</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2551,91 +2551,95 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_839200104(1골), 경남FC가즈아_853221467(1골), 경남FC가즈아_225238224(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-19 08:35:13</t>
+          <t>2026-09-19 11:35:15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), UNIT_848180930(1골), 오스트리아_864199266(2골)</t>
+          <t>suma수마_861221162(2골), 셀래스틴_852241461(2골)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-19 08:24:13</t>
+          <t>2026-09-19 11:32:23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4_8</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(4골), ZD장인지참치_840247263(2골), ZD장인지참치_839200104(4골), ZD장인지참치_840191208(2골)</t>
+          <t>개포동덕배_845190048(3골), 개포동덕배_845208722(1골), 개포동덕배_848206113(1골), UNIT_848180930(1골), UNIT_851236403(1골)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-19 08:15:28</t>
+          <t>2026-09-19 11:27:23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2645,29 +2649,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>오스트리아_826204497(1골), 오스트리아_864182152(1골), suma수마_861221162(1골)</t>
+          <t>ZD장인지참치_861182521(1골), ZD장인지참치_851240740(1골), ZD장인지참치_840256630(1골), 경남FC가즈아_518200601(1골)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-19 08:12:24</t>
+          <t>2026-09-19 11:23:35</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2677,29 +2681,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ZD장인지참치_861182521(1골)</t>
+          <t>suma수마_861221162(2골), 셀래스틴_845158023(1골), 셀래스틴_856277179(1골), 셀래스틴_852241461(1골), 셀래스틴_863277643(1골)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-19 08:09:08</t>
+          <t>2026-09-19 11:21:04</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2709,253 +2713,249 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(2골), ZD장인지참치_839200104(1골), ZD장인지참치_848199503(1골), ZD장인지참치_851240740(1골), ZD장인지참치_840191208(1골)</t>
+          <t>개포동덕배_845190048(2골), UNIT_840210736(1골), UNIT_867166676(2골)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-19 08:03:54</t>
+          <t>2026-09-19 11:06:32</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>오스트리아_862140057(1골), 오스트리아_864182152(1골), 오스트리아_851236636(1골), 오스트리아_864199266(2골), suma수마_861221162(1골), suma수마_861190046(1골)</t>
+          <t>A지냐크_848031432(1골), A지냐크_863241496(1골), 경남FC가즈아_864139443(1골), 경남FC가즈아_225238224(1골), 경남FC가즈아_277205156(1골)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-19 05:58:58</t>
+          <t>2026-09-19 10:53:44</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>UNIT_867166676(1골), 비주류중독_840052241(1골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-19 05:47:10</t>
+          <t>2026-09-19 10:46:09</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), UNIT_848180930(2골), 비주류중독_862180283(1골)</t>
+          <t>A지냐크_848031432(1골), A지냐크_861167134(1골), A지냐크_840236496(1골), A지냐크_863241496(1골), 스페인전도사_858008348(1골), 스페인전도사_867192629(3골), 스페인전도사_866235522(1골)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-19 05:24:55</t>
+          <t>2026-09-19 10:33:32</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Legend독수리_848140601(1골), 경남FC가즈아_225238224(1골), 경남FC가즈아_805267825(1골)</t>
+          <t>A지냐크_848031432(3골), 스페인전도사_866235522(1골), 스페인전도사_861001668(1골)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-19 05:13:36</t>
+          <t>2026-09-19 10:19:19</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>0_4</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Legend독수리_821143001(1골), 경남FC가즈아_853221467(1골)</t>
+          <t>앙쿠_863246191(2골), 앙쿠_848176580(2골)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-19 05:00:44</t>
+          <t>2026-09-19 10:06:31</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Legend독수리_840192505(1골), Legend독수리_839226764(1골), 비주류중독_839247699(2골), 비주류중독_840052241(2골)</t>
+          <t>A지냐크_848031432(1골), A지냐크_861167134(1골), A지냐크_867214101(1골), 앙쿠_863246191(2골), 앙쿠_848176580(1골)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-19 04:48:52</t>
+          <t>2026-09-19 09:48:12</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_4</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Legend독수리_821143001(2골), 비주류중독_848006975(1골), 비주류중독_862180283(1골), 비주류중독_839247699(1골)</t>
+          <t>UNIT_840192883(1골), UNIT_848265695(1골), UNIT_848180930(3골), 검정소_868013128(4골)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-19 04:11:38</t>
+          <t>2026-09-19 09:36:18</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2965,51 +2965,51 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Legend독수리_840192505(2골), 셀래스틴_852241461(1골), 셀래스틴_845158023(1골), 셀래스틴_863277643(1골)</t>
+          <t>검정소_868192181(1골)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:02</t>
+          <t>2026-09-19 09:21:02</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Legend독수리_821143001(3골), Legend독수리_836054050(1골), Legend독수리_861000246(1골), 셀래스틴_863277643(1골)</t>
+          <t>앙쿠_851194765(2골), 검정소_868013128(2골)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-19 03:15:22</t>
+          <t>2026-09-19 09:14:49</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2_6</t>
+          <t>3_5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3029,29 +3029,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>여수가스_846001551(1골), 여수가스_861215732(1골), ZD장인지참치_840256630(1골), ZD장인지참치_839200104(3골), ZD장인지참치_840191208(1골), ZD장인지참치_840247263(1골)</t>
+          <t>오스트리아_864182152(2골), 오스트리아_851236636(1골), ZD장인지참치_840256630(1골), ZD장인지참치_839200104(3골), ZD장인지참치_840191208(1골)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-19 03:03:53</t>
+          <t>2026-09-19 09:10:07</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3061,29 +3061,29 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>여수가스_861215732(1골), 여수가스_861162895(2골), ZD장인지참치_840191208(2골)</t>
+          <t>앙쿠_848176580(2골), 앙쿠_851194765(1골), 검정소_867241096(1골)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-19 01:33:00</t>
+          <t>2026-09-19 09:03:03</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3093,56 +3093,56 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>겐지간지_852231443(1골), 겐지간지_814231747(3골), Gucci와퍼_839200104(2골), Gucci와퍼_852010264(1골)</t>
+          <t>오스트리아_862140057(1골), 오스트리아_864199266(2골), ZD장인지참치_840256630(1골)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-19 01:18:46</t>
+          <t>2026-09-19 08:47:53</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>겐지간지_814231747(1골), Gucci와퍼_852168473(1골), Gucci와퍼_839200104(1골)</t>
+          <t>UNIT_840192883(2골), UNIT_867166676(3골), 오스트리아_864182152(1골), 오스트리아_864199266(1골)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-19 01:06:48</t>
+          <t>2026-09-19 08:36:31</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3160,44 +3160,44 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-19 00:56:16</t>
+          <t>2026-09-19 08:35:13</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2_7</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>겐지간지_861001668(1골), 겐지간지_818179813(1골), ZD장인지참치_861182521(1골), ZD장인지참치_840191208(3골), ZD장인지참치_839200104(3골)</t>
+          <t>UNIT_867166676(2골), UNIT_848180930(1골), 오스트리아_864199266(2골)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-19 00:43:56</t>
+          <t>2026-09-19 08:24:13</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0_5</t>
+          <t>4_8</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3217,37 +3217,641 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(3골), ZD장인지참치_839200104(2골)</t>
+          <t>스페인전도사_867192629(4골), ZD장인지참치_840247263(2골), ZD장인지참치_839200104(4골), ZD장인지참치_840191208(2골)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>2026-09-19 08:15:28</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>오스트리아_826204497(1골), 오스트리아_864182152(1골), suma수마_861221162(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:12:24</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>스페인전도사</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0_1</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_861182521(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:09:08</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>스페인전도사</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>스페인전도사_867192629(2골), ZD장인지참치_839200104(1골), ZD장인지참치_848199503(1골), ZD장인지참치_851240740(1골), ZD장인지참치_840191208(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:03:54</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>오스트리아_862140057(1골), 오스트리아_864182152(1골), 오스트리아_851236636(1골), 오스트리아_864199266(2골), suma수마_861221162(1골), suma수마_861190046(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:58:58</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1골), 비주류중독_840052241(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:47:10</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>4_1</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), UNIT_848180930(2골), 비주류중독_862180283(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:24:55</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Legend독수리_848140601(1골), 경남FC가즈아_225238224(1골), 경남FC가즈아_805267825(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:13:36</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Legend독수리_821143001(1골), 경남FC가즈아_853221467(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:00:44</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Legend독수리_840192505(1골), Legend독수리_839226764(1골), 비주류중독_839247699(2골), 비주류중독_840052241(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:48:52</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Legend독수리_821143001(2골), 비주류중독_848006975(1골), 비주류중독_862180283(1골), 비주류중독_839247699(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:11:38</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Legend독수리_840192505(2골), 셀래스틴_852241461(1골), 셀래스틴_845158023(1골), 셀래스틴_863277643(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:00:02</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Legend독수리_821143001(3골), Legend독수리_836054050(1골), Legend독수리_861000246(1골), 셀래스틴_863277643(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:15:22</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2_6</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>여수가스_846001551(1골), 여수가스_861215732(1골), ZD장인지참치_840256630(1골), ZD장인지참치_839200104(3골), ZD장인지참치_840191208(1골), ZD장인지참치_840247263(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:03:53</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>여수가스_861215732(1골), 여수가스_861162895(2골), ZD장인지참치_840191208(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:33:00</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>겐지간지_852231443(1골), 겐지간지_814231747(3골), Gucci와퍼_839200104(2골), Gucci와퍼_852010264(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:18:46</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>겐지간지_814231747(1골), Gucci와퍼_852168473(1골), Gucci와퍼_839200104(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:06:48</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0_0</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:56:16</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2_7</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>겐지간지_861001668(1골), 겐지간지_818179813(1골), ZD장인지참치_861182521(1골), ZD장인지참치_840191208(3골), ZD장인지참치_839200104(3골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:43:56</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>0_5</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(3골), ZD장인지참치_839200104(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t>2026-09-18 17:47:34</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>스페인전도사</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>여수가스</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>2_2</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>무</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>스페인전도사_867192629(1골), 스페인전도사_866235522(1골), 여수가스_861162895(1골), 여수가스_861215732(1골)</t>
         </is>
@@ -3264,7 +3868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3302,22 +3906,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:27:42</t>
+          <t>2026-09-20 15:26:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3327,248 +3931,244 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>호야국2인_851216409(1도움), 호야국2인_846192505(1도움), 개포동덕배_845190048(1도움), 개포동덕배_845168473(1도움), 개포동덕배_845208722(2도움)</t>
+          <t>0708ManUtd_848183277(2도움), 0708ManUtd_868001397(1도움), 0708ManUtd_848037576(1도움), 은안_866241236(1도움), 은안_848143001(1도움), 은안_846210514(1도움), 은안_852237692(2도움)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20 11:16:23</t>
+          <t>2026-09-20 15:15:36</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>호야국2인_851216409(1도움), 호야국2인_848227236(1도움), 호야국2인_848232293(1도움), 호야국2인_846192505(1도움), 개포동덕배_852225375(1도움), 개포동덕배_845168473(1도움), 개포동덕배_845190048(2도움)</t>
+          <t>0708ManUtd_851226161(1도움), 0708ManUtd_848183277(2도움), 0708ManUtd_867232656(1도움), 은안_856246420(1도움), 은안_848231866(1도움)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20 10:36:38</t>
+          <t>2026-09-20 14:55:27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6_0</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>호야국2인_846192505(2도움), 호야국2인_848232293(1도움), 호야국2인_851216409(2도움), 호야국2인_848216435(1도움)</t>
+          <t>0708ManUtd_868001397(1도움), 0708ManUtd_834239053(1도움), 비주류중독_840052241(1도움), 비주류중독_848006975(1도움), 비주류중독_839247699(1도움)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20 10:25:22</t>
+          <t>2026-09-20 14:43:23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>호야국2인_851216409(1도움), 호야국2인_848216435(1도움)</t>
+          <t>0708ManUtd_848183277(1도움), 0708ManUtd_848238794(1도움), UNIT_840192883(1도움), UNIT_840228251(1도움), UNIT_840225782(1도움)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20 10:10:07</t>
+          <t>2026-09-20 14:31:41</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>여수가스_861162895(2도움), 여수가스_852216393(1도움), 여수가스_828231747(1도움), 겐지간지_863243780(1도움), 겐지간지_845158023(2도움)</t>
+          <t>Gucci차붐_851221671(1도움), Gucci차붐_853272733(1도움), 비주류중독_834239977(1도움), 비주류중독_848006975(1도움), 비주류중독_821214622(1도움)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20 09:58:44</t>
+          <t>2026-09-20 14:20:24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>여수가스_861162895(2도움), 여수가스_846001551(1도움), 여수가스_852216393(1도움), 겐지간지_848170890(1도움)</t>
+          <t>Gucci차붐_864033730(1도움), 비주류중독_840052241(1도움), 비주류중독_862180283(2도움)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20 08:25:43</t>
+          <t>2026-09-20 14:16:35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6_3</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>개포동덕배_852225375(1도움), 개포동덕배_845208722(2도움), 개포동덕배_856202126(2도움), 개포동덕배_848206113(1도움), 스페인전도사_851236295(1도움), 스페인전도사_866235522(1도움)</t>
+          <t>0708ManUtd_848183277(1도움), Legend독수리_861007518(1도움)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20 08:14:10</t>
+          <t>2026-09-20 14:05:22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>개포동덕배_856202126(3도움), 개포동덕배_845208722(4도움), 스페인전도사_851216435(1도움), 스페인전도사_851224415(1도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20 08:13:05</t>
+          <t>2026-09-20 14:01:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3583,29 +4183,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>suma수마_861013383(1도움), suma수마_861190046(1도움), 셀래스틴_863277643(2도움)</t>
+          <t>0708ManUtd_848037576(1도움), 0708ManUtd_834239053(1도움), Legend독수리_864039943(1도움)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20 08:02:06</t>
+          <t>2026-09-20 13:12:16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3615,51 +4215,51 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>suma수마_840001114(1도움), suma수마_861221162(1도움), suma수마_848225439(2도움), 셀래스틴_846199564(1도움), 셀래스틴_856277179(1도움)</t>
+          <t>은안_856246420(1도움), 은안_848143001(1도움), 은안_851242641(1도움), 은안_866241236(1도움), 겐지간지_845158023(1도움)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20 07:39:16</t>
+          <t>2026-09-20 13:12:13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>킹왕두</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>A지냐크_863241496(1도움), A지냐크_867214101(1도움), 겐지간지_856237679(1도움), 겐지간지_845158023(1도움)</t>
+          <t>킹왕두_848203376(1도움), UNIT_848265695(1도움), UNIT_840210736(1도움)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-20 07:25:46</t>
+          <t>2026-09-20 12:59:17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3669,93 +4269,93 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>겐지간지_814231747(1도움)</t>
+          <t>은안_846210514(1도움), 은안_836239085(1도움), 은안_848231866(1도움), 은안_848143001(1도움), 겐지간지_848170890(1도움)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20 07:08:13</t>
+          <t>2026-09-20 12:56:53</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>킹왕두</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Legend독수리_840205988(1도움), Legend독수리_836054050(1도움), Legend독수리_861000246(1도움), 겐지간지_826247635(1도움)</t>
+          <t>킹왕두_829013743(1도움), 킹왕두_856209331(1도움), UNIT_840228251(1도움), UNIT_840216150(1도움), UNIT_840225782(2도움)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-20 06:55:35</t>
+          <t>2026-09-20 12:46:14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>겐지간지_845158023(1도움), 겐지간지_814231747(1도움), 겐지간지_856237679(1도움)</t>
+          <t>은안_866241236(1도움), 은안_848143001(3도움), 은안_856246420(1도움), suma수마_861013383(1도움)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-20 06:18:57</t>
+          <t>2026-09-20 12:34:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3765,98 +4365,98 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0_2</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>suma수마_861013383(1도움), suma수마_861190046(1도움)</t>
+          <t>은안_866241236(1도움), 은안_848143001(1도움), 은안_852237692(1도움), 은안_856246420(1도움), suma수마_861221162(1도움), suma수마_861013383(2도움)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-20 06:05:40</t>
+          <t>2026-09-20 12:31:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2_10</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>A지냐크_848031432(1도움), A지냐크_861167134(1도움), suma수마_861190046(3도움), suma수마_840001114(3도움), suma수마_848225439(1도움), suma수마_861013383(1도움)</t>
+          <t>개포동덕배_856202126(2도움), 개포동덕배_845190048(1도움), 개포동덕배_845208722(1도움), 개포동덕배_845168473(1도움), 개포동덕배_863212622(2도움), ZD장인지참치_848199503(1도움), ZD장인지참치_851240740(1도움)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-20 05:45:06</t>
+          <t>2026-09-20 12:24:08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>suma수마_848225439(1도움), suma수마_826223697(1도움), suma수마_861190046(1도움), suma수마_851234112(1도움), suma수마_840001114(1도움), ShangHaiPortFC_256164959(1도움)</t>
+          <t>셀래스틴_863277643(1도움)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-20 05:33:58</t>
+          <t>2026-09-20 12:20:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3871,125 +4471,125 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>suma수마_861013383(1도움), suma수마_845192190(1도움), suma수마_861190046(1도움), ShangHaiPortFC_861051412(2도움), ShangHaiPortFC_848031432(1도움)</t>
+          <t>개포동덕배_845190048(2도움), 개포동덕배_848206113(1도움), 개포동덕배_856202126(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_840256630(2도움)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-20 05:20:20</t>
+          <t>2026-09-20 12:13:37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1도움), 앙쿠_863246191(3도움), ShangHaiPortFC_861051412(2도움)</t>
+          <t>방덕_867001040(1도움), 셀래스틴_863277643(1도움), 셀래스틴_852241461(2도움)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-20 05:09:38</t>
+          <t>2026-09-20 11:27:42</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4_0</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1도움), 앙쿠_851194765(1도움), 앙쿠_856247103(1도움), 앙쿠_814226161(1도움)</t>
+          <t>호야국2인_846192505(1도움), 호야국2인_851216409(1도움), 개포동덕배_845190048(1도움), 개포동덕배_845208722(2도움), 개포동덕배_845168473(1도움)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-20 03:47:49</t>
+          <t>2026-09-20 11:16:23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Legend독수리_840205988(1도움), 셀래스틴_852241461(1도움), 셀래스틴_856277179(1도움), 셀래스틴_846199564(1도움)</t>
+          <t>호야국2인_846192505(1도움), 호야국2인_851216409(1도움), 호야국2인_848227236(1도움), 호야국2인_848232293(1도움), 개포동덕배_852225375(1도움), 개포동덕배_845168473(1도움), 개포동덕배_845190048(2도움)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-20 03:44:09</t>
+          <t>2026-09-20 10:36:38</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8_3</t>
+          <t>6_0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3999,29 +4599,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2도움), 앙쿠_814226161(1도움), 앙쿠_863246191(2도움), 앙쿠_851194765(2도움), ShangHaiPortFC_845231138(1도움), ShangHaiPortFC_827143001(1도움)</t>
+          <t>호야국2인_846192505(2도움), 호야국2인_848232293(1도움), 호야국2인_851216409(2도움), 호야국2인_848216435(1도움)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-20 03:36:07</t>
+          <t>2026-09-20 10:25:22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4031,29 +4631,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Legend독수리_829200145(2도움), Legend독수리_839226764(1도움), 셀래스틴_852241461(1도움), 셀래스틴_863251854(1도움)</t>
+          <t>호야국2인_851216409(1도움), 호야국2인_848216435(1도움)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-20 03:31:53</t>
+          <t>2026-09-20 10:10:07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6_1</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4063,29 +4663,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1도움), 앙쿠_863246191(1도움), 앙쿠_846186345(1도움), 앙쿠_856247103(1도움), ShangHaiPortFC_845231138(1도움)</t>
+          <t>여수가스_852216393(1도움), 여수가스_828231747(1도움), 여수가스_861162895(2도움), 겐지간지_845158023(2도움), 겐지간지_863243780(1도움)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-20 03:17:22</t>
+          <t>2026-09-20 09:58:44</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4095,61 +4695,61 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), 셀래스틴_856277179(1도움), 셀래스틴_848230938(1도움)</t>
+          <t>여수가스_861162895(2도움), 여수가스_846001551(1도움), 여수가스_852216393(1도움), 겐지간지_848170890(1도움)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-20 03:17:01</t>
+          <t>2026-09-20 08:25:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>6_3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Legend독수리_864039943(1도움), Legend독수리_852229880(1도움), ShangHaiPortFC_827143001(2도움), ShangHaiPortFC_284190813(1도움), ShangHaiPortFC_845231138(1도움)</t>
+          <t>개포동덕배_852225375(1도움), 개포동덕배_845208722(2도움), 개포동덕배_856202126(2도움), 개포동덕배_848206113(1도움), 스페인전도사_851236295(1도움), 스페인전도사_866235522(1도움)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-20 03:05:59</t>
+          <t>2026-09-20 08:14:10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8_3</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4159,125 +4759,125 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Legend독수리_866259399(1도움), Legend독수리_839226764(4도움), Legend독수리_861230025(1도움), ShangHaiPortFC_845231138(1도움), ShangHaiPortFC_848031432(1도움), ShangHaiPortFC_284190813(1도움)</t>
+          <t>개포동덕배_856202126(3도움), 개포동덕배_845208722(4도움), 스페인전도사_851216435(1도움), 스페인전도사_851224415(1도움)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-19 16:32:52</t>
+          <t>2026-09-20 08:13:05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(2도움), 스페인전도사_866235522(1도움), 스페인전도사_851224415(1도움), 여수가스_101001625(1도움)</t>
+          <t>suma수마_861013383(1도움), suma수마_861190046(1도움), 셀래스틴_863277643(2도움)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-19 16:20:51</t>
+          <t>2026-09-20 08:02:06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1_4</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>스페인전도사_866235522(1도움), 여수가스_861162895(1도움), 여수가스_861215732(1도움), 여수가스_852274967(2도움)</t>
+          <t>suma수마_840001114(1도움), suma수마_861221162(1도움), suma수마_848225439(2도움), 셀래스틴_846199564(1도움), 셀래스틴_856277179(1도움)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-19 15:34:28</t>
+          <t>2026-09-20 07:39:16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3_8</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UNIT_840225782(1도움), UNIT_829274967(1도움), UNIT_840216150(1도움), Voor_852233700(1도움), Voor_845009676(5도움)</t>
+          <t>A지냐크_863241496(1도움), A지냐크_867214101(1도움), 겐지간지_856237679(1도움), 겐지간지_845158023(1도움)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-19 15:21:21</t>
+          <t>2026-09-20 07:25:46</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4287,93 +4887,93 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_848180930(1도움), Voor_852001201(1도움), Voor_852233700(1도움), Voor_845001620(1도움)</t>
+          <t>겐지간지_814231747(1도움)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-19 15:17:09</t>
+          <t>2026-09-20 07:08:13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>스페인전도사_845224574(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(2도움), 콩콩콩룔_851236496(1도움)</t>
+          <t>Legend독수리_840205988(1도움), Legend독수리_836054050(1도움), Legend독수리_861000246(1도움), 겐지간지_826247635(1도움)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-19 15:08:18</t>
+          <t>2026-09-20 06:55:35</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>은안_866241236(1도움), 은안_848239818(1도움), Voor_845247090(1도움), Voor_852233700(1도움)</t>
+          <t>겐지간지_845158023(1도움), 겐지간지_814231747(1도움), 겐지간지_856237679(1도움)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-19 15:05:47</t>
+          <t>2026-09-20 06:18:57</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>0_2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4383,29 +4983,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>스페인전도사_858008348(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_851236496(1도움)</t>
+          <t>suma수마_861013383(1도움), suma수마_861190046(1도움)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-19 14:56:37</t>
+          <t>2026-09-20 06:05:40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2_8</t>
+          <t>2_10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4415,61 +5015,61 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>은안_866241236(1도움), 은안_848143001(1도움), Voor_845247090(2도움), Voor_845009676(1도움), Voor_852233700(1도움), Voor_845001620(2도움), Voor_858020775(2도움)</t>
+          <t>A지냐크_848031432(1도움), A지냐크_861167134(1도움), suma수마_861190046(3도움), suma수마_840001114(3도움), suma수마_848225439(1도움), suma수마_861013383(1도움)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-19 14:24:16</t>
+          <t>2026-09-20 05:45:06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움)</t>
+          <t>suma수마_848225439(1도움), suma수마_826223697(1도움), suma수마_861190046(1도움), suma수마_851234112(1도움), suma수마_840001114(1도움), ShangHaiPortFC_256164959(1도움)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-19 14:13:53</t>
+          <t>2026-09-20 05:33:58</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5_5</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4479,14 +5079,14 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(1도움), 앙쿠_848176580(2도움), 앙쿠_846193747(1도움), UNIT_867166676(1도움), UNIT_840225782(3도움), UNIT_840228251(1도움)</t>
+          <t>suma수마_861013383(1도움), suma수마_845192190(1도움), suma수마_861190046(1도움), ShangHaiPortFC_861051412(2도움), ShangHaiPortFC_848031432(1도움)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-19 13:54:08</t>
+          <t>2026-09-20 05:20:20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4496,12 +5096,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4511,14 +5111,14 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_814226161(1도움), 앙쿠_863246191(1도움), 앙쿠_846193747(1도움), UNIT_840210736(1도움), UNIT_863250723(1도움), UNIT_840228251(1도움), UNIT_840192883(1도움)</t>
+          <t>앙쿠_848176580(1도움), 앙쿠_863246191(3도움), ShangHaiPortFC_861051412(2도움)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-19 13:36:20</t>
+          <t>2026-09-20 05:09:38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4528,12 +5128,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4543,29 +5143,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>앙쿠_846186345(1도움), 앙쿠_863246191(1도움)</t>
+          <t>앙쿠_848176580(1도움), 앙쿠_851194765(1도움), 앙쿠_856247103(1도움), 앙쿠_814226161(1도움)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-19 13:25:57</t>
+          <t>2026-09-20 03:47:49</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4575,51 +5175,51 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), UNIT_840225782(1도움), UNIT_840228251(1도움), UNIT_840210736(1도움)</t>
+          <t>Legend독수리_840205988(1도움), 셀래스틴_852241461(1도움), 셀래스틴_856277179(1도움), 셀래스틴_846199564(1도움)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-19 12:33:16</t>
+          <t>2026-09-20 03:44:09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>8_3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_840210736(1도움), 셀래스틴_846199564(1도움), 셀래스틴_845158023(1도움), 셀래스틴_856277179(1도움)</t>
+          <t>앙쿠_848176580(2도움), 앙쿠_814226161(1도움), 앙쿠_863246191(2도움), 앙쿠_851194765(2도움), ShangHaiPortFC_845231138(1도움), ShangHaiPortFC_827143001(1도움)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-19 12:20:50</t>
+          <t>2026-09-20 03:36:07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4629,7 +5229,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4639,14 +5239,14 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UNIT_863250723(1도움), UNIT_840192883(1도움), UNIT_840228251(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>Legend독수리_829200145(2도움), Legend독수리_839226764(1도움), 셀래스틴_852241461(1도움), 셀래스틴_863251854(1도움)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-19 12:10:22</t>
+          <t>2026-09-20 03:31:53</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4656,12 +5256,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4671,19 +5271,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(3도움), 앙쿠_856247103(1도움), suma수마_840001114(1도움)</t>
+          <t>앙쿠_848176580(1도움), 앙쿠_863246191(1도움), 앙쿠_846186345(1도움), 앙쿠_856247103(1도움), ShangHaiPortFC_845231138(1도움)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-19 12:06:46</t>
+          <t>2026-09-20 03:17:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4693,71 +5293,71 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840256630(1도움), ZD장인지참치_839200104(1도움), 셀래스틴_855239231(3도움), 셀래스틴_856277179(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), 셀래스틴_856277179(1도움), 셀래스틴_848230938(1도움)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-19 11:59:22</t>
+          <t>2026-09-20 03:17:01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_863233084(1도움), 앙쿠_848176580(2도움), 앙쿠_814226161(1도움), suma수마_826223697(1도움), suma수마_861221162(1도움)</t>
+          <t>Legend독수리_864039943(1도움), Legend독수리_852229880(1도움), ShangHaiPortFC_827143001(2도움), ShangHaiPortFC_284190813(1도움), ShangHaiPortFC_845231138(1도움)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-19 11:55:57</t>
+          <t>2026-09-20 03:05:59</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>8_3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4767,157 +5367,157 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ZD장인지참치_861182521(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), 셀래스틴_863277643(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>Legend독수리_866259399(1도움), Legend독수리_839226764(4도움), Legend독수리_861230025(1도움), ShangHaiPortFC_845231138(1도움), ShangHaiPortFC_848031432(1도움), ShangHaiPortFC_284190813(1도움)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-19 11:38:35</t>
+          <t>2026-09-19 16:32:52</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840256630(1도움), 경남FC가즈아_805207730(1도움), 경남FC가즈아_225238224(1도움)</t>
+          <t>스페인전도사_867192629(2도움), 스페인전도사_866235522(1도움), 스페인전도사_851224415(1도움), 여수가스_101001625(1도움)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-19 11:35:15</t>
+          <t>2026-09-19 16:20:51</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>suma수마_848225439(1도움), 셀래스틴_863251854(1도움), 셀래스틴_863277643(1도움)</t>
+          <t>스페인전도사_866235522(1도움), 여수가스_861162895(1도움), 여수가스_861215732(1도움), 여수가스_852274967(2도움)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-19 11:32:23</t>
+          <t>2026-09-19 15:34:28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_8</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(1도움), 개포동덕배_863212622(1도움), 개포동덕배_856202126(2도움), UNIT_840192883(1도움), UNIT_840228251(1도움)</t>
+          <t>UNIT_840225782(1도움), UNIT_829274967(1도움), UNIT_840216150(1도움), Voor_852233700(1도움), Voor_845009676(5도움)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-19 11:27:23</t>
+          <t>2026-09-19 15:21:21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(1도움), 경남FC가즈아_277205156(1도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_848180930(1도움), Voor_852001201(1도움), Voor_852233700(1도움), Voor_845001620(1도움)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-19 11:23:35</t>
+          <t>2026-09-19 15:17:09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4927,61 +5527,61 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>suma수마_861190046(1도움), suma수마_845192190(1도움), 셀래스틴_845158023(1도움), 셀래스틴_848230938(1도움), 셀래스틴_855239231(1도움), 셀래스틴_863251854(1도움)</t>
+          <t>스페인전도사_845224574(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(2도움), 콩콩콩룔_851236496(1도움)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-19 11:21:04</t>
+          <t>2026-09-19 15:08:18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>개포동덕배_848206113(1도움), 개포동덕배_856202126(1도움), UNIT_845207439(1도움), UNIT_840210736(1도움), UNIT_867166676(1도움)</t>
+          <t>은안_866241236(1도움), 은안_848239818(1도움), Voor_845247090(1도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-19 11:06:32</t>
+          <t>2026-09-19 15:05:47</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4991,29 +5591,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>A지냐크_848226851(1도움), A지냐크_863241496(1도움), 경남FC가즈아_830228007(1도움), 경남FC가즈아_805207730(1도움), 경남FC가즈아_853221467(1도움)</t>
+          <t>스페인전도사_858008348(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_851236496(1도움)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-19 10:53:44</t>
+          <t>2026-09-19 14:56:37</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_8</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5021,27 +5621,31 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>은안_866241236(1도움), 은안_848143001(1도움), Voor_845247090(2도움), Voor_845009676(1도움), Voor_852233700(1도움), Voor_845001620(2도움), Voor_858020775(2도움)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-19 10:46:09</t>
+          <t>2026-09-19 14:24:16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4_5</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5051,29 +5655,29 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>A지냐크_834271400(1도움), A지냐크_848226851(1도움), A지냐크_863241496(1도움), 스페인전도사_867192629(1도움), 스페인전도사_866235522(1도움), 스페인전도사_861001668(1도움), 스페인전도사_851216435(1도움)</t>
+          <t>UNIT_840192883(1도움)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-19 10:33:32</t>
+          <t>2026-09-19 14:13:53</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>5_5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5083,110 +5687,110 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>A지냐크_855213648(3도움), 스페인전도사_851216435(1도움)</t>
+          <t>앙쿠_863246191(1도움), 앙쿠_848176580(2도움), 앙쿠_846193747(1도움), UNIT_867166676(1도움), UNIT_840225782(3도움), UNIT_840228251(1도움)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-19 10:19:19</t>
+          <t>2026-09-19 13:54:08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0_4</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움), 앙쿠_848176580(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_814226161(1도움), 앙쿠_863246191(1도움), 앙쿠_846193747(1도움), UNIT_840210736(1도움), UNIT_863250723(1도움), UNIT_840228251(1도움), UNIT_840192883(1도움)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-19 10:06:31</t>
+          <t>2026-09-19 13:36:20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>A지냐크_848226851(1도움), A지냐크_863241496(2도움), 앙쿠_851194765(2도움), 앙쿠_863246191(1도움)</t>
+          <t>앙쿠_846186345(1도움), 앙쿠_863246191(1도움)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-19 09:48:12</t>
+          <t>2026-09-19 13:25:57</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>검정소</t>
-        </is>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>UNIT_840225782(2도움), UNIT_840192883(1도움), UNIT_867166676(1도움), UNIT_848180930(1도움), 검정소_868192181(1도움), 검정소_861005003(1도움), 검정소_851241721(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), UNIT_840225782(1도움), UNIT_840228251(1도움), UNIT_840210736(1도움)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-19 09:36:18</t>
+          <t>2026-09-19 12:33:16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5196,140 +5800,140 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>검정소_868013128(1도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_840210736(1도움), 셀래스틴_846199564(1도움), 셀래스틴_845158023(1도움), 셀래스틴_856277179(1도움)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-19 09:21:02</t>
+          <t>2026-09-19 12:20:50</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>앙쿠_856216460(1도움), 앙쿠_848176580(1도움), 검정소_861005003(2도움)</t>
+          <t>UNIT_863250723(1도움), UNIT_840192883(1도움), UNIT_840228251(1도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-19 09:14:49</t>
+          <t>2026-09-19 12:10:22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3_5</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>오스트리아_851216275(1도움), 오스트리아_864199266(1도움), 오스트리아_291223790(1도움), ZD장인지참치_851240740(1도움), ZD장인지참치_861182521(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(1도움)</t>
+          <t>앙쿠_851194765(3도움), 앙쿠_856247103(1도움), suma수마_840001114(1도움)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-19 09:10:07</t>
+          <t>2026-09-19 12:06:46</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(2도움), 검정소_868192181(1도움)</t>
+          <t>ZD장인지참치_840256630(1도움), ZD장인지참치_839200104(1도움), 셀래스틴_855239231(3도움), 셀래스틴_856277179(1도움)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-19 09:03:03</t>
+          <t>2026-09-19 11:59:22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5339,29 +5943,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>오스트리아_851216275(1도움), 오스트리아_862140057(1도움), 오스트리아_864199266(1도움), ZD장인지참치_839200104(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_863233084(1도움), 앙쿠_848176580(2도움), 앙쿠_814226161(1도움), suma수마_826223697(1도움), suma수마_861221162(1도움)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-19 08:47:53</t>
+          <t>2026-09-19 11:55:57</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5371,29 +5975,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UNIT_840216150(1도움), UNIT_867166676(1도움), UNIT_848180930(1도움), UNIT_829274967(1도움), 오스트리아_864191566(1도움)</t>
+          <t>ZD장인지참치_861182521(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), 셀래스틴_863277643(1도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-19 08:36:31</t>
+          <t>2026-09-19 11:38:35</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5401,91 +6005,95 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840256630(1도움), 경남FC가즈아_805207730(1도움), 경남FC가즈아_225238224(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-19 08:35:13</t>
+          <t>2026-09-19 11:35:15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UNIT_840225782(1도움), UNIT_840228251(2도움), 오스트리아_851221671(1도움)</t>
+          <t>suma수마_848225439(1도움), 셀래스틴_863251854(1도움), 셀래스틴_863277643(1도움)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-19 08:24:13</t>
+          <t>2026-09-19 11:32:23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4_8</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>스페인전도사_866235522(1도움), 스페인전도사_845224574(1도움), ZD장인지참치_848199503(3도움), ZD장인지참치_851240740(1도움), ZD장인지참치_861182521(3도움), ZD장인지참치_840191208(1도움)</t>
+          <t>개포동덕배_845190048(1도움), 개포동덕배_863212622(1도움), 개포동덕배_856202126(2도움), UNIT_840192883(1도움), UNIT_840228251(1도움)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-19 08:15:28</t>
+          <t>2026-09-19 11:27:23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5495,29 +6103,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>오스트리아_862140057(1도움), 오스트리아_856245253(1도움), suma수마_861190046(1도움)</t>
+          <t>ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(1도움), 경남FC가즈아_277205156(1도움)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-19 08:12:24</t>
+          <t>2026-09-19 11:23:35</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5527,29 +6135,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(1도움)</t>
+          <t>suma수마_861190046(1도움), suma수마_845192190(1도움), 셀래스틴_845158023(1도움), 셀래스틴_848230938(1도움), 셀래스틴_855239231(1도움), 셀래스틴_863251854(1도움)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-19 08:09:08</t>
+          <t>2026-09-19 11:21:04</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5559,253 +6167,249 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>스페인전도사_866235522(2도움), ZD장인지참치_861182521(1도움), ZD장인지참치_839200104(2도움), ZD장인지참치_840191208(1도움)</t>
+          <t>개포동덕배_848206113(1도움), 개포동덕배_856202126(1도움), UNIT_845207439(1도움), UNIT_840210736(1도움), UNIT_867166676(1도움)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-19 08:03:54</t>
+          <t>2026-09-19 11:06:32</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>오스트리아_851216275(3도움), suma수마_861190046(1도움), suma수마_848225439(1도움)</t>
+          <t>A지냐크_848226851(1도움), A지냐크_863241496(1도움), 경남FC가즈아_830228007(1도움), 경남FC가즈아_805207730(1도움), 경남FC가즈아_853221467(1도움)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-19 05:58:58</t>
+          <t>2026-09-19 10:53:44</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>UNIT_848180930(1도움), 비주류중독_848006975(1도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-19 05:47:10</t>
+          <t>2026-09-19 10:46:09</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_848265695(1도움), UNIT_840228251(1도움), UNIT_829274967(1도움), 비주류중독_840052241(1도움)</t>
+          <t>A지냐크_834271400(1도움), A지냐크_848226851(1도움), A지냐크_863241496(1도움), 스페인전도사_867192629(1도움), 스페인전도사_866235522(1도움), 스페인전도사_861001668(1도움), 스페인전도사_851216435(1도움)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-19 05:24:55</t>
+          <t>2026-09-19 10:33:32</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Legend독수리_840205988(1도움), 경남FC가즈아_853221467(1도움), 경남FC가즈아_805267825(1도움)</t>
+          <t>A지냐크_855213648(3도움), 스페인전도사_851216435(1도움)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-19 05:13:36</t>
+          <t>2026-09-19 10:19:19</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>0_4</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>경남FC가즈아_518251161(1도움)</t>
+          <t>앙쿠_856247103(1도움), 앙쿠_848176580(1도움)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-19 05:00:44</t>
+          <t>2026-09-19 10:06:31</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Legend독수리_861230025(1도움), Legend독수리_866259399(1도움), 비주류중독_834239977(3도움), 비주류중독_839247699(1도움)</t>
+          <t>A지냐크_848226851(1도움), A지냐크_863241496(2도움), 앙쿠_851194765(2도움), 앙쿠_863246191(1도움)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-19 04:48:52</t>
+          <t>2026-09-19 09:48:12</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_4</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Legend독수리_836054050(1도움), Legend독수리_840205988(1도움), 비주류중독_848006975(1도움), 비주류중독_829203376(1도움), 비주류중독_839247699(1도움)</t>
+          <t>UNIT_840225782(2도움), UNIT_840192883(1도움), UNIT_867166676(1도움), UNIT_848180930(1도움), 검정소_868192181(1도움), 검정소_861005003(1도움), 검정소_851241721(1도움)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-19 04:11:38</t>
+          <t>2026-09-19 09:36:18</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5815,51 +6419,51 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Legend독수리_852229880(1도움), Legend독수리_861230025(1도움), 셀래스틴_856277179(1도움)</t>
+          <t>검정소_868013128(1도움)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:02</t>
+          <t>2026-09-19 09:21:02</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Legend독수리_861007518(1도움), Legend독수리_852229880(1도움), Legend독수리_836054050(1도움), Legend독수리_840205988(1도움), 셀래스틴_845158023(1도움)</t>
+          <t>앙쿠_856216460(1도움), 앙쿠_848176580(1도움), 검정소_861005003(2도움)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-19 03:15:22</t>
+          <t>2026-09-19 09:14:49</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5869,7 +6473,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2_6</t>
+          <t>3_5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5879,29 +6483,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>여수가스_861215732(1도움), 여수가스_101001625(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(2도움), ZD장인지참치_848210035(1도움), ZD장인지참치_840247263(1도움)</t>
+          <t>오스트리아_851216275(1도움), 오스트리아_864199266(1도움), 오스트리아_291223790(1도움), ZD장인지참치_851240740(1도움), ZD장인지참치_861182521(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(1도움)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-19 03:03:53</t>
+          <t>2026-09-19 09:10:07</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5911,29 +6515,29 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>여수가스_828231747(1도움), 여수가스_861215732(1도움), 여수가스_846001551(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
+          <t>앙쿠_851194765(2도움), 검정소_868192181(1도움)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-19 01:33:00</t>
+          <t>2026-09-19 09:03:03</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5943,56 +6547,56 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>겐지간지_826247635(1도움), 겐지간지_852231443(2도움), 겐지간지_814231747(1도움), Gucci와퍼_852168473(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_851210697(1도움)</t>
+          <t>오스트리아_851216275(1도움), 오스트리아_862140057(1도움), 오스트리아_864199266(1도움), ZD장인지참치_839200104(1도움)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-19 01:18:46</t>
+          <t>2026-09-19 08:47:53</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>겐지간지_826247635(1도움), Gucci와퍼_852168473(1도움), Gucci와퍼_840208574(1도움)</t>
+          <t>UNIT_840216150(1도움), UNIT_867166676(1도움), UNIT_848180930(1도움), UNIT_829274967(1도움), 오스트리아_864191566(1도움)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-19 01:06:48</t>
+          <t>2026-09-19 08:36:31</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6010,44 +6614,44 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-19 00:56:16</t>
+          <t>2026-09-19 08:35:13</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2_7</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>겐지간지_863252145(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_840191208(3도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움)</t>
+          <t>UNIT_840225782(1도움), UNIT_840228251(2도움), 오스트리아_851221671(1도움)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-19 00:43:56</t>
+          <t>2026-09-19 08:24:13</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6057,7 +6661,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0_5</t>
+          <t>4_8</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6067,37 +6671,641 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840256630(1도움), ZD장인지참치_839200104(2도움), ZD장인지참치_848199503(1도움)</t>
+          <t>스페인전도사_866235522(1도움), 스페인전도사_845224574(1도움), ZD장인지참치_848199503(3도움), ZD장인지참치_851240740(1도움), ZD장인지참치_861182521(3도움), ZD장인지참치_840191208(1도움)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>2026-09-19 08:15:28</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>오스트리아_862140057(1도움), 오스트리아_856245253(1도움), suma수마_861190046(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:12:24</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>스페인전도사</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0_1</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:09:08</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>스페인전도사</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>스페인전도사_866235522(2도움), ZD장인지참치_861182521(1도움), ZD장인지참치_839200104(2도움), ZD장인지참치_840191208(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:03:54</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>오스트리아_851216275(3도움), suma수마_861190046(1도움), suma수마_848225439(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:58:58</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1도움), 비주류중독_848006975(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:47:10</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>4_1</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1도움), UNIT_848265695(1도움), UNIT_840228251(1도움), UNIT_829274967(1도움), 비주류중독_840052241(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:24:55</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Legend독수리_840205988(1도움), 경남FC가즈아_853221467(1도움), 경남FC가즈아_805267825(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:13:36</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_518251161(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:00:44</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Legend독수리_861230025(1도움), Legend독수리_866259399(1도움), 비주류중독_834239977(3도움), 비주류중독_839247699(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:48:52</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Legend독수리_836054050(1도움), Legend독수리_840205988(1도움), 비주류중독_848006975(1도움), 비주류중독_829203376(1도움), 비주류중독_839247699(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:11:38</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Legend독수리_852229880(1도움), Legend독수리_861230025(1도움), 셀래스틴_856277179(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:00:02</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Legend독수리_861007518(1도움), Legend독수리_852229880(1도움), Legend독수리_836054050(1도움), Legend독수리_840205988(1도움), 셀래스틴_845158023(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:15:22</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2_6</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>여수가스_861215732(1도움), 여수가스_101001625(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(2도움), ZD장인지참치_848210035(1도움), ZD장인지참치_840247263(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:03:53</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>여수가스_828231747(1도움), 여수가스_861215732(1도움), 여수가스_846001551(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:33:00</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>겐지간지_826247635(1도움), 겐지간지_852231443(2도움), 겐지간지_814231747(1도움), Gucci와퍼_852168473(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_851210697(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:18:46</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>겐지간지_826247635(1도움), Gucci와퍼_852168473(1도움), Gucci와퍼_840208574(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:06:48</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0_0</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:56:16</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2_7</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>겐지간지_863252145(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_840191208(3도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:43:56</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>0_5</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840256630(1도움), ZD장인지참치_839200104(2도움), ZD장인지참치_848199503(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t>2026-09-18 17:47:34</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>스페인전도사</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>여수가스</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>2_2</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>무</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>스페인전도사_867192629(1도움), 스페인전도사_861001668(1도움), 여수가스_846001551(1도움), 여수가스_828231747(1도움)</t>
         </is>

--- a/API데이터_경기_득점_및_도움_기록.xlsx
+++ b/API데이터_경기_득점_및_도움_기록.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,54 +452,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20 15:26:30</t>
+          <t>2026-09-21 15:12:55</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4_5</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0708ManUtd_851226161(2골), 0708ManUtd_868001397(1골), 0708ManUtd_848037576(1골), 은안_866241236(2골), 은안_848143001(1골), 은안_852237692(1골), 은안_856246420(1골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_848176580(1골), 앙쿠_866266039(1골), Special블루_848230666(1골), Special블루_861001419(2골)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20 15:15:36</t>
+          <t>2026-09-21 15:02:23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -509,14 +509,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0708ManUtd_851226161(1골), 0708ManUtd_848037576(1골), 0708ManUtd_834239053(2골), 은안_852237692(1골), 은안_848143001(1골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_848176580(1골), Special블루_848230666(1골)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20 14:55:27</t>
+          <t>2026-09-21 14:26:25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -526,29 +526,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0708ManUtd_848037576(1골), 0708ManUtd_848238794(1골), 비주류중독_840052241(1골), 비주류중독_848006975(1골), 비주류중독_839247699(1골)</t>
+          <t>0708ManUtd_848037576(2골), 0708ManUtd_848238794(1골), Gucci와퍼_852010264(1골), Gucci와퍼_839200104(1골)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20 14:43:23</t>
+          <t>2026-09-21 14:14:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -558,76 +558,72 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0708ManUtd_848037576(1골), 0708ManUtd_834239053(1골), 0708ManUtd_848238794(1골), UNIT_848180930(3골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20 14:31:41</t>
+          <t>2026-09-21 14:13:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gucci차붐_853272992(2골), 비주류중독_839247699(2골), 비주류중독_863224258(1골)</t>
+          <t>0708ManUtd_868001397(1골), 0708ManUtd_848037576(1골), Gucci와퍼_852168473(1골)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20 14:20:24</t>
+          <t>2026-09-21 13:49:20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>4_6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -637,14 +633,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gucci차붐_853272733(1골), 비주류중독_840052241(1골), 비주류중독_825000240(1골), 비주류중독_839247699(1골)</t>
+          <t>0708ManUtd_848238794(1골), 0708ManUtd_848037576(1골), 0708ManUtd_868001397(2골), ZD장인지참치_840247263(2골), ZD장인지참치_840191208(1골), ZD장인지참치_839200104(3골)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20 14:16:35</t>
+          <t>2026-09-21 13:37:50</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -654,57 +650,61 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0708ManUtd_848037576(1골), Legend독수리_866259399(1골)</t>
+          <t>0708ManUtd_848037576(2골), ZD장인지참치_839200104(1골), ZD장인지참치_840247263(2골)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20 14:05:22</t>
+          <t>2026-09-21 13:23:22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>5_4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Voor_845009676(4골), Voor_852233700(1골), 콩콩콩룔_848189505(1골), 콩콩콩룔_866223710(3골)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01:34</t>
+          <t>2026-09-21 13:23:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -729,29 +729,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0708ManUtd_851226161(1골), 0708ManUtd_868001397(1골), Legend독수리_861000246(1골), Legend독수리_861007518(1골)</t>
+          <t>0708ManUtd_868001397(1골), 셀래스틴_836158023(1골)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20 13:12:16</t>
+          <t>2026-09-21 13:22:31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -761,157 +761,157 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>은안_852237692(1골), 은안_856246420(1골), 은안_851242641(1골), 은안_866241236(2골), 겐지간지_863243780(1골)</t>
+          <t>개포동덕배_845208722(1골), 개포동덕배_856202126(1골), 개포동덕배_845190048(3골), Gucci와퍼_852213331(1골), Gucci와퍼_852168473(1골)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20 13:12:13</t>
+          <t>2026-09-21 13:11:54</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>킹왕두</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>킹왕두_856209331(1골), UNIT_848180930(1골), UNIT_851236403(1골)</t>
+          <t>0708ManUtd_868001397(3골), 0708ManUtd_848183277(1골), 0708ManUtd_848037576(1골), 0708ManUtd_848238794(1골), 셀래스틴_856277179(1골)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-20 12:59:17</t>
+          <t>2026-09-21 13:11:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>은안_848143001(2골), 은안_866241236(2골), 은안_856251517(1골), 겐지간지_852231443(1골)</t>
+          <t>Voor_845247090(1골), Voor_845239231(1골), 콩콩콩룔_866223710(1골), 콩콩콩룔_848189505(1골), 콩콩콩룔_867223848(1골)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20 12:56:53</t>
+          <t>2026-09-21 13:10:19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>킹왕두</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>킹왕두_861049369(1골), 킹왕두_846181291(1골), UNIT_848265695(1골), UNIT_867166676(3골), UNIT_848180930(1골)</t>
+          <t>개포동덕배_845190048(2골), 개포동덕배_856202126(2골), Gucci와퍼_852010264(1골), Gucci와퍼_852028765(1골)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-20 12:46:14</t>
+          <t>2026-09-21 09:01:23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>킹왕두</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6_1</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>은안_852237692(1골), 은안_866241236(2골), 은안_848143001(2골), 은안_856246420(1골), suma수마_861221162(1골)</t>
+          <t>킹왕두_861049369(1골), UNIT_867166676(5골)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-20 12:34:11</t>
+          <t>2026-09-21 04:51:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -921,14 +921,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>은안_866241236(2골), 은안_848143001(1골), 은안_852237692(1골), suma수마_840001114(1골), suma수마_861221162(1골), suma수마_848225439(1골)</t>
+          <t>개포동덕배_845208722(1골), 개포동덕배_856202126(1골), 개포동덕배_863212622(1골), 개포동덕배_845190048(4골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(1골)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-20 12:31:41</t>
+          <t>2026-09-21 04:40:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -938,268 +938,268 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>개포동덕배_856202126(2골), 개포동덕배_845190048(4골), 개포동덕배_845208722(1골), ZD장인지참치_840191208(2골)</t>
+          <t>개포동덕배_856202126(2골), 콩콩콩룔_848189505(1골), 콩콩콩룔_867223848(2골)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-20 12:24:08</t>
+          <t>2026-09-21 04:07:23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>셀래스틴_855239231(1골)</t>
+          <t>ZD장인지참치_840191208(2골), ZD장인지참치_840256630(1골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(1골)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-20 12:20:02</t>
+          <t>2026-09-21 03:56:39</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(2골), 개포동덕배_845208722(1골), 개포동덕배_856202126(1골), ZD장인지참치_848199503(2골), ZD장인지참치_840191208(1골)</t>
+          <t>ZD장인지참치_839200104(1골), 콩콩콩룔_866223710(1골)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-20 12:13:37</t>
+          <t>2026-09-21 03:32:52</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>방덕_856228093(1골), 셀래스틴_863277643(2골), 셀래스틴_852241461(1골)</t>
+          <t>여수가스_101001625(1골), 여수가스_861215732(3골), 여수가스_846001551(1골), ZD장인지참치_861182521(1골), ZD장인지참치_840256630(1골), ZD장인지참치_839200104(2골), ZD장인지참치_840191208(1골)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-20 11:27:42</t>
+          <t>2026-09-21 03:20:08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(1골), 호야국2인_851216409(1골), 개포동덕배_845190048(1골), 개포동덕배_856202126(3골), 개포동덕배_848206113(1골)</t>
+          <t>여수가스_861215732(1골), 여수가스_861162895(3골), ZD장인지참치_840191208(1골), ZD장인지참치_839200104(2골)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-20 11:16:23</t>
+          <t>2026-09-21 03:06:36</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>호야국2인_846192505(1골), 호야국2인_845198219(1골), 호야국2인_851216409(1골), 호야국2인_848232293(1골), 개포동덕배_845168473(1골), 개포동덕배_845190048(1골), 개포동덕배_856202126(2골)</t>
+          <t>여수가스_861162895(1골), 콩콩콩룔_866223710(1골), 콩콩콩룔_867223848(1골), 콩콩콩룔_848189505(1골)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-20 10:36:38</t>
+          <t>2026-09-21 02:55:11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6_0</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(3골), 호야국2인_845198219(1골), 호야국2인_848216435(2골)</t>
+          <t>여수가스_861215732(1골), 콩콩콩룔_851236496(1골), 콩콩콩룔_867223848(2골)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-20 10:25:22</t>
+          <t>2026-09-20 15:26:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>호야국2인_848216435(1골), 호야국2인_848232293(1골)</t>
+          <t>0708ManUtd_851226161(2골), 0708ManUtd_868001397(1골), 0708ManUtd_848037576(1골), 은안_866241236(2골), 은안_848143001(1골), 은안_852237692(1골), 은안_856246420(1골)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-20 10:10:07</t>
+          <t>2026-09-20 15:15:36</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1209,243 +1209,239 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>여수가스_861215732(4골), 겐지간지_856237679(1골), 겐지간지_814231747(1골), 겐지간지_826247635(1골)</t>
+          <t>0708ManUtd_851226161(1골), 0708ManUtd_848037576(1골), 0708ManUtd_834239053(2골), 은안_852237692(1골), 은안_848143001(1골)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-20 09:58:44</t>
+          <t>2026-09-20 14:55:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>여수가스_861162895(1골), 여수가스_861215732(2골), 여수가스_846001551(1골), 겐지간지_814231747(1골)</t>
+          <t>0708ManUtd_848037576(1골), 0708ManUtd_848238794(1골), 비주류중독_840052241(1골), 비주류중독_848006975(1골), 비주류중독_839247699(1골)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-20 08:25:43</t>
+          <t>2026-09-20 14:43:23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6_3</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>개포동덕배_845208722(1골), 개포동덕배_856202126(2골), 개포동덕배_845190048(3골), 스페인전도사_845224574(1골), 스페인전도사_867192629(2골)</t>
+          <t>0708ManUtd_848037576(1골), 0708ManUtd_834239053(1골), 0708ManUtd_848238794(1골), UNIT_848180930(3골)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-20 08:14:10</t>
+          <t>2026-09-20 14:31:41</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>개포동덕배_856202126(1골), 개포동덕배_863212622(1골), 개포동덕배_845190048(4골), 개포동덕배_863234396(1골), 스페인전도사_867192629(1골), 스페인전도사_866235522(1골)</t>
+          <t>Gucci차붐_853272992(2골), 비주류중독_839247699(2골), 비주류중독_863224258(1골)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-20 08:13:05</t>
+          <t>2026-09-20 14:20:24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>suma수마_861190046(1골), suma수마_861221162(1골), 셀래스틴_863251854(1골), 셀래스틴_856277179(1골)</t>
+          <t>Gucci차붐_853272733(1골), 비주류중독_840052241(1골), 비주류중독_825000240(1골), 비주류중독_839247699(1골)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-20 08:02:06</t>
+          <t>2026-09-20 14:16:35</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>suma수마_861190046(2골), suma수마_861221162(2골), 셀래스틴_861026709(1골), 셀래스틴_852241461(1골), 셀래스틴_836158023(1골)</t>
+          <t>0708ManUtd_848037576(1골), Legend독수리_866259399(1골)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-20 07:39:16</t>
+          <t>2026-09-20 14:05:22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>A지냐크_861167134(2골), A지냐크_855213648(1골), 겐지간지_856237679(1골), 겐지간지_814231747(1골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-20 07:25:46</t>
+          <t>2026-09-20 14:01:34</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>겐지간지_856237679(1골)</t>
+          <t>0708ManUtd_851226161(1골), 0708ManUtd_868001397(1골), Legend독수리_861000246(1골), Legend독수리_861007518(1골)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-20 07:08:13</t>
+          <t>2026-09-20 13:12:16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1455,7 +1451,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1465,29 +1461,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Legend독수리_836054050(1골), Legend독수리_848140601(1골), Legend독수리_864039943(2골), 겐지간지_852231443(1골)</t>
+          <t>은안_852237692(1골), 은안_856246420(1골), 은안_851242641(1골), 은안_866241236(2골), 겐지간지_863243780(1골)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-20 06:55:35</t>
+          <t>2026-09-20 13:12:13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>킹왕두</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1497,61 +1493,61 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Legend독수리_840192505(1골), 겐지간지_848170890(1골), 겐지간지_814231747(1골), 겐지간지_856237679(1골)</t>
+          <t>킹왕두_856209331(1골), UNIT_848180930(1골), UNIT_851236403(1골)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-20 06:18:57</t>
+          <t>2026-09-20 12:59:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0_2</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>suma수마_861221162(2골)</t>
+          <t>은안_848143001(2골), 은안_866241236(2골), 은안_856251517(1골), 겐지간지_852231443(1골)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-20 06:05:40</t>
+          <t>2026-09-20 12:56:53</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>킹왕두</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2_10</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1561,29 +1557,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>A지냐크_848031432(1골), A지냐크_861167134(1골), suma수마_861221162(10골)</t>
+          <t>킹왕두_861049369(1골), 킹왕두_846181291(1골), UNIT_848265695(1골), UNIT_867166676(3골), UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-20 05:45:06</t>
+          <t>2026-09-20 12:46:14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>은안</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>suma수마</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>ShangHaiPortFC</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1593,26 +1589,26 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>suma수마_861013383(1골), suma수마_861190046(1골), suma수마_861221162(3골), ShangHaiPortFC_861051412(1골), ShangHaiPortFC_845231138(1골)</t>
+          <t>은안_852237692(1골), 은안_866241236(2골), 은안_848143001(2골), 은안_856246420(1골), suma수마_861221162(1골)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-20 05:33:58</t>
+          <t>2026-09-20 12:34:11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>은안</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>suma수마</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>ShangHaiPortFC</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>4_3</t>
@@ -1625,29 +1621,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>suma수마_861190046(2골), suma수마_861221162(2골), ShangHaiPortFC_864191910(1골), ShangHaiPortFC_848031432(2골)</t>
+          <t>은안_866241236(2골), 은안_848143001(1골), 은안_852237692(1골), suma수마_840001114(1골), suma수마_861221162(1골), suma수마_848225439(1골)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-20 05:20:20</t>
+          <t>2026-09-20 12:31:41</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1657,189 +1653,189 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2골), 앙쿠_851194765(2골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_827143001(1골)</t>
+          <t>개포동덕배_856202126(2골), 개포동덕배_845190048(4골), 개포동덕배_845208722(1골), ZD장인지참치_840191208(2골)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-20 05:09:38</t>
+          <t>2026-09-20 12:24:08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4_0</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>앙쿠_846193747(1골), 앙쿠_814226161(1골), 앙쿠_863246191(2골)</t>
+          <t>셀래스틴_855239231(1골)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-20 03:47:49</t>
+          <t>2026-09-20 12:20:02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Legend독수리_840192505(2골), Legend독수리_861007518(1골), 셀래스틴_863277643(1골), 셀래스틴_852241461(2골), 셀래스틴_856277179(1골)</t>
+          <t>개포동덕배_845190048(2골), 개포동덕배_845208722(1골), 개포동덕배_856202126(1골), ZD장인지참치_848199503(2골), ZD장인지참치_840191208(1골)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-20 03:44:09</t>
+          <t>2026-09-20 12:13:37</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8_3</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(3골), 앙쿠_863246191(2골), 앙쿠_851194765(3골), ShangHaiPortFC_848031432(2골), ShangHaiPortFC_864191910(1골)</t>
+          <t>방덕_856228093(1골), 셀래스틴_863277643(2골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-20 03:36:07</t>
+          <t>2026-09-20 11:27:42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Legend독수리_840192505(1골), Legend독수리_861230025(1골), Legend독수리_839226764(1골), 셀래스틴_856277179(2골)</t>
+          <t>호야국2인_848232293(1골), 호야국2인_851216409(1골), 개포동덕배_845190048(1골), 개포동덕배_856202126(3골), 개포동덕배_848206113(1골)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-20 03:31:53</t>
+          <t>2026-09-20 11:16:23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>6_1</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2골), 앙쿠_863246191(2골), 앙쿠_863232488(1골), 앙쿠_866266039(1골), ShangHaiPortFC_864191910(1골)</t>
+          <t>호야국2인_846192505(1골), 호야국2인_845198219(1골), 호야국2인_851216409(1골), 호야국2인_848232293(1골), 개포동덕배_845168473(1골), 개포동덕배_845190048(1골), 개포동덕배_856202126(2골)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-20 03:17:22</t>
+          <t>2026-09-20 10:36:38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>6_0</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1849,61 +1845,61 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 앙쿠_848176580(2골), 셀래스틴_852241461(1골), 셀래스틴_845158023(1골)</t>
+          <t>호야국2인_848232293(3골), 호야국2인_845198219(1골), 호야국2인_848216435(2골)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-20 03:17:01</t>
+          <t>2026-09-20 10:25:22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Legend독수리_861007518(1골), Legend독수리_821143001(1골), ShangHaiPortFC_864191910(4골)</t>
+          <t>호야국2인_848216435(1골), 호야국2인_848232293(1골)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-20 03:05:59</t>
+          <t>2026-09-20 10:10:07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8_3</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1913,24 +1909,24 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Legend독수리_840192505(4골), Legend독수리_866259399(2골), Legend독수리_839226764(1골), Legend독수리_861230025(1골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_284190813(1골), ShangHaiPortFC_861051412(1골)</t>
+          <t>여수가스_861215732(4골), 겐지간지_856237679(1골), 겐지간지_814231747(1골), 겐지간지_826247635(1골)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-19 16:32:52</t>
+          <t>2026-09-20 09:58:44</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1945,189 +1941,189 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(2골), 스페인전도사_866235522(2골), 여수가스_861215732(1골)</t>
+          <t>여수가스_861162895(1골), 여수가스_861215732(2골), 여수가스_846001551(1골), 겐지간지_814231747(1골)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-19 16:20:51</t>
+          <t>2026-09-20 08:25:43</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>스페인전도사</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>여수가스</t>
-        </is>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1_4</t>
+          <t>6_3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(1골), 여수가스_861162895(1골), 여수가스_861215732(3골)</t>
+          <t>개포동덕배_845208722(1골), 개포동덕배_856202126(2골), 개포동덕배_845190048(3골), 스페인전도사_845224574(1골), 스페인전도사_867192629(2골)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-19 15:34:28</t>
+          <t>2026-09-20 08:14:10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3_8</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_867166676(2골), Voor_845247090(1골), Voor_852233700(2골), Voor_845009676(1골), Voor_858020775(2골), Voor_851238616(1골), Voor_845001620(1골)</t>
+          <t>개포동덕배_856202126(1골), 개포동덕배_863212622(1골), 개포동덕배_845190048(4골), 개포동덕배_863234396(1골), 스페인전도사_867192629(1골), 스페인전도사_866235522(1골)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-19 15:21:21</t>
+          <t>2026-09-20 08:13:05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), Voor_845247090(1골), Voor_845009676(2골)</t>
+          <t>suma수마_861190046(1골), suma수마_861221162(1골), 셀래스틴_863251854(1골), 셀래스틴_856277179(1골)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-19 15:17:09</t>
+          <t>2026-09-20 08:02:06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(1골), 스페인전도사_845224574(1골), 콩콩콩룔_866223710(3골), 콩콩콩룔_867220502(1골), 콩콩콩룔_867223848(1골)</t>
+          <t>suma수마_861190046(2골), suma수마_861221162(2골), 셀래스틴_861026709(1골), 셀래스틴_852241461(1골), 셀래스틴_836158023(1골)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-19 15:08:18</t>
+          <t>2026-09-20 07:39:16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>은안_866241236(1골), 은안_856246420(1골), Voor_845009676(1골), Voor_858020775(1골)</t>
+          <t>A지냐크_861167134(2골), A지냐크_855213648(1골), 겐지간지_856237679(1골), 겐지간지_814231747(1골)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-19 15:05:47</t>
+          <t>2026-09-20 07:25:46</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2137,61 +2133,61 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(1골), 콩콩콩룔_848189505(1골), 콩콩콩룔_866223710(1골)</t>
+          <t>겐지간지_856237679(1골)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-19 14:56:37</t>
+          <t>2026-09-20 07:08:13</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2_8</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>은안_866241236(1골), 은안_856246420(1골), Voor_845009676(2골), Voor_852233700(4골), Voor_858020775(2골)</t>
+          <t>Legend독수리_836054050(1골), Legend독수리_848140601(1골), Legend독수리_864039943(2골), 겐지간지_852231443(1골)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-19 14:24:16</t>
+          <t>2026-09-20 06:55:35</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2201,93 +2197,93 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골)</t>
+          <t>Legend독수리_840192505(1골), 겐지간지_848170890(1골), 겐지간지_814231747(1골), 겐지간지_856237679(1골)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-19 14:13:53</t>
+          <t>2026-09-20 06:18:57</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5_5</t>
+          <t>0_2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(2골), 앙쿠_851194765(3골), UNIT_867166676(1골), UNIT_848180930(4골)</t>
+          <t>suma수마_861221162(2골)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-19 13:54:08</t>
+          <t>2026-09-20 06:05:40</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>2_10</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 앙쿠_848176580(3골), UNIT_867166676(4골)</t>
+          <t>A지냐크_848031432(1골), A지냐크_861167134(1골), suma수마_861221162(10골)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-19 13:36:20</t>
+          <t>2026-09-20 05:45:06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2297,93 +2293,93 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>앙쿠_866266039(1골), 앙쿠_848176580(1골)</t>
+          <t>suma수마_861013383(1골), suma수마_861190046(1골), suma수마_861221162(3골), ShangHaiPortFC_861051412(1골), ShangHaiPortFC_845231138(1골)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-19 13:25:57</t>
+          <t>2026-09-20 05:33:58</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>앙쿠_863232488(1골), 앙쿠_848176580(1골), UNIT_848180930(1골), UNIT_840228251(1골), UNIT_840192883(1골)</t>
+          <t>suma수마_861190046(2골), suma수마_861221162(2골), ShangHaiPortFC_864191910(1골), ShangHaiPortFC_848031432(2골)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-19 12:33:16</t>
+          <t>2026-09-20 05:20:20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), UNIT_848180930(2골), 셀래스틴_868222481(1골), 셀래스틴_852241461(2골)</t>
+          <t>앙쿠_848176580(2골), 앙쿠_851194765(2골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_827143001(1골)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-19 12:20:50</t>
+          <t>2026-09-20 05:09:38</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2393,93 +2389,93 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), UNIT_840228251(1골), 셀래스틴_863277643(1골)</t>
+          <t>앙쿠_846193747(1골), 앙쿠_814226161(1골), 앙쿠_863246191(2골)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-19 12:10:22</t>
+          <t>2026-09-20 03:47:49</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(3골), 앙쿠_866266039(1골), suma수마_861013383(1골), suma수마_861221162(1골)</t>
+          <t>Legend독수리_840192505(2골), Legend독수리_861007518(1골), 셀래스틴_863277643(1골), 셀래스틴_852241461(2골), 셀래스틴_856277179(1골)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-19 12:06:46</t>
+          <t>2026-09-20 03:44:09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>8_3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2골), 셀래스틴_863277643(1골), 셀래스틴_845158023(2골), 셀래스틴_863251854(1골)</t>
+          <t>앙쿠_848176580(3골), 앙쿠_863246191(2골), 앙쿠_851194765(3골), ShangHaiPortFC_848031432(2골), ShangHaiPortFC_864191910(1골)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-19 11:59:22</t>
+          <t>2026-09-20 03:36:07</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2489,29 +2485,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2골), 앙쿠_863246191(2골), 앙쿠_866266039(1골), suma수마_840001114(1골), suma수마_861190046(1골)</t>
+          <t>Legend독수리_840192505(1골), Legend독수리_861230025(1골), Legend독수리_839226764(1골), 셀래스틴_856277179(2골)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-19 11:55:57</t>
+          <t>2026-09-20 03:31:53</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2521,93 +2517,93 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(1골), ZD장인지참치_852213331(1골), 셀래스틴_846199564(1골), 셀래스틴_863277643(1골), 셀래스틴_856277179(1골)</t>
+          <t>앙쿠_848176580(2골), 앙쿠_863246191(2골), 앙쿠_863232488(1골), 앙쿠_866266039(1골), ShangHaiPortFC_864191910(1골)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-19 11:38:35</t>
+          <t>2026-09-20 03:17:22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ZD장인지참치_839200104(1골), 경남FC가즈아_853221467(1골), 경남FC가즈아_225238224(1골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_848176580(2골), 셀래스틴_852241461(1골), 셀래스틴_845158023(1골)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-19 11:35:15</t>
+          <t>2026-09-20 03:17:01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>suma수마_861221162(2골), 셀래스틴_852241461(2골)</t>
+          <t>Legend독수리_861007518(1골), Legend독수리_821143001(1골), ShangHaiPortFC_864191910(4골)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-19 11:32:23</t>
+          <t>2026-09-20 03:05:59</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>8_3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2617,29 +2613,29 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(3골), 개포동덕배_845208722(1골), 개포동덕배_848206113(1골), UNIT_848180930(1골), UNIT_851236403(1골)</t>
+          <t>Legend독수리_840192505(4골), Legend독수리_866259399(2골), Legend독수리_839226764(1골), Legend독수리_861230025(1골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_284190813(1골), ShangHaiPortFC_861051412(1골)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-19 11:27:23</t>
+          <t>2026-09-19 16:32:52</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2649,29 +2645,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ZD장인지참치_861182521(1골), ZD장인지참치_851240740(1골), ZD장인지참치_840256630(1골), 경남FC가즈아_518200601(1골)</t>
+          <t>스페인전도사_867192629(2골), 스페인전도사_866235522(2골), 여수가스_861215732(1골)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-19 11:23:35</t>
+          <t>2026-09-19 16:20:51</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2681,29 +2677,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>suma수마_861221162(2골), 셀래스틴_845158023(1골), 셀래스틴_856277179(1골), 셀래스틴_852241461(1골), 셀래스틴_863277643(1골)</t>
+          <t>스페인전도사_867192629(1골), 여수가스_861162895(1골), 여수가스_861215732(3골)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-19 11:21:04</t>
+          <t>2026-09-19 15:34:28</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_8</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2713,24 +2709,24 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(2골), UNIT_840210736(1골), UNIT_867166676(2골)</t>
+          <t>UNIT_848180930(1골), UNIT_867166676(2골), Voor_845247090(1골), Voor_852233700(2골), Voor_845009676(1골), Voor_858020775(2골), Voor_851238616(1골), Voor_845001620(1골)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-19 11:06:32</t>
+          <t>2026-09-19 15:21:21</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2745,29 +2741,29 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>A지냐크_848031432(1골), A지냐크_863241496(1골), 경남FC가즈아_864139443(1골), 경남FC가즈아_225238224(1골), 경남FC가즈아_277205156(1골)</t>
+          <t>UNIT_867166676(2골), Voor_845247090(1골), Voor_845009676(2골)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-19 10:53:44</t>
+          <t>2026-09-19 15:17:09</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2775,91 +2771,95 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>스페인전도사_867192629(1골), 스페인전도사_845224574(1골), 콩콩콩룔_866223710(3골), 콩콩콩룔_867220502(1골), 콩콩콩룔_867223848(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-19 10:46:09</t>
+          <t>2026-09-19 15:08:18</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4_5</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>A지냐크_848031432(1골), A지냐크_861167134(1골), A지냐크_840236496(1골), A지냐크_863241496(1골), 스페인전도사_858008348(1골), 스페인전도사_867192629(3골), 스페인전도사_866235522(1골)</t>
+          <t>은안_866241236(1골), 은안_856246420(1골), Voor_845009676(1골), Voor_858020775(1골)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-19 10:33:32</t>
+          <t>2026-09-19 15:05:47</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>A지냐크_848031432(3골), 스페인전도사_866235522(1골), 스페인전도사_861001668(1골)</t>
+          <t>스페인전도사_867192629(1골), 콩콩콩룔_848189505(1골), 콩콩콩룔_866223710(1골)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-19 10:19:19</t>
+          <t>2026-09-19 14:56:37</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0_4</t>
+          <t>2_8</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2869,61 +2869,61 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(2골), 앙쿠_848176580(2골)</t>
+          <t>은안_866241236(1골), 은안_856246420(1골), Voor_845009676(2골), Voor_852233700(4골), Voor_858020775(2골)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-19 10:06:31</t>
+          <t>2026-09-19 14:24:16</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>A지냐크_848031432(1골), A지냐크_861167134(1골), A지냐크_867214101(1골), 앙쿠_863246191(2골), 앙쿠_848176580(1골)</t>
+          <t>UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-19 09:48:12</t>
+          <t>2026-09-19 14:13:53</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>검정소</t>
-        </is>
-      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>5_5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2933,46 +2933,46 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1골), UNIT_848265695(1골), UNIT_848180930(3골), 검정소_868013128(4골)</t>
+          <t>앙쿠_863246191(2골), 앙쿠_851194765(3골), UNIT_867166676(1골), UNIT_848180930(4골)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-19 09:36:18</t>
+          <t>2026-09-19 13:54:08</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>검정소</t>
-        </is>
-      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>검정소_868192181(1골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_848176580(3골), UNIT_867166676(4골)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-19 09:21:02</t>
+          <t>2026-09-19 13:36:20</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2982,44 +2982,44 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(2골), 검정소_868013128(2골)</t>
+          <t>앙쿠_866266039(1골), 앙쿠_848176580(1골)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-19 09:14:49</t>
+          <t>2026-09-19 13:25:57</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>3_5</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3029,56 +3029,56 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>오스트리아_864182152(2골), 오스트리아_851236636(1골), ZD장인지참치_840256630(1골), ZD장인지참치_839200104(3골), ZD장인지참치_840191208(1골)</t>
+          <t>앙쿠_863232488(1골), 앙쿠_848176580(1골), UNIT_848180930(1골), UNIT_840228251(1골), UNIT_840192883(1골)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-19 09:10:07</t>
+          <t>2026-09-19 12:33:16</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2골), 앙쿠_851194765(1골), 검정소_867241096(1골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(2골), 셀래스틴_868222481(1골), 셀래스틴_852241461(2골)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-19 09:03:03</t>
+          <t>2026-09-19 12:20:50</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3093,29 +3093,29 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>오스트리아_862140057(1골), 오스트리아_864199266(2골), ZD장인지참치_840256630(1골)</t>
+          <t>UNIT_848180930(2골), UNIT_840228251(1골), 셀래스틴_863277643(1골)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-19 08:47:53</t>
+          <t>2026-09-19 12:10:22</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3125,29 +3125,29 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>UNIT_840192883(2골), UNIT_867166676(3골), 오스트리아_864182152(1골), 오스트리아_864199266(1골)</t>
+          <t>앙쿠_848176580(3골), 앙쿠_866266039(1골), suma수마_861013383(1골), suma수마_861221162(1골)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-19 08:36:31</t>
+          <t>2026-09-19 12:06:46</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3155,27 +3155,31 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(2골), 셀래스틴_863277643(1골), 셀래스틴_845158023(2골), 셀래스틴_863251854(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-19 08:35:13</t>
+          <t>2026-09-19 11:59:22</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3185,157 +3189,157 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), UNIT_848180930(1골), 오스트리아_864199266(2골)</t>
+          <t>앙쿠_848176580(2골), 앙쿠_863246191(2골), 앙쿠_866266039(1골), suma수마_840001114(1골), suma수마_861190046(1골)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-19 08:24:13</t>
+          <t>2026-09-19 11:55:57</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>4_8</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(4골), ZD장인지참치_840247263(2골), ZD장인지참치_839200104(4골), ZD장인지참치_840191208(2골)</t>
+          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(1골), ZD장인지참치_852213331(1골), 셀래스틴_846199564(1골), 셀래스틴_863277643(1골), 셀래스틴_856277179(1골)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-19 08:15:28</t>
+          <t>2026-09-19 11:38:35</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>오스트리아_826204497(1골), 오스트리아_864182152(1골), suma수마_861221162(1골)</t>
+          <t>ZD장인지참치_839200104(1골), 경남FC가즈아_853221467(1골), 경남FC가즈아_225238224(1골)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-19 08:12:24</t>
+          <t>2026-09-19 11:35:15</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ZD장인지참치_861182521(1골)</t>
+          <t>suma수마_861221162(2골), 셀래스틴_852241461(2골)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-19 08:09:08</t>
+          <t>2026-09-19 11:32:23</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(2골), ZD장인지참치_839200104(1골), ZD장인지참치_848199503(1골), ZD장인지참치_851240740(1골), ZD장인지참치_840191208(1골)</t>
+          <t>개포동덕배_845190048(3골), 개포동덕배_845208722(1골), 개포동덕배_848206113(1골), UNIT_848180930(1골), UNIT_851236403(1골)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-19 08:03:54</t>
+          <t>2026-09-19 11:27:23</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3345,83 +3349,83 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>오스트리아_862140057(1골), 오스트리아_864182152(1골), 오스트리아_851236636(1골), 오스트리아_864199266(2골), suma수마_861221162(1골), suma수마_861190046(1골)</t>
+          <t>ZD장인지참치_861182521(1골), ZD장인지참치_851240740(1골), ZD장인지참치_840256630(1골), 경남FC가즈아_518200601(1골)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-19 05:58:58</t>
+          <t>2026-09-19 11:23:35</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), 비주류중독_840052241(1골)</t>
+          <t>suma수마_861221162(2골), 셀래스틴_845158023(1골), 셀래스틴_856277179(1골), 셀래스틴_852241461(1골), 셀래스틴_863277643(1골)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-19 05:47:10</t>
+          <t>2026-09-19 11:21:04</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>비주류중독</t>
-        </is>
-      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), UNIT_848180930(2골), 비주류중독_862180283(1골)</t>
+          <t>개포동덕배_845190048(2골), UNIT_840210736(1골), UNIT_867166676(2골)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-19 05:24:55</t>
+          <t>2026-09-19 11:06:32</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3431,7 +3435,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3441,19 +3445,19 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Legend독수리_848140601(1골), 경남FC가즈아_225238224(1골), 경남FC가즈아_805267825(1골)</t>
+          <t>A지냐크_848031432(1골), A지냐크_863241496(1골), 경남FC가즈아_864139443(1골), 경남FC가즈아_225238224(1골), 경남FC가즈아_277205156(1골)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-19 05:13:36</t>
+          <t>2026-09-19 10:53:44</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3463,39 +3467,35 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Legend독수리_821143001(1골), 경남FC가즈아_853221467(1골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-19 05:00:44</t>
+          <t>2026-09-19 10:46:09</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3505,61 +3505,61 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Legend독수리_840192505(1골), Legend독수리_839226764(1골), 비주류중독_839247699(2골), 비주류중독_840052241(2골)</t>
+          <t>A지냐크_848031432(1골), A지냐크_861167134(1골), A지냐크_840236496(1골), A지냐크_863241496(1골), 스페인전도사_858008348(1골), 스페인전도사_867192629(3골), 스페인전도사_866235522(1골)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-19 04:48:52</t>
+          <t>2026-09-19 10:33:32</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Legend독수리_821143001(2골), 비주류중독_848006975(1골), 비주류중독_862180283(1골), 비주류중독_839247699(1골)</t>
+          <t>A지냐크_848031432(3골), 스페인전도사_866235522(1골), 스페인전도사_861001668(1골)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-19 04:11:38</t>
+          <t>2026-09-19 10:19:19</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>0_4</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3569,157 +3569,157 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Legend독수리_840192505(2골), 셀래스틴_852241461(1골), 셀래스틴_845158023(1골), 셀래스틴_863277643(1골)</t>
+          <t>앙쿠_863246191(2골), 앙쿠_848176580(2골)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:02</t>
+          <t>2026-09-19 10:06:31</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Legend독수리_821143001(3골), Legend독수리_836054050(1골), Legend독수리_861000246(1골), 셀래스틴_863277643(1골)</t>
+          <t>A지냐크_848031432(1골), A지냐크_861167134(1골), A지냐크_867214101(1골), 앙쿠_863246191(2골), 앙쿠_848176580(1골)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-19 03:15:22</t>
+          <t>2026-09-19 09:48:12</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2_6</t>
+          <t>5_4</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>여수가스_846001551(1골), 여수가스_861215732(1골), ZD장인지참치_840256630(1골), ZD장인지참치_839200104(3골), ZD장인지참치_840191208(1골), ZD장인지참치_840247263(1골)</t>
+          <t>UNIT_840192883(1골), UNIT_848265695(1골), UNIT_848180930(3골), 검정소_868013128(4골)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-19 03:03:53</t>
+          <t>2026-09-19 09:36:18</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>여수가스_861215732(1골), 여수가스_861162895(2골), ZD장인지참치_840191208(2골)</t>
+          <t>검정소_868192181(1골)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-19 01:33:00</t>
+          <t>2026-09-19 09:21:02</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>겐지간지_852231443(1골), 겐지간지_814231747(3골), Gucci와퍼_839200104(2골), Gucci와퍼_852010264(1골)</t>
+          <t>앙쿠_851194765(2골), 검정소_868013128(2골)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-19 01:18:46</t>
+          <t>2026-09-19 09:14:49</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>3_5</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3729,47 +3729,51 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>겐지간지_814231747(1골), Gucci와퍼_852168473(1골), Gucci와퍼_839200104(1골)</t>
+          <t>오스트리아_864182152(2골), 오스트리아_851236636(1골), ZD장인지참치_840256630(1골), ZD장인지참치_839200104(3골), ZD장인지참치_840191208(1골)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-19 01:06:48</t>
+          <t>2026-09-19 09:10:07</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(2골), 앙쿠_851194765(1골), 검정소_867241096(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-19 00:56:16</t>
+          <t>2026-09-19 09:03:03</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3779,79 +3783,775 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2_7</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>겐지간지_861001668(1골), 겐지간지_818179813(1골), ZD장인지참치_861182521(1골), ZD장인지참치_840191208(3골), ZD장인지참치_839200104(3골)</t>
+          <t>오스트리아_862140057(1골), 오스트리아_864199266(2골), ZD장인지참치_840256630(1골)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-19 00:43:56</t>
+          <t>2026-09-19 08:47:53</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0_5</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(3골), ZD장인지참치_839200104(2골)</t>
+          <t>UNIT_840192883(2골), UNIT_867166676(3골), 오스트리아_864182152(1골), 오스트리아_864199266(1골)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>2026-09-19 08:36:31</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0_0</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:35:13</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), UNIT_848180930(1골), 오스트리아_864199266(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:24:13</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>스페인전도사</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4_8</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>스페인전도사_867192629(4골), ZD장인지참치_840247263(2골), ZD장인지참치_839200104(4골), ZD장인지참치_840191208(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:15:28</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>오스트리아_826204497(1골), 오스트리아_864182152(1골), suma수마_861221162(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:12:24</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>스페인전도사</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>0_1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_861182521(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:09:08</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>스페인전도사</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>스페인전도사_867192629(2골), ZD장인지참치_839200104(1골), ZD장인지참치_848199503(1골), ZD장인지참치_851240740(1골), ZD장인지참치_840191208(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:03:54</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>오스트리아_862140057(1골), 오스트리아_864182152(1골), 오스트리아_851236636(1골), 오스트리아_864199266(2골), suma수마_861221162(1골), suma수마_861190046(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:58:58</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1골), 비주류중독_840052241(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:47:10</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>4_1</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), UNIT_848180930(2골), 비주류중독_862180283(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:24:55</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Legend독수리_848140601(1골), 경남FC가즈아_225238224(1골), 경남FC가즈아_805267825(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:13:36</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Legend독수리_821143001(1골), 경남FC가즈아_853221467(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:00:44</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Legend독수리_840192505(1골), Legend독수리_839226764(1골), 비주류중독_839247699(2골), 비주류중독_840052241(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:48:52</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Legend독수리_821143001(2골), 비주류중독_848006975(1골), 비주류중독_862180283(1골), 비주류중독_839247699(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:11:38</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Legend독수리_840192505(2골), 셀래스틴_852241461(1골), 셀래스틴_845158023(1골), 셀래스틴_863277643(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:00:02</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Legend독수리_821143001(3골), Legend독수리_836054050(1골), Legend독수리_861000246(1골), 셀래스틴_863277643(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:15:22</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2_6</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>여수가스_846001551(1골), 여수가스_861215732(1골), ZD장인지참치_840256630(1골), ZD장인지참치_839200104(3골), ZD장인지참치_840191208(1골), ZD장인지참치_840247263(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:03:53</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>여수가스_861215732(1골), 여수가스_861162895(2골), ZD장인지참치_840191208(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:33:00</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>겐지간지_852231443(1골), 겐지간지_814231747(3골), Gucci와퍼_839200104(2골), Gucci와퍼_852010264(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:18:46</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>겐지간지_814231747(1골), Gucci와퍼_852168473(1골), Gucci와퍼_839200104(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:06:48</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>0_0</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:56:16</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2_7</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>겐지간지_861001668(1골), 겐지간지_818179813(1골), ZD장인지참치_861182521(1골), ZD장인지참치_840191208(3골), ZD장인지참치_839200104(3골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:43:56</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0_5</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(3골), ZD장인지참치_839200104(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
           <t>2026-09-18 17:47:34</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>스페인전도사</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>여수가스</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>2_2</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>무</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>스페인전도사_867192629(1골), 스페인전도사_866235522(1골), 여수가스_861162895(1골), 여수가스_861215732(1골)</t>
         </is>
@@ -3868,7 +4568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3906,54 +4606,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20 15:26:30</t>
+          <t>2026-09-21 15:12:55</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4_5</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0708ManUtd_848183277(2도움), 0708ManUtd_868001397(1도움), 0708ManUtd_848037576(1도움), 은안_866241236(1도움), 은안_848143001(1도움), 은안_846210514(1도움), 은안_852237692(2도움)</t>
+          <t>앙쿠_846186345(1도움), 앙쿠_848176580(1도움), Special블루_863234378(1도움), Special블루_856243715(1도움), Special블루_856246669(1도움)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20 15:15:36</t>
+          <t>2026-09-21 15:02:23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3963,14 +4663,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0708ManUtd_851226161(1도움), 0708ManUtd_848183277(2도움), 0708ManUtd_867232656(1도움), 은안_856246420(1도움), 은안_848231866(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_848176580(1도움), Special블루_856243715(1도움)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20 14:55:27</t>
+          <t>2026-09-21 14:26:25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3980,29 +4680,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0708ManUtd_868001397(1도움), 0708ManUtd_834239053(1도움), 비주류중독_840052241(1도움), 비주류중독_848006975(1도움), 비주류중독_839247699(1도움)</t>
+          <t>0708ManUtd_834239053(1도움), 0708ManUtd_863239231(1도움), 0708ManUtd_868001397(1도움), Gucci와퍼_839200104(1도움)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20 14:43:23</t>
+          <t>2026-09-21 14:14:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4012,76 +4712,72 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0708ManUtd_848183277(1도움), 0708ManUtd_848238794(1도움), UNIT_840192883(1도움), UNIT_840228251(1도움), UNIT_840225782(1도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20 14:31:41</t>
+          <t>2026-09-21 14:13:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gucci차붐_851221671(1도움), Gucci차붐_853272733(1도움), 비주류중독_834239977(1도움), 비주류중독_848006975(1도움), 비주류중독_821214622(1도움)</t>
+          <t>0708ManUtd_848238794(2도움), Gucci와퍼_852028765(1도움)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20 14:20:24</t>
+          <t>2026-09-21 13:49:20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>4_6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4091,14 +4787,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gucci차붐_864033730(1도움), 비주류중독_840052241(1도움), 비주류중독_862180283(2도움)</t>
+          <t>0708ManUtd_848238794(1도움), 0708ManUtd_868001397(1도움), ZD장인지참치_840191208(1도움), ZD장인지참치_851240740(1도움), ZD장인지참치_861182521(3도움)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20 14:16:35</t>
+          <t>2026-09-21 13:37:50</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4108,57 +4804,61 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0708ManUtd_848183277(1도움), Legend독수리_861007518(1도움)</t>
+          <t>0708ManUtd_834239053(1도움), 0708ManUtd_851226161(1도움), ZD장인지참치_840191208(1도움), ZD장인지참치_848210035(1도움), ZD장인지참치_861182521(1도움)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20 14:05:22</t>
+          <t>2026-09-21 13:23:22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>5_4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Voor_858020775(1도움), Voor_845001620(1도움), Voor_852233700(2도움), Voor_851238616(1도움), 콩콩콩룔_848189505(2도움), 콩콩콩룔_866223710(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01:34</t>
+          <t>2026-09-21 13:23:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4168,12 +4868,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4183,29 +4883,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0708ManUtd_848037576(1도움), 0708ManUtd_834239053(1도움), Legend독수리_864039943(1도움)</t>
+          <t>셀래스틴_856277179(1도움)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20 13:12:16</t>
+          <t>2026-09-21 13:22:31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4215,157 +4915,157 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>은안_856246420(1도움), 은안_848143001(1도움), 은안_851242641(1도움), 은안_866241236(1도움), 겐지간지_845158023(1도움)</t>
+          <t>개포동덕배_845168473(1도움), 개포동덕배_863212622(1도움), 개포동덕배_863234396(1도움), 개포동덕배_845208722(1도움), 개포동덕배_856202126(1도움), Gucci와퍼_852168473(1도움), Gucci와퍼_852208128(1도움)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20 13:12:13</t>
+          <t>2026-09-21 13:11:54</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>킹왕두</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>킹왕두_848203376(1도움), UNIT_848265695(1도움), UNIT_840210736(1도움)</t>
+          <t>0708ManUtd_868001397(2도움), 0708ManUtd_834239053(1도움), 0708ManUtd_848037576(1도움), 0708ManUtd_848238794(1도움), 0708ManUtd_851226161(1도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-20 12:59:17</t>
+          <t>2026-09-21 13:11:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>은안_846210514(1도움), 은안_836239085(1도움), 은안_848231866(1도움), 은안_848143001(1도움), 겐지간지_848170890(1도움)</t>
+          <t>Voor_851238616(1도움), Voor_858020775(1도움), 콩콩콩룔_866223710(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_840228302(1도움)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20 12:56:53</t>
+          <t>2026-09-21 13:10:19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>킹왕두</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>킹왕두_829013743(1도움), 킹왕두_856209331(1도움), UNIT_840228251(1도움), UNIT_840216150(1도움), UNIT_840225782(2도움)</t>
+          <t>개포동덕배_863212622(1도움), 개포동덕배_845168473(1도움), 개포동덕배_848206113(1도움), 개포동덕배_845208722(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_851210697(1도움)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-20 12:46:14</t>
+          <t>2026-09-21 09:01:23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>킹왕두</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6_1</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>은안_866241236(1도움), 은안_848143001(3도움), 은안_856246420(1도움), suma수마_861013383(1도움)</t>
+          <t>킹왕두_829013743(1도움), UNIT_840192883(1도움), UNIT_840228251(2도움), UNIT_848180930(2도움)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-20 12:34:11</t>
+          <t>2026-09-21 04:51:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4375,14 +5075,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>은안_866241236(1도움), 은안_848143001(1도움), 은안_852237692(1도움), 은안_856246420(1도움), suma수마_861221162(1도움), suma수마_861013383(2도움)</t>
+          <t>개포동덕배_845208722(1도움), 개포동덕배_856202126(2도움), 개포동덕배_863212622(1도움), 개포동덕배_845168473(2도움), 개포동덕배_845190048(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(1도움)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-20 12:31:41</t>
+          <t>2026-09-21 04:40:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4392,268 +5092,268 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>개포동덕배_856202126(2도움), 개포동덕배_845190048(1도움), 개포동덕배_845208722(1도움), 개포동덕배_845168473(1도움), 개포동덕배_863212622(2도움), ZD장인지참치_848199503(1도움), ZD장인지참치_851240740(1도움)</t>
+          <t>개포동덕배_845168473(1도움), 개포동덕배_845208722(1도움), 콩콩콩룔_866223710(1도움), 콩콩콩룔_867220502(2도움)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-20 12:24:08</t>
+          <t>2026-09-21 04:07:23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>셀래스틴_863277643(1도움)</t>
+          <t>ZD장인지참치_839200104(2도움), 콩콩콩룔_848189505(1도움)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-20 12:20:02</t>
+          <t>2026-09-21 03:56:39</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(2도움), 개포동덕배_848206113(1도움), 개포동덕배_856202126(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_840256630(2도움)</t>
+          <t>ZD장인지참치_848199503(1도움), 콩콩콩룔_867220502(1도움)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-20 12:13:37</t>
+          <t>2026-09-21 03:32:52</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>방덕_867001040(1도움), 셀래스틴_863277643(1도움), 셀래스틴_852241461(2도움)</t>
+          <t>여수가스_828231747(1도움), 여수가스_861162895(2도움), ZD장인지참치_861182521(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_840191208(2도움)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-20 11:27:42</t>
+          <t>2026-09-21 03:20:08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>호야국2인_846192505(1도움), 호야국2인_851216409(1도움), 개포동덕배_845190048(1도움), 개포동덕배_845208722(2도움), 개포동덕배_845168473(1도움)</t>
+          <t>여수가스_861215732(1도움), 여수가스_828231747(1도움), 여수가스_861162895(1도움), 여수가스_846001551(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_840191208(1도움)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-20 11:16:23</t>
+          <t>2026-09-21 03:06:36</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>호야국2인_846192505(1도움), 호야국2인_851216409(1도움), 호야국2인_848227236(1도움), 호야국2인_848232293(1도움), 개포동덕배_852225375(1도움), 개포동덕배_845168473(1도움), 개포동덕배_845190048(2도움)</t>
+          <t>여수가스_846188567(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(1도움), 콩콩콩룔_851236496(1도움)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-20 10:36:38</t>
+          <t>2026-09-21 02:55:11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6_0</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>호야국2인_846192505(2도움), 호야국2인_848232293(1도움), 호야국2인_851216409(2도움), 호야국2인_848216435(1도움)</t>
+          <t>여수가스_868135455(1도움), 콩콩콩룔_861006235(1도움), 콩콩콩룔_848189505(2도움)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-20 10:25:22</t>
+          <t>2026-09-20 15:26:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>호야국2인_851216409(1도움), 호야국2인_848216435(1도움)</t>
+          <t>0708ManUtd_848183277(2도움), 0708ManUtd_868001397(1도움), 0708ManUtd_848037576(1도움), 은안_866241236(1도움), 은안_848143001(1도움), 은안_846210514(1도움), 은안_852237692(2도움)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-20 10:10:07</t>
+          <t>2026-09-20 15:15:36</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4663,243 +5363,239 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>여수가스_852216393(1도움), 여수가스_828231747(1도움), 여수가스_861162895(2도움), 겐지간지_845158023(2도움), 겐지간지_863243780(1도움)</t>
+          <t>0708ManUtd_851226161(1도움), 0708ManUtd_848183277(2도움), 0708ManUtd_867232656(1도움), 은안_856246420(1도움), 은안_848231866(1도움)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-20 09:58:44</t>
+          <t>2026-09-20 14:55:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>여수가스_861162895(2도움), 여수가스_846001551(1도움), 여수가스_852216393(1도움), 겐지간지_848170890(1도움)</t>
+          <t>0708ManUtd_868001397(1도움), 0708ManUtd_834239053(1도움), 비주류중독_840052241(1도움), 비주류중독_848006975(1도움), 비주류중독_839247699(1도움)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-20 08:25:43</t>
+          <t>2026-09-20 14:43:23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6_3</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>개포동덕배_852225375(1도움), 개포동덕배_845208722(2도움), 개포동덕배_856202126(2도움), 개포동덕배_848206113(1도움), 스페인전도사_851236295(1도움), 스페인전도사_866235522(1도움)</t>
+          <t>0708ManUtd_848183277(1도움), 0708ManUtd_848238794(1도움), UNIT_840192883(1도움), UNIT_840228251(1도움), UNIT_840225782(1도움)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-20 08:14:10</t>
+          <t>2026-09-20 14:31:41</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>개포동덕배_856202126(3도움), 개포동덕배_845208722(4도움), 스페인전도사_851216435(1도움), 스페인전도사_851224415(1도움)</t>
+          <t>Gucci차붐_851221671(1도움), Gucci차붐_853272733(1도움), 비주류중독_834239977(1도움), 비주류중독_848006975(1도움), 비주류중독_821214622(1도움)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-20 08:13:05</t>
+          <t>2026-09-20 14:20:24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>suma수마_861013383(1도움), suma수마_861190046(1도움), 셀래스틴_863277643(2도움)</t>
+          <t>Gucci차붐_864033730(1도움), 비주류중독_840052241(1도움), 비주류중독_862180283(2도움)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-20 08:02:06</t>
+          <t>2026-09-20 14:16:35</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>suma수마_840001114(1도움), suma수마_861221162(1도움), suma수마_848225439(2도움), 셀래스틴_846199564(1도움), 셀래스틴_856277179(1도움)</t>
+          <t>0708ManUtd_848183277(1도움), Legend독수리_861007518(1도움)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-20 07:39:16</t>
+          <t>2026-09-20 14:05:22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>A지냐크_863241496(1도움), A지냐크_867214101(1도움), 겐지간지_856237679(1도움), 겐지간지_845158023(1도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-20 07:25:46</t>
+          <t>2026-09-20 14:01:34</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>겐지간지_814231747(1도움)</t>
+          <t>0708ManUtd_848037576(1도움), 0708ManUtd_834239053(1도움), Legend독수리_864039943(1도움)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-20 07:08:13</t>
+          <t>2026-09-20 13:12:16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4909,7 +5605,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4919,29 +5615,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Legend독수리_840205988(1도움), Legend독수리_836054050(1도움), Legend독수리_861000246(1도움), 겐지간지_826247635(1도움)</t>
+          <t>은안_856246420(1도움), 은안_848143001(1도움), 은안_851242641(1도움), 은안_866241236(1도움), 겐지간지_845158023(1도움)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-20 06:55:35</t>
+          <t>2026-09-20 13:12:13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>킹왕두</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4951,61 +5647,61 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>겐지간지_845158023(1도움), 겐지간지_814231747(1도움), 겐지간지_856237679(1도움)</t>
+          <t>킹왕두_848203376(1도움), UNIT_848265695(1도움), UNIT_840210736(1도움)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-20 06:18:57</t>
+          <t>2026-09-20 12:59:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0_2</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>suma수마_861013383(1도움), suma수마_861190046(1도움)</t>
+          <t>은안_846210514(1도움), 은안_836239085(1도움), 은안_848231866(1도움), 은안_848143001(1도움), 겐지간지_848170890(1도움)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-20 06:05:40</t>
+          <t>2026-09-20 12:56:53</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>킹왕두</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2_10</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5015,29 +5711,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>A지냐크_848031432(1도움), A지냐크_861167134(1도움), suma수마_861190046(3도움), suma수마_840001114(3도움), suma수마_848225439(1도움), suma수마_861013383(1도움)</t>
+          <t>킹왕두_829013743(1도움), 킹왕두_856209331(1도움), UNIT_840228251(1도움), UNIT_840216150(1도움), UNIT_840225782(2도움)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-20 05:45:06</t>
+          <t>2026-09-20 12:46:14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>은안</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>suma수마</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>ShangHaiPortFC</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5047,26 +5743,26 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>suma수마_848225439(1도움), suma수마_826223697(1도움), suma수마_861190046(1도움), suma수마_851234112(1도움), suma수마_840001114(1도움), ShangHaiPortFC_256164959(1도움)</t>
+          <t>은안_866241236(1도움), 은안_848143001(3도움), 은안_856246420(1도움), suma수마_861013383(1도움)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-20 05:33:58</t>
+          <t>2026-09-20 12:34:11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>은안</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>suma수마</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>ShangHaiPortFC</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>4_3</t>
@@ -5079,29 +5775,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>suma수마_861013383(1도움), suma수마_845192190(1도움), suma수마_861190046(1도움), ShangHaiPortFC_861051412(2도움), ShangHaiPortFC_848031432(1도움)</t>
+          <t>은안_866241236(1도움), 은안_848143001(1도움), 은안_852237692(1도움), 은안_856246420(1도움), suma수마_861221162(1도움), suma수마_861013383(2도움)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-20 05:20:20</t>
+          <t>2026-09-20 12:31:41</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5111,189 +5807,189 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1도움), 앙쿠_863246191(3도움), ShangHaiPortFC_861051412(2도움)</t>
+          <t>개포동덕배_856202126(2도움), 개포동덕배_845190048(1도움), 개포동덕배_845208722(1도움), 개포동덕배_845168473(1도움), 개포동덕배_863212622(2도움), ZD장인지참치_848199503(1도움), ZD장인지참치_851240740(1도움)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-20 05:09:38</t>
+          <t>2026-09-20 12:24:08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4_0</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1도움), 앙쿠_851194765(1도움), 앙쿠_856247103(1도움), 앙쿠_814226161(1도움)</t>
+          <t>셀래스틴_863277643(1도움)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-20 03:47:49</t>
+          <t>2026-09-20 12:20:02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Legend독수리_840205988(1도움), 셀래스틴_852241461(1도움), 셀래스틴_856277179(1도움), 셀래스틴_846199564(1도움)</t>
+          <t>개포동덕배_845190048(2도움), 개포동덕배_848206113(1도움), 개포동덕배_856202126(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_840256630(2도움)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-20 03:44:09</t>
+          <t>2026-09-20 12:13:37</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8_3</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2도움), 앙쿠_814226161(1도움), 앙쿠_863246191(2도움), 앙쿠_851194765(2도움), ShangHaiPortFC_845231138(1도움), ShangHaiPortFC_827143001(1도움)</t>
+          <t>방덕_867001040(1도움), 셀래스틴_863277643(1도움), 셀래스틴_852241461(2도움)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-20 03:36:07</t>
+          <t>2026-09-20 11:27:42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Legend독수리_829200145(2도움), Legend독수리_839226764(1도움), 셀래스틴_852241461(1도움), 셀래스틴_863251854(1도움)</t>
+          <t>호야국2인_846192505(1도움), 호야국2인_851216409(1도움), 개포동덕배_845190048(1도움), 개포동덕배_845208722(2도움), 개포동덕배_845168473(1도움)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-20 03:31:53</t>
+          <t>2026-09-20 11:16:23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>6_1</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1도움), 앙쿠_863246191(1도움), 앙쿠_846186345(1도움), 앙쿠_856247103(1도움), ShangHaiPortFC_845231138(1도움)</t>
+          <t>호야국2인_846192505(1도움), 호야국2인_851216409(1도움), 호야국2인_848227236(1도움), 호야국2인_848232293(1도움), 개포동덕배_852225375(1도움), 개포동덕배_845168473(1도움), 개포동덕배_845190048(2도움)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-20 03:17:22</t>
+          <t>2026-09-20 10:36:38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>6_0</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5303,61 +5999,61 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), 셀래스틴_856277179(1도움), 셀래스틴_848230938(1도움)</t>
+          <t>호야국2인_846192505(2도움), 호야국2인_848232293(1도움), 호야국2인_851216409(2도움), 호야국2인_848216435(1도움)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-20 03:17:01</t>
+          <t>2026-09-20 10:25:22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Legend독수리_864039943(1도움), Legend독수리_852229880(1도움), ShangHaiPortFC_827143001(2도움), ShangHaiPortFC_284190813(1도움), ShangHaiPortFC_845231138(1도움)</t>
+          <t>호야국2인_851216409(1도움), 호야국2인_848216435(1도움)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-20 03:05:59</t>
+          <t>2026-09-20 10:10:07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8_3</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5367,24 +6063,24 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Legend독수리_866259399(1도움), Legend독수리_839226764(4도움), Legend독수리_861230025(1도움), ShangHaiPortFC_845231138(1도움), ShangHaiPortFC_848031432(1도움), ShangHaiPortFC_284190813(1도움)</t>
+          <t>여수가스_852216393(1도움), 여수가스_828231747(1도움), 여수가스_861162895(2도움), 겐지간지_845158023(2도움), 겐지간지_863243780(1도움)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-19 16:32:52</t>
+          <t>2026-09-20 09:58:44</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5399,189 +6095,189 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>스페인전도사_867192629(2도움), 스페인전도사_866235522(1도움), 스페인전도사_851224415(1도움), 여수가스_101001625(1도움)</t>
+          <t>여수가스_861162895(2도움), 여수가스_846001551(1도움), 여수가스_852216393(1도움), 겐지간지_848170890(1도움)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-19 16:20:51</t>
+          <t>2026-09-20 08:25:43</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>스페인전도사</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>여수가스</t>
-        </is>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1_4</t>
+          <t>6_3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>스페인전도사_866235522(1도움), 여수가스_861162895(1도움), 여수가스_861215732(1도움), 여수가스_852274967(2도움)</t>
+          <t>개포동덕배_852225375(1도움), 개포동덕배_845208722(2도움), 개포동덕배_856202126(2도움), 개포동덕배_848206113(1도움), 스페인전도사_851236295(1도움), 스페인전도사_866235522(1도움)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-19 15:34:28</t>
+          <t>2026-09-20 08:14:10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3_8</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UNIT_840225782(1도움), UNIT_829274967(1도움), UNIT_840216150(1도움), Voor_852233700(1도움), Voor_845009676(5도움)</t>
+          <t>개포동덕배_856202126(3도움), 개포동덕배_845208722(4도움), 스페인전도사_851216435(1도움), 스페인전도사_851224415(1도움)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-19 15:21:21</t>
+          <t>2026-09-20 08:13:05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_848180930(1도움), Voor_852001201(1도움), Voor_852233700(1도움), Voor_845001620(1도움)</t>
+          <t>suma수마_861013383(1도움), suma수마_861190046(1도움), 셀래스틴_863277643(2도움)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-19 15:17:09</t>
+          <t>2026-09-20 08:02:06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>스페인전도사_845224574(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(2도움), 콩콩콩룔_851236496(1도움)</t>
+          <t>suma수마_840001114(1도움), suma수마_861221162(1도움), suma수마_848225439(2도움), 셀래스틴_846199564(1도움), 셀래스틴_856277179(1도움)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-19 15:08:18</t>
+          <t>2026-09-20 07:39:16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>은안_866241236(1도움), 은안_848239818(1도움), Voor_845247090(1도움), Voor_852233700(1도움)</t>
+          <t>A지냐크_863241496(1도움), A지냐크_867214101(1도움), 겐지간지_856237679(1도움), 겐지간지_845158023(1도움)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-19 15:05:47</t>
+          <t>2026-09-20 07:25:46</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5591,61 +6287,61 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>스페인전도사_858008348(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_851236496(1도움)</t>
+          <t>겐지간지_814231747(1도움)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-19 14:56:37</t>
+          <t>2026-09-20 07:08:13</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2_8</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>은안_866241236(1도움), 은안_848143001(1도움), Voor_845247090(2도움), Voor_845009676(1도움), Voor_852233700(1도움), Voor_845001620(2도움), Voor_858020775(2도움)</t>
+          <t>Legend독수리_840205988(1도움), Legend독수리_836054050(1도움), Legend독수리_861000246(1도움), 겐지간지_826247635(1도움)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-19 14:24:16</t>
+          <t>2026-09-20 06:55:35</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5655,93 +6351,93 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움)</t>
+          <t>겐지간지_845158023(1도움), 겐지간지_814231747(1도움), 겐지간지_856237679(1도움)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-19 14:13:53</t>
+          <t>2026-09-20 06:18:57</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5_5</t>
+          <t>0_2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(1도움), 앙쿠_848176580(2도움), 앙쿠_846193747(1도움), UNIT_867166676(1도움), UNIT_840225782(3도움), UNIT_840228251(1도움)</t>
+          <t>suma수마_861013383(1도움), suma수마_861190046(1도움)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-19 13:54:08</t>
+          <t>2026-09-20 06:05:40</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>2_10</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_814226161(1도움), 앙쿠_863246191(1도움), 앙쿠_846193747(1도움), UNIT_840210736(1도움), UNIT_863250723(1도움), UNIT_840228251(1도움), UNIT_840192883(1도움)</t>
+          <t>A지냐크_848031432(1도움), A지냐크_861167134(1도움), suma수마_861190046(3도움), suma수마_840001114(3도움), suma수마_848225439(1도움), suma수마_861013383(1도움)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-19 13:36:20</t>
+          <t>2026-09-20 05:45:06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5751,93 +6447,93 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>앙쿠_846186345(1도움), 앙쿠_863246191(1도움)</t>
+          <t>suma수마_848225439(1도움), suma수마_826223697(1도움), suma수마_861190046(1도움), suma수마_851234112(1도움), suma수마_840001114(1도움), ShangHaiPortFC_256164959(1도움)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-19 13:25:57</t>
+          <t>2026-09-20 05:33:58</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), UNIT_840225782(1도움), UNIT_840228251(1도움), UNIT_840210736(1도움)</t>
+          <t>suma수마_861013383(1도움), suma수마_845192190(1도움), suma수마_861190046(1도움), ShangHaiPortFC_861051412(2도움), ShangHaiPortFC_848031432(1도움)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-19 12:33:16</t>
+          <t>2026-09-20 05:20:20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_840210736(1도움), 셀래스틴_846199564(1도움), 셀래스틴_845158023(1도움), 셀래스틴_856277179(1도움)</t>
+          <t>앙쿠_848176580(1도움), 앙쿠_863246191(3도움), ShangHaiPortFC_861051412(2도움)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-19 12:20:50</t>
+          <t>2026-09-20 05:09:38</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5847,93 +6543,93 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>UNIT_863250723(1도움), UNIT_840192883(1도움), UNIT_840228251(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>앙쿠_848176580(1도움), 앙쿠_851194765(1도움), 앙쿠_856247103(1도움), 앙쿠_814226161(1도움)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-19 12:10:22</t>
+          <t>2026-09-20 03:47:49</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(3도움), 앙쿠_856247103(1도움), suma수마_840001114(1도움)</t>
+          <t>Legend독수리_840205988(1도움), 셀래스틴_852241461(1도움), 셀래스틴_856277179(1도움), 셀래스틴_846199564(1도움)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-19 12:06:46</t>
+          <t>2026-09-20 03:44:09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>8_3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840256630(1도움), ZD장인지참치_839200104(1도움), 셀래스틴_855239231(3도움), 셀래스틴_856277179(1도움)</t>
+          <t>앙쿠_848176580(2도움), 앙쿠_814226161(1도움), 앙쿠_863246191(2도움), 앙쿠_851194765(2도움), ShangHaiPortFC_845231138(1도움), ShangHaiPortFC_827143001(1도움)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-19 11:59:22</t>
+          <t>2026-09-20 03:36:07</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5943,29 +6639,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_863233084(1도움), 앙쿠_848176580(2도움), 앙쿠_814226161(1도움), suma수마_826223697(1도움), suma수마_861221162(1도움)</t>
+          <t>Legend독수리_829200145(2도움), Legend독수리_839226764(1도움), 셀래스틴_852241461(1도움), 셀래스틴_863251854(1도움)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-19 11:55:57</t>
+          <t>2026-09-20 03:31:53</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5975,93 +6671,93 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ZD장인지참치_861182521(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), 셀래스틴_863277643(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>앙쿠_848176580(1도움), 앙쿠_863246191(1도움), 앙쿠_846186345(1도움), 앙쿠_856247103(1도움), ShangHaiPortFC_845231138(1도움)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-19 11:38:35</t>
+          <t>2026-09-20 03:17:22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840256630(1도움), 경남FC가즈아_805207730(1도움), 경남FC가즈아_225238224(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), 셀래스틴_856277179(1도움), 셀래스틴_848230938(1도움)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-19 11:35:15</t>
+          <t>2026-09-20 03:17:01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>suma수마_848225439(1도움), 셀래스틴_863251854(1도움), 셀래스틴_863277643(1도움)</t>
+          <t>Legend독수리_864039943(1도움), Legend독수리_852229880(1도움), ShangHaiPortFC_827143001(2도움), ShangHaiPortFC_284190813(1도움), ShangHaiPortFC_845231138(1도움)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-19 11:32:23</t>
+          <t>2026-09-20 03:05:59</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>8_3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6071,29 +6767,29 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(1도움), 개포동덕배_863212622(1도움), 개포동덕배_856202126(2도움), UNIT_840192883(1도움), UNIT_840228251(1도움)</t>
+          <t>Legend독수리_866259399(1도움), Legend독수리_839226764(4도움), Legend독수리_861230025(1도움), ShangHaiPortFC_845231138(1도움), ShangHaiPortFC_848031432(1도움), ShangHaiPortFC_284190813(1도움)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-19 11:27:23</t>
+          <t>2026-09-19 16:32:52</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6103,29 +6799,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(1도움), 경남FC가즈아_277205156(1도움)</t>
+          <t>스페인전도사_867192629(2도움), 스페인전도사_866235522(1도움), 스페인전도사_851224415(1도움), 여수가스_101001625(1도움)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-19 11:23:35</t>
+          <t>2026-09-19 16:20:51</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6135,29 +6831,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>suma수마_861190046(1도움), suma수마_845192190(1도움), 셀래스틴_845158023(1도움), 셀래스틴_848230938(1도움), 셀래스틴_855239231(1도움), 셀래스틴_863251854(1도움)</t>
+          <t>스페인전도사_866235522(1도움), 여수가스_861162895(1도움), 여수가스_861215732(1도움), 여수가스_852274967(2도움)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-19 11:21:04</t>
+          <t>2026-09-19 15:34:28</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_8</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6167,24 +6863,24 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>개포동덕배_848206113(1도움), 개포동덕배_856202126(1도움), UNIT_845207439(1도움), UNIT_840210736(1도움), UNIT_867166676(1도움)</t>
+          <t>UNIT_840225782(1도움), UNIT_829274967(1도움), UNIT_840216150(1도움), Voor_852233700(1도움), Voor_845009676(5도움)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-19 11:06:32</t>
+          <t>2026-09-19 15:21:21</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6199,29 +6895,29 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>A지냐크_848226851(1도움), A지냐크_863241496(1도움), 경남FC가즈아_830228007(1도움), 경남FC가즈아_805207730(1도움), 경남FC가즈아_853221467(1도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_848180930(1도움), Voor_852001201(1도움), Voor_852233700(1도움), Voor_845001620(1도움)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-19 10:53:44</t>
+          <t>2026-09-19 15:17:09</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6229,91 +6925,95 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>스페인전도사_845224574(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(2도움), 콩콩콩룔_851236496(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-19 10:46:09</t>
+          <t>2026-09-19 15:08:18</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4_5</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>A지냐크_834271400(1도움), A지냐크_848226851(1도움), A지냐크_863241496(1도움), 스페인전도사_867192629(1도움), 스페인전도사_866235522(1도움), 스페인전도사_861001668(1도움), 스페인전도사_851216435(1도움)</t>
+          <t>은안_866241236(1도움), 은안_848239818(1도움), Voor_845247090(1도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-19 10:33:32</t>
+          <t>2026-09-19 15:05:47</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>A지냐크_855213648(3도움), 스페인전도사_851216435(1도움)</t>
+          <t>스페인전도사_858008348(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_851236496(1도움)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-19 10:19:19</t>
+          <t>2026-09-19 14:56:37</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0_4</t>
+          <t>2_8</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6323,61 +7023,61 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움), 앙쿠_848176580(1도움)</t>
+          <t>은안_866241236(1도움), 은안_848143001(1도움), Voor_845247090(2도움), Voor_845009676(1도움), Voor_852233700(1도움), Voor_845001620(2도움), Voor_858020775(2도움)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-19 10:06:31</t>
+          <t>2026-09-19 14:24:16</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A지냐크</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>A지냐크_848226851(1도움), A지냐크_863241496(2도움), 앙쿠_851194765(2도움), 앙쿠_863246191(1도움)</t>
+          <t>UNIT_840192883(1도움)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-19 09:48:12</t>
+          <t>2026-09-19 14:13:53</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>검정소</t>
-        </is>
-      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>5_5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6387,46 +7087,46 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>UNIT_840225782(2도움), UNIT_840192883(1도움), UNIT_867166676(1도움), UNIT_848180930(1도움), 검정소_868192181(1도움), 검정소_861005003(1도움), 검정소_851241721(1도움)</t>
+          <t>앙쿠_863246191(1도움), 앙쿠_848176580(2도움), 앙쿠_846193747(1도움), UNIT_867166676(1도움), UNIT_840225782(3도움), UNIT_840228251(1도움)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-19 09:36:18</t>
+          <t>2026-09-19 13:54:08</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>검정소</t>
-        </is>
-      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>검정소_868013128(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_814226161(1도움), 앙쿠_863246191(1도움), 앙쿠_846193747(1도움), UNIT_840210736(1도움), UNIT_863250723(1도움), UNIT_840228251(1도움), UNIT_840192883(1도움)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-19 09:21:02</t>
+          <t>2026-09-19 13:36:20</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6436,44 +7136,44 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>앙쿠_856216460(1도움), 앙쿠_848176580(1도움), 검정소_861005003(2도움)</t>
+          <t>앙쿠_846186345(1도움), 앙쿠_863246191(1도움)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-19 09:14:49</t>
+          <t>2026-09-19 13:25:57</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>3_5</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -6483,56 +7183,56 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>오스트리아_851216275(1도움), 오스트리아_864199266(1도움), 오스트리아_291223790(1도움), ZD장인지참치_851240740(1도움), ZD장인지참치_861182521(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), UNIT_840225782(1도움), UNIT_840228251(1도움), UNIT_840210736(1도움)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-19 09:10:07</t>
+          <t>2026-09-19 12:33:16</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(2도움), 검정소_868192181(1도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_840210736(1도움), 셀래스틴_846199564(1도움), 셀래스틴_845158023(1도움), 셀래스틴_856277179(1도움)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-19 09:03:03</t>
+          <t>2026-09-19 12:20:50</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6547,29 +7247,29 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>오스트리아_851216275(1도움), 오스트리아_862140057(1도움), 오스트리아_864199266(1도움), ZD장인지참치_839200104(1도움)</t>
+          <t>UNIT_863250723(1도움), UNIT_840192883(1도움), UNIT_840228251(1도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-19 08:47:53</t>
+          <t>2026-09-19 12:10:22</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6579,29 +7279,29 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>UNIT_840216150(1도움), UNIT_867166676(1도움), UNIT_848180930(1도움), UNIT_829274967(1도움), 오스트리아_864191566(1도움)</t>
+          <t>앙쿠_851194765(3도움), 앙쿠_856247103(1도움), suma수마_840001114(1도움)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-19 08:36:31</t>
+          <t>2026-09-19 12:06:46</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6609,27 +7309,31 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840256630(1도움), ZD장인지참치_839200104(1도움), 셀래스틴_855239231(3도움), 셀래스틴_856277179(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-19 08:35:13</t>
+          <t>2026-09-19 11:59:22</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6639,157 +7343,157 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>UNIT_840225782(1도움), UNIT_840228251(2도움), 오스트리아_851221671(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_863233084(1도움), 앙쿠_848176580(2도움), 앙쿠_814226161(1도움), suma수마_826223697(1도움), suma수마_861221162(1도움)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-19 08:24:13</t>
+          <t>2026-09-19 11:55:57</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>4_8</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>스페인전도사_866235522(1도움), 스페인전도사_845224574(1도움), ZD장인지참치_848199503(3도움), ZD장인지참치_851240740(1도움), ZD장인지참치_861182521(3도움), ZD장인지참치_840191208(1도움)</t>
+          <t>ZD장인지참치_861182521(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), 셀래스틴_863277643(1도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-19 08:15:28</t>
+          <t>2026-09-19 11:38:35</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>오스트리아_862140057(1도움), 오스트리아_856245253(1도움), suma수마_861190046(1도움)</t>
+          <t>ZD장인지참치_840256630(1도움), 경남FC가즈아_805207730(1도움), 경남FC가즈아_225238224(1도움)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-19 08:12:24</t>
+          <t>2026-09-19 11:35:15</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(1도움)</t>
+          <t>suma수마_848225439(1도움), 셀래스틴_863251854(1도움), 셀래스틴_863277643(1도움)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-19 08:09:08</t>
+          <t>2026-09-19 11:32:23</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>스페인전도사</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>스페인전도사_866235522(2도움), ZD장인지참치_861182521(1도움), ZD장인지참치_839200104(2도움), ZD장인지참치_840191208(1도움)</t>
+          <t>개포동덕배_845190048(1도움), 개포동덕배_863212622(1도움), 개포동덕배_856202126(2도움), UNIT_840192883(1도움), UNIT_840228251(1도움)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-19 08:03:54</t>
+          <t>2026-09-19 11:27:23</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6799,83 +7503,83 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>오스트리아_851216275(3도움), suma수마_861190046(1도움), suma수마_848225439(1도움)</t>
+          <t>ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(1도움), 경남FC가즈아_277205156(1도움)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-19 05:58:58</t>
+          <t>2026-09-19 11:23:35</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), 비주류중독_848006975(1도움)</t>
+          <t>suma수마_861190046(1도움), suma수마_845192190(1도움), 셀래스틴_845158023(1도움), 셀래스틴_848230938(1도움), 셀래스틴_855239231(1도움), 셀래스틴_863251854(1도움)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-19 05:47:10</t>
+          <t>2026-09-19 11:21:04</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>비주류중독</t>
-        </is>
-      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_848265695(1도움), UNIT_840228251(1도움), UNIT_829274967(1도움), 비주류중독_840052241(1도움)</t>
+          <t>개포동덕배_848206113(1도움), 개포동덕배_856202126(1도움), UNIT_845207439(1도움), UNIT_840210736(1도움), UNIT_867166676(1도움)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-19 05:24:55</t>
+          <t>2026-09-19 11:06:32</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6885,7 +7589,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6895,19 +7599,19 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Legend독수리_840205988(1도움), 경남FC가즈아_853221467(1도움), 경남FC가즈아_805267825(1도움)</t>
+          <t>A지냐크_848226851(1도움), A지냐크_863241496(1도움), 경남FC가즈아_830228007(1도움), 경남FC가즈아_805207730(1도움), 경남FC가즈아_853221467(1도움)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-19 05:13:36</t>
+          <t>2026-09-19 10:53:44</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6917,39 +7621,35 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>경남FC가즈아_518251161(1도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-19 05:00:44</t>
+          <t>2026-09-19 10:46:09</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6959,61 +7659,61 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Legend독수리_861230025(1도움), Legend독수리_866259399(1도움), 비주류중독_834239977(3도움), 비주류중독_839247699(1도움)</t>
+          <t>A지냐크_834271400(1도움), A지냐크_848226851(1도움), A지냐크_863241496(1도움), 스페인전도사_867192629(1도움), 스페인전도사_866235522(1도움), 스페인전도사_861001668(1도움), 스페인전도사_851216435(1도움)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-19 04:48:52</t>
+          <t>2026-09-19 10:33:32</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>스페인전도사</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Legend독수리_836054050(1도움), Legend독수리_840205988(1도움), 비주류중독_848006975(1도움), 비주류중독_829203376(1도움), 비주류중독_839247699(1도움)</t>
+          <t>A지냐크_855213648(3도움), 스페인전도사_851216435(1도움)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-19 04:11:38</t>
+          <t>2026-09-19 10:19:19</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>0_4</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -7023,157 +7723,157 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Legend독수리_852229880(1도움), Legend독수리_861230025(1도움), 셀래스틴_856277179(1도움)</t>
+          <t>앙쿠_856247103(1도움), 앙쿠_848176580(1도움)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-19 04:00:02</t>
+          <t>2026-09-19 10:06:31</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Legend독수리_861007518(1도움), Legend독수리_852229880(1도움), Legend독수리_836054050(1도움), Legend독수리_840205988(1도움), 셀래스틴_845158023(1도움)</t>
+          <t>A지냐크_848226851(1도움), A지냐크_863241496(2도움), 앙쿠_851194765(2도움), 앙쿠_863246191(1도움)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-19 03:15:22</t>
+          <t>2026-09-19 09:48:12</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2_6</t>
+          <t>5_4</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>여수가스_861215732(1도움), 여수가스_101001625(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(2도움), ZD장인지참치_848210035(1도움), ZD장인지참치_840247263(1도움)</t>
+          <t>UNIT_840225782(2도움), UNIT_840192883(1도움), UNIT_867166676(1도움), UNIT_848180930(1도움), 검정소_868192181(1도움), 검정소_861005003(1도움), 검정소_851241721(1도움)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-19 03:03:53</t>
+          <t>2026-09-19 09:36:18</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>0_1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>여수가스_828231747(1도움), 여수가스_861215732(1도움), 여수가스_846001551(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
+          <t>검정소_868013128(1도움)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-19 01:33:00</t>
+          <t>2026-09-19 09:21:02</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>겐지간지_826247635(1도움), 겐지간지_852231443(2도움), 겐지간지_814231747(1도움), Gucci와퍼_852168473(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_851210697(1도움)</t>
+          <t>앙쿠_856216460(1도움), 앙쿠_848176580(1도움), 검정소_861005003(2도움)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-19 01:18:46</t>
+          <t>2026-09-19 09:14:49</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>3_5</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7183,47 +7883,51 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>겐지간지_826247635(1도움), Gucci와퍼_852168473(1도움), Gucci와퍼_840208574(1도움)</t>
+          <t>오스트리아_851216275(1도움), 오스트리아_864199266(1도움), 오스트리아_291223790(1도움), ZD장인지참치_851240740(1도움), ZD장인지참치_861182521(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(1도움)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-19 01:06:48</t>
+          <t>2026-09-19 09:10:07</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(2도움), 검정소_868192181(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-19 00:56:16</t>
+          <t>2026-09-19 09:03:03</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7233,79 +7937,775 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2_7</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>겐지간지_863252145(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_840191208(3도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움)</t>
+          <t>오스트리아_851216275(1도움), 오스트리아_862140057(1도움), 오스트리아_864199266(1도움), ZD장인지참치_839200104(1도움)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-19 00:43:56</t>
+          <t>2026-09-19 08:47:53</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0_5</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840256630(1도움), ZD장인지참치_839200104(2도움), ZD장인지참치_848199503(1도움)</t>
+          <t>UNIT_840216150(1도움), UNIT_867166676(1도움), UNIT_848180930(1도움), UNIT_829274967(1도움), 오스트리아_864191566(1도움)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>2026-09-19 08:36:31</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0_0</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:35:13</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>UNIT_840225782(1도움), UNIT_840228251(2도움), 오스트리아_851221671(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:24:13</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>스페인전도사</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4_8</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>스페인전도사_866235522(1도움), 스페인전도사_845224574(1도움), ZD장인지참치_848199503(3도움), ZD장인지참치_851240740(1도움), ZD장인지참치_861182521(3도움), ZD장인지참치_840191208(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:15:28</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>오스트리아_862140057(1도움), 오스트리아_856245253(1도움), suma수마_861190046(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:12:24</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>스페인전도사</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>0_1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:09:08</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>스페인전도사</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>스페인전도사_866235522(2도움), ZD장인지참치_861182521(1도움), ZD장인지참치_839200104(2도움), ZD장인지참치_840191208(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:03:54</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>오스트리아_851216275(3도움), suma수마_861190046(1도움), suma수마_848225439(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:58:58</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1도움), 비주류중독_848006975(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:47:10</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>4_1</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1도움), UNIT_848265695(1도움), UNIT_840228251(1도움), UNIT_829274967(1도움), 비주류중독_840052241(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:24:55</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Legend독수리_840205988(1도움), 경남FC가즈아_853221467(1도움), 경남FC가즈아_805267825(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:13:36</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_518251161(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:00:44</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Legend독수리_861230025(1도움), Legend독수리_866259399(1도움), 비주류중독_834239977(3도움), 비주류중독_839247699(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:48:52</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Legend독수리_836054050(1도움), Legend독수리_840205988(1도움), 비주류중독_848006975(1도움), 비주류중독_829203376(1도움), 비주류중독_839247699(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:11:38</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Legend독수리_852229880(1도움), Legend독수리_861230025(1도움), 셀래스틴_856277179(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:00:02</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Legend독수리_861007518(1도움), Legend독수리_852229880(1도움), Legend독수리_836054050(1도움), Legend독수리_840205988(1도움), 셀래스틴_845158023(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:15:22</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2_6</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>여수가스_861215732(1도움), 여수가스_101001625(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840191208(2도움), ZD장인지참치_848210035(1도움), ZD장인지참치_840247263(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:03:53</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>여수가스_828231747(1도움), 여수가스_861215732(1도움), 여수가스_846001551(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:33:00</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>겐지간지_826247635(1도움), 겐지간지_852231443(2도움), 겐지간지_814231747(1도움), Gucci와퍼_852168473(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_851210697(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:18:46</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>겐지간지_826247635(1도움), Gucci와퍼_852168473(1도움), Gucci와퍼_840208574(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:06:48</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>0_0</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:56:16</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2_7</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>겐지간지_863252145(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_840191208(3도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:43:56</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0_5</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840256630(1도움), ZD장인지참치_839200104(2도움), ZD장인지참치_848199503(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
           <t>2026-09-18 17:47:34</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>스페인전도사</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>여수가스</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>2_2</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>무</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>스페인전도사_867192629(1도움), 스페인전도사_861001668(1도움), 여수가스_846001551(1도움), 여수가스_828231747(1도움)</t>
         </is>

--- a/API데이터_경기_득점_및_도움_기록.xlsx
+++ b/API데이터_경기_득점_및_도움_기록.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:33:47</t>
+          <t>2026-09-24 16:30:57</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -462,29 +462,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(2골), 셀래스틴_836158023(2골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_851194765(1골), 앙쿠_866266039(1골), UNIT_867166676(1골), UNIT_840228251(1골)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23 13:23:09</t>
+          <t>2026-09-24 16:14:16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -494,12 +494,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1_0</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -509,14 +509,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>앙쿠_866266039(1골)</t>
+          <t>앙쿠_866266039(1골), 앙쿠_848176580(1골), 앙쿠_863246191(1골), UNIT_867166676(3골), UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23 13:08:58</t>
+          <t>2026-09-24 15:57:54</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -526,12 +526,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -541,221 +541,221 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_863246191(2골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_863246191(3골), UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23 12:58:26</t>
+          <t>2026-09-24 13:42:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_866266039(1골), ZD장인지참치_840191208(2골)</t>
+          <t>UNIT_848180930(2골), UNIT_840228251(1골), UNIT_840192883(1골), 셀래스틴_856277179(1골)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-23 12:28:11</t>
+          <t>2026-09-24 13:30:05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0708ManUtd_848183277(1골), 0708ManUtd_863239231(1골), 0708ManUtd_848238794(1골), 0708ManUtd_868001397(2골), 0708ManUtd_848037576(1골), 겐지간지_814231747(2골)</t>
+          <t>UNIT_867166676(1골), 셀래스틴_856277179(1골), 셀래스틴_861005680(1골), 셀래스틴_861142754(1골)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-23 12:19:39</t>
+          <t>2026-09-24 09:29:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>아들러_840191208(1골), ZD장인지참치_839200104(2골), ZD장인지참치_840191208(1골), ZD장인지참치_840247263(2골)</t>
+          <t>여수가스_861215732(2골), 여수가스_861162895(2골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_861051412(1골)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-23 12:19:35</t>
+          <t>2026-09-24 09:16:26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>경남FC가즈아_225238224(2골), 콩콩콩룔_848189505(1골), 콩콩콩룔_866223710(3골)</t>
+          <t>여수가스_861215732(4골), ShangHaiPortFC_845231138(1골), ShangHaiPortFC_848031432(2골)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-23 12:15:41</t>
+          <t>2026-09-24 08:18:47</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>2_7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0708ManUtd_868001397(1골), 0708ManUtd_848037576(2골), 0708ManUtd_848183277(1골), 겐지간지_863256196(1골), 겐지간지_814231747(1골), 겐지간지_845158023(1골)</t>
+          <t>은안_866241236(1골), 은안_848143001(1골), 방덕_868135455(1골), 방덕_868009676(6골)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-23 12:07:26</t>
+          <t>2026-09-24 08:06:58</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>아들러_855232639(1골), 아들러_861000570(1골), 아들러_840191208(2골), 아들러_866251377(1골), ZD장인지참치_839200104(2골), ZD장인지참치_840191208(1골), ZD장인지참치_840256630(1골)</t>
+          <t>은안_856246420(1골), 은안_866241236(1골), 방덕_861077787(1골), 방덕_868009676(1골), 방덕_848007512(1골)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-23 12:05:58</t>
+          <t>2026-09-24 04:51:33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -765,61 +765,61 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>경남FC가즈아_225238224(2골), 콩콩콩룔_867223848(1골)</t>
+          <t>ZD장인지참치_840191208(1골), ZD장인지참치_839200104(2골), 용신_856202126(1골)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-23 11:53:57</t>
+          <t>2026-09-24 04:40:44</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>아들러_866251377(1골), 아들러_855232639(1골)</t>
+          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(1골), ZD장인지참치_851240740(1골), 용신_863245367(1골), 용신_820264453(1골), 용신_101173731(1골), 용신_273227535(1골), 용신_856202126(1골)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-23 11:42:25</t>
+          <t>2026-09-24 04:19:09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5_0</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -829,29 +829,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>아들러_866251377(1골), 아들러_840191208(3골), 아들러_861000570(1골)</t>
+          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(2골), 비주류중독_848006975(1골), 비주류중독_839247699(1골), 비주류중독_825000240(1골), 비주류중독_840052241(1골)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-23 11:29:03</t>
+          <t>2026-09-24 04:02:44</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -859,127 +859,123 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>앙쿠_851194765(1골), 아들러_840191208(2골), 아들러_852232730(1골)</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-23 10:27:43</t>
+          <t>2026-09-24 03:45:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>아들러_840191208(2골), 콩콩콩룔_867223848(2골), 콩콩콩룔_866223710(2골)</t>
+          <t>UNIT_867166676(4골), UNIT_848180930(1골), ZD장인지참치_840247263(1골), ZD장인지참치_840191208(2골)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-23 10:15:56</t>
+          <t>2026-09-24 02:48:31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>아들러_840191208(2골), 콩콩콩룔_866223710(1골), 콩콩콩룔_851236496(1골)</t>
+          <t>여수가스_861215732(1골), 여수가스_846188567(1골), 여수가스_828231747(1골), 방덕_827191189(1골), 방덕_101001419(1골), 방덕_861077787(1골), 방덕_848231478(2골)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-23 08:46:09</t>
+          <t>2026-09-23 17:59:32</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>오스트리아_291223790(2골), 겐지간지_845158023(1골)</t>
+          <t>0708ManUtd_834239053(1골), 0708ManUtd_851226161(1골), 여수가스_861215732(3골)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-23 08:35:42</t>
+          <t>2026-09-23 17:47:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -989,37 +985,581 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>오스트리아_851221671(1골), 오스트리아_864199266(2골), 겐지간지_856237679(1골)</t>
+          <t>0708ManUtd_848037576(1골), 0708ManUtd_868001397(1골), 0708ManUtd_851226161(1골), 0708ManUtd_848238794(1골), 여수가스_861215732(3골)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>2026-09-23 13:33:47</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>앙쿠_863246191(2골), 셀래스틴_836158023(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:23:09</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1_0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>앙쿠_866266039(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:08:58</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1골), 앙쿠_863246191(2골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:58:26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1골), 앙쿠_866266039(1골), ZD장인지참치_840191208(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:28:11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6_2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0708ManUtd_848183277(1골), 0708ManUtd_863239231(1골), 0708ManUtd_848238794(1골), 0708ManUtd_868001397(2골), 0708ManUtd_848037576(1골), 겐지간지_814231747(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:19:39</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1_5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>아들러_840191208(1골), ZD장인지참치_839200104(2골), ZD장인지참치_840191208(1골), ZD장인지참치_840247263(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:19:35</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_225238224(2골), 콩콩콩룔_848189505(1골), 콩콩콩룔_866223710(3골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:15:41</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0708ManUtd_868001397(1골), 0708ManUtd_848037576(2골), 0708ManUtd_848183277(1골), 겐지간지_863256196(1골), 겐지간지_814231747(1골), 겐지간지_845158023(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:07:26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>5_4</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>아들러_855232639(1골), 아들러_861000570(1골), 아들러_840191208(2골), 아들러_866251377(1골), ZD장인지참치_839200104(2골), ZD장인지참치_840191208(1골), ZD장인지참치_840256630(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:05:58</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_225238224(2골), 콩콩콩룔_867223848(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:53:57</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>아들러_866251377(1골), 아들러_855232639(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:42:25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>5_0</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>아들러_866251377(1골), 아들러_840191208(3골), 아들러_861000570(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:29:03</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(1골), 아들러_840191208(2골), 아들러_852232730(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:27:43</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>아들러_840191208(2골), 콩콩콩룔_867223848(2골), 콩콩콩룔_866223710(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:15:56</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>아들러_840191208(2골), 콩콩콩룔_866223710(1골), 콩콩콩룔_851236496(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:46:09</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>오스트리아_291223790(2골), 겐지간지_845158023(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:35:42</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>오스트리아_851221671(1골), 오스트리아_864199266(2골), 겐지간지_856237679(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>2026-09-22 14:15:38</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>셀래스틴</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>1_2</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>패</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>UNIT_848180930(1골), 셀래스틴_856277179(1골), 셀래스틴_836158023(1골)</t>
         </is>
@@ -1036,7 +1576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1074,7 +1614,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:33:47</t>
+          <t>2026-09-24 16:30:57</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1084,29 +1624,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), 셀래스틴_863251854(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>앙쿠_846193747(1도움), 앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_840192883(1도움), UNIT_840225782(1도움)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23 13:23:09</t>
+          <t>2026-09-24 16:14:16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1116,12 +1656,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1_0</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1131,14 +1671,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_848135455(1도움), UNIT_863250723(1도움), UNIT_840216150(1도움), UNIT_840210736(1도움)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23 13:08:58</t>
+          <t>2026-09-24 15:57:54</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1148,12 +1688,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1163,221 +1703,221 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(3도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
+          <t>앙쿠_851194765(3도움), 앙쿠_848176580(1도움)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23 12:58:26</t>
+          <t>2026-09-24 13:42:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_839200104(1도움)</t>
+          <t>UNIT_840210736(1도움), UNIT_840228251(1도움), UNIT_867166676(1도움)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-23 12:28:11</t>
+          <t>2026-09-24 13:30:05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0708ManUtd_851226161(2도움), 0708ManUtd_848238794(2도움), 0708ManUtd_868001397(1도움), 겐지간지_856237679(1도움)</t>
+          <t>UNIT_840228251(1도움), 셀래스틴_848230938(1도움), 셀래스틴_863277643(1도움), 셀래스틴_861142754(1도움)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-23 12:19:39</t>
+          <t>2026-09-24 09:29:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>아들러_814192318(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_848210035(1도움), ZD장인지참치_840191208(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_848199503(1도움)</t>
+          <t>여수가스_845020289(1도움), 여수가스_828231747(1도움), 여수가스_868135455(1도움), 여수가스_846001551(1도움), ShangHaiPortFC_284190813(1도움), ShangHaiPortFC_861051412(1도움)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-23 12:19:35</t>
+          <t>2026-09-24 09:16:26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>경남FC가즈아_853221467(2도움), 콩콩콩룔_867223848(2도움)</t>
+          <t>여수가스_846001551(1도움), 여수가스_828231747(1도움), 여수가스_852274967(1도움), 여수가스_861162895(1도움), ShangHaiPortFC_845231138(1도움), ShangHaiPortFC_861051412(1도움)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-23 12:15:41</t>
+          <t>2026-09-24 08:18:47</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>2_7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0708ManUtd_868001397(2도움), 0708ManUtd_848037576(1도움), 0708ManUtd_851226161(1도움), 겐지간지_861001668(1도움), 겐지간지_826247635(1도움), 겐지간지_852231443(1도움)</t>
+          <t>은안_856251517(1도움), 방덕_868135455(1도움), 방덕_848231478(1도움), 방덕_848007512(1도움), 방덕_861077787(2도움), 방덕_868009676(1도움), 방덕_856226268(1도움)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-23 12:07:26</t>
+          <t>2026-09-24 08:06:58</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>아들러_855232639(2도움), 아들러_861000570(1도움), 아들러_840191208(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_861182521(2도움)</t>
+          <t>은안_856246420(1도움), 은안_848231866(1도움), 방덕_861077787(1도움), 방덕_848007512(1도움)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-23 12:05:58</t>
+          <t>2026-09-24 04:51:33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1387,61 +1927,61 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>경남FC가즈아_277205156(1도움), 경남FC가즈아_518251161(1도움), 콩콩콩룔_851236496(1도움)</t>
+          <t>ZD장인지참치_848210035(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_839200104(1도움), 용신_866200104(1도움)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-23 11:53:57</t>
+          <t>2026-09-24 04:40:44</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>아들러_861000570(2도움)</t>
+          <t>ZD장인지참치_840191208(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_851240740(1도움), 용신_863245367(2도움), 용신_273227535(1도움), 용신_848216267(1도움)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-23 11:42:25</t>
+          <t>2026-09-24 04:19:09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5_0</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1451,29 +1991,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>아들러_866251377(1도움), 아들러_855232639(1도움), 아들러_840191208(1도움), 아들러_840208574(1도움)</t>
+          <t>ZD장인지참치_861182521(2도움), ZD장인지참치_840256630(1도움), ZD장인지참치_851240740(1도움), 비주류중독_848006975(1도움), 비주류중독_839247699(1도움), 비주류중독_852253149(1도움)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-23 11:29:03</t>
+          <t>2026-09-24 04:02:44</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1481,127 +2021,123 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>앙쿠_863246191(1도움), 아들러_840191208(1도움), 아들러_852232730(1도움)</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-23 10:27:43</t>
+          <t>2026-09-24 03:45:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>아들러_866251377(1도움), 아들러_852232730(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_866223710(1도움), 콩콩콩룔_861006235(1도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_840225782(1도움), UNIT_848135455(1도움), UNIT_848180930(1도움), UNIT_840192883(1도움), ZD장인지참치_848210035(1도움), ZD장인지참치_839200104(2도움)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-23 10:15:56</t>
+          <t>2026-09-24 02:48:31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>아들러_291225126(2도움), 콩콩콩룔_867220502(1도움)</t>
+          <t>여수가스_861162895(1도움), 여수가스_868135455(1도움), 방덕_868009676(1도움), 방덕_101001419(1도움), 방덕_863184200(1도움), 방덕_867001040(1도움)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-23 08:46:09</t>
+          <t>2026-09-23 17:59:32</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>오스트리아_864182152(1도움), 겐지간지_826247635(1도움)</t>
+          <t>0708ManUtd_834239053(1도움), 0708ManUtd_868001397(1도움), 여수가스_868135455(1도움), 여수가스_828231747(1도움), 여수가스_845020289(1도움)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-23 08:35:42</t>
+          <t>2026-09-23 17:47:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1611,37 +2147,581 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(2도움), 겐지간지_814231747(1도움)</t>
+          <t>0708ManUtd_834239053(1도움), 0708ManUtd_868001397(1도움), 0708ManUtd_851226161(1도움), 0708ManUtd_848238794(1도움), 여수가스_861162895(1도움), 여수가스_828231747(1도움)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>2026-09-23 13:33:47</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), 셀래스틴_863251854(1도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:23:09</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1_0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>앙쿠_856247103(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:08:58</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(3도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:58:26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_839200104(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:28:11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6_2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0708ManUtd_851226161(2도움), 0708ManUtd_848238794(2도움), 0708ManUtd_868001397(1도움), 겐지간지_856237679(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:19:39</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1_5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>아들러_814192318(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_848210035(1도움), ZD장인지참치_840191208(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_848199503(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:19:35</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_853221467(2도움), 콩콩콩룔_867223848(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:15:41</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0708ManUtd_868001397(2도움), 0708ManUtd_848037576(1도움), 0708ManUtd_851226161(1도움), 겐지간지_861001668(1도움), 겐지간지_826247635(1도움), 겐지간지_852231443(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:07:26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>5_4</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>아들러_855232639(2도움), 아들러_861000570(1도움), 아들러_840191208(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_861182521(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:05:58</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_277205156(1도움), 경남FC가즈아_518251161(1도움), 콩콩콩룔_851236496(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:53:57</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>아들러_861000570(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:42:25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>5_0</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>아들러_866251377(1도움), 아들러_855232639(1도움), 아들러_840191208(1도움), 아들러_840208574(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:29:03</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>앙쿠_863246191(1도움), 아들러_840191208(1도움), 아들러_852232730(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:27:43</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>아들러_866251377(1도움), 아들러_852232730(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_866223710(1도움), 콩콩콩룔_861006235(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:15:56</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>아들러_291225126(2도움), 콩콩콩룔_867220502(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:46:09</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>오스트리아_864182152(1도움), 겐지간지_826247635(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:35:42</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(2도움), 겐지간지_814231747(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>2026-09-22 14:15:38</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>셀래스틴</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>1_2</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>패</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>UNIT_840192883(1도움), 셀래스틴_852277643(1도움), 셀래스틴_852241461(1도움)</t>
         </is>

--- a/API데이터_경기_득점_및_도움_기록.xlsx
+++ b/API데이터_경기_득점_및_도움_기록.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,22 +452,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:30:57</t>
+          <t>2026-09-26 12:19:23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>6_4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -477,29 +477,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_851194765(1골), 앙쿠_866266039(1골), UNIT_867166676(1골), UNIT_840228251(1골)</t>
+          <t>ZD장인지참치_851240740(1골), ZD장인지참치_840191208(4골), ZD장인지참치_839200104(1골), 셀래스틴_846001551(1골), 셀래스틴_848194765(2골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24 16:14:16</t>
+          <t>2026-09-26 12:08:13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -509,78 +509,78 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>앙쿠_866266039(1골), 앙쿠_848176580(1골), 앙쿠_863246191(1골), UNIT_867166676(3골), UNIT_848180930(1골)</t>
+          <t>ZD장인지참치_840191208(2골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-24 15:57:54</t>
+          <t>2026-09-26 08:26:23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_863246191(3골), UNIT_848180930(1골)</t>
+          <t>오스트리아_851221671(1골), Special블루_856246669(1골), Special블루_863248148(1골), Special블루_855241651(1골)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-24 13:42:25</t>
+          <t>2026-09-25 15:57:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>0_3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), UNIT_840228251(1골), UNIT_840192883(1골), 셀래스틴_856277179(1골)</t>
+          <t>Voor_845009676(1골), Voor_845247090(1골), Voor_852233700(1골)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-24 13:30:05</t>
+          <t>2026-09-25 09:45:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -590,12 +590,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -605,29 +605,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), 셀래스틴_856277179(1골), 셀래스틴_861005680(1골), 셀래스틴_861142754(1골)</t>
+          <t>UNIT_848180930(1골), UNIT_840228251(2골), 방덕_848007512(1골), 방덕_868009676(3골)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-24 09:29:12</t>
+          <t>2026-09-25 09:33:41</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -637,51 +637,51 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>여수가스_861215732(2골), 여수가스_861162895(2골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_861051412(1골)</t>
+          <t>UNIT_848180930(1골), UNIT_840192883(1골), UNIT_867166676(1골), 방덕_861077787(1골), 방덕_868009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-24 09:16:26</t>
+          <t>2026-09-25 09:22:20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>여수가스_861215732(4골), ShangHaiPortFC_845231138(1골), ShangHaiPortFC_848031432(2골)</t>
+          <t>UNIT_867166676(1골), UNIT_840192883(1골), 방덕_868009676(1골), 방덕_868135455(1골), 방덕_861077787(1골)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-24 08:18:47</t>
+          <t>2026-09-25 09:10:55</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -691,29 +691,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2_7</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>은안_866241236(1골), 은안_848143001(1골), 방덕_868135455(1골), 방덕_868009676(6골)</t>
+          <t>UNIT_840192883(1골), 방덕_868009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-24 08:06:58</t>
+          <t>2026-09-25 08:53:47</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -723,103 +723,103 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>은안_856246420(1골), 은안_866241236(1골), 방덕_861077787(1골), 방덕_868009676(1골), 방덕_848007512(1골)</t>
+          <t>UNIT_848180930(1골), UNIT_840192883(1골), 방덕_861077787(1골), 방덕_101001419(1골)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-24 04:51:33</t>
+          <t>2026-09-25 08:42:15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(1골), ZD장인지참치_839200104(2골), 용신_856202126(1골)</t>
+          <t>UNIT_867166676(2골), 방덕_868135455(2골), 방덕_856228093(1골)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-24 04:40:44</t>
+          <t>2026-09-24 16:30:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4_5</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(1골), ZD장인지참치_851240740(1골), 용신_863245367(1골), 용신_820264453(1골), 용신_101173731(1골), 용신_273227535(1골), 용신_856202126(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_851194765(1골), 앙쿠_866266039(1골), UNIT_867166676(1골), UNIT_840228251(1골)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-24 04:19:09</t>
+          <t>2026-09-24 16:14:16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -829,42 +829,46 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(2골), 비주류중독_848006975(1골), 비주류중독_839247699(1골), 비주류중독_825000240(1골), 비주류중독_840052241(1골)</t>
+          <t>앙쿠_866266039(1골), 앙쿠_848176580(1골), 앙쿠_863246191(1골), UNIT_867166676(3골), UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-24 04:02:44</t>
+          <t>2026-09-24 15:57:54</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1골), 앙쿠_863246191(3골), UNIT_848180930(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-24 03:45:56</t>
+          <t>2026-09-24 13:42:25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,12 +878,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -889,29 +893,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UNIT_867166676(4골), UNIT_848180930(1골), ZD장인지참치_840247263(1골), ZD장인지참치_840191208(2골)</t>
+          <t>UNIT_848180930(2골), UNIT_840228251(1골), UNIT_840192883(1골), 셀래스틴_856277179(1골)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-24 02:48:31</t>
+          <t>2026-09-24 13:30:05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3_5</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -921,56 +925,56 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>여수가스_861215732(1골), 여수가스_846188567(1골), 여수가스_828231747(1골), 방덕_827191189(1골), 방덕_101001419(1골), 방덕_861077787(1골), 방덕_848231478(2골)</t>
+          <t>UNIT_867166676(1골), 셀래스틴_856277179(1골), 셀래스틴_861005680(1골), 셀래스틴_861142754(1골)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-23 17:59:32</t>
+          <t>2026-09-24 09:29:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0708ManUtd_834239053(1골), 0708ManUtd_851226161(1골), 여수가스_861215732(3골)</t>
+          <t>여수가스_861215732(2골), 여수가스_861162895(2골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_861051412(1골)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-23 17:47:25</t>
+          <t>2026-09-24 09:16:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -985,93 +989,93 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0708ManUtd_848037576(1골), 0708ManUtd_868001397(1골), 0708ManUtd_851226161(1골), 0708ManUtd_848238794(1골), 여수가스_861215732(3골)</t>
+          <t>여수가스_861215732(4골), ShangHaiPortFC_845231138(1골), ShangHaiPortFC_848031432(2골)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-23 13:33:47</t>
+          <t>2026-09-24 08:18:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>2_7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(2골), 셀래스틴_836158023(2골)</t>
+          <t>은안_866241236(1골), 은안_848143001(1골), 방덕_868135455(1골), 방덕_868009676(6골)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-23 13:23:09</t>
+          <t>2026-09-24 08:06:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1_0</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>앙쿠_866266039(1골)</t>
+          <t>은안_856246420(1골), 은안_866241236(1골), 방덕_861077787(1골), 방덕_868009676(1골), 방덕_848007512(1골)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-23 13:08:58</t>
+          <t>2026-09-24 04:51:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1081,61 +1085,61 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_863246191(2골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골)</t>
+          <t>ZD장인지참치_840191208(1골), ZD장인지참치_839200104(2골), 용신_856202126(1골)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-23 12:58:26</t>
+          <t>2026-09-24 04:40:44</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_866266039(1골), ZD장인지참치_840191208(2골)</t>
+          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(1골), ZD장인지참치_851240740(1골), 용신_863245367(1골), 용신_820264453(1골), 용신_101173731(1골), 용신_273227535(1골), 용신_856202126(1골)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-23 12:28:11</t>
+          <t>2026-09-24 04:19:09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6_2</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1145,29 +1149,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0708ManUtd_848183277(1골), 0708ManUtd_863239231(1골), 0708ManUtd_848238794(1골), 0708ManUtd_868001397(2골), 0708ManUtd_848037576(1골), 겐지간지_814231747(2골)</t>
+          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(2골), 비주류중독_848006975(1골), 비주류중독_839247699(1골), 비주류중독_825000240(1골), 비주류중독_840052241(1골)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-23 12:19:39</t>
+          <t>2026-09-24 04:02:44</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1175,127 +1179,123 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>아들러_840191208(1골), ZD장인지참치_839200104(2골), ZD장인지참치_840191208(1골), ZD장인지참치_840247263(2골)</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-23 12:19:35</t>
+          <t>2026-09-24 03:45:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>경남FC가즈아_225238224(2골), 콩콩콩룔_848189505(1골), 콩콩콩룔_866223710(3골)</t>
+          <t>UNIT_867166676(4골), UNIT_848180930(1골), ZD장인지참치_840247263(1골), ZD장인지참치_840191208(2골)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-23 12:15:41</t>
+          <t>2026-09-24 02:48:31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>3_5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0708ManUtd_868001397(1골), 0708ManUtd_848037576(2골), 0708ManUtd_848183277(1골), 겐지간지_863256196(1골), 겐지간지_814231747(1골), 겐지간지_845158023(1골)</t>
+          <t>여수가스_861215732(1골), 여수가스_846188567(1골), 여수가스_828231747(1골), 방덕_827191189(1골), 방덕_101001419(1골), 방덕_861077787(1골), 방덕_848231478(2골)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-23 12:07:26</t>
+          <t>2026-09-23 17:59:32</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>아들러_855232639(1골), 아들러_861000570(1골), 아들러_840191208(2골), 아들러_866251377(1골), ZD장인지참치_839200104(2골), ZD장인지참치_840191208(1골), ZD장인지참치_840256630(1골)</t>
+          <t>0708ManUtd_834239053(1골), 0708ManUtd_851226161(1골), 여수가스_861215732(3골)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-23 12:05:58</t>
+          <t>2026-09-23 17:47:25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1305,61 +1305,61 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>경남FC가즈아_225238224(2골), 콩콩콩룔_867223848(1골)</t>
+          <t>0708ManUtd_848037576(1골), 0708ManUtd_868001397(1골), 0708ManUtd_851226161(1골), 0708ManUtd_848238794(1골), 여수가스_861215732(3골)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-23 11:53:57</t>
+          <t>2026-09-23 13:33:47</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>아들러_866251377(1골), 아들러_855232639(1골)</t>
+          <t>앙쿠_863246191(2골), 셀래스틴_836158023(2골)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-23 11:42:25</t>
+          <t>2026-09-23 13:23:09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5_0</t>
+          <t>1_0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1369,14 +1369,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>아들러_866251377(1골), 아들러_840191208(3골), 아들러_861000570(1골)</t>
+          <t>앙쿠_866266039(1골)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-23 11:29:03</t>
+          <t>2026-09-23 13:08:58</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1386,180 +1386,500 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 아들러_840191208(2골), 아들러_852232730(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_863246191(2골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-23 10:27:43</t>
+          <t>2026-09-23 12:58:26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>아들러_840191208(2골), 콩콩콩룔_867223848(2골), 콩콩콩룔_866223710(2골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_866266039(1골), ZD장인지참치_840191208(2골)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-23 10:15:56</t>
+          <t>2026-09-23 12:28:11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>6_2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>아들러_840191208(2골), 콩콩콩룔_866223710(1골), 콩콩콩룔_851236496(1골)</t>
+          <t>0708ManUtd_848183277(1골), 0708ManUtd_863239231(1골), 0708ManUtd_848238794(1골), 0708ManUtd_868001397(2골), 0708ManUtd_848037576(1골), 겐지간지_814231747(2골)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-23 08:46:09</t>
+          <t>2026-09-23 12:19:39</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>오스트리아_291223790(2골), 겐지간지_845158023(1골)</t>
+          <t>아들러_840191208(1골), ZD장인지참치_839200104(2골), ZD장인지참치_840191208(1골), ZD장인지참치_840247263(2골)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-23 08:35:42</t>
+          <t>2026-09-23 12:19:35</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>오스트리아_851221671(1골), 오스트리아_864199266(2골), 겐지간지_856237679(1골)</t>
+          <t>경남FC가즈아_225238224(2골), 콩콩콩룔_848189505(1골), 콩콩콩룔_866223710(3골)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>2026-09-23 12:15:41</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0708ManUtd_868001397(1골), 0708ManUtd_848037576(2골), 0708ManUtd_848183277(1골), 겐지간지_863256196(1골), 겐지간지_814231747(1골), 겐지간지_845158023(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:07:26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>5_4</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>아들러_855232639(1골), 아들러_861000570(1골), 아들러_840191208(2골), 아들러_866251377(1골), ZD장인지참치_839200104(2골), ZD장인지참치_840191208(1골), ZD장인지참치_840256630(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:05:58</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_225238224(2골), 콩콩콩룔_867223848(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:53:57</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>아들러_866251377(1골), 아들러_855232639(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:42:25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>5_0</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>아들러_866251377(1골), 아들러_840191208(3골), 아들러_861000570(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:29:03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(1골), 아들러_840191208(2골), 아들러_852232730(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:27:43</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>아들러_840191208(2골), 콩콩콩룔_867223848(2골), 콩콩콩룔_866223710(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:15:56</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>아들러_840191208(2골), 콩콩콩룔_866223710(1골), 콩콩콩룔_851236496(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:46:09</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>오스트리아_291223790(2골), 겐지간지_845158023(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:35:42</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>오스트리아_851221671(1골), 오스트리아_864199266(2골), 겐지간지_856237679(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>2026-09-22 14:15:38</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>셀래스틴</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>1_2</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>패</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>UNIT_848180930(1골), 셀래스틴_856277179(1골), 셀래스틴_836158023(1골)</t>
         </is>
@@ -1576,7 +1896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1614,22 +1934,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:30:57</t>
+          <t>2026-09-26 12:19:23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>6_4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1639,29 +1959,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>앙쿠_846193747(1도움), 앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_840192883(1도움), UNIT_840225782(1도움)</t>
+          <t>ZD장인지참치_840191208(1도움), ZD장인지참치_839200104(2도움), ZD장인지참치_840253149(2도움), 셀래스틴_846001551(1도움), 셀래스틴_852259694(1도움), 셀래스틴_852241461(2도움)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24 16:14:16</t>
+          <t>2026-09-26 12:08:13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1671,78 +1991,78 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_848135455(1도움), UNIT_863250723(1도움), UNIT_840216150(1도움), UNIT_840210736(1도움)</t>
+          <t>ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-24 15:57:54</t>
+          <t>2026-09-26 08:26:23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(3도움), 앙쿠_848176580(1도움)</t>
+          <t>오스트리아_851216275(1도움), Special블루_861001419(2도움)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-24 13:42:25</t>
+          <t>2026-09-25 15:57:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>0_3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UNIT_840210736(1도움), UNIT_840228251(1도움), UNIT_867166676(1도움)</t>
+          <t>Voor_835183277(1도움), Voor_852233700(1도움), Voor_856256079(1도움)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-24 13:30:05</t>
+          <t>2026-09-25 09:45:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1752,12 +2072,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1767,29 +2087,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), 셀래스틴_848230938(1도움), 셀래스틴_863277643(1도움), 셀래스틴_861142754(1도움)</t>
+          <t>UNIT_840210736(1도움), UNIT_867166676(1도움), UNIT_840192883(1도움), 방덕_861077787(1도움), 방덕_856233096(1도움)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-24 09:29:12</t>
+          <t>2026-09-25 09:33:41</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1799,51 +2119,51 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>여수가스_845020289(1도움), 여수가스_828231747(1도움), 여수가스_868135455(1도움), 여수가스_846001551(1도움), ShangHaiPortFC_284190813(1도움), ShangHaiPortFC_861051412(1도움)</t>
+          <t>UNIT_848180930(1도움), UNIT_840192883(1도움), UNIT_867166676(1도움), 방덕_848007512(1도움), 방덕_848231478(1도움)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-24 09:16:26</t>
+          <t>2026-09-25 09:22:20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>여수가스_846001551(1도움), 여수가스_828231747(1도움), 여수가스_852274967(1도움), 여수가스_861162895(1도움), ShangHaiPortFC_845231138(1도움), ShangHaiPortFC_861051412(1도움)</t>
+          <t>UNIT_840192883(1도움), 방덕_848231478(2도움), 방덕_868009676(1도움)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-24 08:18:47</t>
+          <t>2026-09-25 09:10:55</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1853,29 +2173,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2_7</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>은안_856251517(1도움), 방덕_868135455(1도움), 방덕_848231478(1도움), 방덕_848007512(1도움), 방덕_861077787(2도움), 방덕_868009676(1도움), 방덕_856226268(1도움)</t>
+          <t>UNIT_840228251(1도움), 방덕_868135455(1도움)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-24 08:06:58</t>
+          <t>2026-09-25 08:53:47</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1885,103 +2205,103 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>은안_856246420(1도움), 은안_848231866(1도움), 방덕_861077787(1도움), 방덕_848007512(1도움)</t>
+          <t>UNIT_867166676(2도움), 방덕_861077787(1도움), 방덕_868135455(1도움)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-24 04:51:33</t>
+          <t>2026-09-25 08:42:15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ZD장인지참치_848210035(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_839200104(1도움), 용신_866200104(1도움)</t>
+          <t>UNIT_840192883(1도움), UNIT_829274967(1도움), 방덕_848007512(1도움), 방덕_867001040(1도움), 방덕_101001419(1도움)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-24 04:40:44</t>
+          <t>2026-09-24 16:30:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4_5</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_851240740(1도움), 용신_863245367(2도움), 용신_273227535(1도움), 용신_848216267(1도움)</t>
+          <t>앙쿠_846193747(1도움), 앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_840192883(1도움), UNIT_840225782(1도움)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-24 04:19:09</t>
+          <t>2026-09-24 16:14:16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1991,42 +2311,46 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ZD장인지참치_861182521(2도움), ZD장인지참치_840256630(1도움), ZD장인지참치_851240740(1도움), 비주류중독_848006975(1도움), 비주류중독_839247699(1도움), 비주류중독_852253149(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_848135455(1도움), UNIT_863250723(1도움), UNIT_840216150(1도움), UNIT_840210736(1도움)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-24 04:02:44</t>
+          <t>2026-09-24 15:57:54</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(3도움), 앙쿠_848176580(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-24 03:45:56</t>
+          <t>2026-09-24 13:42:25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2036,12 +2360,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2051,29 +2375,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_840225782(1도움), UNIT_848135455(1도움), UNIT_848180930(1도움), UNIT_840192883(1도움), ZD장인지참치_848210035(1도움), ZD장인지참치_839200104(2도움)</t>
+          <t>UNIT_840210736(1도움), UNIT_840228251(1도움), UNIT_867166676(1도움)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-24 02:48:31</t>
+          <t>2026-09-24 13:30:05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3_5</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2083,56 +2407,56 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>여수가스_861162895(1도움), 여수가스_868135455(1도움), 방덕_868009676(1도움), 방덕_101001419(1도움), 방덕_863184200(1도움), 방덕_867001040(1도움)</t>
+          <t>UNIT_840228251(1도움), 셀래스틴_848230938(1도움), 셀래스틴_863277643(1도움), 셀래스틴_861142754(1도움)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-23 17:59:32</t>
+          <t>2026-09-24 09:29:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0708ManUtd_834239053(1도움), 0708ManUtd_868001397(1도움), 여수가스_868135455(1도움), 여수가스_828231747(1도움), 여수가스_845020289(1도움)</t>
+          <t>여수가스_845020289(1도움), 여수가스_828231747(1도움), 여수가스_868135455(1도움), 여수가스_846001551(1도움), ShangHaiPortFC_284190813(1도움), ShangHaiPortFC_861051412(1도움)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-23 17:47:25</t>
+          <t>2026-09-24 09:16:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2147,93 +2471,93 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0708ManUtd_834239053(1도움), 0708ManUtd_868001397(1도움), 0708ManUtd_851226161(1도움), 0708ManUtd_848238794(1도움), 여수가스_861162895(1도움), 여수가스_828231747(1도움)</t>
+          <t>여수가스_846001551(1도움), 여수가스_828231747(1도움), 여수가스_852274967(1도움), 여수가스_861162895(1도움), ShangHaiPortFC_845231138(1도움), ShangHaiPortFC_861051412(1도움)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-23 13:33:47</t>
+          <t>2026-09-24 08:18:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>2_7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), 셀래스틴_863251854(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>은안_856251517(1도움), 방덕_868135455(1도움), 방덕_848231478(1도움), 방덕_848007512(1도움), 방덕_861077787(2도움), 방덕_868009676(1도움), 방덕_856226268(1도움)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-23 13:23:09</t>
+          <t>2026-09-24 08:06:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1_0</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움)</t>
+          <t>은안_856246420(1도움), 은안_848231866(1도움), 방덕_861077787(1도움), 방덕_848007512(1도움)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-23 13:08:58</t>
+          <t>2026-09-24 04:51:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2243,61 +2567,61 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(3도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
+          <t>ZD장인지참치_848210035(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_839200104(1도움), 용신_866200104(1도움)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-23 12:58:26</t>
+          <t>2026-09-24 04:40:44</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_839200104(1도움)</t>
+          <t>ZD장인지참치_840191208(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_851240740(1도움), 용신_863245367(2도움), 용신_273227535(1도움), 용신_848216267(1도움)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-23 12:28:11</t>
+          <t>2026-09-24 04:19:09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6_2</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2307,29 +2631,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0708ManUtd_851226161(2도움), 0708ManUtd_848238794(2도움), 0708ManUtd_868001397(1도움), 겐지간지_856237679(1도움)</t>
+          <t>ZD장인지참치_861182521(2도움), ZD장인지참치_840256630(1도움), ZD장인지참치_851240740(1도움), 비주류중독_848006975(1도움), 비주류중독_839247699(1도움), 비주류중독_852253149(1도움)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-23 12:19:39</t>
+          <t>2026-09-24 04:02:44</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2337,127 +2661,123 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>아들러_814192318(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_848210035(1도움), ZD장인지참치_840191208(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_848199503(1도움)</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-23 12:19:35</t>
+          <t>2026-09-24 03:45:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>경남FC가즈아_853221467(2도움), 콩콩콩룔_867223848(2도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_840225782(1도움), UNIT_848135455(1도움), UNIT_848180930(1도움), UNIT_840192883(1도움), ZD장인지참치_848210035(1도움), ZD장인지참치_839200104(2도움)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-23 12:15:41</t>
+          <t>2026-09-24 02:48:31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>3_5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0708ManUtd_868001397(2도움), 0708ManUtd_848037576(1도움), 0708ManUtd_851226161(1도움), 겐지간지_861001668(1도움), 겐지간지_826247635(1도움), 겐지간지_852231443(1도움)</t>
+          <t>여수가스_861162895(1도움), 여수가스_868135455(1도움), 방덕_868009676(1도움), 방덕_101001419(1도움), 방덕_863184200(1도움), 방덕_867001040(1도움)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-23 12:07:26</t>
+          <t>2026-09-23 17:59:32</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>아들러_855232639(2도움), 아들러_861000570(1도움), 아들러_840191208(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_861182521(2도움)</t>
+          <t>0708ManUtd_834239053(1도움), 0708ManUtd_868001397(1도움), 여수가스_868135455(1도움), 여수가스_828231747(1도움), 여수가스_845020289(1도움)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-23 12:05:58</t>
+          <t>2026-09-23 17:47:25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2467,61 +2787,61 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>경남FC가즈아_277205156(1도움), 경남FC가즈아_518251161(1도움), 콩콩콩룔_851236496(1도움)</t>
+          <t>0708ManUtd_834239053(1도움), 0708ManUtd_868001397(1도움), 0708ManUtd_851226161(1도움), 0708ManUtd_848238794(1도움), 여수가스_861162895(1도움), 여수가스_828231747(1도움)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-23 11:53:57</t>
+          <t>2026-09-23 13:33:47</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>아들러_861000570(2도움)</t>
+          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), 셀래스틴_863251854(1도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-23 11:42:25</t>
+          <t>2026-09-23 13:23:09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5_0</t>
+          <t>1_0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2531,14 +2851,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>아들러_866251377(1도움), 아들러_855232639(1도움), 아들러_840191208(1도움), 아들러_840208574(1도움)</t>
+          <t>앙쿠_856247103(1도움)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-23 11:29:03</t>
+          <t>2026-09-23 13:08:58</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2548,180 +2868,500 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(1도움), 아들러_840191208(1도움), 아들러_852232730(1도움)</t>
+          <t>앙쿠_851194765(3도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-23 10:27:43</t>
+          <t>2026-09-23 12:58:26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>아들러_866251377(1도움), 아들러_852232730(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_866223710(1도움), 콩콩콩룔_861006235(1도움)</t>
+          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_839200104(1도움)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-23 10:15:56</t>
+          <t>2026-09-23 12:28:11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>6_2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>아들러_291225126(2도움), 콩콩콩룔_867220502(1도움)</t>
+          <t>0708ManUtd_851226161(2도움), 0708ManUtd_848238794(2도움), 0708ManUtd_868001397(1도움), 겐지간지_856237679(1도움)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-23 08:46:09</t>
+          <t>2026-09-23 12:19:39</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>오스트리아_864182152(1도움), 겐지간지_826247635(1도움)</t>
+          <t>아들러_814192318(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_848210035(1도움), ZD장인지참치_840191208(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_848199503(1도움)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-23 08:35:42</t>
+          <t>2026-09-23 12:19:35</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(2도움), 겐지간지_814231747(1도움)</t>
+          <t>경남FC가즈아_853221467(2도움), 콩콩콩룔_867223848(2도움)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>2026-09-23 12:15:41</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0708ManUtd_868001397(2도움), 0708ManUtd_848037576(1도움), 0708ManUtd_851226161(1도움), 겐지간지_861001668(1도움), 겐지간지_826247635(1도움), 겐지간지_852231443(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:07:26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>5_4</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>아들러_855232639(2도움), 아들러_861000570(1도움), 아들러_840191208(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_861182521(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:05:58</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_277205156(1도움), 경남FC가즈아_518251161(1도움), 콩콩콩룔_851236496(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:53:57</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>아들러_861000570(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:42:25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>5_0</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>아들러_866251377(1도움), 아들러_855232639(1도움), 아들러_840191208(1도움), 아들러_840208574(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:29:03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>앙쿠_863246191(1도움), 아들러_840191208(1도움), 아들러_852232730(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:27:43</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>아들러_866251377(1도움), 아들러_852232730(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_866223710(1도움), 콩콩콩룔_861006235(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:15:56</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>아들러_291225126(2도움), 콩콩콩룔_867220502(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:46:09</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>오스트리아_864182152(1도움), 겐지간지_826247635(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:35:42</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(2도움), 겐지간지_814231747(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>2026-09-22 14:15:38</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>셀래스틴</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>1_2</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>패</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>UNIT_840192883(1도움), 셀래스틴_852277643(1도움), 셀래스틴_852241461(1도움)</t>
         </is>

--- a/API데이터_경기_득점_및_도움_기록.xlsx
+++ b/API데이터_경기_득점_및_도움_기록.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,54 +452,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-26 12:19:23</t>
+          <t>2026-09-27 15:43:53</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6_4</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ZD장인지참치_851240740(1골), ZD장인지참치_840191208(4골), ZD장인지참치_839200104(1골), 셀래스틴_846001551(1골), 셀래스틴_848194765(2골), 셀래스틴_852241461(1골)</t>
+          <t>UNIT_867166676(2골), UNIT_848180930(1골), Voor_858025420(1골), Voor_856256079(1골), Voor_835183277(1골)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-26 12:08:13</t>
+          <t>2026-09-27 15:26:14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -509,29 +509,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2골), 셀래스틴_861005680(1골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(2골), Voor_852001201(1골), Voor_852233700(2골)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-26 08:26:23</t>
+          <t>2026-09-27 15:09:40</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>0_6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -541,19 +541,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>오스트리아_851221671(1골), Special블루_856246669(1골), Special블루_863248148(1골), Special블루_855241651(1골)</t>
+          <t>Voor_845009676(1골), Voor_845001116(1골), Voor_852233700(1골), Voor_835183277(2골), Voor_280206585(1골)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-25 15:57:51</t>
+          <t>2026-09-27 14:57:41</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0_3</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -573,29 +573,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Voor_845009676(1골), Voor_845247090(1골), Voor_852233700(1골)</t>
+          <t>UNIT_848180930(1골), UNIT_867166676(2골), Voor_858025420(1골), Voor_852233700(3골)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-25 09:45:28</t>
+          <t>2026-09-27 14:54:39</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -605,189 +605,189 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_840228251(2골), 방덕_848007512(1골), 방덕_868009676(3골)</t>
+          <t>호야국2인_835171877(1골), Gucci차붐_864176403(1골), Gucci차붐_864247686(1골)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-25 09:33:41</t>
+          <t>2026-09-27 14:43:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_840192883(1골), UNIT_867166676(1골), 방덕_861077787(1골), 방덕_868009676(1골)</t>
+          <t>호야국2인_846192505(1골), Gucci차붐_864176403(2골), Gucci차붐_851221671(1골), Gucci차붐_853227659(1골), Gucci차붐_864247686(1골)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-25 09:22:20</t>
+          <t>2026-09-27 14:37:29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), UNIT_840192883(1골), 방덕_868009676(1골), 방덕_868135455(1골), 방덕_861077787(1골)</t>
+          <t>피파왕초보구단주_846208722(1골), 피파왕초보구단주_861005661(3골), Voor_845247090(1골)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-25 09:10:55</t>
+          <t>2026-09-27 14:26:49</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>1_6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1골), 방덕_868009676(1골)</t>
+          <t>피파왕초보구단주_861005661(1골), Voor_835183277(1골), Voor_845009676(2골), Voor_845247090(1골), Voor_856256079(1골), Voor_852233700(1골)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-25 08:53:47</t>
+          <t>2026-09-27 14:11:46</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_840192883(1골), 방덕_861077787(1골), 방덕_101001419(1골)</t>
+          <t>경남FC가즈아_805267825(1골), Voor_845009676(2골)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-25 08:42:15</t>
+          <t>2026-09-27 14:08:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), 방덕_868135455(2골), 방덕_856228093(1골)</t>
+          <t>0708ManUtd_868037576(2골)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-24 16:30:57</t>
+          <t>2026-09-27 13:58:06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -797,93 +797,93 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_851194765(1골), 앙쿠_866266039(1골), UNIT_867166676(1골), UNIT_840228251(1골)</t>
+          <t>0708ManUtd_868001397(2골), 0708ManUtd_834239053(1골), 0708ManUtd_868037576(1골)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-24 16:14:16</t>
+          <t>2026-09-27 13:41:37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>앙쿠_866266039(1골), 앙쿠_848176580(1골), 앙쿠_863246191(1골), UNIT_867166676(3골), UNIT_848180930(1골)</t>
+          <t>겐지간지_814231747(1골), 피파왕초보구단주_861005661(2골), 피파왕초보구단주_846208722(3골)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-24 15:57:54</t>
+          <t>2026-09-27 13:29:35</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>1_8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_863246191(3골), UNIT_848180930(1골)</t>
+          <t>겐지간지_856237679(1골), 피파왕초보구단주_861005661(1골), 피파왕초보구단주_856209331(2골), 피파왕초보구단주_846231281(1골), 피파왕초보구단주_867000027(2골), 피파왕초보구단주_846208722(2골)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-24 13:42:25</t>
+          <t>2026-09-27 11:36:34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -893,61 +893,61 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), UNIT_840228251(1골), UNIT_840192883(1골), 셀래스틴_856277179(1골)</t>
+          <t>개포동덕배_845190048(5골), 개포동덕배_863212622(1골), 여수가스_861215732(1골)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-24 13:30:05</t>
+          <t>2026-09-27 11:24:41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), 셀래스틴_856277179(1골), 셀래스틴_861005680(1골), 셀래스틴_861142754(1골)</t>
+          <t>개포동덕배_845208722(1골), 개포동덕배_856202126(2골), 개포동덕배_848206113(1골), 개포동덕배_845190048(3골), 여수가스_861162895(1골), 여수가스_828231747(1골)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-24 09:29:12</t>
+          <t>2026-09-27 10:09:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -957,29 +957,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>여수가스_861215732(2골), 여수가스_861162895(2골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_861051412(1골)</t>
+          <t>개포동덕배_845190048(4골), 아들러_840191208(2골), 아들러_866251377(1골)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-24 09:16:26</t>
+          <t>2026-09-27 09:57:50</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -989,29 +989,29 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>여수가스_861215732(4골), ShangHaiPortFC_845231138(1골), ShangHaiPortFC_848031432(2골)</t>
+          <t>개포동덕배_856202126(3골), 개포동덕배_863212622(1골), 아들러_866251377(2골)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-24 08:18:47</t>
+          <t>2026-09-27 09:29:41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2_7</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1021,29 +1021,29 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>은안_866241236(1골), 은안_848143001(1골), 방덕_868135455(1골), 방덕_868009676(6골)</t>
+          <t>겐지간지_814231747(2골), 경남FC가즈아_225238224(2골), 경남FC가즈아_805267825(1골)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-24 08:06:58</t>
+          <t>2026-09-27 09:18:24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1053,29 +1053,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>은안_856246420(1골), 은안_866241236(1골), 방덕_861077787(1골), 방덕_868009676(1골), 방덕_848007512(1골)</t>
+          <t>겐지간지_814231747(1골), 경남FC가즈아_225238224(1골), 경남FC가즈아_805267825(1골)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-24 04:51:33</t>
+          <t>2026-09-27 09:14:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>5_4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1085,61 +1085,61 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(1골), ZD장인지참치_839200104(2골), 용신_856202126(1골)</t>
+          <t>아들러_861000570(1골), 아들러_840208574(1골), 아들러_866251377(1골), 아들러_840191208(2골), Gucci와퍼_852010264(1골), Gucci와퍼_864200104(2골), Gucci와퍼_852168473(1골)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-24 04:40:44</t>
+          <t>2026-09-27 09:00:07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4_5</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(1골), ZD장인지참치_851240740(1골), 용신_863245367(1골), 용신_820264453(1골), 용신_101173731(1골), 용신_273227535(1골), 용신_856202126(1골)</t>
+          <t>아들러_862140057(1골), 아들러_840191208(1골), 아들러_855232639(1골), 아들러_291225126(1골), Gucci와퍼_852168473(1골)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-24 04:19:09</t>
+          <t>2026-09-27 08:20:21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1149,29 +1149,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(2골), 비주류중독_848006975(1골), 비주류중독_839247699(1골), 비주류중독_825000240(1골), 비주류중독_840052241(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_863246191(5골), 겐지간지_856237679(1골)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-24 04:02:44</t>
+          <t>2026-09-27 08:15:02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1179,27 +1179,31 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>개포동덕배_845190048(1골), 개포동덕배_848206113(1골), 경남FC가즈아_225238224(2골), 경남FC가즈아_805267825(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-24 03:45:56</t>
+          <t>2026-09-27 08:08:47</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1209,93 +1213,93 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UNIT_867166676(4골), UNIT_848180930(1골), ZD장인지참치_840247263(1골), ZD장인지참치_840191208(2골)</t>
+          <t>앙쿠_863246191(3골), 앙쿠_848176580(2골), 겐지간지_848170890(1골), 겐지간지_814231747(1골)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-24 02:48:31</t>
+          <t>2026-09-27 08:02:59</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3_5</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>여수가스_861215732(1골), 여수가스_846188567(1골), 여수가스_828231747(1골), 방덕_827191189(1골), 방덕_101001419(1골), 방덕_861077787(1골), 방덕_848231478(2골)</t>
+          <t>개포동덕배_845190048(3골), 개포동덕배_845208722(1골), 경남FC가즈아_225238224(3골), 경남FC가즈아_805267825(1골)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-23 17:59:32</t>
+          <t>2026-09-27 07:50:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0708ManUtd_834239053(1골), 0708ManUtd_851226161(1골), 여수가스_861215732(3골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_863246191(2골), 앙쿠_856247103(1골)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-23 17:47:25</t>
+          <t>2026-09-27 07:47:08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1305,14 +1309,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0708ManUtd_848037576(1골), 0708ManUtd_868001397(1골), 0708ManUtd_851226161(1골), 0708ManUtd_848238794(1골), 여수가스_861215732(3골)</t>
+          <t>Legend독수리_840192505(2골), Legend독수리_846001845(3골), Special블루_877001625(1골), Special블루_856246669(1골), Special블루_861047390(1골)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-23 13:33:47</t>
+          <t>2026-09-27 07:40:08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1322,44 +1326,44 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(2골), 셀래스틴_836158023(2골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_851194765(2골)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-23 13:23:09</t>
+          <t>2026-09-26 20:23:39</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1_0</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1369,88 +1373,88 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>앙쿠_866266039(1골)</t>
+          <t>UNIT_848180930(3골), UNIT_867166676(1골), Voor_845247090(1골), Voor_858025420(2골)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-23 13:08:58</t>
+          <t>2026-09-26 20:11:13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_863246191(2골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골)</t>
+          <t>UNIT_840192883(1골), UNIT_840228251(1골), Voor_861000027(1골), Voor_845009676(1골), Voor_858025420(1골)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-23 12:58:26</t>
+          <t>2026-09-26 19:59:04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_866266039(1골), ZD장인지참치_840191208(2골)</t>
+          <t>UNIT_848180930(2골), UNIT_867166676(1골), Voor_845009676(1골), Voor_852233700(1골), Voor_835183277(1골)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-23 12:28:11</t>
+          <t>2026-09-26 19:42:33</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1465,29 +1469,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0708ManUtd_848183277(1골), 0708ManUtd_863239231(1골), 0708ManUtd_848238794(1골), 0708ManUtd_868001397(2골), 0708ManUtd_848037576(1골), 겐지간지_814231747(2골)</t>
+          <t>UNIT_848180930(2골), UNIT_840228251(2골), UNIT_867166676(2골), Voor_835183277(1골), Voor_845009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-23 12:19:39</t>
+          <t>2026-09-26 19:28:32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>7_8</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1497,61 +1501,61 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>아들러_840191208(1골), ZD장인지참치_839200104(2골), ZD장인지참치_840191208(1골), ZD장인지참치_840247263(2골)</t>
+          <t>UNIT_852053302(1골), UNIT_840192883(1골), UNIT_867166676(3골), UNIT_840228251(2골), Voor_852233700(4골), Voor_845009676(1골), Voor_858020775(1골), Voor_835183277(1골), Voor_846184943(1골)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-23 12:19:35</t>
+          <t>2026-09-26 14:04:42</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>경남FC가즈아_225238224(2골), 콩콩콩룔_848189505(1골), 콩콩콩룔_866223710(3골)</t>
+          <t>UNIT_840228251(2골), UNIT_840192883(1골), UNIT_867166676(1골), Special블루_856246669(1골), Special블루_848230666(2골)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-23 12:15:41</t>
+          <t>2026-09-26 13:54:24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1561,29 +1565,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0708ManUtd_868001397(1골), 0708ManUtd_848037576(2골), 0708ManUtd_848183277(1골), 겐지간지_863256196(1골), 겐지간지_814231747(1골), 겐지간지_845158023(1골)</t>
+          <t>UNIT_848180930(3골), UNIT_867166676(1골), Special블루_863234378(1골), Special블루_855241651(1골)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-23 12:07:26</t>
+          <t>2026-09-26 13:43:16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1593,29 +1597,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>아들러_855232639(1골), 아들러_861000570(1골), 아들러_840191208(2골), 아들러_866251377(1골), ZD장인지참치_839200104(2골), ZD장인지참치_840191208(1골), ZD장인지참치_840256630(1골)</t>
+          <t>UNIT_867166676(2골), UNIT_848180930(2골), UNIT_840228251(1골), Special블루_855241651(1골)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-23 12:05:58</t>
+          <t>2026-09-26 13:32:03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1625,29 +1629,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>경남FC가즈아_225238224(2골), 콩콩콩룔_867223848(1골)</t>
+          <t>UNIT_848135455(1골), UNIT_848180930(1골), UNIT_840192883(1골), Special블루_855241651(1골)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-23 11:53:57</t>
+          <t>2026-09-26 13:20:21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>6_3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1657,29 +1661,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>아들러_866251377(1골), 아들러_855232639(1골)</t>
+          <t>개포동덕배_856202126(1골), 개포동덕배_856275298(1골), 개포동덕배_863212622(1골), 개포동덕배_845190048(3골), Special블루_856246669(1골), Special블루_861001419(1골), Special블루_848230666(1골)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-23 11:42:25</t>
+          <t>2026-09-26 13:08:55</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5_0</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1689,197 +1693,1441 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>아들러_866251377(1골), 아들러_840191208(3골), 아들러_861000570(1골)</t>
+          <t>개포동덕배_845208722(1골), 개포동덕배_856202126(1골), 개포동덕배_845190048(3골), Special블루_863234378(1골), Special블루_851251805(1골), Special블루_848230666(1골)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-23 11:29:03</t>
+          <t>2026-09-26 12:19:23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>6_4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 아들러_840191208(2골), 아들러_852232730(1골)</t>
+          <t>ZD장인지참치_840191208(4골), ZD장인지참치_839200104(1골), ZD장인지참치_851240740(1골), 셀래스틴_848194765(2골), 셀래스틴_852241461(1골), 셀래스틴_846001551(1골)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-23 10:27:43</t>
+          <t>2026-09-26 12:08:13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>아들러_840191208(2골), 콩콩콩룔_867223848(2골), 콩콩콩룔_866223710(2골)</t>
+          <t>ZD장인지참치_840191208(2골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-23 10:15:56</t>
+          <t>2026-09-26 08:26:23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>아들러_840191208(2골), 콩콩콩룔_866223710(1골), 콩콩콩룔_851236496(1골)</t>
+          <t>오스트리아_851221671(1골), Special블루_856246669(1골), Special블루_863248148(1골), Special블루_855241651(1골)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-23 08:46:09</t>
+          <t>2026-09-25 15:57:51</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>0_3</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>오스트리아_291223790(2골), 겐지간지_845158023(1골)</t>
+          <t>Voor_845009676(1골), Voor_845247090(1골), Voor_852233700(1골)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-23 08:35:42</t>
+          <t>2026-09-25 09:45:28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>오스트리아_851221671(1골), 오스트리아_864199266(2골), 겐지간지_856237679(1골)</t>
+          <t>UNIT_848180930(1골), UNIT_840228251(2골), 방덕_848007512(1골), 방덕_868009676(3골)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>2026-09-25 09:33:41</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), UNIT_840192883(1골), UNIT_867166676(1골), 방덕_861077787(1골), 방덕_868009676(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:22:20</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1골), UNIT_840192883(1골), 방덕_868009676(1골), 방덕_868135455(1골), 방덕_861077787(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:10:55</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(1골), 방덕_868009676(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-25 08:53:47</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), UNIT_840192883(1골), 방덕_861077787(1골), 방덕_101001419(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-25 08:42:15</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), 방덕_868135455(2골), 방덕_856228093(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:30:57</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1골), 앙쿠_851194765(1골), 앙쿠_866266039(1골), UNIT_867166676(1골), UNIT_840228251(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:14:16</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3_4</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>앙쿠_866266039(1골), 앙쿠_848176580(1골), 앙쿠_863246191(1골), UNIT_867166676(3골), UNIT_848180930(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:57:54</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>4_1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1골), 앙쿠_863246191(3골), UNIT_848180930(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:42:25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4_1</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(2골), UNIT_840228251(1골), UNIT_840192883(1골), 셀래스틴_856277179(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:30:05</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1골), 셀래스틴_856277179(1골), 셀래스틴_861005680(1골), 셀래스틴_861142754(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:29:12</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>여수가스_861215732(2골), 여수가스_861162895(2골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_861051412(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:16:26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>여수가스_861215732(4골), ShangHaiPortFC_845231138(1골), ShangHaiPortFC_848031432(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:18:47</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>은안</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2_7</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>은안_866241236(1골), 은안_848143001(1골), 방덕_868135455(1골), 방덕_868009676(6골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:06:58</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>은안</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>은안_856246420(1골), 은안_866241236(1골), 방덕_861077787(1골), 방덕_868009676(1골), 방덕_848007512(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:51:33</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(1골), ZD장인지참치_839200104(2골), 용신_856202126(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:40:44</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>4_5</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(1골), ZD장인지참치_851240740(1골), 용신_863245367(1골), 용신_820264453(1골), 용신_101173731(1골), 용신_273227535(1골), 용신_856202126(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:19:09</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>4_4</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(2골), 비주류중독_848006975(1골), 비주류중독_839247699(1골), 비주류중독_825000240(1골), 비주류중독_840052241(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:02:44</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0_0</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-24 03:45:56</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>5_3</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(4골), UNIT_848180930(1골), ZD장인지참치_840247263(1골), ZD장인지참치_840191208(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-24 02:48:31</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>3_5</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>여수가스_861215732(1골), 여수가스_846188567(1골), 여수가스_828231747(1골), 방덕_827191189(1골), 방덕_101001419(1골), 방덕_861077787(1골), 방덕_848231478(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:59:32</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0708ManUtd_834239053(1골), 0708ManUtd_851226161(1골), 여수가스_861215732(3골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:47:25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0708ManUtd_848037576(1골), 0708ManUtd_868001397(1골), 0708ManUtd_851226161(1골), 0708ManUtd_848238794(1골), 여수가스_861215732(3골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:33:47</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>앙쿠_863246191(2골), 셀래스틴_836158023(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:23:09</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1_0</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>앙쿠_866266039(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:08:58</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1골), 앙쿠_863246191(2골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:58:26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1골), 앙쿠_866266039(1골), ZD장인지참치_840191208(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:28:11</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>6_2</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0708ManUtd_848183277(1골), 0708ManUtd_863239231(1골), 0708ManUtd_848238794(1골), 0708ManUtd_868001397(2골), 0708ManUtd_848037576(1골), 겐지간지_814231747(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:19:39</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1_5</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>아들러_840191208(1골), ZD장인지참치_839200104(2골), ZD장인지참치_840191208(1골), ZD장인지참치_840247263(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:19:35</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_225238224(2골), 콩콩콩룔_848189505(1골), 콩콩콩룔_866223710(3골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:15:41</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0708ManUtd_868001397(1골), 0708ManUtd_848037576(2골), 0708ManUtd_848183277(1골), 겐지간지_863256196(1골), 겐지간지_814231747(1골), 겐지간지_845158023(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:07:26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>5_4</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>아들러_855232639(1골), 아들러_861000570(1골), 아들러_840191208(2골), 아들러_866251377(1골), ZD장인지참치_839200104(2골), ZD장인지참치_840191208(1골), ZD장인지참치_840256630(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:05:58</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_225238224(2골), 콩콩콩룔_867223848(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:53:57</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>아들러_866251377(1골), 아들러_855232639(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:42:25</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>5_0</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>아들러_866251377(1골), 아들러_840191208(3골), 아들러_861000570(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:29:03</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(1골), 아들러_840191208(2골), 아들러_852232730(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:27:43</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>아들러_840191208(2골), 콩콩콩룔_867223848(2골), 콩콩콩룔_866223710(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:15:56</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>아들러_840191208(2골), 콩콩콩룔_866223710(1골), 콩콩콩룔_851236496(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:46:09</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>오스트리아_291223790(2골), 겐지간지_845158023(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:35:42</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>오스트리아_851221671(1골), 오스트리아_864199266(2골), 겐지간지_856237679(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>2026-09-22 14:15:38</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>셀래스틴</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>1_2</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>UNIT_848180930(1골), 셀래스틴_856277179(1골), 셀래스틴_836158023(1골)</t>
         </is>
@@ -1896,7 +3144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1934,54 +3182,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-26 12:19:23</t>
+          <t>2026-09-27 15:43:53</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6_4</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(1도움), ZD장인지참치_839200104(2도움), ZD장인지참치_840253149(2도움), 셀래스틴_846001551(1도움), 셀래스틴_852259694(1도움), 셀래스틴_852241461(2도움)</t>
+          <t>UNIT_848180930(1도움), UNIT_839013383(1도움), UNIT_840228251(1도움), Voor_845247090(1도움), Voor_280206585(1도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-26 12:08:13</t>
+          <t>2026-09-27 15:26:14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1991,29 +3239,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
+          <t>UNIT_840228251(2도움), UNIT_848180930(1도움), Voor_845009676(1도움), Voor_835183277(2도움)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-26 08:26:23</t>
+          <t>2026-09-27 15:09:40</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>0_6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2023,19 +3271,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>오스트리아_851216275(1도움), Special블루_861001419(2도움)</t>
+          <t>Voor_861000027(1도움), Voor_845239231(1도움)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-25 15:57:51</t>
+          <t>2026-09-27 14:57:41</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2045,7 +3293,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0_3</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2055,29 +3303,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Voor_835183277(1도움), Voor_852233700(1도움), Voor_856256079(1도움)</t>
+          <t>UNIT_840210736(1도움), UNIT_848180930(2도움), Voor_856256079(1도움), Voor_845247090(1도움), Voor_835183277(1도움)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-25 09:45:28</t>
+          <t>2026-09-27 14:54:39</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2087,189 +3335,189 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UNIT_840210736(1도움), UNIT_867166676(1도움), UNIT_840192883(1도움), 방덕_861077787(1도움), 방덕_856233096(1도움)</t>
+          <t>호야국2인_845201024(1도움), Gucci차붐_853272733(1도움), Gucci차붐_864084333(1도움)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-25 09:33:41</t>
+          <t>2026-09-27 14:43:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_840192883(1도움), UNIT_867166676(1도움), 방덕_848007512(1도움), 방덕_848231478(1도움)</t>
+          <t>호야국2인_848227236(1도움), Gucci차붐_864084333(2도움), Gucci차붐_851221671(1도움), Gucci차붐_864247686(1도움), Gucci차붐_853272733(1도움)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-25 09:22:20</t>
+          <t>2026-09-27 14:37:29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움), 방덕_848231478(2도움), 방덕_868009676(1도움)</t>
+          <t>피파왕초보구단주_846208722(1도움), 피파왕초보구단주_851243057(1도움), 피파왕초보구단주_846045197(1도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-25 09:10:55</t>
+          <t>2026-09-27 14:26:49</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>1_6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), 방덕_868135455(1도움)</t>
+          <t>Voor_845247090(1도움), Voor_856256079(1도움), Voor_852233700(3도움)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-25 08:53:47</t>
+          <t>2026-09-27 14:11:46</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2도움), 방덕_861077787(1도움), 방덕_868135455(1도움)</t>
+          <t>Voor_852233700(1도움), Voor_835183277(1도움)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-25 08:42:15</t>
+          <t>2026-09-27 14:08:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움), UNIT_829274967(1도움), 방덕_848007512(1도움), 방덕_867001040(1도움), 방덕_101001419(1도움)</t>
+          <t>0708ManUtd_848238794(1도움), 0708ManUtd_868001397(1도움)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-24 16:30:57</t>
+          <t>2026-09-27 13:58:06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2279,93 +3527,93 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>앙쿠_846193747(1도움), 앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_840192883(1도움), UNIT_840225782(1도움)</t>
+          <t>0708ManUtd_834239053(1도움), 0708ManUtd_834231281(1도움), 0708ManUtd_868037576(2도움)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-24 16:14:16</t>
+          <t>2026-09-27 13:41:37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_848135455(1도움), UNIT_863250723(1도움), UNIT_840216150(1도움), UNIT_840210736(1도움)</t>
+          <t>겐지간지_856237679(1도움), 피파왕초보구단주_846045197(1도움), 피파왕초보구단주_856209331(1도움), 피파왕초보구단주_846208722(1도움), 피파왕초보구단주_867000027(2도움)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-24 15:57:54</t>
+          <t>2026-09-27 13:29:35</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>1_8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(3도움), 앙쿠_848176580(1도움)</t>
+          <t>겐지간지_852241461(1도움), 피파왕초보구단주_861005661(1도움), 피파왕초보구단주_856209331(1도움), 피파왕초보구단주_846231281(2도움), 피파왕초보구단주_867000027(2도움), 피파왕초보구단주_846045197(1도움), 피파왕초보구단주_846208722(1도움)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-24 13:42:25</t>
+          <t>2026-09-27 11:36:34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2375,61 +3623,61 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UNIT_840210736(1도움), UNIT_840228251(1도움), UNIT_867166676(1도움)</t>
+          <t>개포동덕배_856275298(1도움), 개포동덕배_848206113(1도움), 개포동덕배_856202126(2도움), 개포동덕배_852225375(1도움), 개포동덕배_845208722(1도움), 여수가스_846001551(1도움)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-24 13:30:05</t>
+          <t>2026-09-27 11:24:41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), 셀래스틴_848230938(1도움), 셀래스틴_863277643(1도움), 셀래스틴_861142754(1도움)</t>
+          <t>개포동덕배_845208722(2도움), 개포동덕배_856202126(1도움), 개포동덕배_856275298(1도움), 개포동덕배_848206113(1도움), 개포동덕배_845190048(1도움), 여수가스_828231747(1도움), 여수가스_846001551(1도움)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-24 09:29:12</t>
+          <t>2026-09-27 10:09:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2439,29 +3687,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>여수가스_845020289(1도움), 여수가스_828231747(1도움), 여수가스_868135455(1도움), 여수가스_846001551(1도움), ShangHaiPortFC_284190813(1도움), ShangHaiPortFC_861051412(1도움)</t>
+          <t>개포동덕배_856202126(2도움), 개포동덕배_845208722(1도움), 개포동덕배_856275298(1도움), 아들러_291225126(1도움), 아들러_840208574(1도움), 아들러_852232730(1도움)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-24 09:16:26</t>
+          <t>2026-09-27 09:57:50</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2471,29 +3719,29 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>여수가스_846001551(1도움), 여수가스_828231747(1도움), 여수가스_852274967(1도움), 여수가스_861162895(1도움), ShangHaiPortFC_845231138(1도움), ShangHaiPortFC_861051412(1도움)</t>
+          <t>개포동덕배_845208722(1도움), 개포동덕배_863212622(2도움), 아들러_852232730(2도움)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-24 08:18:47</t>
+          <t>2026-09-27 09:29:41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2_7</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2503,29 +3751,29 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>은안_856251517(1도움), 방덕_868135455(1도움), 방덕_848231478(1도움), 방덕_848007512(1도움), 방덕_861077787(2도움), 방덕_868009676(1도움), 방덕_856226268(1도움)</t>
+          <t>겐지간지_856237679(1도움), 겐지간지_852231443(1도움), 경남FC가즈아_853221467(2도움)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-24 08:06:58</t>
+          <t>2026-09-27 09:18:24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2535,29 +3783,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>은안_856246420(1도움), 은안_848231866(1도움), 방덕_861077787(1도움), 방덕_848007512(1도움)</t>
+          <t>겐지간지_856237679(1도움), 경남FC가즈아_853221467(2도움)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-24 04:51:33</t>
+          <t>2026-09-27 09:14:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>5_4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2567,61 +3815,61 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ZD장인지참치_848210035(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_839200104(1도움), 용신_866200104(1도움)</t>
+          <t>아들러_861000570(1도움), 아들러_840208574(1도움), 아들러_866251377(1도움), 아들러_840221363(1도움), 아들러_855232639(1도움), Gucci와퍼_852010264(2도움), Gucci와퍼_852028765(1도움), Gucci와퍼_852168473(1도움)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-24 04:40:44</t>
+          <t>2026-09-27 09:00:07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4_5</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_851240740(1도움), 용신_863245367(2도움), 용신_273227535(1도움), 용신_848216267(1도움)</t>
+          <t>아들러_861000570(1도움), 아들러_840208574(1도움), 아들러_851244257(1도움), 아들러_291225126(1도움), Gucci와퍼_864200104(1도움)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-24 04:19:09</t>
+          <t>2026-09-27 08:20:21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2631,29 +3879,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ZD장인지참치_861182521(2도움), ZD장인지참치_840256630(1도움), ZD장인지참치_851240740(1도움), 비주류중독_848006975(1도움), 비주류중독_839247699(1도움), 비주류중독_852253149(1도움)</t>
+          <t>앙쿠_846186345(1도움), 앙쿠_846193747(1도움), 앙쿠_851194765(4도움), 겐지간지_852231443(1도움)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-24 04:02:44</t>
+          <t>2026-09-27 08:15:02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2661,27 +3909,31 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>개포동덕배_845190048(1도움), 개포동덕배_863212622(1도움), 경남FC가즈아_805207730(1도움), 경남FC가즈아_853221467(2도움)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-24 03:45:56</t>
+          <t>2026-09-27 08:08:47</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2691,93 +3943,93 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_840225782(1도움), UNIT_848135455(1도움), UNIT_848180930(1도움), UNIT_840192883(1도움), ZD장인지참치_848210035(1도움), ZD장인지참치_839200104(2도움)</t>
+          <t>앙쿠_851194765(3도움), 앙쿠_863246191(1도움), 앙쿠_848176580(1도움), 겐지간지_856237679(1도움), 겐지간지_852231443(1도움)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-24 02:48:31</t>
+          <t>2026-09-27 08:02:59</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3_5</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>여수가스_861162895(1도움), 여수가스_868135455(1도움), 방덕_868009676(1도움), 방덕_101001419(1도움), 방덕_863184200(1도움), 방덕_867001040(1도움)</t>
+          <t>개포동덕배_856202126(1도움), 개포동덕배_863212622(2도움), 개포동덕배_848206113(1도움), 경남FC가즈아_805267825(1도움), 경남FC가즈아_853221467(1도움), 경남FC가즈아_518251161(1도움), 경남FC가즈아_830228007(1도움)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-23 17:59:32</t>
+          <t>2026-09-27 07:50:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0708ManUtd_834239053(1도움), 0708ManUtd_868001397(1도움), 여수가스_868135455(1도움), 여수가스_828231747(1도움), 여수가스_845020289(1도움)</t>
+          <t>앙쿠_851194765(2도움), 앙쿠_863246191(1도움), 앙쿠_848176580(1도움)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-23 17:47:25</t>
+          <t>2026-09-27 07:47:08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2787,14 +4039,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0708ManUtd_834239053(1도움), 0708ManUtd_868001397(1도움), 0708ManUtd_851226161(1도움), 0708ManUtd_848238794(1도움), 여수가스_861162895(1도움), 여수가스_828231747(1도움)</t>
+          <t>Legend독수리_852229880(1도움), Legend독수리_839226764(2도움), Special블루_877001625(1도움), Special블루_863248148(1도움), Special블루_848230666(1도움)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-23 13:33:47</t>
+          <t>2026-09-27 07:40:08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2804,44 +4056,44 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), 셀래스틴_863251854(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>앙쿠_814226161(1도움), 앙쿠_863246191(1도움), 앙쿠_848176580(1도움)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-23 13:23:09</t>
+          <t>2026-09-26 20:23:39</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1_0</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2851,88 +4103,88 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_840192883(3도움), Voor_845009676(1도움), Voor_845247090(1도움), Voor_856256079(1도움)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-23 13:08:58</t>
+          <t>2026-09-26 20:11:13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(3도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
+          <t>UNIT_829274967(1도움), UNIT_848180930(1도움), Voor_845247090(1도움), Voor_856256079(1도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-23 12:58:26</t>
+          <t>2026-09-26 19:59:04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_839200104(1도움)</t>
+          <t>UNIT_848180930(1도움), UNIT_840225782(1도움), UNIT_867166676(1도움), Voor_845247090(2도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-23 12:28:11</t>
+          <t>2026-09-26 19:42:33</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2947,29 +4199,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0708ManUtd_851226161(2도움), 0708ManUtd_848238794(2도움), 0708ManUtd_868001397(1도움), 겐지간지_856237679(1도움)</t>
+          <t>UNIT_848135455(1도움), UNIT_840192883(2도움), UNIT_840228251(2도움), UNIT_840210736(1도움), Voor_856256079(1도움)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-23 12:19:39</t>
+          <t>2026-09-26 19:28:32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>7_8</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2979,61 +4231,61 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>아들러_814192318(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_848210035(1도움), ZD장인지참치_840191208(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_848199503(1도움)</t>
+          <t>UNIT_840192883(2도움), UNIT_863250723(1도움), UNIT_840228251(1도움), UNIT_829274967(1도움), Voor_861000027(3도움), Voor_852233700(1도움), Voor_845009676(1도움), Voor_848216150(1도움), Voor_856256079(2도움)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-23 12:19:35</t>
+          <t>2026-09-26 14:04:42</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>경남FC가즈아_853221467(2도움), 콩콩콩룔_867223848(2도움)</t>
+          <t>UNIT_848180930(2도움), UNIT_840192883(1도움), UNIT_867166676(1도움), Special블루_848034079(2도움), Special블루_861001419(1도움)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-23 12:15:41</t>
+          <t>2026-09-26 13:54:24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3043,29 +4295,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0708ManUtd_868001397(2도움), 0708ManUtd_848037576(1도움), 0708ManUtd_851226161(1도움), 겐지간지_861001668(1도움), 겐지간지_826247635(1도움), 겐지간지_852231443(1도움)</t>
+          <t>UNIT_848180930(1도움), UNIT_840210736(1도움), UNIT_867166676(2도움), Special블루_855241651(1도움), Special블루_848202652(1도움)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-23 12:07:26</t>
+          <t>2026-09-26 13:43:16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3075,29 +4327,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>아들러_855232639(2도움), 아들러_861000570(1도움), 아들러_840191208(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_861182521(2도움)</t>
+          <t>UNIT_840210736(1도움), UNIT_840225782(1도움), UNIT_840228251(2도움), Special블루_848202652(1도움)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-23 12:05:58</t>
+          <t>2026-09-26 13:32:03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3107,29 +4359,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>경남FC가즈아_277205156(1도움), 경남FC가즈아_518251161(1도움), 콩콩콩룔_851236496(1도움)</t>
+          <t>UNIT_867166676(1도움), UNIT_848180930(1도움), UNIT_840192883(1도움), Special블루_848034079(1도움)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-23 11:53:57</t>
+          <t>2026-09-26 13:20:21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>6_3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3139,29 +4391,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>아들러_861000570(2도움)</t>
+          <t>개포동덕배_845208722(2도움), 개포동덕배_856202126(1도움), 개포동덕배_848206113(1도움), 개포동덕배_866229558(1도움), Special블루_848034079(1도움), Special블루_851251805(2도움)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-23 11:42:25</t>
+          <t>2026-09-26 13:08:55</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5_0</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3171,197 +4423,1441 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>아들러_866251377(1도움), 아들러_855232639(1도움), 아들러_840191208(1도움), 아들러_840208574(1도움)</t>
+          <t>개포동덕배_845208722(1도움), 개포동덕배_856202126(1도움), 개포동덕배_845190048(1도움), 개포동덕배_848206113(1도움), 개포동덕배_866229558(1도움), Special블루_855241651(1도움), Special블루_848034079(1도움), Special블루_856246669(1도움)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-23 11:29:03</t>
+          <t>2026-09-26 12:19:23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>6_4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(1도움), 아들러_840191208(1도움), 아들러_852232730(1도움)</t>
+          <t>ZD장인지참치_840191208(1도움), ZD장인지참치_839200104(2도움), ZD장인지참치_840253149(2도움), 셀래스틴_852259694(1도움), 셀래스틴_852241461(2도움), 셀래스틴_846001551(1도움)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-23 10:27:43</t>
+          <t>2026-09-26 12:08:13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>아들러_866251377(1도움), 아들러_852232730(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_866223710(1도움), 콩콩콩룔_861006235(1도움)</t>
+          <t>ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-23 10:15:56</t>
+          <t>2026-09-26 08:26:23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>아들러_291225126(2도움), 콩콩콩룔_867220502(1도움)</t>
+          <t>오스트리아_851216275(1도움), Special블루_861001419(2도움)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-23 08:46:09</t>
+          <t>2026-09-25 15:57:51</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>0_3</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>오스트리아_864182152(1도움), 겐지간지_826247635(1도움)</t>
+          <t>Voor_835183277(1도움), Voor_852233700(1도움), Voor_856256079(1도움)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-23 08:35:42</t>
+          <t>2026-09-25 09:45:28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(2도움), 겐지간지_814231747(1도움)</t>
+          <t>UNIT_840210736(1도움), UNIT_867166676(1도움), UNIT_840192883(1도움), 방덕_861077787(1도움), 방덕_856233096(1도움)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>2026-09-25 09:33:41</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1도움), UNIT_840192883(1도움), UNIT_867166676(1도움), 방덕_848007512(1도움), 방덕_848231478(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:22:20</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(1도움), 방덕_848231478(2도움), 방덕_868009676(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:10:55</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>UNIT_840228251(1도움), 방덕_868135455(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-25 08:53:47</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2도움), 방덕_861077787(1도움), 방덕_868135455(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-25 08:42:15</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(1도움), UNIT_829274967(1도움), 방덕_848007512(1도움), 방덕_867001040(1도움), 방덕_101001419(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:30:57</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>앙쿠_846193747(1도움), 앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_840192883(1도움), UNIT_840225782(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:14:16</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3_4</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_848135455(1도움), UNIT_863250723(1도움), UNIT_840216150(1도움), UNIT_840210736(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:57:54</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>4_1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(3도움), 앙쿠_848176580(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:42:25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4_1</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>UNIT_840210736(1도움), UNIT_840228251(1도움), UNIT_867166676(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:30:05</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>UNIT_840228251(1도움), 셀래스틴_848230938(1도움), 셀래스틴_863277643(1도움), 셀래스틴_861142754(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:29:12</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>여수가스_845020289(1도움), 여수가스_828231747(1도움), 여수가스_868135455(1도움), 여수가스_846001551(1도움), ShangHaiPortFC_284190813(1도움), ShangHaiPortFC_861051412(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:16:26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>여수가스_846001551(1도움), 여수가스_828231747(1도움), 여수가스_852274967(1도움), 여수가스_861162895(1도움), ShangHaiPortFC_845231138(1도움), ShangHaiPortFC_861051412(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:18:47</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>은안</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2_7</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>은안_856251517(1도움), 방덕_868135455(1도움), 방덕_848231478(1도움), 방덕_848007512(1도움), 방덕_861077787(2도움), 방덕_868009676(1도움), 방덕_856226268(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:06:58</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>은안</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>은안_856246420(1도움), 은안_848231866(1도움), 방덕_861077787(1도움), 방덕_848007512(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:51:33</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_848210035(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_839200104(1도움), 용신_866200104(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:40:44</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>4_5</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_851240740(1도움), 용신_863245367(2도움), 용신_273227535(1도움), 용신_848216267(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:19:09</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>4_4</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_861182521(2도움), ZD장인지참치_840256630(1도움), ZD장인지참치_851240740(1도움), 비주류중독_848006975(1도움), 비주류중독_839247699(1도움), 비주류중독_852253149(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:02:44</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0_0</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-24 03:45:56</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>5_3</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>UNIT_840228251(1도움), UNIT_840225782(1도움), UNIT_848135455(1도움), UNIT_848180930(1도움), UNIT_840192883(1도움), ZD장인지참치_848210035(1도움), ZD장인지참치_839200104(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-24 02:48:31</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>3_5</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>여수가스_861162895(1도움), 여수가스_868135455(1도움), 방덕_868009676(1도움), 방덕_101001419(1도움), 방덕_863184200(1도움), 방덕_867001040(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:59:32</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0708ManUtd_834239053(1도움), 0708ManUtd_868001397(1도움), 여수가스_868135455(1도움), 여수가스_828231747(1도움), 여수가스_845020289(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:47:25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0708ManUtd_834239053(1도움), 0708ManUtd_868001397(1도움), 0708ManUtd_851226161(1도움), 0708ManUtd_848238794(1도움), 여수가스_861162895(1도움), 여수가스_828231747(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:33:47</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), 셀래스틴_863251854(1도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:23:09</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1_0</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>앙쿠_856247103(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:08:58</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(3도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:58:26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_839200104(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:28:11</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>6_2</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0708ManUtd_851226161(2도움), 0708ManUtd_848238794(2도움), 0708ManUtd_868001397(1도움), 겐지간지_856237679(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:19:39</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1_5</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>아들러_814192318(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_848210035(1도움), ZD장인지참치_840191208(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_848199503(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:19:35</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_853221467(2도움), 콩콩콩룔_867223848(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:15:41</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0708ManUtd_868001397(2도움), 0708ManUtd_848037576(1도움), 0708ManUtd_851226161(1도움), 겐지간지_861001668(1도움), 겐지간지_826247635(1도움), 겐지간지_852231443(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:07:26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>5_4</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>아들러_855232639(2도움), 아들러_861000570(1도움), 아들러_840191208(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_861182521(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:05:58</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_277205156(1도움), 경남FC가즈아_518251161(1도움), 콩콩콩룔_851236496(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:53:57</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>아들러_861000570(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:42:25</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>5_0</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>아들러_866251377(1도움), 아들러_855232639(1도움), 아들러_840191208(1도움), 아들러_840208574(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:29:03</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>앙쿠_863246191(1도움), 아들러_840191208(1도움), 아들러_852232730(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:27:43</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>아들러_866251377(1도움), 아들러_852232730(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_866223710(1도움), 콩콩콩룔_861006235(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:15:56</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>아들러_291225126(2도움), 콩콩콩룔_867220502(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:46:09</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>오스트리아_864182152(1도움), 겐지간지_826247635(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:35:42</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(2도움), 겐지간지_814231747(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>2026-09-22 14:15:38</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>셀래스틴</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>1_2</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>UNIT_840192883(1도움), 셀래스틴_852277643(1도움), 셀래스틴_852241461(1도움)</t>
         </is>

--- a/API데이터_경기_득점_및_도움_기록.xlsx
+++ b/API데이터_경기_득점_및_도움_기록.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-27 15:43:53</t>
+          <t>2026-09-28 16:10:58</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -462,29 +462,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>5_5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), UNIT_848180930(1골), Voor_858025420(1골), Voor_856256079(1골), Voor_835183277(1골)</t>
+          <t>UNIT_848180930(4골), UNIT_840228251(1골), 용신_101173731(2골), 용신_866200104(1골), 용신_856202126(2골)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-27 15:26:14</t>
+          <t>2026-09-28 15:58:54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -494,29 +494,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), UNIT_848180930(2골), Voor_852001201(1골), Voor_852233700(2골)</t>
+          <t>UNIT_848180930(1골), UNIT_863250723(1골), 용신_866200104(2골), 용신_856202126(1골)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-27 15:09:40</t>
+          <t>2026-09-28 15:43:33</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -526,76 +526,76 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0_6</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Voor_845009676(1골), Voor_845001116(1골), Voor_852233700(1골), Voor_835183277(2골), Voor_280206585(1골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(1골), 용신_826251421(1골)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-27 14:57:41</t>
+          <t>2026-09-28 15:28:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_867166676(2골), Voor_858025420(1골), Voor_852233700(3골)</t>
+          <t>Gucci차붐_851221671(1골), Gucci차붐_864176403(2골), Gucci와퍼_852168473(1골), Gucci와퍼_864200104(2골)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-27 14:54:39</t>
+          <t>2026-09-28 15:17:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -605,29 +605,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>호야국2인_835171877(1골), Gucci차붐_864176403(1골), Gucci차붐_864247686(1골)</t>
+          <t>Gucci차붐_853272733(1골), Gucci와퍼_864200104(2골), Gucci와퍼_852028765(2골)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-27 14:43:34</t>
+          <t>2026-09-28 15:12:41</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -637,29 +637,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>호야국2인_846192505(1골), Gucci차붐_864176403(2골), Gucci차붐_851221671(1골), Gucci차붐_853227659(1골), Gucci차붐_864247686(1골)</t>
+          <t>A지냐크_867001116(1골), 검정소_868192181(1골), 검정소_100214100(2골)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-27 14:37:29</t>
+          <t>2026-09-28 15:05:03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -669,29 +669,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_846208722(1골), 피파왕초보구단주_861005661(3골), Voor_845247090(1골)</t>
+          <t>Special블루_861047390(1골), Special블루_861006975(2골), Gucci와퍼_864200104(1골), Gucci와퍼_852010264(1골)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-27 14:26:49</t>
+          <t>2026-09-28 15:00:41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -701,61 +701,61 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_861005661(1골), Voor_835183277(1골), Voor_845009676(2골), Voor_845247090(1골), Voor_856256079(1골), Voor_852233700(1골)</t>
+          <t>A지냐크_867214101(1골), A지냐크_861001668(1골), 검정소_868192181(3골), 검정소_100214100(1골), 검정소_867241096(1골)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-27 14:11:46</t>
+          <t>2026-09-28 14:53:37</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>경남FC가즈아_805267825(1골), Voor_845009676(2골)</t>
+          <t>Special블루_877001625(1골), Special블루_868001419(1골), Special블루_856246669(1골), Gucci와퍼_864200104(1골)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-27 14:08:17</t>
+          <t>2026-09-28 14:38:43</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -765,253 +765,245 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0708ManUtd_868037576(2골)</t>
+          <t>A지냐크_848031432(3골), Special블루_877001625(1골)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-27 13:58:06</t>
+          <t>2026-09-28 14:26:52</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4_0</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0708ManUtd_868001397(2골), 0708ManUtd_834239053(1골), 0708ManUtd_868037576(1골)</t>
+          <t>A지냐크_861167134(1골), A지냐크_848031432(1골), Special블루_856246669(1골), Special블루_868001419(1골), Special블루_877001625(2골)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-27 13:41:37</t>
+          <t>2026-09-28 13:58:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>겐지간지_814231747(1골), 피파왕초보구단주_861005661(2골), 피파왕초보구단주_846208722(3골)</t>
+          <t>0708ManUtd_868037576(1골), 0708ManUtd_848238794(1골), 0708ManUtd_868001397(1골), suma수마_861221162(1골)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-27 13:29:35</t>
+          <t>2026-09-28 13:47:56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1_8</t>
+          <t>5_0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>겐지간지_856237679(1골), 피파왕초보구단주_861005661(1골), 피파왕초보구단주_856209331(2골), 피파왕초보구단주_846231281(1골), 피파왕초보구단주_867000027(2골), 피파왕초보구단주_846208722(2골)</t>
+          <t>0708ManUtd_868001397(3골), 0708ManUtd_848238794(2골)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-27 11:36:34</t>
+          <t>2026-09-28 13:34:44</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(5골), 개포동덕배_863212622(1골), 여수가스_861215732(1골)</t>
+          <t>A지냐크_867166676(1골), A지냐크_848031432(1골), 경남FC가즈아_805267825(2골), 경남FC가즈아_225238224(1골)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-27 11:24:41</t>
+          <t>2026-09-28 13:21:28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>개포동덕배_845208722(1골), 개포동덕배_856202126(2골), 개포동덕배_848206113(1골), 개포동덕배_845190048(3골), 여수가스_861162895(1골), 여수가스_828231747(1골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-27 10:09:38</t>
+          <t>2026-09-28 13:19:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>0_4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(4골), 아들러_840191208(2골), 아들러_866251377(1골)</t>
+          <t>경남FC가즈아_225238224(1골), 경남FC가즈아_805267825(3골)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-27 09:57:50</t>
+          <t>2026-09-28 13:07:55</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>개포동덕배_856202126(3골), 개포동덕배_863212622(1골), 아들러_866251377(2골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:41</t>
+          <t>2026-09-28 12:20:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1021,110 +1013,110 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>겐지간지_814231747(2골), 경남FC가즈아_225238224(2골), 경남FC가즈아_805267825(1골)</t>
+          <t>경남FC가즈아_225238224(1골), 경남FC가즈아_853221467(1골), 용신_101173731(1골), 용신_856202126(3골), 용신_279241096(1골)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-27 09:18:24</t>
+          <t>2026-09-28 12:10:44</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>겐지간지_814231747(1골), 경남FC가즈아_225238224(1골), 경남FC가즈아_805267825(1골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_848176580(3골), 앙쿠_863246191(1골), 셀래스틴_848231866(2골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-27 09:14:22</t>
+          <t>2026-09-28 12:08:37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>2_7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>아들러_861000570(1골), 아들러_840208574(1골), 아들러_866251377(1골), 아들러_840191208(2골), Gucci와퍼_852010264(1골), Gucci와퍼_864200104(2골), Gucci와퍼_852168473(1골)</t>
+          <t>경남FC가즈아_225238224(1골), 경남FC가즈아_805267825(1골), 용신_856202126(4골), 용신_101173731(1골), 용신_866200104(2골)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-27 09:00:07</t>
+          <t>2026-09-28 11:57:16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>아들러_862140057(1골), 아들러_840191208(1골), 아들러_855232639(1골), 아들러_291225126(1골), Gucci와퍼_852168473(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_851194765(1골), 셀래스틴_846001551(2골)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-27 08:20:21</t>
+          <t>2026-09-28 11:45:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1134,12 +1126,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6_1</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1149,46 +1141,46 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_863246191(5골), 겐지간지_856237679(1골)</t>
+          <t>앙쿠_866266039(1골), 앙쿠_846193747(1골), 앙쿠_848176580(1골), 앙쿠_851194765(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-27 08:15:02</t>
+          <t>2026-09-28 11:34:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>12_2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(1골), 개포동덕배_848206113(1골), 경남FC가즈아_225238224(2골), 경남FC가즈아_805267825(1골)</t>
+          <t>앙쿠_848176580(3골), 앙쿠_866266039(2골), 앙쿠_851194765(1골), 앙쿠_863246191(6골), 셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-27 08:08:47</t>
+          <t>2026-09-28 11:21:23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1198,76 +1190,76 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(3골), 앙쿠_848176580(2골), 겐지간지_848170890(1골), 겐지간지_814231747(1골)</t>
+          <t>앙쿠_863246191(1골), 앙쿠_848176580(1골), 셀래스틴_861005680(1골), 셀래스틴_848231866(1골)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-27 08:02:59</t>
+          <t>2026-09-28 09:56:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(3골), 개포동덕배_845208722(1골), 경남FC가즈아_225238224(3골), 경남FC가즈아_805267825(1골)</t>
+          <t>방덕_861077787(1골), 방덕_101001419(1골), 콩콩콩룔_867223848(2골), 콩콩콩룔_866223710(2골)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-27 07:50:56</t>
+          <t>2026-09-28 09:44:32</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4_0</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1277,61 +1269,61 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 앙쿠_863246191(2골), 앙쿠_856247103(1골)</t>
+          <t>방덕_101001419(1골), 방덕_868009676(1골), 방덕_861077787(2골), 콩콩콩룔_866223710(1골)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-27 07:47:08</t>
+          <t>2026-09-27 15:43:53</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Legend독수리_840192505(2골), Legend독수리_846001845(3골), Special블루_877001625(1골), Special블루_856246669(1골), Special블루_861047390(1골)</t>
+          <t>UNIT_867166676(2골), UNIT_848180930(1골), Voor_835183277(1골), Voor_856256079(1골), Voor_858025420(1골)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-27 07:40:08</t>
+          <t>2026-09-27 15:26:14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1341,14 +1333,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_851194765(2골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(2골), Voor_852233700(2골), Voor_852001201(1골)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-26 20:23:39</t>
+          <t>2026-09-27 15:09:40</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1363,24 +1355,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>0_6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UNIT_848180930(3골), UNIT_867166676(1골), Voor_845247090(1골), Voor_858025420(2골)</t>
+          <t>Voor_280206585(1골), Voor_845009676(1골), Voor_852233700(1골), Voor_845001116(1골), Voor_835183277(2골)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-26 20:11:13</t>
+          <t>2026-09-27 14:57:41</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1395,7 +1387,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1405,29 +1397,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1골), UNIT_840228251(1골), Voor_861000027(1골), Voor_845009676(1골), Voor_858025420(1골)</t>
+          <t>UNIT_867166676(2골), UNIT_848180930(1골), Voor_858025420(1골), Voor_852233700(3골)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-26 19:59:04</t>
+          <t>2026-09-27 14:54:39</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1437,51 +1429,51 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), UNIT_867166676(1골), Voor_845009676(1골), Voor_852233700(1골), Voor_835183277(1골)</t>
+          <t>호야국2인_835171877(1골), Gucci차붐_864176403(1골), Gucci차붐_864247686(1골)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-26 19:42:33</t>
+          <t>2026-09-27 14:43:34</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6_2</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), UNIT_840228251(2골), UNIT_867166676(2골), Voor_835183277(1골), Voor_845009676(1골)</t>
+          <t>호야국2인_846192505(1골), Gucci차붐_864247686(1골), Gucci차붐_864176403(2골), Gucci차붐_851221671(1골), Gucci차붐_853227659(1골)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-26 19:28:32</t>
+          <t>2026-09-27 14:37:29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1491,103 +1483,103 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7_8</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UNIT_852053302(1골), UNIT_840192883(1골), UNIT_867166676(3골), UNIT_840228251(2골), Voor_852233700(4골), Voor_845009676(1골), Voor_858020775(1골), Voor_835183277(1골), Voor_846184943(1골)</t>
+          <t>피파왕초보구단주_861005661(3골), 피파왕초보구단주_846208722(1골), Voor_845247090(1골)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-26 14:04:42</t>
+          <t>2026-09-27 14:26:49</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>1_6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UNIT_840228251(2골), UNIT_840192883(1골), UNIT_867166676(1골), Special블루_856246669(1골), Special블루_848230666(2골)</t>
+          <t>피파왕초보구단주_861005661(1골), Voor_845247090(1골), Voor_856256079(1골), Voor_845009676(2골), Voor_835183277(1골), Voor_852233700(1골)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-26 13:54:24</t>
+          <t>2026-09-27 14:11:46</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UNIT_848180930(3골), UNIT_867166676(1골), Special블루_863234378(1골), Special블루_855241651(1골)</t>
+          <t>경남FC가즈아_805267825(1골), Voor_845009676(2골)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-26 13:43:16</t>
+          <t>2026-09-27 14:08:17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1597,29 +1589,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), UNIT_848180930(2골), UNIT_840228251(1골), Special블루_855241651(1골)</t>
+          <t>0708ManUtd_868037576(2골)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-26 13:32:03</t>
+          <t>2026-09-27 13:58:06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1629,93 +1621,93 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UNIT_848135455(1골), UNIT_848180930(1골), UNIT_840192883(1골), Special블루_855241651(1골)</t>
+          <t>0708ManUtd_868001397(2골), 0708ManUtd_834239053(1골), 0708ManUtd_868037576(1골)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-26 13:20:21</t>
+          <t>2026-09-27 13:41:37</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6_3</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>개포동덕배_856202126(1골), 개포동덕배_856275298(1골), 개포동덕배_863212622(1골), 개포동덕배_845190048(3골), Special블루_856246669(1골), Special블루_861001419(1골), Special블루_848230666(1골)</t>
+          <t>겐지간지_814231747(1골), 피파왕초보구단주_861005661(2골), 피파왕초보구단주_846208722(3골)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-26 13:08:55</t>
+          <t>2026-09-27 13:29:35</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>1_8</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>개포동덕배_845208722(1골), 개포동덕배_856202126(1골), 개포동덕배_845190048(3골), Special블루_863234378(1골), Special블루_851251805(1골), Special블루_848230666(1골)</t>
+          <t>겐지간지_856237679(1골), 피파왕초보구단주_861005661(1골), 피파왕초보구단주_856209331(2골), 피파왕초보구단주_846231281(1골), 피파왕초보구단주_867000027(2골), 피파왕초보구단주_846208722(2골)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-26 12:19:23</t>
+          <t>2026-09-27 11:36:34</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6_4</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1725,29 +1717,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(4골), ZD장인지참치_839200104(1골), ZD장인지참치_851240740(1골), 셀래스틴_848194765(2골), 셀래스틴_852241461(1골), 셀래스틴_846001551(1골)</t>
+          <t>개포동덕배_845190048(5골), 개포동덕배_863212622(1골), 여수가스_861215732(1골)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-26 12:08:13</t>
+          <t>2026-09-27 11:24:41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1757,93 +1749,93 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2골), 셀래스틴_861005680(1골)</t>
+          <t>개포동덕배_845208722(1골), 개포동덕배_856202126(2골), 개포동덕배_848206113(1골), 개포동덕배_845190048(3골), 여수가스_861162895(1골), 여수가스_828231747(1골)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-26 08:26:23</t>
+          <t>2026-09-27 10:09:38</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>오스트리아_851221671(1골), Special블루_856246669(1골), Special블루_863248148(1골), Special블루_855241651(1골)</t>
+          <t>개포동덕배_845190048(4골), 아들러_840191208(2골), 아들러_866251377(1골)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-25 15:57:51</t>
+          <t>2026-09-27 09:57:50</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Voor_845009676(1골), Voor_845247090(1골), Voor_852233700(1골)</t>
+          <t>개포동덕배_856202126(3골), 개포동덕배_863212622(1골), 아들러_866251377(2골)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-25 09:45:28</t>
+          <t>2026-09-27 09:29:41</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1853,152 +1845,152 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_840228251(2골), 방덕_848007512(1골), 방덕_868009676(3골)</t>
+          <t>겐지간지_814231747(2골), 경남FC가즈아_225238224(2골), 경남FC가즈아_805267825(1골)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-25 09:33:41</t>
+          <t>2026-09-27 09:18:24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_840192883(1골), UNIT_867166676(1골), 방덕_861077787(1골), 방덕_868009676(1골)</t>
+          <t>겐지간지_814231747(1골), 경남FC가즈아_225238224(1골), 경남FC가즈아_805267825(1골)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-25 09:22:20</t>
+          <t>2026-09-27 09:14:22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), UNIT_840192883(1골), 방덕_868009676(1골), 방덕_868135455(1골), 방덕_861077787(1골)</t>
+          <t>아들러_861000570(1골), 아들러_840208574(1골), 아들러_866251377(1골), 아들러_840191208(2골), Gucci와퍼_852010264(1골), Gucci와퍼_864200104(2골), Gucci와퍼_852168473(1골)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-25 09:10:55</t>
+          <t>2026-09-27 09:00:07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1골), 방덕_868009676(1골)</t>
+          <t>아들러_862140057(1골), 아들러_840191208(1골), 아들러_855232639(1골), 아들러_291225126(1골), Gucci와퍼_852168473(1골)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-25 08:53:47</t>
+          <t>2026-09-27 08:20:21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_840192883(1골), 방덕_861077787(1골), 방덕_101001419(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_863246191(5골), 겐지간지_856237679(1골)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-25 08:42:15</t>
+          <t>2026-09-27 08:15:02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2013,14 +2005,14 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), 방덕_868135455(2골), 방덕_856228093(1골)</t>
+          <t>개포동덕배_845190048(1골), 개포동덕배_848206113(1골), 경남FC가즈아_225238224(2골), 경남FC가즈아_805267825(1골)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-24 16:30:57</t>
+          <t>2026-09-27 08:08:47</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2030,12 +2022,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2045,46 +2037,46 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_851194765(1골), 앙쿠_866266039(1골), UNIT_867166676(1골), UNIT_840228251(1골)</t>
+          <t>앙쿠_863246191(3골), 앙쿠_848176580(2골), 겐지간지_848170890(1골), 겐지간지_814231747(1골)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-24 16:14:16</t>
+          <t>2026-09-27 08:02:59</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>앙쿠_866266039(1골), 앙쿠_848176580(1골), 앙쿠_863246191(1골), UNIT_867166676(3골), UNIT_848180930(1골)</t>
+          <t>개포동덕배_845190048(3골), 개포동덕배_845208722(1골), 경남FC가즈아_225238224(3골), 경남FC가즈아_805267825(1골)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-24 15:57:54</t>
+          <t>2026-09-27 07:50:56</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2094,12 +2086,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2109,29 +2101,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_863246191(3골), UNIT_848180930(1골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_863246191(2골), 앙쿠_856247103(1골)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-24 13:42:25</t>
+          <t>2026-09-27 07:47:08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2141,61 +2133,61 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), UNIT_840228251(1골), UNIT_840192883(1골), 셀래스틴_856277179(1골)</t>
+          <t>Legend독수리_840192505(2골), Legend독수리_846001845(3골), Special블루_877001625(1골), Special블루_856246669(1골), Special블루_861047390(1골)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-24 13:30:05</t>
+          <t>2026-09-27 07:40:08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>3_0</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), 셀래스틴_856277179(1골), 셀래스틴_861005680(1골), 셀래스틴_861142754(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_851194765(2골)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-24 09:29:12</t>
+          <t>2026-09-26 20:23:39</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2205,61 +2197,61 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>여수가스_861215732(2골), 여수가스_861162895(2골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_861051412(1골)</t>
+          <t>UNIT_848180930(3골), UNIT_867166676(1골), Voor_845247090(1골), Voor_858025420(2골)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-24 09:16:26</t>
+          <t>2026-09-26 20:11:13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>여수가스_861215732(4골), ShangHaiPortFC_845231138(1골), ShangHaiPortFC_848031432(2골)</t>
+          <t>UNIT_840192883(1골), UNIT_840228251(1골), Voor_861000027(1골), Voor_845009676(1골), Voor_858025420(1골)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-24 08:18:47</t>
+          <t>2026-09-26 19:59:04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2_7</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2269,125 +2261,125 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>은안_866241236(1골), 은안_848143001(1골), 방덕_868135455(1골), 방덕_868009676(6골)</t>
+          <t>UNIT_848180930(2골), UNIT_867166676(1골), Voor_845009676(1골), Voor_852233700(1골), Voor_835183277(1골)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-24 08:06:58</t>
+          <t>2026-09-26 19:42:33</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>6_2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>은안_856246420(1골), 은안_866241236(1골), 방덕_861077787(1골), 방덕_868009676(1골), 방덕_848007512(1골)</t>
+          <t>UNIT_848180930(2골), UNIT_840228251(2골), UNIT_867166676(2골), Voor_835183277(1골), Voor_845009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-24 04:51:33</t>
+          <t>2026-09-26 19:28:32</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>7_8</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(1골), ZD장인지참치_839200104(2골), 용신_856202126(1골)</t>
+          <t>UNIT_852053302(1골), UNIT_840192883(1골), UNIT_867166676(3골), UNIT_840228251(2골), Voor_852233700(4골), Voor_845009676(1골), Voor_858020775(1골), Voor_835183277(1골), Voor_846184943(1골)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-24 04:40:44</t>
+          <t>2026-09-26 14:04:42</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4_5</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(1골), ZD장인지참치_851240740(1골), 용신_863245367(1골), 용신_820264453(1골), 용신_101173731(1골), 용신_273227535(1골), 용신_856202126(1골)</t>
+          <t>UNIT_840228251(2골), UNIT_840192883(1골), UNIT_867166676(1골), Special블루_856246669(1골), Special블루_848230666(2골)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-24 04:19:09</t>
+          <t>2026-09-26 13:54:24</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2397,42 +2389,46 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(2골), 비주류중독_848006975(1골), 비주류중독_839247699(1골), 비주류중독_825000240(1골), 비주류중독_840052241(1골)</t>
+          <t>UNIT_848180930(3골), UNIT_867166676(1골), Special블루_863234378(1골), Special블루_855241651(1골)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-24 04:02:44</t>
+          <t>2026-09-26 13:43:16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), UNIT_848180930(2골), UNIT_840228251(1골), Special블루_855241651(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-24 03:45:56</t>
+          <t>2026-09-26 13:32:03</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2442,12 +2438,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2457,93 +2453,93 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>UNIT_867166676(4골), UNIT_848180930(1골), ZD장인지참치_840247263(1골), ZD장인지참치_840191208(2골)</t>
+          <t>UNIT_848135455(1골), UNIT_848180930(1골), UNIT_840192883(1골), Special블루_855241651(1골)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-24 02:48:31</t>
+          <t>2026-09-26 13:20:21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3_5</t>
+          <t>6_3</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>여수가스_861215732(1골), 여수가스_846188567(1골), 여수가스_828231747(1골), 방덕_827191189(1골), 방덕_101001419(1골), 방덕_861077787(1골), 방덕_848231478(2골)</t>
+          <t>개포동덕배_856202126(1골), 개포동덕배_856275298(1골), 개포동덕배_863212622(1골), 개포동덕배_845190048(3골), Special블루_856246669(1골), Special블루_861001419(1골), Special블루_848230666(1골)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-23 17:59:32</t>
+          <t>2026-09-26 13:08:55</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0708ManUtd_834239053(1골), 0708ManUtd_851226161(1골), 여수가스_861215732(3골)</t>
+          <t>개포동덕배_845208722(1골), 개포동덕배_856202126(1골), 개포동덕배_845190048(3골), Special블루_863234378(1골), Special블루_851251805(1골), Special블루_848230666(1골)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-23 17:47:25</t>
+          <t>2026-09-26 12:19:23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>6_4</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2553,19 +2549,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0708ManUtd_848037576(1골), 0708ManUtd_868001397(1골), 0708ManUtd_851226161(1골), 0708ManUtd_848238794(1골), 여수가스_861215732(3골)</t>
+          <t>ZD장인지참치_840191208(4골), ZD장인지참치_839200104(1골), ZD장인지참치_851240740(1골), 셀래스틴_848194765(2골), 셀래스틴_852241461(1골), 셀래스틴_846001551(1골)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-23 13:33:47</t>
+          <t>2026-09-26 12:08:13</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2575,135 +2571,135 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(2골), 셀래스틴_836158023(2골)</t>
+          <t>ZD장인지참치_840191208(2골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-23 13:23:09</t>
+          <t>2026-09-26 08:26:23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1_0</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>앙쿠_866266039(1골)</t>
+          <t>오스트리아_851221671(1골), Special블루_856246669(1골), Special블루_863248148(1골), Special블루_855241651(1골)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-23 13:08:58</t>
+          <t>2026-09-25 15:57:51</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>0_3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_863246191(2골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골)</t>
+          <t>Voor_845009676(1골), Voor_845247090(1골), Voor_852233700(1골)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-23 12:58:26</t>
+          <t>2026-09-25 09:45:28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_866266039(1골), ZD장인지참치_840191208(2골)</t>
+          <t>UNIT_848180930(1골), UNIT_840228251(2골), 방덕_848007512(1골), 방덕_868009676(3골)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-23 12:28:11</t>
+          <t>2026-09-25 09:33:41</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2713,29 +2709,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0708ManUtd_848183277(1골), 0708ManUtd_863239231(1골), 0708ManUtd_848238794(1골), 0708ManUtd_868001397(2골), 0708ManUtd_848037576(1골), 겐지간지_814231747(2골)</t>
+          <t>UNIT_848180930(1골), UNIT_840192883(1골), UNIT_867166676(1골), 방덕_861077787(1골), 방덕_868009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-23 12:19:39</t>
+          <t>2026-09-25 09:22:20</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2745,125 +2741,125 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>아들러_840191208(1골), ZD장인지참치_839200104(2골), ZD장인지참치_840191208(1골), ZD장인지참치_840247263(2골)</t>
+          <t>UNIT_867166676(1골), UNIT_840192883(1골), 방덕_868009676(1골), 방덕_868135455(1골), 방덕_861077787(1골)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-23 12:19:35</t>
+          <t>2026-09-25 09:10:55</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>경남FC가즈아_225238224(2골), 콩콩콩룔_848189505(1골), 콩콩콩룔_866223710(3골)</t>
+          <t>UNIT_840192883(1골), 방덕_868009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-23 12:15:41</t>
+          <t>2026-09-25 08:53:47</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0708ManUtd_868001397(1골), 0708ManUtd_848037576(2골), 0708ManUtd_848183277(1골), 겐지간지_863256196(1골), 겐지간지_814231747(1골), 겐지간지_845158023(1골)</t>
+          <t>UNIT_848180930(1골), UNIT_840192883(1골), 방덕_861077787(1골), 방덕_101001419(1골)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-23 12:07:26</t>
+          <t>2026-09-25 08:42:15</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>아들러_855232639(1골), 아들러_861000570(1골), 아들러_840191208(2골), 아들러_866251377(1골), ZD장인지참치_839200104(2골), ZD장인지참치_840191208(1골), ZD장인지참치_840256630(1골)</t>
+          <t>UNIT_867166676(2골), 방덕_868135455(2골), 방덕_856228093(1골)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-23 12:05:58</t>
+          <t>2026-09-24 16:30:57</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2873,29 +2869,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>경남FC가즈아_225238224(2골), 콩콩콩룔_867223848(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_851194765(1골), 앙쿠_866266039(1골), UNIT_867166676(1골), UNIT_840228251(1골)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-23 11:53:57</t>
+          <t>2026-09-24 16:14:16</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2905,29 +2901,29 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>아들러_866251377(1골), 아들러_855232639(1골)</t>
+          <t>앙쿠_866266039(1골), 앙쿠_848176580(1골), 앙쿠_863246191(1골), UNIT_867166676(3골), UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-23 11:42:25</t>
+          <t>2026-09-24 15:57:54</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5_0</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2937,61 +2933,61 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>아들러_866251377(1골), 아들러_840191208(3골), 아들러_861000570(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_863246191(3골), UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-23 11:29:03</t>
+          <t>2026-09-24 13:42:25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 아들러_840191208(2골), 아들러_852232730(1골)</t>
+          <t>UNIT_848180930(2골), UNIT_840228251(1골), UNIT_840192883(1골), 셀래스틴_856277179(1골)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-23 10:27:43</t>
+          <t>2026-09-24 13:30:05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3001,61 +2997,61 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>아들러_840191208(2골), 콩콩콩룔_867223848(2골), 콩콩콩룔_866223710(2골)</t>
+          <t>UNIT_867166676(1골), 셀래스틴_856277179(1골), 셀래스틴_861005680(1골), 셀래스틴_861142754(1골)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-23 10:15:56</t>
+          <t>2026-09-24 09:29:12</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>아들러_840191208(2골), 콩콩콩룔_866223710(1골), 콩콩콩룔_851236496(1골)</t>
+          <t>여수가스_861215732(2골), 여수가스_861162895(2골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_861051412(1골)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-23 08:46:09</t>
+          <t>2026-09-24 09:16:26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3065,69 +3061,897 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>오스트리아_291223790(2골), 겐지간지_845158023(1골)</t>
+          <t>여수가스_861215732(4골), ShangHaiPortFC_845231138(1골), ShangHaiPortFC_848031432(2골)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-23 08:35:42</t>
+          <t>2026-09-24 08:18:47</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_7</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>오스트리아_851221671(1골), 오스트리아_864199266(2골), 겐지간지_856237679(1골)</t>
+          <t>은안_866241236(1골), 은안_848143001(1골), 방덕_868135455(1골), 방덕_868009676(6골)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>2026-09-24 08:06:58</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>은안</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>은안_856246420(1골), 은안_866241236(1골), 방덕_861077787(1골), 방덕_868009676(1골), 방덕_848007512(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:51:33</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(1골), ZD장인지참치_839200104(2골), 용신_856202126(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:40:44</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>4_5</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(1골), ZD장인지참치_851240740(1골), 용신_863245367(1골), 용신_820264453(1골), 용신_101173731(1골), 용신_273227535(1골), 용신_856202126(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:19:09</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>4_4</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(2골), ZD장인지참치_839200104(2골), 비주류중독_848006975(1골), 비주류중독_839247699(1골), 비주류중독_825000240(1골), 비주류중독_840052241(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:02:44</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>0_0</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-24 03:45:56</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>5_3</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(4골), UNIT_848180930(1골), ZD장인지참치_840247263(1골), ZD장인지참치_840191208(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-24 02:48:31</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3_5</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>여수가스_861215732(1골), 여수가스_846188567(1골), 여수가스_828231747(1골), 방덕_827191189(1골), 방덕_101001419(1골), 방덕_861077787(1골), 방덕_848231478(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:59:32</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0708ManUtd_834239053(1골), 0708ManUtd_851226161(1골), 여수가스_861215732(3골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:47:25</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0708ManUtd_848037576(1골), 0708ManUtd_868001397(1골), 0708ManUtd_851226161(1골), 0708ManUtd_848238794(1골), 여수가스_861215732(3골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:33:47</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>앙쿠_863246191(2골), 셀래스틴_836158023(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:23:09</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1_0</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>앙쿠_866266039(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:08:58</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1골), 앙쿠_863246191(2골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:58:26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1골), 앙쿠_866266039(1골), ZD장인지참치_840191208(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:28:11</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>6_2</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0708ManUtd_848183277(1골), 0708ManUtd_863239231(1골), 0708ManUtd_848238794(1골), 0708ManUtd_868001397(2골), 0708ManUtd_848037576(1골), 겐지간지_814231747(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:19:39</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>1_5</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>아들러_840191208(1골), ZD장인지참치_839200104(2골), ZD장인지참치_840191208(1골), ZD장인지참치_840247263(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:19:35</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_225238224(2골), 콩콩콩룔_848189505(1골), 콩콩콩룔_866223710(3골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:15:41</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0708ManUtd_868001397(1골), 0708ManUtd_848037576(2골), 0708ManUtd_848183277(1골), 겐지간지_863256196(1골), 겐지간지_814231747(1골), 겐지간지_845158023(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:07:26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>5_4</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>아들러_855232639(1골), 아들러_861000570(1골), 아들러_840191208(2골), 아들러_866251377(1골), ZD장인지참치_839200104(2골), ZD장인지참치_840191208(1골), ZD장인지참치_840256630(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:05:58</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_225238224(2골), 콩콩콩룔_867223848(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:53:57</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>아들러_866251377(1골), 아들러_855232639(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:42:25</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>5_0</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>아들러_866251377(1골), 아들러_840191208(3골), 아들러_861000570(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:29:03</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(1골), 아들러_840191208(2골), 아들러_852232730(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:27:43</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>아들러_840191208(2골), 콩콩콩룔_867223848(2골), 콩콩콩룔_866223710(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:15:56</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>아들러_840191208(2골), 콩콩콩룔_866223710(1골), 콩콩콩룔_851236496(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:46:09</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>오스트리아_291223790(2골), 겐지간지_845158023(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:35:42</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>오스트리아_851221671(1골), 오스트리아_864199266(2골), 겐지간지_856237679(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
           <t>2026-09-22 14:15:38</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>셀래스틴</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>1_2</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>UNIT_848180930(1골), 셀래스틴_856277179(1골), 셀래스틴_836158023(1골)</t>
         </is>
@@ -3144,7 +3968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3182,7 +4006,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-27 15:43:53</t>
+          <t>2026-09-28 16:10:58</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3192,29 +4016,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>5_5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_839013383(1도움), UNIT_840228251(1도움), Voor_845247090(1도움), Voor_280206585(1도움), Voor_852233700(1도움)</t>
+          <t>UNIT_867166676(1도움), UNIT_848180930(1도움), UNIT_840210736(1도움), UNIT_840228251(1도움), 용신_101173731(1도움), 용신_826251421(1도움), 용신_863177003(1도움), 용신_848216267(1도움)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-27 15:26:14</t>
+          <t>2026-09-28 15:58:54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3224,29 +4048,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UNIT_840228251(2도움), UNIT_848180930(1도움), Voor_845009676(1도움), Voor_835183277(2도움)</t>
+          <t>UNIT_867166676(1도움), UNIT_840192883(1도움), 용신_291213648(1도움), 용신_826251421(1도움), 용신_866200104(1도움)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-27 15:09:40</t>
+          <t>2026-09-28 15:43:33</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3256,76 +4080,76 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0_6</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Voor_861000027(1도움), Voor_845239231(1도움)</t>
+          <t>UNIT_848180930(1도움), UNIT_840210736(1도움)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-27 14:57:41</t>
+          <t>2026-09-28 15:28:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UNIT_840210736(1도움), UNIT_848180930(2도움), Voor_856256079(1도움), Voor_845247090(1도움), Voor_835183277(1도움)</t>
+          <t>Gucci차붐_864084333(2도움), Gucci차붐_853227659(1도움), Gucci와퍼_852010264(1도움), Gucci와퍼_852028765(1도움), Gucci와퍼_852168473(1도움)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-27 14:54:39</t>
+          <t>2026-09-28 15:17:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3335,29 +4159,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>호야국2인_845201024(1도움), Gucci차붐_853272733(1도움), Gucci차붐_864084333(1도움)</t>
+          <t>Gucci차붐_864247686(1도움), Gucci와퍼_852010264(2도움), Gucci와퍼_852168473(1도움), Gucci와퍼_840208574(1도움)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-27 14:43:34</t>
+          <t>2026-09-28 15:12:41</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3367,29 +4191,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>호야국2인_848227236(1도움), Gucci차붐_864084333(2도움), Gucci차붐_851221671(1도움), Gucci차붐_864247686(1도움), Gucci차붐_853272733(1도움)</t>
+          <t>A지냐크_840210736(1도움), 검정소_861005003(1도움), 검정소_851241721(2도움)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-27 14:37:29</t>
+          <t>2026-09-28 15:05:03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3399,29 +4223,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_846208722(1도움), 피파왕초보구단주_851243057(1도움), 피파왕초보구단주_846045197(1도움), Voor_852233700(1도움)</t>
+          <t>Special블루_851251805(1도움), Special블루_863248148(1도움), Special블루_868001419(1도움), Gucci와퍼_852168473(1도움), Gucci와퍼_852010264(1도움)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-27 14:26:49</t>
+          <t>2026-09-28 15:00:41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3431,61 +4255,61 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Voor_845247090(1도움), Voor_856256079(1도움), Voor_852233700(3도움)</t>
+          <t>A지냐크_867214101(1도움), A지냐크_863241496(1도움), 검정소_868192181(1도움), 검정소_861005003(1도움), 검정소_851241721(1도움), 검정소_867241096(1도움), 검정소_861214098(1도움)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-27 14:11:46</t>
+          <t>2026-09-28 14:53:37</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Voor_852233700(1도움), Voor_835183277(1도움)</t>
+          <t>Special블루_861047390(1도움), Special블루_863248148(1도움), Special블루_861006975(1도움), Gucci와퍼_852028765(1도움)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-27 14:08:17</t>
+          <t>2026-09-28 14:38:43</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3495,253 +4319,245 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0708ManUtd_848238794(1도움), 0708ManUtd_868001397(1도움)</t>
+          <t>A지냐크_855213648(2도움), Special블루_861047390(1도움)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-27 13:58:06</t>
+          <t>2026-09-28 14:26:52</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4_0</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0708ManUtd_834239053(1도움), 0708ManUtd_834231281(1도움), 0708ManUtd_868037576(2도움)</t>
+          <t>A지냐크_863241496(2도움), Special블루_856246669(1도움), Special블루_848034079(1도움), Special블루_861047390(1도움), Special블루_861006975(1도움)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-27 13:41:37</t>
+          <t>2026-09-28 13:58:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>겐지간지_856237679(1도움), 피파왕초보구단주_846045197(1도움), 피파왕초보구단주_856209331(1도움), 피파왕초보구단주_846208722(1도움), 피파왕초보구단주_867000027(2도움)</t>
+          <t>0708ManUtd_868037576(1도움), 0708ManUtd_867232656(1도움), 0708ManUtd_868001397(1도움), suma수마_861190046(1도움)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-27 13:29:35</t>
+          <t>2026-09-28 13:47:56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1_8</t>
+          <t>5_0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>겐지간지_852241461(1도움), 피파왕초보구단주_861005661(1도움), 피파왕초보구단주_856209331(1도움), 피파왕초보구단주_846231281(2도움), 피파왕초보구단주_867000027(2도움), 피파왕초보구단주_846045197(1도움), 피파왕초보구단주_846208722(1도움)</t>
+          <t>0708ManUtd_868037576(2도움), 0708ManUtd_834239053(1도움), 0708ManUtd_835183277(1도움), 0708ManUtd_848238794(1도움)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-27 11:36:34</t>
+          <t>2026-09-28 13:34:44</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>개포동덕배_856275298(1도움), 개포동덕배_848206113(1도움), 개포동덕배_856202126(2도움), 개포동덕배_852225375(1도움), 개포동덕배_845208722(1도움), 여수가스_846001551(1도움)</t>
+          <t>A지냐크_861167134(1도움), A지냐크_867214101(1도움), 경남FC가즈아_277205156(1도움), 경남FC가즈아_830228007(1도움)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-27 11:24:41</t>
+          <t>2026-09-28 13:21:28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>개포동덕배_845208722(2도움), 개포동덕배_856202126(1도움), 개포동덕배_856275298(1도움), 개포동덕배_848206113(1도움), 개포동덕배_845190048(1도움), 여수가스_828231747(1도움), 여수가스_846001551(1도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-27 10:09:38</t>
+          <t>2026-09-28 13:19:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>0_4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>개포동덕배_856202126(2도움), 개포동덕배_845208722(1도움), 개포동덕배_856275298(1도움), 아들러_291225126(1도움), 아들러_840208574(1도움), 아들러_852232730(1도움)</t>
+          <t>경남FC가즈아_853221467(1도움), 경남FC가즈아_805207730(2도움)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-27 09:57:50</t>
+          <t>2026-09-28 13:07:55</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>개포동덕배_845208722(1도움), 개포동덕배_863212622(2도움), 아들러_852232730(2도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-27 09:29:41</t>
+          <t>2026-09-28 12:20:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3751,110 +4567,110 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>겐지간지_856237679(1도움), 겐지간지_852231443(1도움), 경남FC가즈아_853221467(2도움)</t>
+          <t>경남FC가즈아_518200601(1도움), 경남FC가즈아_805267825(1도움), 용신_101173731(2도움), 용신_863245367(1도움), 용신_291213648(1도움)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-27 09:18:24</t>
+          <t>2026-09-28 12:10:44</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>겐지간지_856237679(1도움), 경남FC가즈아_853221467(2도움)</t>
+          <t>앙쿠_851194765(3도움), 앙쿠_814226161(1도움), 셀래스틴_848230938(1도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-27 09:14:22</t>
+          <t>2026-09-28 12:08:37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>2_7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>아들러_861000570(1도움), 아들러_840208574(1도움), 아들러_866251377(1도움), 아들러_840221363(1도움), 아들러_855232639(1도움), Gucci와퍼_852010264(2도움), Gucci와퍼_852028765(1도움), Gucci와퍼_852168473(1도움)</t>
+          <t>경남FC가즈아_805267825(1도움), 경남FC가즈아_518251161(1도움), 용신_863245367(3도움), 용신_866200104(1도움), 용신_848216267(1도움), 용신_291213648(1도움)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-27 09:00:07</t>
+          <t>2026-09-28 11:57:16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>아들러_861000570(1도움), 아들러_840208574(1도움), 아들러_851244257(1도움), 아들러_291225126(1도움), Gucci와퍼_864200104(1도움)</t>
+          <t>앙쿠_863246191(1도움), 앙쿠_846193747(1도움), 셀래스틴_861005680(1도움)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-27 08:20:21</t>
+          <t>2026-09-28 11:45:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3864,12 +4680,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6_1</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3879,46 +4695,46 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>앙쿠_846186345(1도움), 앙쿠_846193747(1도움), 앙쿠_851194765(4도움), 겐지간지_852231443(1도움)</t>
+          <t>앙쿠_846186345(1도움), 앙쿠_863246191(2도움), 앙쿠_851194765(1도움)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-27 08:15:02</t>
+          <t>2026-09-28 11:34:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>12_2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(1도움), 개포동덕배_863212622(1도움), 경남FC가즈아_805207730(1도움), 경남FC가즈아_853221467(2도움)</t>
+          <t>앙쿠_848176580(3도움), 앙쿠_851194765(4도움), 앙쿠_863246191(3도움), 앙쿠_846186345(2도움), 셀래스틴_848231866(1도움)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-27 08:08:47</t>
+          <t>2026-09-28 11:21:23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3928,76 +4744,76 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(3도움), 앙쿠_863246191(1도움), 앙쿠_848176580(1도움), 겐지간지_856237679(1도움), 겐지간지_852231443(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_814226161(1도움), 셀래스틴_852259694(1도움), 셀래스틴_846001551(1도움)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-27 08:02:59</t>
+          <t>2026-09-28 09:56:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>개포동덕배_856202126(1도움), 개포동덕배_863212622(2도움), 개포동덕배_848206113(1도움), 경남FC가즈아_805267825(1도움), 경남FC가즈아_853221467(1도움), 경남FC가즈아_518251161(1도움), 경남FC가즈아_830228007(1도움)</t>
+          <t>방덕_868009676(1도움), 방덕_827191189(1도움), 콩콩콩룔_848189505(3도움)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-27 07:50:56</t>
+          <t>2026-09-28 09:44:32</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4_0</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4007,61 +4823,61 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(2도움), 앙쿠_863246191(1도움), 앙쿠_848176580(1도움)</t>
+          <t>방덕_848007512(1도움), 방덕_868009676(3도움), 콩콩콩룔_867220502(1도움)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-27 07:47:08</t>
+          <t>2026-09-27 15:43:53</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Legend독수리_852229880(1도움), Legend독수리_839226764(2도움), Special블루_877001625(1도움), Special블루_863248148(1도움), Special블루_848230666(1도움)</t>
+          <t>UNIT_839013383(1도움), UNIT_840228251(1도움), UNIT_848180930(1도움), Voor_845247090(1도움), Voor_280206585(1도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-27 07:40:08</t>
+          <t>2026-09-27 15:26:14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4071,14 +4887,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>앙쿠_814226161(1도움), 앙쿠_863246191(1도움), 앙쿠_848176580(1도움)</t>
+          <t>UNIT_848180930(1도움), UNIT_840228251(2도움), Voor_845009676(1도움), Voor_835183277(2도움)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-26 20:23:39</t>
+          <t>2026-09-27 15:09:40</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4093,24 +4909,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>0_6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_840192883(3도움), Voor_845009676(1도움), Voor_845247090(1도움), Voor_856256079(1도움)</t>
+          <t>Voor_861000027(1도움), Voor_845239231(1도움)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-26 20:11:13</t>
+          <t>2026-09-27 14:57:41</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4125,7 +4941,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4135,29 +4951,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UNIT_829274967(1도움), UNIT_848180930(1도움), Voor_845247090(1도움), Voor_856256079(1도움), Voor_852233700(1도움)</t>
+          <t>UNIT_840210736(1도움), UNIT_848180930(2도움), Voor_856256079(1도움), Voor_845247090(1도움), Voor_835183277(1도움)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-26 19:59:04</t>
+          <t>2026-09-27 14:54:39</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4167,51 +4983,51 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_840225782(1도움), UNIT_867166676(1도움), Voor_845247090(2도움), Voor_852233700(1도움)</t>
+          <t>호야국2인_845201024(1도움), Gucci차붐_853272733(1도움), Gucci차붐_864084333(1도움)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-26 19:42:33</t>
+          <t>2026-09-27 14:43:34</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6_2</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UNIT_848135455(1도움), UNIT_840192883(2도움), UNIT_840228251(2도움), UNIT_840210736(1도움), Voor_856256079(1도움)</t>
+          <t>호야국2인_848227236(1도움), Gucci차붐_864247686(1도움), Gucci차붐_853272733(1도움), Gucci차붐_851221671(1도움), Gucci차붐_864084333(2도움)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-26 19:28:32</t>
+          <t>2026-09-27 14:37:29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4221,103 +5037,103 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7_8</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UNIT_840192883(2도움), UNIT_863250723(1도움), UNIT_840228251(1도움), UNIT_829274967(1도움), Voor_861000027(3도움), Voor_852233700(1도움), Voor_845009676(1도움), Voor_848216150(1도움), Voor_856256079(2도움)</t>
+          <t>피파왕초보구단주_851243057(1도움), 피파왕초보구단주_846045197(1도움), 피파왕초보구단주_846208722(1도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-26 14:04:42</t>
+          <t>2026-09-27 14:26:49</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>1_6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2도움), UNIT_840192883(1도움), UNIT_867166676(1도움), Special블루_848034079(2도움), Special블루_861001419(1도움)</t>
+          <t>Voor_845247090(1도움), Voor_856256079(1도움), Voor_852233700(3도움)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-26 13:54:24</t>
+          <t>2026-09-27 14:11:46</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_840210736(1도움), UNIT_867166676(2도움), Special블루_855241651(1도움), Special블루_848202652(1도움)</t>
+          <t>Voor_852233700(1도움), Voor_835183277(1도움)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-26 13:43:16</t>
+          <t>2026-09-27 14:08:17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4327,29 +5143,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UNIT_840210736(1도움), UNIT_840225782(1도움), UNIT_840228251(2도움), Special블루_848202652(1도움)</t>
+          <t>0708ManUtd_848238794(1도움), 0708ManUtd_868001397(1도움)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-26 13:32:03</t>
+          <t>2026-09-27 13:58:06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4359,93 +5175,93 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1도움), UNIT_848180930(1도움), UNIT_840192883(1도움), Special블루_848034079(1도움)</t>
+          <t>0708ManUtd_834239053(1도움), 0708ManUtd_834231281(1도움), 0708ManUtd_868037576(2도움)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-26 13:20:21</t>
+          <t>2026-09-27 13:41:37</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6_3</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>개포동덕배_845208722(2도움), 개포동덕배_856202126(1도움), 개포동덕배_848206113(1도움), 개포동덕배_866229558(1도움), Special블루_848034079(1도움), Special블루_851251805(2도움)</t>
+          <t>겐지간지_856237679(1도움), 피파왕초보구단주_846045197(1도움), 피파왕초보구단주_856209331(1도움), 피파왕초보구단주_846208722(1도움), 피파왕초보구단주_867000027(2도움)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-26 13:08:55</t>
+          <t>2026-09-27 13:29:35</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>1_8</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>개포동덕배_845208722(1도움), 개포동덕배_856202126(1도움), 개포동덕배_845190048(1도움), 개포동덕배_848206113(1도움), 개포동덕배_866229558(1도움), Special블루_855241651(1도움), Special블루_848034079(1도움), Special블루_856246669(1도움)</t>
+          <t>겐지간지_852241461(1도움), 피파왕초보구단주_861005661(1도움), 피파왕초보구단주_856209331(1도움), 피파왕초보구단주_846231281(2도움), 피파왕초보구단주_867000027(2도움), 피파왕초보구단주_846045197(1도움), 피파왕초보구단주_846208722(1도움)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-26 12:19:23</t>
+          <t>2026-09-27 11:36:34</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6_4</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4455,29 +5271,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(1도움), ZD장인지참치_839200104(2도움), ZD장인지참치_840253149(2도움), 셀래스틴_852259694(1도움), 셀래스틴_852241461(2도움), 셀래스틴_846001551(1도움)</t>
+          <t>개포동덕배_856275298(1도움), 개포동덕배_848206113(1도움), 개포동덕배_856202126(2도움), 개포동덕배_852225375(1도움), 개포동덕배_845208722(1도움), 여수가스_846001551(1도움)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-26 12:08:13</t>
+          <t>2026-09-27 11:24:41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4487,93 +5303,93 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
+          <t>개포동덕배_845208722(2도움), 개포동덕배_856202126(1도움), 개포동덕배_856275298(1도움), 개포동덕배_848206113(1도움), 개포동덕배_845190048(1도움), 여수가스_828231747(1도움), 여수가스_846001551(1도움)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-26 08:26:23</t>
+          <t>2026-09-27 10:09:38</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>오스트리아_851216275(1도움), Special블루_861001419(2도움)</t>
+          <t>개포동덕배_856202126(2도움), 개포동덕배_845208722(1도움), 개포동덕배_856275298(1도움), 아들러_291225126(1도움), 아들러_840208574(1도움), 아들러_852232730(1도움)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-25 15:57:51</t>
+          <t>2026-09-27 09:57:50</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Voor_835183277(1도움), Voor_852233700(1도움), Voor_856256079(1도움)</t>
+          <t>개포동덕배_845208722(1도움), 개포동덕배_863212622(2도움), 아들러_852232730(2도움)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-25 09:45:28</t>
+          <t>2026-09-27 09:29:41</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4583,152 +5399,152 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UNIT_840210736(1도움), UNIT_867166676(1도움), UNIT_840192883(1도움), 방덕_861077787(1도움), 방덕_856233096(1도움)</t>
+          <t>겐지간지_856237679(1도움), 겐지간지_852231443(1도움), 경남FC가즈아_853221467(2도움)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-25 09:33:41</t>
+          <t>2026-09-27 09:18:24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_840192883(1도움), UNIT_867166676(1도움), 방덕_848007512(1도움), 방덕_848231478(1도움)</t>
+          <t>겐지간지_856237679(1도움), 경남FC가즈아_853221467(2도움)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-25 09:22:20</t>
+          <t>2026-09-27 09:14:22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움), 방덕_848231478(2도움), 방덕_868009676(1도움)</t>
+          <t>아들러_861000570(1도움), 아들러_840208574(1도움), 아들러_866251377(1도움), 아들러_840221363(1도움), 아들러_855232639(1도움), Gucci와퍼_852010264(2도움), Gucci와퍼_852028765(1도움), Gucci와퍼_852168473(1도움)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-25 09:10:55</t>
+          <t>2026-09-27 09:00:07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), 방덕_868135455(1도움)</t>
+          <t>아들러_861000570(1도움), 아들러_840208574(1도움), 아들러_851244257(1도움), 아들러_291225126(1도움), Gucci와퍼_864200104(1도움)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-25 08:53:47</t>
+          <t>2026-09-27 08:20:21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2도움), 방덕_861077787(1도움), 방덕_868135455(1도움)</t>
+          <t>앙쿠_846186345(1도움), 앙쿠_846193747(1도움), 앙쿠_851194765(4도움), 겐지간지_852231443(1도움)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-25 08:42:15</t>
+          <t>2026-09-27 08:15:02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4743,14 +5559,14 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움), UNIT_829274967(1도움), 방덕_848007512(1도움), 방덕_867001040(1도움), 방덕_101001419(1도움)</t>
+          <t>개포동덕배_845190048(1도움), 개포동덕배_863212622(1도움), 경남FC가즈아_805207730(1도움), 경남FC가즈아_853221467(2도움)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-24 16:30:57</t>
+          <t>2026-09-27 08:08:47</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4760,12 +5576,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4775,46 +5591,46 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>앙쿠_846193747(1도움), 앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_840192883(1도움), UNIT_840225782(1도움)</t>
+          <t>앙쿠_851194765(3도움), 앙쿠_863246191(1도움), 앙쿠_848176580(1도움), 겐지간지_856237679(1도움), 겐지간지_852231443(1도움)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-24 16:14:16</t>
+          <t>2026-09-27 08:02:59</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_848135455(1도움), UNIT_863250723(1도움), UNIT_840216150(1도움), UNIT_840210736(1도움)</t>
+          <t>개포동덕배_856202126(1도움), 개포동덕배_863212622(2도움), 개포동덕배_848206113(1도움), 경남FC가즈아_805267825(1도움), 경남FC가즈아_853221467(1도움), 경남FC가즈아_518251161(1도움), 경남FC가즈아_830228007(1도움)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-24 15:57:54</t>
+          <t>2026-09-27 07:50:56</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4824,12 +5640,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4839,29 +5655,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(3도움), 앙쿠_848176580(1도움)</t>
+          <t>앙쿠_851194765(2도움), 앙쿠_863246191(1도움), 앙쿠_848176580(1도움)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-24 13:42:25</t>
+          <t>2026-09-27 07:47:08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4871,61 +5687,61 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UNIT_840210736(1도움), UNIT_840228251(1도움), UNIT_867166676(1도움)</t>
+          <t>Legend독수리_852229880(1도움), Legend독수리_839226764(2도움), Special블루_877001625(1도움), Special블루_863248148(1도움), Special블루_848230666(1도움)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-24 13:30:05</t>
+          <t>2026-09-27 07:40:08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>3_0</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), 셀래스틴_848230938(1도움), 셀래스틴_863277643(1도움), 셀래스틴_861142754(1도움)</t>
+          <t>앙쿠_814226161(1도움), 앙쿠_863246191(1도움), 앙쿠_848176580(1도움)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-24 09:29:12</t>
+          <t>2026-09-26 20:23:39</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4935,61 +5751,61 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>여수가스_845020289(1도움), 여수가스_828231747(1도움), 여수가스_868135455(1도움), 여수가스_846001551(1도움), ShangHaiPortFC_284190813(1도움), ShangHaiPortFC_861051412(1도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_840192883(3도움), Voor_845009676(1도움), Voor_845247090(1도움), Voor_856256079(1도움)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-24 09:16:26</t>
+          <t>2026-09-26 20:11:13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>여수가스_846001551(1도움), 여수가스_828231747(1도움), 여수가스_852274967(1도움), 여수가스_861162895(1도움), ShangHaiPortFC_845231138(1도움), ShangHaiPortFC_861051412(1도움)</t>
+          <t>UNIT_829274967(1도움), UNIT_848180930(1도움), Voor_845247090(1도움), Voor_856256079(1도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-24 08:18:47</t>
+          <t>2026-09-26 19:59:04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2_7</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4999,125 +5815,125 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>은안_856251517(1도움), 방덕_868135455(1도움), 방덕_848231478(1도움), 방덕_848007512(1도움), 방덕_861077787(2도움), 방덕_868009676(1도움), 방덕_856226268(1도움)</t>
+          <t>UNIT_848180930(1도움), UNIT_840225782(1도움), UNIT_867166676(1도움), Voor_845247090(2도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-24 08:06:58</t>
+          <t>2026-09-26 19:42:33</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>6_2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>은안_856246420(1도움), 은안_848231866(1도움), 방덕_861077787(1도움), 방덕_848007512(1도움)</t>
+          <t>UNIT_848135455(1도움), UNIT_840192883(2도움), UNIT_840228251(2도움), UNIT_840210736(1도움), Voor_856256079(1도움)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-24 04:51:33</t>
+          <t>2026-09-26 19:28:32</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>7_8</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ZD장인지참치_848210035(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_839200104(1도움), 용신_866200104(1도움)</t>
+          <t>UNIT_840192883(2도움), UNIT_863250723(1도움), UNIT_840228251(1도움), UNIT_829274967(1도움), Voor_861000027(3도움), Voor_852233700(1도움), Voor_845009676(1도움), Voor_848216150(1도움), Voor_856256079(2도움)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-24 04:40:44</t>
+          <t>2026-09-26 14:04:42</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4_5</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_851240740(1도움), 용신_863245367(2도움), 용신_273227535(1도움), 용신_848216267(1도움)</t>
+          <t>UNIT_848180930(2도움), UNIT_840192883(1도움), UNIT_867166676(1도움), Special블루_848034079(2도움), Special블루_861001419(1도움)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-24 04:19:09</t>
+          <t>2026-09-26 13:54:24</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4_4</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5127,42 +5943,46 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ZD장인지참치_861182521(2도움), ZD장인지참치_840256630(1도움), ZD장인지참치_851240740(1도움), 비주류중독_848006975(1도움), 비주류중독_839247699(1도움), 비주류중독_852253149(1도움)</t>
+          <t>UNIT_848180930(1도움), UNIT_840210736(1도움), UNIT_867166676(2도움), Special블루_855241651(1도움), Special블루_848202652(1도움)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-24 04:02:44</t>
+          <t>2026-09-26 13:43:16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>UNIT_840210736(1도움), UNIT_840225782(1도움), UNIT_840228251(2도움), Special블루_848202652(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-24 03:45:56</t>
+          <t>2026-09-26 13:32:03</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5172,12 +5992,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5187,93 +6007,93 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_840225782(1도움), UNIT_848135455(1도움), UNIT_848180930(1도움), UNIT_840192883(1도움), ZD장인지참치_848210035(1도움), ZD장인지참치_839200104(2도움)</t>
+          <t>UNIT_867166676(1도움), UNIT_848180930(1도움), UNIT_840192883(1도움), Special블루_848034079(1도움)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-24 02:48:31</t>
+          <t>2026-09-26 13:20:21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3_5</t>
+          <t>6_3</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>여수가스_861162895(1도움), 여수가스_868135455(1도움), 방덕_868009676(1도움), 방덕_101001419(1도움), 방덕_863184200(1도움), 방덕_867001040(1도움)</t>
+          <t>개포동덕배_845208722(2도움), 개포동덕배_856202126(1도움), 개포동덕배_848206113(1도움), 개포동덕배_866229558(1도움), Special블루_848034079(1도움), Special블루_851251805(2도움)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-23 17:59:32</t>
+          <t>2026-09-26 13:08:55</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0708ManUtd_834239053(1도움), 0708ManUtd_868001397(1도움), 여수가스_868135455(1도움), 여수가스_828231747(1도움), 여수가스_845020289(1도움)</t>
+          <t>개포동덕배_845208722(1도움), 개포동덕배_856202126(1도움), 개포동덕배_845190048(1도움), 개포동덕배_848206113(1도움), 개포동덕배_866229558(1도움), Special블루_855241651(1도움), Special블루_848034079(1도움), Special블루_856246669(1도움)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-23 17:47:25</t>
+          <t>2026-09-26 12:19:23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>6_4</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5283,19 +6103,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0708ManUtd_834239053(1도움), 0708ManUtd_868001397(1도움), 0708ManUtd_851226161(1도움), 0708ManUtd_848238794(1도움), 여수가스_861162895(1도움), 여수가스_828231747(1도움)</t>
+          <t>ZD장인지참치_840191208(1도움), ZD장인지참치_839200104(2도움), ZD장인지참치_840253149(2도움), 셀래스틴_852259694(1도움), 셀래스틴_852241461(2도움), 셀래스틴_846001551(1도움)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-23 13:33:47</t>
+          <t>2026-09-26 12:08:13</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5305,135 +6125,135 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), 셀래스틴_863251854(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-23 13:23:09</t>
+          <t>2026-09-26 08:26:23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>오스트리아</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1_0</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움)</t>
+          <t>오스트리아_851216275(1도움), Special블루_861001419(2도움)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-23 13:08:58</t>
+          <t>2026-09-25 15:57:51</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>0_3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(3도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
+          <t>Voor_835183277(1도움), Voor_852233700(1도움), Voor_856256079(1도움)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-23 12:58:26</t>
+          <t>2026-09-25 09:45:28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_839200104(1도움)</t>
+          <t>UNIT_840210736(1도움), UNIT_867166676(1도움), UNIT_840192883(1도움), 방덕_861077787(1도움), 방덕_856233096(1도움)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-23 12:28:11</t>
+          <t>2026-09-25 09:33:41</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5443,29 +6263,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0708ManUtd_851226161(2도움), 0708ManUtd_848238794(2도움), 0708ManUtd_868001397(1도움), 겐지간지_856237679(1도움)</t>
+          <t>UNIT_848180930(1도움), UNIT_840192883(1도움), UNIT_867166676(1도움), 방덕_848007512(1도움), 방덕_848231478(1도움)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-23 12:19:39</t>
+          <t>2026-09-25 09:22:20</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5475,125 +6295,125 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>아들러_814192318(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_848210035(1도움), ZD장인지참치_840191208(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_848199503(1도움)</t>
+          <t>UNIT_840192883(1도움), 방덕_848231478(2도움), 방덕_868009676(1도움)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-23 12:19:35</t>
+          <t>2026-09-25 09:10:55</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>경남FC가즈아_853221467(2도움), 콩콩콩룔_867223848(2도움)</t>
+          <t>UNIT_840228251(1도움), 방덕_868135455(1도움)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-23 12:15:41</t>
+          <t>2026-09-25 08:53:47</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0708ManUtd_868001397(2도움), 0708ManUtd_848037576(1도움), 0708ManUtd_851226161(1도움), 겐지간지_861001668(1도움), 겐지간지_826247635(1도움), 겐지간지_852231443(1도움)</t>
+          <t>UNIT_867166676(2도움), 방덕_861077787(1도움), 방덕_868135455(1도움)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-23 12:07:26</t>
+          <t>2026-09-25 08:42:15</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>아들러_855232639(2도움), 아들러_861000570(1도움), 아들러_840191208(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_861182521(2도움)</t>
+          <t>UNIT_840192883(1도움), UNIT_829274967(1도움), 방덕_848007512(1도움), 방덕_867001040(1도움), 방덕_101001419(1도움)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-23 12:05:58</t>
+          <t>2026-09-24 16:30:57</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5603,29 +6423,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>경남FC가즈아_277205156(1도움), 경남FC가즈아_518251161(1도움), 콩콩콩룔_851236496(1도움)</t>
+          <t>앙쿠_846193747(1도움), 앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_840192883(1도움), UNIT_840225782(1도움)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-23 11:53:57</t>
+          <t>2026-09-24 16:14:16</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5635,29 +6455,29 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>아들러_861000570(2도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_848135455(1도움), UNIT_863250723(1도움), UNIT_840216150(1도움), UNIT_840210736(1도움)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-23 11:42:25</t>
+          <t>2026-09-24 15:57:54</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5_0</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5667,61 +6487,61 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>아들러_866251377(1도움), 아들러_855232639(1도움), 아들러_840191208(1도움), 아들러_840208574(1도움)</t>
+          <t>앙쿠_851194765(3도움), 앙쿠_848176580(1도움)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-23 11:29:03</t>
+          <t>2026-09-24 13:42:25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(1도움), 아들러_840191208(1도움), 아들러_852232730(1도움)</t>
+          <t>UNIT_840210736(1도움), UNIT_840228251(1도움), UNIT_867166676(1도움)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-23 10:27:43</t>
+          <t>2026-09-24 13:30:05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5731,61 +6551,61 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>아들러_866251377(1도움), 아들러_852232730(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_866223710(1도움), 콩콩콩룔_861006235(1도움)</t>
+          <t>UNIT_840228251(1도움), 셀래스틴_848230938(1도움), 셀래스틴_863277643(1도움), 셀래스틴_861142754(1도움)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-23 10:15:56</t>
+          <t>2026-09-24 09:29:12</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>아들러_291225126(2도움), 콩콩콩룔_867220502(1도움)</t>
+          <t>여수가스_845020289(1도움), 여수가스_828231747(1도움), 여수가스_868135455(1도움), 여수가스_846001551(1도움), ShangHaiPortFC_284190813(1도움), ShangHaiPortFC_861051412(1도움)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-23 08:46:09</t>
+          <t>2026-09-24 09:16:26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5795,69 +6615,897 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>오스트리아_864182152(1도움), 겐지간지_826247635(1도움)</t>
+          <t>여수가스_846001551(1도움), 여수가스_828231747(1도움), 여수가스_852274967(1도움), 여수가스_861162895(1도움), ShangHaiPortFC_845231138(1도움), ShangHaiPortFC_861051412(1도움)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-23 08:35:42</t>
+          <t>2026-09-24 08:18:47</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_7</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(2도움), 겐지간지_814231747(1도움)</t>
+          <t>은안_856251517(1도움), 방덕_868135455(1도움), 방덕_848231478(1도움), 방덕_848007512(1도움), 방덕_861077787(2도움), 방덕_868009676(1도움), 방덕_856226268(1도움)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>2026-09-24 08:06:58</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>은안</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>은안_856246420(1도움), 은안_848231866(1도움), 방덕_861077787(1도움), 방덕_848007512(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:51:33</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_848210035(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_839200104(1도움), 용신_866200104(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:40:44</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>4_5</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_851240740(1도움), 용신_863245367(2도움), 용신_273227535(1도움), 용신_848216267(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:19:09</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>4_4</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_861182521(2도움), ZD장인지참치_840256630(1도움), ZD장인지참치_851240740(1도움), 비주류중독_848006975(1도움), 비주류중독_839247699(1도움), 비주류중독_852253149(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:02:44</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>0_0</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-24 03:45:56</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>5_3</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>UNIT_840228251(1도움), UNIT_840225782(1도움), UNIT_848135455(1도움), UNIT_848180930(1도움), UNIT_840192883(1도움), ZD장인지참치_848210035(1도움), ZD장인지참치_839200104(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-24 02:48:31</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3_5</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>여수가스_861162895(1도움), 여수가스_868135455(1도움), 방덕_868009676(1도움), 방덕_101001419(1도움), 방덕_863184200(1도움), 방덕_867001040(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:59:32</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0708ManUtd_834239053(1도움), 0708ManUtd_868001397(1도움), 여수가스_868135455(1도움), 여수가스_828231747(1도움), 여수가스_845020289(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:47:25</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>여수가스</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0708ManUtd_834239053(1도움), 0708ManUtd_868001397(1도움), 0708ManUtd_851226161(1도움), 0708ManUtd_848238794(1도움), 여수가스_861162895(1도움), 여수가스_828231747(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:33:47</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), 셀래스틴_863251854(1도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:23:09</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1_0</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>앙쿠_856247103(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:08:58</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(3도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:58:26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_839200104(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:28:11</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>6_2</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0708ManUtd_851226161(2도움), 0708ManUtd_848238794(2도움), 0708ManUtd_868001397(1도움), 겐지간지_856237679(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:19:39</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>1_5</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>아들러_814192318(1도움), ZD장인지참치_861182521(1도움), ZD장인지참치_848210035(1도움), ZD장인지참치_840191208(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_848199503(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:19:35</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_853221467(2도움), 콩콩콩룔_867223848(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:15:41</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0708ManUtd_868001397(2도움), 0708ManUtd_848037576(1도움), 0708ManUtd_851226161(1도움), 겐지간지_861001668(1도움), 겐지간지_826247635(1도움), 겐지간지_852231443(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:07:26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>5_4</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>아들러_855232639(2도움), 아들러_861000570(1도움), 아들러_840191208(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_861182521(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:05:58</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_277205156(1도움), 경남FC가즈아_518251161(1도움), 콩콩콩룔_851236496(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:53:57</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>아들러_861000570(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:42:25</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>5_0</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>아들러_866251377(1도움), 아들러_855232639(1도움), 아들러_840191208(1도움), 아들러_840208574(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:29:03</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>앙쿠_863246191(1도움), 아들러_840191208(1도움), 아들러_852232730(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:27:43</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>아들러_866251377(1도움), 아들러_852232730(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_866223710(1도움), 콩콩콩룔_861006235(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:15:56</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>아들러_291225126(2도움), 콩콩콩룔_867220502(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:46:09</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>오스트리아_864182152(1도움), 겐지간지_826247635(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:35:42</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(2도움), 겐지간지_814231747(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
           <t>2026-09-22 14:15:38</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>셀래스틴</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>1_2</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>UNIT_840192883(1도움), 셀래스틴_852277643(1도움), 셀래스틴_852241461(1도움)</t>
         </is>

--- a/API데이터_경기_득점_및_도움_기록.xlsx
+++ b/API데이터_경기_득점_및_도움_기록.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,22 +452,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:16:03</t>
+          <t>2026-10-01 07:54:09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -477,29 +477,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>개포동덕배_848206113(1골), 개포동덕배_845208722(1골), 개포동덕배_856202126(1골), 개포동덕배_845190048(4골), Gucci차붐_864247686(1골), Gucci차붐_864176403(1골)</t>
+          <t>호야국2인_851261865(1골), 호야국2인_846192505(1골), 호야국2인_848232293(1골), 아들러_861000570(1골), 아들러_840191208(1골)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29 14:04:54</t>
+          <t>2026-10-01 07:42:04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -509,61 +509,61 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(3골), 개포동덕배_848206113(1골), Gucci차붐_853272733(1골), Gucci차붐_853242004(1골)</t>
+          <t>호야국2인_848227236(2골), 호야국2인_848232293(1골), 호야국2인_848216435(1골), 호야국2인_851216409(1골), 아들러_291225126(1골), 아들러_866251377(1골)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29 11:20:02</t>
+          <t>2026-10-01 06:47:50</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(2골)</t>
+          <t>호야국2인_845198219(1골), 호야국2인_848232293(2골), 호야국2인_848216435(1골), suma수마_861190046(1골), suma수마_861221162(1골)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29 11:08:25</t>
+          <t>2026-10-01 06:36:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -573,46 +573,46 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_848135455(1골), UNIT_867166676(1골), 콩콩콩룔_866223710(1골), 콩콩콩룔_867223848(1골)</t>
+          <t>호야국2인_851216409(1골), 호야국2인_845198219(1골), 호야국2인_846192505(1골), 호야국2인_848227236(1골), 호야국2인_848232293(1골), suma수마_861013383(1골), suma수마_861221162(1골)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29 10:56:21</t>
+          <t>2026-09-30 17:45:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7_1</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(3골), 오스트리아_851221671(1골), 오스트리아_864182152(1골), 오스트리아_864140057(1골), 오스트리아_851216275(1골), ShangHaiPortFC_864191910(1골)</t>
+          <t>UNIT_867166676(2골), Voor_845009676(1골), Voor_835183277(1골), Voor_852233700(3골)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-29 10:47:10</t>
+          <t>2026-09-30 17:34:22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -622,44 +622,44 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1골), UNIT_867166676(2골), 셀래스틴_848231866(1골), 셀래스틴_848230938(1골)</t>
+          <t>UNIT_848180930(2골), UNIT_840192883(1골), Voor_845009676(1골), Voor_856256079(1골), Voor_852233700(2골)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-29 10:45:30</t>
+          <t>2026-09-30 17:17:18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -669,14 +669,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(2골), 오스트리아_864182152(1골), 오스트리아_864199266(2골), ShangHaiPortFC_861051412(1골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(2골), Voor_852233700(2골)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-29 10:35:32</t>
+          <t>2026-09-30 17:03:54</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -686,29 +686,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), 셀래스틴_846001551(1골), 셀래스틴_852241461(2골)</t>
+          <t>UNIT_867166676(5골), Voor_845009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29 10:18:25</t>
+          <t>2026-09-30 16:46:35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -718,34 +718,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), 셀래스틴_848194765(1골)</t>
+          <t>UNIT_848180930(2골), Voor_845009676(1골), Voor_852233700(2골)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-29 09:24:43</t>
+          <t>2026-09-30 14:01:02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -765,19 +765,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(1골), 오스트리아_851236636(1골), 셀래스틴_846001551(1골), 셀래스틴_861005680(1골), 셀래스틴_848230938(1골)</t>
+          <t>UNIT_861221162(2골), 셀래스틴_861005680(4골), 셀래스틴_848231866(1골)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-29 09:13:08</t>
+          <t>2026-09-30 13:49:10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -787,29 +787,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(1골), 셀래스틴_861005680(1골)</t>
+          <t>UNIT_867166676(3골), UNIT_861221162(2골), 셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-29 09:02:47</t>
+          <t>2026-09-30 13:33:10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -819,79 +819,911 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(1골), 오스트리아_864199266(1골), 오스트리아_864182152(1골), 셀래스틴_861005680(1골)</t>
+          <t>UNIT_848180930(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(3골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-29 08:51:25</t>
+          <t>2026-09-30 13:24:44</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0_2</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>셀래스틴_846001551(1골), 셀래스틴_861005680(1골)</t>
+          <t>Gucci와퍼_864200104(4골), 비주류중독_840052241(1골), 비주류중독_825000240(1골), 비주류중독_839247699(1골)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>2026-09-30 13:21:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), UNIT_867166676(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:12:24</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gucci와퍼_852028765(1골), Gucci와퍼_852168473(1골), 비주류중독_834239977(1골), 비주류중독_840052241(1골), 비주류중독_839247699(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:10:05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(3골), UNIT_840192883(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:57:48</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), UNIT_848180930(1골), 셀래스틴_846001551(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:35:39</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 비주류중독_848006975(2골), 비주류중독_839247699(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:24:21</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:00:21</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(2골), 셀래스틴_861005680(2골), 셀래스틴_852241461(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:47:20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3_4</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>방덕_848007512(1골), 방덕_856228093(1골), 방덕_863184200(1골), Voor_845247090(2골), Voor_852233700(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:35:39</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1_6</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>방덕_101001419(1골), Voor_852233700(3골), Voor_845009676(2골), Voor_845247090(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:27:58</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Legend독수리_825190048(1골), Legend독수리_861081644(1골), Legend독수리_848188350(1골), syma_863228092(1골), syma_856233848(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:16:55</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1_6</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Legend독수리_825190048(1골), syma_866231913(1골), syma_863262863(1골), syma_846001845(3골), syma_852274967(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:04:48</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1골), Legend독수리_852209658(1골), syma_866231913(1골), syma_863228092(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-30 07:53:20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1골), syma_863222665(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:16:03</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>7_2</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>개포동덕배_848206113(1골), 개포동덕배_845208722(1골), 개포동덕배_856202126(1골), 개포동덕배_845190048(4골), Gucci차붐_864247686(1골), Gucci차붐_864176403(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:04:54</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>개포동덕배_845190048(3골), 개포동덕배_848206113(1골), Gucci차붐_853272733(1골), Gucci차붐_853242004(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:20:02</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:08:25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), UNIT_848135455(1골), UNIT_867166676(1골), 콩콩콩룔_866223710(1골), 콩콩콩룔_867223848(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:56:21</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>7_1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(3골), 오스트리아_851221671(1골), 오스트리아_864182152(1골), 오스트리아_864140057(1골), 오스트리아_851216275(1골), ShangHaiPortFC_864191910(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:47:10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>UNIT_840228251(1골), UNIT_867166676(2골), 셀래스틴_848231866(1골), 셀래스틴_848230938(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:45:30</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(2골), 오스트리아_864182152(1골), 오스트리아_864199266(2골), ShangHaiPortFC_861051412(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:35:32</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), 셀래스틴_846001551(1골), 셀래스틴_852241461(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:18:25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), 셀래스틴_848194765(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:24:43</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(1골), 오스트리아_851236636(1골), 셀래스틴_846001551(1골), 셀래스틴_861005680(1골), 셀래스틴_848230938(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:13:08</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:02:47</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(1골), 오스트리아_864199266(1골), 오스트리아_864182152(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-29 08:51:25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0_2</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>셀래스틴_846001551(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>2026-09-29 04:33:11</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>여수가스</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>오스트리아</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>2_3</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>여수가스_828231747(1골), 여수가스_852274967(1골), 오스트리아_864191566(1골), 오스트리아_864199266(2골)</t>
         </is>
@@ -908,7 +1740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,22 +1778,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:16:03</t>
+          <t>2026-10-01 07:54:09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -971,29 +1803,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>개포동덕배_848206113(1도움), 개포동덕배_845208722(3도움), 개포동덕배_856202126(1도움), 개포동덕배_863212622(2도움), Gucci차붐_853272733(1도움), Gucci차붐_864176403(1도움)</t>
+          <t>호야국2인_848227236(2도움), 호야국2인_848232293(1도움), 아들러_866251377(1도움), 아들러_855232639(1도움)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29 14:04:54</t>
+          <t>2026-10-01 07:42:04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1003,61 +1835,61 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>개포동덕배_856202126(1도움), 개포동덕배_863234396(1도움), 개포동덕배_856275298(1도움), 개포동덕배_848206113(1도움), Gucci차붐_864084333(1도움), Gucci차붐_864247686(1도움)</t>
+          <t>호야국2인_848232293(2도움), 호야국2인_848217870(1도움), 호야국2인_851216409(1도움), 아들러_840191208(1도움)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29 11:20:02</t>
+          <t>2026-10-01 06:47:50</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(2도움)</t>
+          <t>호야국2인_848217870(1도움), 호야국2인_848232293(1도움), 호야국2인_852001183(1도움), suma수마_861190046(1도움), suma수마_848225439(1도움)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29 11:08:25</t>
+          <t>2026-10-01 06:36:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1067,46 +1899,46 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UNIT_840192883(2도움), UNIT_848265695(1도움), 콩콩콩룔_851236496(1도움)</t>
+          <t>호야국2인_851216409(1도움), 호야국2인_845198219(1도움), 호야국2인_846192505(1도움), 호야국2인_848216435(1도움), suma수마_826223697(1도움)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29 10:56:21</t>
+          <t>2026-09-30 17:45:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7_1</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>오스트리아_864182152(2도움), 오스트리아_864140057(1도움), 오스트리아_851236636(4도움), ShangHaiPortFC_848031432(1도움)</t>
+          <t>UNIT_840192883(1도움), Voor_856256079(1도움), Voor_861000027(4도움)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-29 10:47:10</t>
+          <t>2026-09-30 17:34:22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1116,44 +1948,44 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_863250723(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+          <t>UNIT_861221162(1도움), UNIT_866247257(1도움), UNIT_840228251(1도움), Voor_845009676(1도움), Voor_858025420(1도움), Voor_835183277(1도움)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-29 10:45:30</t>
+          <t>2026-09-30 17:17:18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1163,14 +1995,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>오스트리아_851221671(1도움), 오스트리아_863223671(1도움), 오스트리아_863240709(1도움), 오스트리아_864140057(1도움), 오스트리아_851216275(1도움), ShangHaiPortFC_827143001(1도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), UNIT_848135455(1도움), Voor_845239231(1도움), Voor_845009676(1도움)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-29 10:35:32</t>
+          <t>2026-09-30 17:03:54</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1180,29 +2012,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1도움), 셀래스틴_848231866(2도움), 셀래스틴_852241461(1도움)</t>
+          <t>UNIT_848180930(1도움), UNIT_840192883(1도움), UNIT_848265695(3도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29 10:18:25</t>
+          <t>2026-09-30 16:46:35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1212,34 +2044,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UNIT_839013383(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), Voor_845009676(1도움), Voor_846184943(1도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-29 09:24:43</t>
+          <t>2026-09-30 14:01:02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1249,7 +2081,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1259,19 +2091,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(1도움), 오스트리아_863240709(1도움), 셀래스틴_846001551(1도움), 셀래스틴_848194765(2도움)</t>
+          <t>UNIT_867166676(2도움), 셀래스틴_848194765(1도움), 셀래스틴_848231866(1도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-29 09:13:08</t>
+          <t>2026-09-30 13:49:10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1281,29 +2113,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>오스트리아_851221671(1도움), 셀래스틴_848231866(1도움)</t>
+          <t>UNIT_840210736(2도움), UNIT_867166676(1도움), UNIT_848135455(1도움), UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852241461(2도움)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-29 09:02:47</t>
+          <t>2026-09-30 13:33:10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1313,79 +2145,911 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(1도움), 오스트리아_864182152(1도움), 오스트리아_851236636(1도움), 셀래스틴_846001551(1도움)</t>
+          <t>UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852259694(1도움), 셀래스틴_861005680(1도움)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-29 08:51:25</t>
+          <t>2026-09-30 13:24:44</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0_2</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>셀래스틴_863200458(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>Gucci와퍼_852168473(3도움), Gucci와퍼_852028765(1도움), 비주류중독_840052241(1도움), 비주류중독_862180283(1도움)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>2026-09-30 13:21:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(1도움), UNIT_840228251(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:12:24</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gucci와퍼_852010264(1도움), 비주류중독_834239977(1도움), 비주류중독_848006975(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:10:05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1도움), UNIT_840192883(2도움), UNIT_840225782(1도움), 셀래스틴_848194765(1도움), 셀래스틴_863200458(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:57:48</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UNIT_863250723(1도움), UNIT_840228251(2도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:35:39</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>셀래스틴_848231866(1도움), 셀래스틴_852259694(1도움), 비주류중독_839247699(1도움), 비주류중독_834239977(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:24:21</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>셀래스틴_852259694(1도움), 셀래스틴_848194765(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:00:21</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>UNIT_840225782(1도움), UNIT_867166676(1도움), 셀래스틴_848013038(1도움), 셀래스틴_852241461(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:47:20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3_4</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>방덕_867001040(1도움), 방덕_848231478(2도움), Voor_845009676(1도움), Voor_845239231(1도움), Voor_835183277(1도움), Voor_848216150(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:35:39</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1_6</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Voor_852233700(2도움), Voor_856256079(1도움), Voor_845009676(2도움), Voor_835183277(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:27:58</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1도움), Legend독수리_852209658(1도움), syma_852274967(1도움), syma_863228092(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:16:55</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1_6</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1도움), syma_866231913(2도움), syma_863222665(4도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:04:48</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Legend독수리_848224425(1도움), Legend독수리_826236703(1도움), syma_856233848(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-30 07:53:20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Legend독수리_861081644(1도움), syma_846001845(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:16:03</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>7_2</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>개포동덕배_848206113(1도움), 개포동덕배_845208722(3도움), 개포동덕배_856202126(1도움), 개포동덕배_863212622(2도움), Gucci차붐_853272733(1도움), Gucci차붐_864176403(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:04:54</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>개포동덕배_856202126(1도움), 개포동덕배_863234396(1도움), 개포동덕배_856275298(1도움), 개포동덕배_848206113(1도움), Gucci차붐_864084333(1도움), Gucci차붐_864247686(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:20:02</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:08:25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(2도움), UNIT_848265695(1도움), 콩콩콩룔_851236496(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:56:21</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>7_1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>오스트리아_864182152(2도움), 오스트리아_864140057(1도움), 오스트리아_851236636(4도움), ShangHaiPortFC_848031432(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:47:10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1도움), UNIT_863250723(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:45:30</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>오스트리아_851221671(1도움), 오스트리아_863223671(1도움), 오스트리아_863240709(1도움), 오스트리아_864140057(1도움), 오스트리아_851216275(1도움), ShangHaiPortFC_827143001(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:35:32</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1도움), 셀래스틴_848231866(2도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:18:25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>UNIT_839013383(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:24:43</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(1도움), 오스트리아_863240709(1도움), 셀래스틴_846001551(1도움), 셀래스틴_848194765(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:13:08</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>오스트리아_851221671(1도움), 셀래스틴_848231866(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:02:47</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(1도움), 오스트리아_864182152(1도움), 오스트리아_851236636(1도움), 셀래스틴_846001551(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-29 08:51:25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0_2</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>셀래스틴_863200458(1도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>2026-09-29 04:33:11</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>여수가스</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>오스트리아</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>2_3</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>여수가스_852216393(1도움), 여수가스_861162895(1도움), 오스트리아_864140057(1도움), 오스트리아_851257075(1도움)</t>
         </is>

--- a/API데이터_경기_득점_및_도움_기록.xlsx
+++ b/API데이터_경기_득점_및_도움_기록.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,86 +452,86 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01 07:54:09</t>
+          <t>2026-10-01 15:50:18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>호야국2인_851261865(1골), 호야국2인_846192505(1골), 호야국2인_848232293(1골), 아들러_861000570(1골), 아들러_840191208(1골)</t>
+          <t>suma수마_861190046(1골), 피파왕초보구단주_861005661(3골)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01 07:42:04</t>
+          <t>2026-10-01 15:38:48</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>호야국2인_848227236(2골), 호야국2인_848232293(1골), 호야국2인_848216435(1골), 호야국2인_851216409(1골), 아들러_291225126(1골), 아들러_866251377(1골)</t>
+          <t>suma수마_861221162(1골), suma수마_861013383(1골), 피파왕초보구단주_846208722(1골), 피파왕초보구단주_856209331(1골)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01 06:47:50</t>
+          <t>2026-10-01 15:24:08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -541,61 +541,61 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>호야국2인_845198219(1골), 호야국2인_848232293(2골), 호야국2인_848216435(1골), suma수마_861190046(1골), suma수마_861221162(1골)</t>
+          <t>피파왕초보구단주_846208722(2골), 피파왕초보구단주_867000027(2골), 피파왕초보구단주_861005661(1골), Gucci와퍼_852208128(1골)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-01 06:36:26</t>
+          <t>2026-10-01 15:12:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>호야국2인_851216409(1골), 호야국2인_845198219(1골), 호야국2인_846192505(1골), 호야국2인_848227236(1골), 호야국2인_848232293(1골), suma수마_861013383(1골), suma수마_861221162(1골)</t>
+          <t>피파왕초보구단주_848209499(1골), 피파왕초보구단주_861005661(2골), Gucci와퍼_840208574(1골), Gucci와퍼_864200104(2골)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-30 17:45:59</t>
+          <t>2026-10-01 14:56:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -605,29 +605,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), Voor_845009676(1골), Voor_835183277(1골), Voor_852233700(3골)</t>
+          <t>0708ManUtd_848238794(1골), 호야국2인_848227236(1골), 호야국2인_848232293(1골)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-30 17:34:22</t>
+          <t>2026-10-01 14:51:31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -637,61 +637,61 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), UNIT_840192883(1골), Voor_845009676(1골), Voor_856256079(1골), Voor_852233700(2골)</t>
+          <t>은안_852237692(1골), Gucci와퍼_852028765(1골), Gucci와퍼_852010264(1골), Gucci와퍼_864200104(2골)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-30 17:17:18</t>
+          <t>2026-10-01 14:45:02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), UNIT_848180930(2골), Voor_852233700(2골)</t>
+          <t>0708ManUtd_868037576(1골), 0708ManUtd_834239053(1골), 호야국2인_851216409(1골), 호야국2인_848232293(1골), 호야국2인_846192505(1골)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-30 17:03:54</t>
+          <t>2026-10-01 14:39:52</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -701,61 +701,61 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UNIT_867166676(5골), Voor_845009676(1골)</t>
+          <t>은안_877143001(3골), 은안_866241236(1골), Gucci와퍼_864200104(1골)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-30 16:46:35</t>
+          <t>2026-10-01 14:31:32</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), Voor_845009676(1골), Voor_852233700(2골)</t>
+          <t>호야국2인_848232293(2골), 호야국2인_851216409(1골), Special블루_868001419(1골), Special블루_861047390(1골), Special블루_856246669(1골)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-30 14:01:02</t>
+          <t>2026-10-01 14:21:07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -765,29 +765,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UNIT_861221162(2골), 셀래스틴_861005680(4골), 셀래스틴_848231866(1골)</t>
+          <t>호야국2인_848232293(1골), Special블루_851251566(1골), Special블루_877001625(1골), Special블루_868001419(1골)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-30 13:49:10</t>
+          <t>2026-10-01 14:08:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -797,24 +797,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UNIT_867166676(3골), UNIT_861221162(2골), 셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
+          <t>호야국2인_846192505(3골), 비주류중독_840052241(2골)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-30 13:33:10</t>
+          <t>2026-10-01 13:58:38</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -829,19 +829,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(3골), 셀래스틴_852241461(1골)</t>
+          <t>호야국2인_848232293(1골), 비주류중독_829203376(1골), 비주류중독_839247699(3골), 비주류중독_840052241(1골)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:44</t>
+          <t>2026-10-01 13:48:03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -851,66 +851,62 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Gucci와퍼_864200104(4골), 비주류중독_840052241(1골), 비주류중독_825000240(1골), 비주류중독_839247699(1골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-30 13:21:00</t>
+          <t>2026-10-01 13:34:35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_867166676(1골)</t>
+          <t>아들러_861000570(1골), Special블루_877001625(1골), Special블루_848230666(1골)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-30 13:12:24</t>
+          <t>2026-10-01 13:24:02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -925,29 +921,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gucci와퍼_852028765(1골), Gucci와퍼_852168473(1골), 비주류중독_834239977(1골), 비주류중독_840052241(1골), 비주류중독_839247699(1골)</t>
+          <t>아들러_855232639(2골), Special블루_868001419(1골), Special블루_877001625(2골)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-30 13:10:05</t>
+          <t>2026-10-01 13:13:07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>7_0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -957,221 +953,213 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UNIT_867166676(3골), UNIT_840192883(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(2골)</t>
+          <t>앙쿠_863246191(4골), 앙쿠_851194765(2골), 앙쿠_856247103(1골)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-30 12:57:48</t>
+          <t>2026-10-01 13:02:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>UNIT_867166676(2골), UNIT_848180930(1골), 셀래스틴_846001551(1골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:39</t>
+          <t>2026-10-01 13:01:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 비주류중독_848006975(2골), 비주류중독_839247699(1골)</t>
+          <t>앙쿠_848176580(1골), syma_867192629(1골)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-30 12:24:21</t>
+          <t>2026-10-01 12:49:37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-30 12:00:21</t>
+          <t>2026-10-01 11:22:46</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), 셀래스틴_861005680(2골), 셀래스틴_852241461(1골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_863246191(2골)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-30 09:47:20</t>
+          <t>2026-10-01 11:15:46</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>방덕_848007512(1골), 방덕_856228093(1골), 방덕_863184200(1골), Voor_845247090(2골), Voor_852233700(2골)</t>
+          <t>suma수마_861190046(1골), suma수마_861221162(3골), suma수마_845192190(1골), 겐지간지_848170890(1골)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-30 09:35:39</t>
+          <t>2026-10-01 11:12:19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>방덕_101001419(1골), Voor_852233700(3골), Voor_845009676(2골), Voor_845247090(1골)</t>
+          <t>앙쿠_814226161(1골), 앙쿠_848176580(2골), Gucci차붐_840191208(1골)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-30 08:27:58</t>
+          <t>2026-10-01 11:03:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1181,125 +1169,125 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Legend독수리_825190048(1골), Legend독수리_861081644(1골), Legend독수리_848188350(1골), syma_863228092(1골), syma_856233848(1골)</t>
+          <t>suma수마_861190046(2골), suma수마_861221162(1골), suma수마_840001114(2골), 겐지간지_814231747(1골), 겐지간지_852241461(1골), 겐지간지_856237679(1골)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-30 08:16:55</t>
+          <t>2026-10-01 07:54:09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Legend독수리_825190048(1골), syma_866231913(1골), syma_863262863(1골), syma_846001845(3골), syma_852274967(1골)</t>
+          <t>호야국2인_851261865(1골), 호야국2인_846192505(1골), 호야국2인_848232293(1골), 아들러_861000570(1골), 아들러_840191208(1골)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-30 08:04:48</t>
+          <t>2026-10-01 07:42:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Legend독수리_861215732(1골), Legend독수리_852209658(1골), syma_866231913(1골), syma_863228092(1골)</t>
+          <t>호야국2인_848227236(2골), 호야국2인_848232293(1골), 호야국2인_848216435(1골), 호야국2인_851216409(1골), 아들러_291225126(1골), 아들러_866251377(1골)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-30 07:53:20</t>
+          <t>2026-10-01 06:47:50</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Legend독수리_861215732(1골), syma_863222665(2골)</t>
+          <t>호야국2인_845198219(1골), 호야국2인_848232293(2골), 호야국2인_848216435(1골), suma수마_861190046(1골), suma수마_861221162(1골)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-29 14:16:03</t>
+          <t>2026-10-01 06:36:26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1309,46 +1297,46 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>개포동덕배_848206113(1골), 개포동덕배_845208722(1골), 개포동덕배_856202126(1골), 개포동덕배_845190048(4골), Gucci차붐_864247686(1골), Gucci차붐_864176403(1골)</t>
+          <t>호야국2인_851216409(1골), 호야국2인_845198219(1골), 호야국2인_846192505(1골), 호야국2인_848227236(1골), 호야국2인_848232293(1골), suma수마_861013383(1골), suma수마_861221162(1골)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-29 14:04:54</t>
+          <t>2026-09-30 17:45:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(3골), 개포동덕배_848206113(1골), Gucci차붐_853272733(1골), Gucci차붐_853242004(1골)</t>
+          <t>UNIT_867166676(2골), Voor_845009676(1골), Voor_835183277(1골), Voor_852233700(3골)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-29 11:20:02</t>
+          <t>2026-09-30 17:34:22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1358,12 +1346,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1373,14 +1361,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(2골)</t>
+          <t>UNIT_848180930(2골), UNIT_840192883(1골), Voor_845009676(1골), Voor_856256079(1골), Voor_852233700(2골)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-29 11:08:25</t>
+          <t>2026-09-30 17:17:18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1390,7 +1378,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1405,29 +1393,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_848135455(1골), UNIT_867166676(1골), 콩콩콩룔_866223710(1골), 콩콩콩룔_867223848(1골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(2골), Voor_852233700(2골)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-29 10:56:21</t>
+          <t>2026-09-30 17:03:54</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7_1</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1437,14 +1425,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(3골), 오스트리아_851221671(1골), 오스트리아_864182152(1골), 오스트리아_864140057(1골), 오스트리아_851216275(1골), ShangHaiPortFC_864191910(1골)</t>
+          <t>UNIT_867166676(5골), Voor_845009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-29 10:47:10</t>
+          <t>2026-09-30 16:46:35</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1454,61 +1442,61 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1골), UNIT_867166676(2골), 셀래스틴_848231866(1골), 셀래스틴_848230938(1골)</t>
+          <t>UNIT_848180930(2골), Voor_845009676(1골), Voor_852233700(2골)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-29 10:45:30</t>
+          <t>2026-09-30 14:01:02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(2골), 오스트리아_864182152(1골), 오스트리아_864199266(2골), ShangHaiPortFC_861051412(1골)</t>
+          <t>UNIT_861221162(2골), 셀래스틴_861005680(4골), 셀래스틴_848231866(1골)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-29 10:35:32</t>
+          <t>2026-09-30 13:49:10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1523,24 +1511,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), 셀래스틴_846001551(1골), 셀래스틴_852241461(2골)</t>
+          <t>UNIT_867166676(3골), UNIT_861221162(2골), 셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-29 10:18:25</t>
+          <t>2026-09-30 13:33:10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1555,61 +1543,61 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), 셀래스틴_848194765(1골)</t>
+          <t>UNIT_848180930(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(3골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-29 09:24:43</t>
+          <t>2026-09-30 13:24:44</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(1골), 오스트리아_851236636(1골), 셀래스틴_846001551(1골), 셀래스틴_861005680(1골), 셀래스틴_848230938(1골)</t>
+          <t>Gucci와퍼_864200104(4골), 비주류중독_840052241(1골), 비주류중독_825000240(1골), 비주류중독_839247699(1골)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-29 09:13:08</t>
+          <t>2026-09-30 13:21:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1619,61 +1607,61 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(1골), 셀래스틴_861005680(1골)</t>
+          <t>UNIT_848180930(1골), UNIT_867166676(1골)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-29 09:02:47</t>
+          <t>2026-09-30 13:12:24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(1골), 오스트리아_864199266(1골), 오스트리아_864182152(1골), 셀래스틴_861005680(1골)</t>
+          <t>Gucci와퍼_852028765(1골), Gucci와퍼_852168473(1골), 비주류중독_834239977(1골), 비주류중독_840052241(1골), 비주류중독_839247699(1골)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-29 08:51:25</t>
+          <t>2026-09-30 13:10:05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1683,47 +1671,783 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0_2</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>셀래스틴_846001551(1골), 셀래스틴_861005680(1골)</t>
+          <t>UNIT_867166676(3골), UNIT_840192883(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(2골)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>2026-09-30 12:57:48</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), UNIT_848180930(1골), 셀래스틴_846001551(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:35:39</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 비주류중독_848006975(2골), 비주류중독_839247699(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:24:21</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:00:21</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(2골), 셀래스틴_861005680(2골), 셀래스틴_852241461(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:47:20</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3_4</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>방덕_848007512(1골), 방덕_856228093(1골), 방덕_863184200(1골), Voor_845247090(2골), Voor_852233700(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:35:39</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1_6</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>방덕_101001419(1골), Voor_852233700(3골), Voor_845009676(2골), Voor_845247090(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:27:58</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Legend독수리_825190048(1골), Legend독수리_861081644(1골), Legend독수리_848188350(1골), syma_863228092(1골), syma_856233848(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:16:55</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1_6</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Legend독수리_825190048(1골), syma_866231913(1골), syma_863262863(1골), syma_846001845(3골), syma_852274967(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:04:48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1골), Legend독수리_852209658(1골), syma_866231913(1골), syma_863228092(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-30 07:53:20</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1골), syma_863222665(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:16:03</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>7_2</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>개포동덕배_848206113(1골), 개포동덕배_845208722(1골), 개포동덕배_856202126(1골), 개포동덕배_845190048(4골), Gucci차붐_864247686(1골), Gucci차붐_864176403(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:04:54</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>개포동덕배_845190048(3골), 개포동덕배_848206113(1골), Gucci차붐_853272733(1골), Gucci차붐_853242004(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:20:02</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:08:25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), UNIT_848135455(1골), UNIT_867166676(1골), 콩콩콩룔_866223710(1골), 콩콩콩룔_867223848(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:56:21</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>7_1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(3골), 오스트리아_851221671(1골), 오스트리아_864182152(1골), 오스트리아_864140057(1골), 오스트리아_851216275(1골), ShangHaiPortFC_864191910(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:47:10</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>UNIT_840228251(1골), UNIT_867166676(2골), 셀래스틴_848231866(1골), 셀래스틴_848230938(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:45:30</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(2골), 오스트리아_864182152(1골), 오스트리아_864199266(2골), ShangHaiPortFC_861051412(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:35:32</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), 셀래스틴_846001551(1골), 셀래스틴_852241461(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:18:25</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), 셀래스틴_848194765(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:24:43</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(1골), 오스트리아_851236636(1골), 셀래스틴_846001551(1골), 셀래스틴_861005680(1골), 셀래스틴_848230938(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:13:08</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:02:47</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(1골), 오스트리아_864199266(1골), 오스트리아_864182152(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-29 08:51:25</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0_2</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>셀래스틴_846001551(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>2026-09-29 04:33:11</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>여수가스</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>오스트리아</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>2_3</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>여수가스_828231747(1골), 여수가스_852274967(1골), 오스트리아_864191566(1골), 오스트리아_864199266(2골)</t>
         </is>
@@ -1740,7 +2464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1778,86 +2502,86 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01 07:54:09</t>
+          <t>2026-10-01 15:50:18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>호야국2인_848227236(2도움), 호야국2인_848232293(1도움), 아들러_866251377(1도움), 아들러_855232639(1도움)</t>
+          <t>suma수마_861221162(1도움), 피파왕초보구단주_867000027(1도움), 피파왕초보구단주_851243057(2도움)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01 07:42:04</t>
+          <t>2026-10-01 15:38:48</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(2도움), 호야국2인_848217870(1도움), 호야국2인_851216409(1도움), 아들러_840191208(1도움)</t>
+          <t>suma수마_845192190(1도움), suma수마_861190046(1도움), 피파왕초보구단주_867000027(1도움)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01 06:47:50</t>
+          <t>2026-10-01 15:24:08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1867,61 +2591,61 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>호야국2인_848217870(1도움), 호야국2인_848232293(1도움), 호야국2인_852001183(1도움), suma수마_861190046(1도움), suma수마_848225439(1도움)</t>
+          <t>피파왕초보구단주_846208722(1도움), 피파왕초보구단주_856209331(1도움), 피파왕초보구단주_851243057(1도움), 피파왕초보구단주_867000027(1도움), Gucci와퍼_864200104(1도움)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-01 06:36:26</t>
+          <t>2026-10-01 15:12:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>호야국2인_851216409(1도움), 호야국2인_845198219(1도움), 호야국2인_846192505(1도움), 호야국2인_848216435(1도움), suma수마_826223697(1도움)</t>
+          <t>피파왕초보구단주_846208722(1도움), 피파왕초보구단주_867000027(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_864200104(1도움), Gucci와퍼_852168473(1도움)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-30 17:45:59</t>
+          <t>2026-10-01 14:56:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1931,29 +2655,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움), Voor_856256079(1도움), Voor_861000027(4도움)</t>
+          <t>호야국2인_848232293(1도움), 호야국2인_846192505(1도움)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-30 17:34:22</t>
+          <t>2026-10-01 14:51:31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1963,61 +2687,61 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UNIT_861221162(1도움), UNIT_866247257(1도움), UNIT_840228251(1도움), Voor_845009676(1도움), Voor_858025420(1도움), Voor_835183277(1도움)</t>
+          <t>은안_866241236(1도움), Gucci와퍼_851210697(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_840208574(1도움), Gucci와퍼_852010264(1도움)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-30 17:17:18</t>
+          <t>2026-10-01 14:45:02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), UNIT_848135455(1도움), Voor_845239231(1도움), Voor_845009676(1도움)</t>
+          <t>0708ManUtd_834239053(1도움), 호야국2인_846192505(1도움)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-30 17:03:54</t>
+          <t>2026-10-01 14:39:52</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2027,61 +2751,61 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_840192883(1도움), UNIT_848265695(3도움), Voor_852233700(1도움)</t>
+          <t>은안_848231866(1도움), 은안_856251517(1도움), 은안_856246420(1도움), 은안_866241236(1도움), Gucci와퍼_861139720(1도움)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-30 16:46:35</t>
+          <t>2026-10-01 14:31:32</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), Voor_845009676(1도움), Voor_846184943(1도움), Voor_852233700(1도움)</t>
+          <t>호야국2인_851216409(1도움), 호야국2인_845198219(1도움), Special블루_877001625(2도움), Special블루_861006975(1도움)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-30 14:01:02</t>
+          <t>2026-10-01 14:21:07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2091,29 +2815,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2도움), 셀래스틴_848194765(1도움), 셀래스틴_848231866(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>호야국2인_846192505(1도움), Special블루_861006975(1도움), Special블루_856246669(2도움)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-30 13:49:10</t>
+          <t>2026-10-01 14:08:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2123,24 +2847,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UNIT_840210736(2도움), UNIT_867166676(1도움), UNIT_848135455(1도움), UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852241461(2도움)</t>
+          <t>호야국2인_848216435(1도움), 호야국2인_845198219(1도움), 호야국2인_851261865(1도움), 비주류중독_839247699(1도움), 비주류중독_848006975(1도움)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-30 13:33:10</t>
+          <t>2026-10-01 13:58:38</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2155,19 +2879,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852259694(1도움), 셀래스틴_861005680(1도움)</t>
+          <t>비주류중독_848006975(3도움), 비주류중독_839247699(1도움), 비주류중독_840052241(1도움)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:44</t>
+          <t>2026-10-01 13:48:03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2177,66 +2901,62 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Gucci와퍼_852168473(3도움), Gucci와퍼_852028765(1도움), 비주류중독_840052241(1도움), 비주류중독_862180283(1도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-30 13:21:00</t>
+          <t>2026-10-01 13:34:35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움), UNIT_840228251(1도움)</t>
+          <t>아들러_840191208(1도움), Special블루_877001625(1도움)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-30 13:12:24</t>
+          <t>2026-10-01 13:24:02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2251,29 +2971,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gucci와퍼_852010264(1도움), 비주류중독_834239977(1도움), 비주류중독_848006975(1도움)</t>
+          <t>아들러_866251377(1도움), 아들러_861000570(1도움), Special블루_856246669(1도움), Special블루_848230666(1도움), Special블루_861006975(1도움)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-30 13:10:05</t>
+          <t>2026-10-01 13:13:07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>7_0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2283,221 +3003,213 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1도움), UNIT_840192883(2도움), UNIT_840225782(1도움), 셀래스틴_848194765(1도움), 셀래스틴_863200458(1도움)</t>
+          <t>앙쿠_848176580(5도움)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-30 12:57:48</t>
+          <t>2026-10-01 13:02:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>UNIT_863250723(1도움), UNIT_840228251(2도움), 셀래스틴_852241461(1도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:39</t>
+          <t>2026-10-01 13:01:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>셀래스틴_848231866(1도움), 셀래스틴_852259694(1도움), 비주류중독_839247699(1도움), 비주류중독_834239977(2도움)</t>
+          <t>앙쿠_856247103(1도움), syma_851236295(1도움)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-30 12:24:21</t>
+          <t>2026-10-01 12:49:37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>셀래스틴_852259694(1도움), 셀래스틴_848194765(1도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-30 12:00:21</t>
+          <t>2026-10-01 11:22:46</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UNIT_840225782(1도움), UNIT_867166676(1도움), 셀래스틴_848013038(1도움), 셀래스틴_852241461(2도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_848176580(1도움)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-30 09:47:20</t>
+          <t>2026-10-01 11:15:46</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>방덕_867001040(1도움), 방덕_848231478(2도움), Voor_845009676(1도움), Voor_845239231(1도움), Voor_835183277(1도움), Voor_848216150(1도움)</t>
+          <t>suma수마_851234112(1도움), suma수마_840001114(1도움), suma수마_861190046(1도움), suma수마_848225439(1도움), 겐지간지_845183898(1도움)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-30 09:35:39</t>
+          <t>2026-10-01 11:12:19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Voor_852233700(2도움), Voor_856256079(1도움), Voor_845009676(2도움), Voor_835183277(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_848176580(1도움), 앙쿠_863246191(1도움), Gucci차붐_861182521(1도움)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-30 08:27:58</t>
+          <t>2026-10-01 11:03:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2507,125 +3219,125 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Legend독수리_861215732(1도움), Legend독수리_852209658(1도움), syma_852274967(1도움), syma_863228092(1도움)</t>
+          <t>suma수마_861013383(2도움), suma수마_826223697(1도움), suma수마_861221162(1도움), suma수마_840001114(1도움), 겐지간지_852231443(1도움), 겐지간지_845158023(2도움)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-30 08:16:55</t>
+          <t>2026-10-01 07:54:09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Legend독수리_861215732(1도움), syma_866231913(2도움), syma_863222665(4도움)</t>
+          <t>호야국2인_848227236(2도움), 호야국2인_848232293(1도움), 아들러_866251377(1도움), 아들러_855232639(1도움)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-30 08:04:48</t>
+          <t>2026-10-01 07:42:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Legend독수리_848224425(1도움), Legend독수리_826236703(1도움), syma_856233848(1도움)</t>
+          <t>호야국2인_848232293(2도움), 호야국2인_848217870(1도움), 호야국2인_851216409(1도움), 아들러_840191208(1도움)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-30 07:53:20</t>
+          <t>2026-10-01 06:47:50</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Legend독수리_861081644(1도움), syma_846001845(2도움)</t>
+          <t>호야국2인_848217870(1도움), 호야국2인_848232293(1도움), 호야국2인_852001183(1도움), suma수마_861190046(1도움), suma수마_848225439(1도움)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-29 14:16:03</t>
+          <t>2026-10-01 06:36:26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2635,46 +3347,46 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>개포동덕배_848206113(1도움), 개포동덕배_845208722(3도움), 개포동덕배_856202126(1도움), 개포동덕배_863212622(2도움), Gucci차붐_853272733(1도움), Gucci차붐_864176403(1도움)</t>
+          <t>호야국2인_851216409(1도움), 호야국2인_845198219(1도움), 호야국2인_846192505(1도움), 호야국2인_848216435(1도움), suma수마_826223697(1도움)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-29 14:04:54</t>
+          <t>2026-09-30 17:45:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>개포동덕배_856202126(1도움), 개포동덕배_863234396(1도움), 개포동덕배_856275298(1도움), 개포동덕배_848206113(1도움), Gucci차붐_864084333(1도움), Gucci차붐_864247686(1도움)</t>
+          <t>UNIT_840192883(1도움), Voor_856256079(1도움), Voor_861000027(4도움)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-29 11:20:02</t>
+          <t>2026-09-30 17:34:22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,12 +3396,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2699,14 +3411,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(2도움)</t>
+          <t>UNIT_861221162(1도움), UNIT_866247257(1도움), UNIT_840228251(1도움), Voor_845009676(1도움), Voor_858025420(1도움), Voor_835183277(1도움)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-29 11:08:25</t>
+          <t>2026-09-30 17:17:18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2716,7 +3428,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2731,29 +3443,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UNIT_840192883(2도움), UNIT_848265695(1도움), 콩콩콩룔_851236496(1도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), UNIT_848135455(1도움), Voor_845239231(1도움), Voor_845009676(1도움)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-29 10:56:21</t>
+          <t>2026-09-30 17:03:54</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7_1</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2763,14 +3475,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>오스트리아_864182152(2도움), 오스트리아_864140057(1도움), 오스트리아_851236636(4도움), ShangHaiPortFC_848031432(1도움)</t>
+          <t>UNIT_848180930(1도움), UNIT_840192883(1도움), UNIT_848265695(3도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-29 10:47:10</t>
+          <t>2026-09-30 16:46:35</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2780,61 +3492,61 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_863250723(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), Voor_845009676(1도움), Voor_846184943(1도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-29 10:45:30</t>
+          <t>2026-09-30 14:01:02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>오스트리아_851221671(1도움), 오스트리아_863223671(1도움), 오스트리아_863240709(1도움), 오스트리아_864140057(1도움), 오스트리아_851216275(1도움), ShangHaiPortFC_827143001(1도움)</t>
+          <t>UNIT_867166676(2도움), 셀래스틴_848194765(1도움), 셀래스틴_848231866(1도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-29 10:35:32</t>
+          <t>2026-09-30 13:49:10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2849,24 +3561,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1도움), 셀래스틴_848231866(2도움), 셀래스틴_852241461(1도움)</t>
+          <t>UNIT_840210736(2도움), UNIT_867166676(1도움), UNIT_848135455(1도움), UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852241461(2도움)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-29 10:18:25</t>
+          <t>2026-09-30 13:33:10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2881,61 +3593,61 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UNIT_839013383(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+          <t>UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852259694(1도움), 셀래스틴_861005680(1도움)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-29 09:24:43</t>
+          <t>2026-09-30 13:24:44</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(1도움), 오스트리아_863240709(1도움), 셀래스틴_846001551(1도움), 셀래스틴_848194765(2도움)</t>
+          <t>Gucci와퍼_852168473(3도움), Gucci와퍼_852028765(1도움), 비주류중독_840052241(1도움), 비주류중독_862180283(1도움)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-29 09:13:08</t>
+          <t>2026-09-30 13:21:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2945,61 +3657,61 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>오스트리아_851221671(1도움), 셀래스틴_848231866(1도움)</t>
+          <t>UNIT_840192883(1도움), UNIT_840228251(1도움)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-29 09:02:47</t>
+          <t>2026-09-30 13:12:24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(1도움), 오스트리아_864182152(1도움), 오스트리아_851236636(1도움), 셀래스틴_846001551(1도움)</t>
+          <t>Gucci와퍼_852010264(1도움), 비주류중독_834239977(1도움), 비주류중독_848006975(1도움)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-29 08:51:25</t>
+          <t>2026-09-30 13:10:05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3009,47 +3721,783 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0_2</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>셀래스틴_863200458(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>UNIT_867166676(1도움), UNIT_840192883(2도움), UNIT_840225782(1도움), 셀래스틴_848194765(1도움), 셀래스틴_863200458(1도움)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>2026-09-30 12:57:48</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>UNIT_863250723(1도움), UNIT_840228251(2도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:35:39</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>셀래스틴_848231866(1도움), 셀래스틴_852259694(1도움), 비주류중독_839247699(1도움), 비주류중독_834239977(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:24:21</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>셀래스틴_852259694(1도움), 셀래스틴_848194765(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:00:21</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>UNIT_840225782(1도움), UNIT_867166676(1도움), 셀래스틴_848013038(1도움), 셀래스틴_852241461(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:47:20</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3_4</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>방덕_867001040(1도움), 방덕_848231478(2도움), Voor_845009676(1도움), Voor_845239231(1도움), Voor_835183277(1도움), Voor_848216150(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:35:39</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1_6</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Voor_852233700(2도움), Voor_856256079(1도움), Voor_845009676(2도움), Voor_835183277(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:27:58</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1도움), Legend독수리_852209658(1도움), syma_852274967(1도움), syma_863228092(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:16:55</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1_6</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1도움), syma_866231913(2도움), syma_863222665(4도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:04:48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Legend독수리_848224425(1도움), Legend독수리_826236703(1도움), syma_856233848(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-30 07:53:20</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Legend독수리_861081644(1도움), syma_846001845(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:16:03</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>7_2</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>개포동덕배_848206113(1도움), 개포동덕배_845208722(3도움), 개포동덕배_856202126(1도움), 개포동덕배_863212622(2도움), Gucci차붐_853272733(1도움), Gucci차붐_864176403(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:04:54</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>개포동덕배_856202126(1도움), 개포동덕배_863234396(1도움), 개포동덕배_856275298(1도움), 개포동덕배_848206113(1도움), Gucci차붐_864084333(1도움), Gucci차붐_864247686(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:20:02</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:08:25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(2도움), UNIT_848265695(1도움), 콩콩콩룔_851236496(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:56:21</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>7_1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>오스트리아_864182152(2도움), 오스트리아_864140057(1도움), 오스트리아_851236636(4도움), ShangHaiPortFC_848031432(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:47:10</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1도움), UNIT_863250723(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:45:30</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>오스트리아_851221671(1도움), 오스트리아_863223671(1도움), 오스트리아_863240709(1도움), 오스트리아_864140057(1도움), 오스트리아_851216275(1도움), ShangHaiPortFC_827143001(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:35:32</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1도움), 셀래스틴_848231866(2도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:18:25</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>UNIT_839013383(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:24:43</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(1도움), 오스트리아_863240709(1도움), 셀래스틴_846001551(1도움), 셀래스틴_848194765(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:13:08</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>오스트리아_851221671(1도움), 셀래스틴_848231866(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:02:47</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(1도움), 오스트리아_864182152(1도움), 오스트리아_851236636(1도움), 셀래스틴_846001551(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-29 08:51:25</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0_2</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>셀래스틴_863200458(1도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>2026-09-29 04:33:11</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>여수가스</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>오스트리아</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>2_3</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>여수가스_852216393(1도움), 여수가스_861162895(1도움), 오스트리아_864140057(1도움), 오스트리아_851257075(1도움)</t>
         </is>

--- a/API데이터_경기_득점_및_도움_기록.xlsx
+++ b/API데이터_경기_득점_및_도움_기록.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,86 +452,86 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01 15:50:18</t>
+          <t>2026-10-02 16:24:32</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>suma수마_861190046(1골), 피파왕초보구단주_861005661(3골)</t>
+          <t>앙쿠_848176580(2골)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01 15:38:48</t>
+          <t>2026-10-02 16:14:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>suma수마_861221162(1골), suma수마_861013383(1골), 피파왕초보구단주_846208722(1골), 피파왕초보구단주_856209331(1골)</t>
+          <t>앙쿠_848176580(2골), UNIT_867166676(4골)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01 15:24:08</t>
+          <t>2026-10-02 15:54:37</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -541,61 +541,61 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_846208722(2골), 피파왕초보구단주_867000027(2골), 피파왕초보구단주_861005661(1골), Gucci와퍼_852208128(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_814226161(1골), 앙쿠_863246191(1골), 앙쿠_851194765(1골)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-01 15:12:09</t>
+          <t>2026-10-02 15:43:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>0_6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_848209499(1골), 피파왕초보구단주_861005661(2골), Gucci와퍼_840208574(1골), Gucci와퍼_864200104(2골)</t>
+          <t>UNIT_840228251(2골), UNIT_840192883(1골), UNIT_867166676(3골)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-01 14:56:12</t>
+          <t>2026-10-02 15:32:20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -605,29 +605,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0708ManUtd_848238794(1골), 호야국2인_848227236(1골), 호야국2인_848232293(1골)</t>
+          <t>앙쿠_848176580(1골), UNIT_867166676(3골)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-01 14:51:31</t>
+          <t>2026-10-02 15:20:55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1_4</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -635,31 +635,27 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>은안_852237692(1골), Gucci와퍼_852028765(1골), Gucci와퍼_852010264(1골), Gucci와퍼_864200104(2골)</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-01 14:45:02</t>
+          <t>2026-10-02 14:48:41</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -669,244 +665,248 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0708ManUtd_868037576(1골), 0708ManUtd_834239053(1골), 호야국2인_851216409(1골), 호야국2인_848232293(1골), 호야국2인_846192505(1골)</t>
+          <t>앙쿠_848176580(1골), UNIT_840192883(1골), UNIT_867166676(2골)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-01 14:39:52</t>
+          <t>2026-10-02 14:36:35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>은안_877143001(3골), 은안_866241236(1골), Gucci와퍼_864200104(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_863246191(1골), UNIT_867166676(3골)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-01 14:31:32</t>
+          <t>2026-10-02 14:24:08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(2골), 호야국2인_851216409(1골), Special블루_868001419(1골), Special블루_861047390(1골), Special블루_856246669(1골)</t>
+          <t>앙쿠_866266039(1골), 앙쿠_851194765(1골), UNIT_867166676(1골), UNIT_848180930(3골)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-01 14:21:07</t>
+          <t>2026-10-02 14:12:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(1골), Special블루_851251566(1골), Special블루_877001625(1골), Special블루_868001419(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_846193747(2골), 앙쿠_863246191(2골), UNIT_848180930(1골), UNIT_851236403(1골)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-01 14:08:57</t>
+          <t>2026-10-02 14:00:42</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>호야국2인_846192505(3골), 비주류중독_840052241(2골)</t>
+          <t>앙쿠_863246191(2골), 앙쿠_866266039(1골), UNIT_867166676(3골), UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-01 13:58:38</t>
+          <t>2026-10-02 13:50:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(1골), 비주류중독_829203376(1골), 비주류중독_839247699(3골), 비주류중독_840052241(1골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_863246191(2골), 앙쿠_848176580(1골), UNIT_867166676(1골), UNIT_866247257(1골)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-01 13:48:03</t>
+          <t>2026-10-02 12:57:51</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>피파왕초보구단주_861005661(1골), 피파왕초보구단주_846208722(2골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-01 13:34:35</t>
+          <t>2026-10-02 12:45:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>아들러_861000570(1골), Special블루_877001625(1골), Special블루_848230666(1골)</t>
+          <t>피파왕초보구단주_846208722(1골), 피파왕초보구단주_846045197(1골), 피파왕초보구단주_867000027(1골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(2골)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-01 13:24:02</t>
+          <t>2026-10-02 10:04:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -921,89 +921,93 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>아들러_855232639(2골), Special블루_868001419(1골), Special블루_877001625(2골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_848176580(1골), UNIT_867166676(1골), UNIT_848180930(2골)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-01 13:13:07</t>
+          <t>2026-10-01 15:50:18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7_0</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(4골), 앙쿠_851194765(2골), 앙쿠_856247103(1골)</t>
+          <t>suma수마_861190046(1골), 피파왕초보구단주_861005661(3골)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-01 13:02:02</t>
+          <t>2026-10-01 15:38:48</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>suma수마_861221162(1골), suma수마_861013383(1골), 피파왕초보구단주_846208722(1골), 피파왕초보구단주_856209331(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-01 13:01:02</t>
+          <t>2026-10-01 15:24:08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1013,153 +1017,157 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), syma_867192629(1골)</t>
+          <t>피파왕초보구단주_846208722(2골), 피파왕초보구단주_867000027(2골), 피파왕초보구단주_861005661(1골), Gucci와퍼_852208128(1골)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-01 12:49:37</t>
+          <t>2026-10-01 15:12:09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>피파왕초보구단주_848209499(1골), 피파왕초보구단주_861005661(2골), Gucci와퍼_840208574(1골), Gucci와퍼_864200104(2골)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-01 11:22:46</t>
+          <t>2026-10-01 14:56:12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3_0</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 앙쿠_863246191(2골)</t>
+          <t>0708ManUtd_848238794(1골), 호야국2인_848227236(1골), 호야국2인_848232293(1골)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-01 11:15:46</t>
+          <t>2026-10-01 14:51:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>suma수마_861190046(1골), suma수마_861221162(3골), suma수마_845192190(1골), 겐지간지_848170890(1골)</t>
+          <t>은안_852237692(1골), Gucci와퍼_852028765(1골), Gucci와퍼_852010264(1골), Gucci와퍼_864200104(2골)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-01 11:12:19</t>
+          <t>2026-10-01 14:45:02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>앙쿠_814226161(1골), 앙쿠_848176580(2골), Gucci차붐_840191208(1골)</t>
+          <t>0708ManUtd_868037576(1골), 0708ManUtd_834239053(1골), 호야국2인_851216409(1골), 호야국2인_848232293(1골), 호야국2인_846192505(1골)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-01 11:03:11</t>
+          <t>2026-10-01 14:39:52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1169,14 +1177,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>suma수마_861190046(2골), suma수마_861221162(1골), suma수마_840001114(2골), 겐지간지_814231747(1골), 겐지간지_852241461(1골), 겐지간지_856237679(1골)</t>
+          <t>은안_877143001(3골), 은안_866241236(1골), Gucci와퍼_864200104(1골)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-01 07:54:09</t>
+          <t>2026-10-01 14:31:32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1186,29 +1194,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>호야국2인_851261865(1골), 호야국2인_846192505(1골), 호야국2인_848232293(1골), 아들러_861000570(1골), 아들러_840191208(1골)</t>
+          <t>호야국2인_848232293(2골), 호야국2인_851216409(1골), Special블루_868001419(1골), Special블루_861047390(1골), Special블루_856246669(1골)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-01 07:42:04</t>
+          <t>2026-10-01 14:21:07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1218,29 +1226,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>호야국2인_848227236(2골), 호야국2인_848232293(1골), 호야국2인_848216435(1골), 호야국2인_851216409(1골), 아들러_291225126(1골), 아들러_866251377(1골)</t>
+          <t>호야국2인_848232293(1골), Special블루_851251566(1골), Special블루_877001625(1골), Special블루_868001419(1골)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-01 06:47:50</t>
+          <t>2026-10-01 14:08:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1250,12 +1258,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1265,14 +1273,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>호야국2인_845198219(1골), 호야국2인_848232293(2골), 호야국2인_848216435(1골), suma수마_861190046(1골), suma수마_861221162(1골)</t>
+          <t>호야국2인_846192505(3골), 비주류중독_840052241(2골)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-01 06:36:26</t>
+          <t>2026-10-01 13:58:38</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1282,44 +1290,44 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>호야국2인_851216409(1골), 호야국2인_845198219(1골), 호야국2인_846192505(1골), 호야국2인_848227236(1골), 호야국2인_848232293(1골), suma수마_861013383(1골), suma수마_861221162(1골)</t>
+          <t>호야국2인_848232293(1골), 비주류중독_829203376(1골), 비주류중독_839247699(3골), 비주류중독_840052241(1골)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-30 17:45:59</t>
+          <t>2026-10-01 13:48:03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1327,31 +1335,27 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>UNIT_867166676(2골), Voor_845009676(1골), Voor_835183277(1골), Voor_852233700(3골)</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-30 17:34:22</t>
+          <t>2026-10-01 13:34:35</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1361,61 +1365,61 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), UNIT_840192883(1골), Voor_845009676(1골), Voor_856256079(1골), Voor_852233700(2골)</t>
+          <t>아들러_861000570(1골), Special블루_877001625(1골), Special블루_848230666(1골)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-30 17:17:18</t>
+          <t>2026-10-01 13:24:02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), UNIT_848180930(2골), Voor_852233700(2골)</t>
+          <t>아들러_855232639(2골), Special블루_868001419(1골), Special블루_877001625(2골)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-30 17:03:54</t>
+          <t>2026-10-01 13:13:07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>7_0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1425,29 +1429,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UNIT_867166676(5골), Voor_845009676(1골)</t>
+          <t>앙쿠_863246191(4골), 앙쿠_851194765(2골), 앙쿠_856247103(1골)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-30 16:46:35</t>
+          <t>2026-10-01 13:02:02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1455,127 +1459,119 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>UNIT_848180930(2골), Voor_845009676(1골), Voor_852233700(2골)</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-30 14:01:02</t>
+          <t>2026-10-01 13:01:02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UNIT_861221162(2골), 셀래스틴_861005680(4골), 셀래스틴_848231866(1골)</t>
+          <t>앙쿠_848176580(1골), syma_867192629(1골)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-30 13:49:10</t>
+          <t>2026-10-01 12:49:37</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>UNIT_867166676(3골), UNIT_861221162(2골), 셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-30 13:33:10</t>
+          <t>2026-10-01 11:22:46</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>3_0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(3골), 셀래스틴_852241461(1골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_863246191(2골)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:44</t>
+          <t>2026-10-01 11:15:46</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1585,29 +1581,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gucci와퍼_864200104(4골), 비주류중독_840052241(1골), 비주류중독_825000240(1골), 비주류중독_839247699(1골)</t>
+          <t>suma수마_861190046(1골), suma수마_861221162(3골), suma수마_845192190(1골), 겐지간지_848170890(1골)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-30 13:21:00</t>
+          <t>2026-10-01 11:12:19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1617,61 +1613,61 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_867166676(1골)</t>
+          <t>앙쿠_814226161(1골), 앙쿠_848176580(2골), Gucci차붐_840191208(1골)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-30 13:12:24</t>
+          <t>2026-10-01 11:03:11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gucci와퍼_852028765(1골), Gucci와퍼_852168473(1골), 비주류중독_834239977(1골), 비주류중독_840052241(1골), 비주류중독_839247699(1골)</t>
+          <t>suma수마_861190046(2골), suma수마_861221162(1골), suma수마_840001114(2골), 겐지간지_814231747(1골), 겐지간지_852241461(1골), 겐지간지_856237679(1골)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-30 13:10:05</t>
+          <t>2026-10-01 07:54:09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1681,29 +1677,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UNIT_867166676(3골), UNIT_840192883(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(2골)</t>
+          <t>호야국2인_851261865(1골), 호야국2인_846192505(1골), 호야국2인_848232293(1골), 아들러_861000570(1골), 아들러_840191208(1골)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-30 12:57:48</t>
+          <t>2026-10-01 07:42:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1713,61 +1709,61 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), UNIT_848180930(1골), 셀래스틴_846001551(1골)</t>
+          <t>호야국2인_848227236(2골), 호야국2인_848232293(1골), 호야국2인_848216435(1골), 호야국2인_851216409(1골), 아들러_291225126(1골), 아들러_866251377(1골)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:39</t>
+          <t>2026-10-01 06:47:50</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 비주류중독_848006975(2골), 비주류중독_839247699(1골)</t>
+          <t>호야국2인_845198219(1골), 호야국2인_848232293(2골), 호야국2인_848216435(1골), suma수마_861190046(1골), suma수마_861221162(1골)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-30 12:24:21</t>
+          <t>2026-10-01 06:36:26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1777,14 +1773,14 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
+          <t>호야국2인_851216409(1골), 호야국2인_845198219(1골), 호야국2인_846192505(1골), 호야국2인_848227236(1골), 호야국2인_848232293(1골), suma수마_861013383(1골), suma수마_861221162(1골)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-30 12:00:21</t>
+          <t>2026-09-30 17:45:59</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1794,12 +1790,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1809,19 +1805,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), 셀래스틴_861005680(2골), 셀래스틴_852241461(1골)</t>
+          <t>UNIT_867166676(2골), Voor_845009676(1골), Voor_835183277(1골), Voor_852233700(3골)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-30 09:47:20</t>
+          <t>2026-09-30 17:34:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1841,19 +1837,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>방덕_848007512(1골), 방덕_856228093(1골), 방덕_863184200(1골), Voor_845247090(2골), Voor_852233700(2골)</t>
+          <t>UNIT_848180930(2골), UNIT_840192883(1골), Voor_845009676(1골), Voor_856256079(1골), Voor_852233700(2골)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-30 09:35:39</t>
+          <t>2026-09-30 17:17:18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1863,39 +1859,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>방덕_101001419(1골), Voor_852233700(3골), Voor_845009676(2골), Voor_845247090(1골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(2골), Voor_852233700(2골)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-30 08:27:58</t>
+          <t>2026-09-30 17:03:54</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1905,29 +1901,29 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Legend독수리_825190048(1골), Legend독수리_861081644(1골), Legend독수리_848188350(1골), syma_863228092(1골), syma_856233848(1골)</t>
+          <t>UNIT_867166676(5골), Voor_845009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-30 08:16:55</t>
+          <t>2026-09-30 16:46:35</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1937,125 +1933,125 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Legend독수리_825190048(1골), syma_866231913(1골), syma_863262863(1골), syma_846001845(3골), syma_852274967(1골)</t>
+          <t>UNIT_848180930(2골), Voor_845009676(1골), Voor_852233700(2골)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-30 08:04:48</t>
+          <t>2026-09-30 14:01:02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Legend독수리_861215732(1골), Legend독수리_852209658(1골), syma_866231913(1골), syma_863228092(1골)</t>
+          <t>UNIT_861221162(2골), 셀래스틴_861005680(4골), 셀래스틴_848231866(1골)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-30 07:53:20</t>
+          <t>2026-09-30 13:49:10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Legend독수리_861215732(1골), syma_863222665(2골)</t>
+          <t>UNIT_867166676(3골), UNIT_861221162(2골), 셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-29 14:16:03</t>
+          <t>2026-09-30 13:33:10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>개포동덕배_848206113(1골), 개포동덕배_845208722(1골), 개포동덕배_856202126(1골), 개포동덕배_845190048(4골), Gucci차붐_864247686(1골), Gucci차붐_864176403(1골)</t>
+          <t>UNIT_848180930(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(3골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-29 14:04:54</t>
+          <t>2026-09-30 13:24:44</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2065,14 +2061,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(3골), 개포동덕배_848206113(1골), Gucci차붐_853272733(1골), Gucci차붐_853242004(1골)</t>
+          <t>Gucci와퍼_864200104(4골), 비주류중독_840052241(1골), 비주류중독_825000240(1골), 비주류중독_839247699(1골)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-29 11:20:02</t>
+          <t>2026-09-30 13:21:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2082,76 +2078,76 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(2골)</t>
+          <t>UNIT_848180930(1골), UNIT_867166676(1골)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-29 11:08:25</t>
+          <t>2026-09-30 13:12:24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_848135455(1골), UNIT_867166676(1골), 콩콩콩룔_866223710(1골), 콩콩콩룔_867223848(1골)</t>
+          <t>Gucci와퍼_852028765(1골), Gucci와퍼_852168473(1골), 비주류중독_834239977(1골), 비주류중독_840052241(1골), 비주류중독_839247699(1골)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-29 10:56:21</t>
+          <t>2026-09-30 13:10:05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7_1</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2161,14 +2157,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(3골), 오스트리아_851221671(1골), 오스트리아_864182152(1골), 오스트리아_864140057(1골), 오스트리아_851216275(1골), ShangHaiPortFC_864191910(1골)</t>
+          <t>UNIT_867166676(3골), UNIT_840192883(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(2골)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-29 10:47:10</t>
+          <t>2026-09-30 12:57:48</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2183,7 +2179,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2193,78 +2189,78 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1골), UNIT_867166676(2골), 셀래스틴_848231866(1골), 셀래스틴_848230938(1골)</t>
+          <t>UNIT_867166676(2골), UNIT_848180930(1골), 셀래스틴_846001551(1골)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-29 10:45:30</t>
+          <t>2026-09-30 12:35:39</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(2골), 오스트리아_864182152(1골), 오스트리아_864199266(2골), ShangHaiPortFC_861051412(1골)</t>
+          <t>셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 비주류중독_848006975(2골), 비주류중독_839247699(1골)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-29 10:35:32</t>
+          <t>2026-09-30 12:24:21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), 셀래스틴_846001551(1골), 셀래스틴_852241461(2골)</t>
+          <t>셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-29 10:18:25</t>
+          <t>2026-09-30 12:00:21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2279,39 +2275,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), 셀래스틴_848194765(1골)</t>
+          <t>UNIT_848180930(2골), 셀래스틴_861005680(2골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-29 09:24:43</t>
+          <t>2026-09-30 09:47:20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2321,61 +2317,61 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(1골), 오스트리아_851236636(1골), 셀래스틴_846001551(1골), 셀래스틴_861005680(1골), 셀래스틴_848230938(1골)</t>
+          <t>방덕_848007512(1골), 방덕_856228093(1골), 방덕_863184200(1골), Voor_845247090(2골), Voor_852233700(2골)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-29 09:13:08</t>
+          <t>2026-09-30 09:35:39</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>1_6</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(1골), 셀래스틴_861005680(1골)</t>
+          <t>방덕_101001419(1골), Voor_852233700(3골), Voor_845009676(2골), Voor_845247090(1골)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-29 09:02:47</t>
+          <t>2026-09-30 08:27:58</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2385,29 +2381,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(1골), 오스트리아_864199266(1골), 오스트리아_864182152(1골), 셀래스틴_861005680(1골)</t>
+          <t>Legend독수리_825190048(1골), Legend독수리_861081644(1골), Legend독수리_848188350(1골), syma_863228092(1골), syma_856233848(1골)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-29 08:51:25</t>
+          <t>2026-09-30 08:16:55</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0_2</t>
+          <t>1_6</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2417,37 +2413,517 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>셀래스틴_846001551(1골), 셀래스틴_861005680(1골)</t>
+          <t>Legend독수리_825190048(1골), syma_866231913(1골), syma_863262863(1골), syma_846001845(3골), syma_852274967(1골)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>2026-09-30 08:04:48</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1골), Legend독수리_852209658(1골), syma_866231913(1골), syma_863228092(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-30 07:53:20</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1골), syma_863222665(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:16:03</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>7_2</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>개포동덕배_848206113(1골), 개포동덕배_845208722(1골), 개포동덕배_856202126(1골), 개포동덕배_845190048(4골), Gucci차붐_864247686(1골), Gucci차붐_864176403(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:04:54</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>개포동덕배_845190048(3골), 개포동덕배_848206113(1골), Gucci차붐_853272733(1골), Gucci차붐_853242004(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:20:02</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:08:25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), UNIT_848135455(1골), UNIT_867166676(1골), 콩콩콩룔_866223710(1골), 콩콩콩룔_867223848(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:56:21</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>7_1</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(3골), 오스트리아_851221671(1골), 오스트리아_864182152(1골), 오스트리아_864140057(1골), 오스트리아_851216275(1골), ShangHaiPortFC_864191910(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:47:10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>UNIT_840228251(1골), UNIT_867166676(2골), 셀래스틴_848231866(1골), 셀래스틴_848230938(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:45:30</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(2골), 오스트리아_864182152(1골), 오스트리아_864199266(2골), ShangHaiPortFC_861051412(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:35:32</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), 셀래스틴_846001551(1골), 셀래스틴_852241461(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:18:25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), 셀래스틴_848194765(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:24:43</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(1골), 오스트리아_851236636(1골), 셀래스틴_846001551(1골), 셀래스틴_861005680(1골), 셀래스틴_848230938(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:13:08</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:02:47</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(1골), 오스트리아_864199266(1골), 오스트리아_864182152(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-29 08:51:25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>0_2</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>셀래스틴_846001551(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>2026-09-29 04:33:11</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>여수가스</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>오스트리아</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>2_3</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>여수가스_828231747(1골), 여수가스_852274967(1골), 오스트리아_864191566(1골), 오스트리아_864199266(2골)</t>
         </is>
@@ -2464,7 +2940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2502,86 +2978,86 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01 15:50:18</t>
+          <t>2026-10-02 16:24:32</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>suma수마_861221162(1도움), 피파왕초보구단주_867000027(1도움), 피파왕초보구단주_851243057(2도움)</t>
+          <t>앙쿠_846193747(2도움)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01 15:38:48</t>
+          <t>2026-10-02 16:14:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>suma수마_845192190(1도움), suma수마_861190046(1도움), 피파왕초보구단주_867000027(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_814226161(1도움), UNIT_840228251(3도움), UNIT_845207439(1도움)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01 15:24:08</t>
+          <t>2026-10-02 15:54:37</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2591,61 +3067,61 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_846208722(1도움), 피파왕초보구단주_856209331(1도움), 피파왕초보구단주_851243057(1도움), 피파왕초보구단주_867000027(1도움), Gucci와퍼_864200104(1도움)</t>
+          <t>앙쿠_863246191(3도움), 앙쿠_851194765(1도움)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-01 15:12:09</t>
+          <t>2026-10-02 15:43:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>0_6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_846208722(1도움), 피파왕초보구단주_867000027(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_864200104(1도움), Gucci와퍼_852168473(1도움)</t>
+          <t>UNIT_840210736(1도움), UNIT_840228251(1도움), UNIT_840225782(1도움), UNIT_840192883(1도움), UNIT_863250723(1도움), UNIT_848135455(1도움)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-01 14:56:12</t>
+          <t>2026-10-02 15:32:20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2655,29 +3131,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(1도움), 호야국2인_846192505(1도움)</t>
+          <t>앙쿠_846193747(1도움), UNIT_840192883(1도움), UNIT_845207439(1도움)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-01 14:51:31</t>
+          <t>2026-10-02 15:20:55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1_4</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2685,31 +3161,27 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>은안_866241236(1도움), Gucci와퍼_851210697(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_840208574(1도움), Gucci와퍼_852010264(1도움)</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-01 14:45:02</t>
+          <t>2026-10-02 14:48:41</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2719,244 +3191,248 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0708ManUtd_834239053(1도움), 호야국2인_846192505(1도움)</t>
+          <t>앙쿠_863246191(1도움), UNIT_840192883(2도움), UNIT_840228251(1도움)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-01 14:39:52</t>
+          <t>2026-10-02 14:36:35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>은안_848231866(1도움), 은안_856251517(1도움), 은안_856246420(1도움), 은안_866241236(1도움), Gucci와퍼_861139720(1도움)</t>
+          <t>앙쿠_863246191(1도움), 앙쿠_851194765(1도움), UNIT_848265695(1도움), UNIT_840192883(2도움)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-01 14:31:32</t>
+          <t>2026-10-02 14:24:08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>호야국2인_851216409(1도움), 호야국2인_845198219(1도움), Special블루_877001625(2도움), Special블루_861006975(1도움)</t>
+          <t>앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_840228251(1도움), UNIT_840192883(2도움), UNIT_840225782(1도움)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-01 14:21:07</t>
+          <t>2026-10-02 14:12:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>호야국2인_846192505(1도움), Special블루_861006975(1도움), Special블루_856246669(2도움)</t>
+          <t>앙쿠_848176580(2도움), 앙쿠_851194765(1도움), UNIT_840192883(2도움)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-01 14:08:57</t>
+          <t>2026-10-02 14:00:42</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>호야국2인_848216435(1도움), 호야국2인_845198219(1도움), 호야국2인_851261865(1도움), 비주류중독_839247699(1도움), 비주류중독_848006975(1도움)</t>
+          <t>앙쿠_848176580(2도움), 앙쿠_856247103(1도움), UNIT_840228251(3도움), UNIT_840225782(1도움)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-01 13:58:38</t>
+          <t>2026-10-02 13:50:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>비주류중독_848006975(3도움), 비주류중독_839247699(1도움), 비주류중독_840052241(1도움)</t>
+          <t>앙쿠_851194765(2도움), 앙쿠_863246191(2도움), UNIT_840228251(1도움)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-01 13:48:03</t>
+          <t>2026-10-02 12:57:51</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>피파왕초보구단주_846045197(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_867220502(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-01 13:34:35</t>
+          <t>2026-10-02 12:45:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>아들러_840191208(1도움), Special블루_877001625(1도움)</t>
+          <t>피파왕초보구단주_846045197(1도움), 피파왕초보구단주_867000027(2도움), 콩콩콩룔_867220502(1도움)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-01 13:24:02</t>
+          <t>2026-10-02 10:04:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2971,89 +3447,93 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>아들러_866251377(1도움), 아들러_861000570(1도움), Special블루_856246669(1도움), Special블루_848230666(1도움), Special블루_861006975(1도움)</t>
+          <t>앙쿠_863246191(1도움), UNIT_840210736(1도움), UNIT_840228251(2도움)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-01 13:13:07</t>
+          <t>2026-10-01 15:50:18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7_0</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(5도움)</t>
+          <t>suma수마_861221162(1도움), 피파왕초보구단주_867000027(1도움), 피파왕초보구단주_851243057(2도움)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-01 13:02:02</t>
+          <t>2026-10-01 15:38:48</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>suma수마_845192190(1도움), suma수마_861190046(1도움), 피파왕초보구단주_867000027(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-01 13:01:02</t>
+          <t>2026-10-01 15:24:08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3063,153 +3543,157 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움), syma_851236295(1도움)</t>
+          <t>피파왕초보구단주_846208722(1도움), 피파왕초보구단주_856209331(1도움), 피파왕초보구단주_851243057(1도움), 피파왕초보구단주_867000027(1도움), Gucci와퍼_864200104(1도움)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-01 12:49:37</t>
+          <t>2026-10-01 15:12:09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>피파왕초보구단주_846208722(1도움), 피파왕초보구단주_867000027(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_864200104(1도움), Gucci와퍼_852168473(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-01 11:22:46</t>
+          <t>2026-10-01 14:56:12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3_0</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_848176580(1도움)</t>
+          <t>호야국2인_848232293(1도움), 호야국2인_846192505(1도움)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-01 11:15:46</t>
+          <t>2026-10-01 14:51:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>suma수마_851234112(1도움), suma수마_840001114(1도움), suma수마_861190046(1도움), suma수마_848225439(1도움), 겐지간지_845183898(1도움)</t>
+          <t>은안_866241236(1도움), Gucci와퍼_851210697(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_840208574(1도움), Gucci와퍼_852010264(1도움)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-01 11:12:19</t>
+          <t>2026-10-01 14:45:02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_848176580(1도움), 앙쿠_863246191(1도움), Gucci차붐_861182521(1도움)</t>
+          <t>0708ManUtd_834239053(1도움), 호야국2인_846192505(1도움)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-01 11:03:11</t>
+          <t>2026-10-01 14:39:52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3219,14 +3703,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>suma수마_861013383(2도움), suma수마_826223697(1도움), suma수마_861221162(1도움), suma수마_840001114(1도움), 겐지간지_852231443(1도움), 겐지간지_845158023(2도움)</t>
+          <t>은안_848231866(1도움), 은안_856251517(1도움), 은안_856246420(1도움), 은안_866241236(1도움), Gucci와퍼_861139720(1도움)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-01 07:54:09</t>
+          <t>2026-10-01 14:31:32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3236,29 +3720,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>호야국2인_848227236(2도움), 호야국2인_848232293(1도움), 아들러_866251377(1도움), 아들러_855232639(1도움)</t>
+          <t>호야국2인_851216409(1도움), 호야국2인_845198219(1도움), Special블루_877001625(2도움), Special블루_861006975(1도움)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-01 07:42:04</t>
+          <t>2026-10-01 14:21:07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3268,29 +3752,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(2도움), 호야국2인_848217870(1도움), 호야국2인_851216409(1도움), 아들러_840191208(1도움)</t>
+          <t>호야국2인_846192505(1도움), Special블루_861006975(1도움), Special블루_856246669(2도움)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-01 06:47:50</t>
+          <t>2026-10-01 14:08:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3300,12 +3784,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3315,14 +3799,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>호야국2인_848217870(1도움), 호야국2인_848232293(1도움), 호야국2인_852001183(1도움), suma수마_861190046(1도움), suma수마_848225439(1도움)</t>
+          <t>호야국2인_848216435(1도움), 호야국2인_845198219(1도움), 호야국2인_851261865(1도움), 비주류중독_839247699(1도움), 비주류중독_848006975(1도움)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-01 06:36:26</t>
+          <t>2026-10-01 13:58:38</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3332,44 +3816,44 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>호야국2인_851216409(1도움), 호야국2인_845198219(1도움), 호야국2인_846192505(1도움), 호야국2인_848216435(1도움), suma수마_826223697(1도움)</t>
+          <t>비주류중독_848006975(3도움), 비주류중독_839247699(1도움), 비주류중독_840052241(1도움)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-30 17:45:59</t>
+          <t>2026-10-01 13:48:03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3377,31 +3861,27 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>UNIT_840192883(1도움), Voor_856256079(1도움), Voor_861000027(4도움)</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-30 17:34:22</t>
+          <t>2026-10-01 13:34:35</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3411,61 +3891,61 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UNIT_861221162(1도움), UNIT_866247257(1도움), UNIT_840228251(1도움), Voor_845009676(1도움), Voor_858025420(1도움), Voor_835183277(1도움)</t>
+          <t>아들러_840191208(1도움), Special블루_877001625(1도움)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-30 17:17:18</t>
+          <t>2026-10-01 13:24:02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), UNIT_848135455(1도움), Voor_845239231(1도움), Voor_845009676(1도움)</t>
+          <t>아들러_866251377(1도움), 아들러_861000570(1도움), Special블루_856246669(1도움), Special블루_848230666(1도움), Special블루_861006975(1도움)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-30 17:03:54</t>
+          <t>2026-10-01 13:13:07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>7_0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3475,29 +3955,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_840192883(1도움), UNIT_848265695(3도움), Voor_852233700(1도움)</t>
+          <t>앙쿠_848176580(5도움)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-30 16:46:35</t>
+          <t>2026-10-01 13:02:02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3505,127 +3985,119 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), Voor_845009676(1도움), Voor_846184943(1도움), Voor_852233700(1도움)</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-30 14:01:02</t>
+          <t>2026-10-01 13:01:02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2도움), 셀래스틴_848194765(1도움), 셀래스틴_848231866(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>앙쿠_856247103(1도움), syma_851236295(1도움)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-30 13:49:10</t>
+          <t>2026-10-01 12:49:37</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>UNIT_840210736(2도움), UNIT_867166676(1도움), UNIT_848135455(1도움), UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852241461(2도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-30 13:33:10</t>
+          <t>2026-10-01 11:22:46</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>3_0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852259694(1도움), 셀래스틴_861005680(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_848176580(1도움)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:44</t>
+          <t>2026-10-01 11:15:46</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3635,29 +4107,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gucci와퍼_852168473(3도움), Gucci와퍼_852028765(1도움), 비주류중독_840052241(1도움), 비주류중독_862180283(1도움)</t>
+          <t>suma수마_851234112(1도움), suma수마_840001114(1도움), suma수마_861190046(1도움), suma수마_848225439(1도움), 겐지간지_845183898(1도움)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-30 13:21:00</t>
+          <t>2026-10-01 11:12:19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3667,61 +4139,61 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움), UNIT_840228251(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_848176580(1도움), 앙쿠_863246191(1도움), Gucci차붐_861182521(1도움)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-30 13:12:24</t>
+          <t>2026-10-01 11:03:11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gucci와퍼_852010264(1도움), 비주류중독_834239977(1도움), 비주류중독_848006975(1도움)</t>
+          <t>suma수마_861013383(2도움), suma수마_826223697(1도움), suma수마_861221162(1도움), suma수마_840001114(1도움), 겐지간지_852231443(1도움), 겐지간지_845158023(2도움)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-30 13:10:05</t>
+          <t>2026-10-01 07:54:09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3731,29 +4203,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1도움), UNIT_840192883(2도움), UNIT_840225782(1도움), 셀래스틴_848194765(1도움), 셀래스틴_863200458(1도움)</t>
+          <t>호야국2인_848227236(2도움), 호야국2인_848232293(1도움), 아들러_866251377(1도움), 아들러_855232639(1도움)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-30 12:57:48</t>
+          <t>2026-10-01 07:42:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3763,61 +4235,61 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UNIT_863250723(1도움), UNIT_840228251(2도움), 셀래스틴_852241461(1도움)</t>
+          <t>호야국2인_848232293(2도움), 호야국2인_848217870(1도움), 호야국2인_851216409(1도움), 아들러_840191208(1도움)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:39</t>
+          <t>2026-10-01 06:47:50</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>셀래스틴_848231866(1도움), 셀래스틴_852259694(1도움), 비주류중독_839247699(1도움), 비주류중독_834239977(2도움)</t>
+          <t>호야국2인_848217870(1도움), 호야국2인_848232293(1도움), 호야국2인_852001183(1도움), suma수마_861190046(1도움), suma수마_848225439(1도움)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-30 12:24:21</t>
+          <t>2026-10-01 06:36:26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3827,14 +4299,14 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>셀래스틴_852259694(1도움), 셀래스틴_848194765(1도움)</t>
+          <t>호야국2인_851216409(1도움), 호야국2인_845198219(1도움), 호야국2인_846192505(1도움), 호야국2인_848216435(1도움), suma수마_826223697(1도움)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-30 12:00:21</t>
+          <t>2026-09-30 17:45:59</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3844,12 +4316,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3859,19 +4331,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UNIT_840225782(1도움), UNIT_867166676(1도움), 셀래스틴_848013038(1도움), 셀래스틴_852241461(2도움)</t>
+          <t>UNIT_840192883(1도움), Voor_856256079(1도움), Voor_861000027(4도움)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-30 09:47:20</t>
+          <t>2026-09-30 17:34:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3891,19 +4363,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>방덕_867001040(1도움), 방덕_848231478(2도움), Voor_845009676(1도움), Voor_845239231(1도움), Voor_835183277(1도움), Voor_848216150(1도움)</t>
+          <t>UNIT_861221162(1도움), UNIT_866247257(1도움), UNIT_840228251(1도움), Voor_845009676(1도움), Voor_858025420(1도움), Voor_835183277(1도움)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-30 09:35:39</t>
+          <t>2026-09-30 17:17:18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3913,39 +4385,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Voor_852233700(2도움), Voor_856256079(1도움), Voor_845009676(2도움), Voor_835183277(1도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), UNIT_848135455(1도움), Voor_845239231(1도움), Voor_845009676(1도움)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-30 08:27:58</t>
+          <t>2026-09-30 17:03:54</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3955,29 +4427,29 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Legend독수리_861215732(1도움), Legend독수리_852209658(1도움), syma_852274967(1도움), syma_863228092(1도움)</t>
+          <t>UNIT_848180930(1도움), UNIT_840192883(1도움), UNIT_848265695(3도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-30 08:16:55</t>
+          <t>2026-09-30 16:46:35</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3987,125 +4459,125 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Legend독수리_861215732(1도움), syma_866231913(2도움), syma_863222665(4도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), Voor_845009676(1도움), Voor_846184943(1도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-30 08:04:48</t>
+          <t>2026-09-30 14:01:02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Legend독수리_848224425(1도움), Legend독수리_826236703(1도움), syma_856233848(1도움)</t>
+          <t>UNIT_867166676(2도움), 셀래스틴_848194765(1도움), 셀래스틴_848231866(1도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-30 07:53:20</t>
+          <t>2026-09-30 13:49:10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Legend독수리_861081644(1도움), syma_846001845(2도움)</t>
+          <t>UNIT_840210736(2도움), UNIT_867166676(1도움), UNIT_848135455(1도움), UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852241461(2도움)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-29 14:16:03</t>
+          <t>2026-09-30 13:33:10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>개포동덕배_848206113(1도움), 개포동덕배_845208722(3도움), 개포동덕배_856202126(1도움), 개포동덕배_863212622(2도움), Gucci차붐_853272733(1도움), Gucci차붐_864176403(1도움)</t>
+          <t>UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852259694(1도움), 셀래스틴_861005680(1도움)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-29 14:04:54</t>
+          <t>2026-09-30 13:24:44</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4115,14 +4587,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>개포동덕배_856202126(1도움), 개포동덕배_863234396(1도움), 개포동덕배_856275298(1도움), 개포동덕배_848206113(1도움), Gucci차붐_864084333(1도움), Gucci차붐_864247686(1도움)</t>
+          <t>Gucci와퍼_852168473(3도움), Gucci와퍼_852028765(1도움), 비주류중독_840052241(1도움), 비주류중독_862180283(1도움)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-29 11:20:02</t>
+          <t>2026-09-30 13:21:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4132,76 +4604,76 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(2도움)</t>
+          <t>UNIT_840192883(1도움), UNIT_840228251(1도움)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-29 11:08:25</t>
+          <t>2026-09-30 13:12:24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UNIT_840192883(2도움), UNIT_848265695(1도움), 콩콩콩룔_851236496(1도움)</t>
+          <t>Gucci와퍼_852010264(1도움), 비주류중독_834239977(1도움), 비주류중독_848006975(1도움)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-29 10:56:21</t>
+          <t>2026-09-30 13:10:05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7_1</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4211,14 +4683,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>오스트리아_864182152(2도움), 오스트리아_864140057(1도움), 오스트리아_851236636(4도움), ShangHaiPortFC_848031432(1도움)</t>
+          <t>UNIT_867166676(1도움), UNIT_840192883(2도움), UNIT_840225782(1도움), 셀래스틴_848194765(1도움), 셀래스틴_863200458(1도움)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-29 10:47:10</t>
+          <t>2026-09-30 12:57:48</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4233,7 +4705,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4243,78 +4715,78 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_863250723(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+          <t>UNIT_863250723(1도움), UNIT_840228251(2도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-29 10:45:30</t>
+          <t>2026-09-30 12:35:39</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>오스트리아_851221671(1도움), 오스트리아_863223671(1도움), 오스트리아_863240709(1도움), 오스트리아_864140057(1도움), 오스트리아_851216275(1도움), ShangHaiPortFC_827143001(1도움)</t>
+          <t>셀래스틴_848231866(1도움), 셀래스틴_852259694(1도움), 비주류중독_839247699(1도움), 비주류중독_834239977(2도움)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-29 10:35:32</t>
+          <t>2026-09-30 12:24:21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1도움), 셀래스틴_848231866(2도움), 셀래스틴_852241461(1도움)</t>
+          <t>셀래스틴_852259694(1도움), 셀래스틴_848194765(1도움)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-29 10:18:25</t>
+          <t>2026-09-30 12:00:21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4329,39 +4801,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>UNIT_839013383(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+          <t>UNIT_840225782(1도움), UNIT_867166676(1도움), 셀래스틴_848013038(1도움), 셀래스틴_852241461(2도움)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-29 09:24:43</t>
+          <t>2026-09-30 09:47:20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4371,61 +4843,61 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(1도움), 오스트리아_863240709(1도움), 셀래스틴_846001551(1도움), 셀래스틴_848194765(2도움)</t>
+          <t>방덕_867001040(1도움), 방덕_848231478(2도움), Voor_845009676(1도움), Voor_845239231(1도움), Voor_835183277(1도움), Voor_848216150(1도움)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-29 09:13:08</t>
+          <t>2026-09-30 09:35:39</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>1_6</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>오스트리아_851221671(1도움), 셀래스틴_848231866(1도움)</t>
+          <t>Voor_852233700(2도움), Voor_856256079(1도움), Voor_845009676(2도움), Voor_835183277(1도움)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-29 09:02:47</t>
+          <t>2026-09-30 08:27:58</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4435,29 +4907,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(1도움), 오스트리아_864182152(1도움), 오스트리아_851236636(1도움), 셀래스틴_846001551(1도움)</t>
+          <t>Legend독수리_861215732(1도움), Legend독수리_852209658(1도움), syma_852274967(1도움), syma_863228092(1도움)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-29 08:51:25</t>
+          <t>2026-09-30 08:16:55</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0_2</t>
+          <t>1_6</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4467,37 +4939,517 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>셀래스틴_863200458(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>Legend독수리_861215732(1도움), syma_866231913(2도움), syma_863222665(4도움)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>2026-09-30 08:04:48</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Legend독수리_848224425(1도움), Legend독수리_826236703(1도움), syma_856233848(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-30 07:53:20</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Legend독수리_861081644(1도움), syma_846001845(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:16:03</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>7_2</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>개포동덕배_848206113(1도움), 개포동덕배_845208722(3도움), 개포동덕배_856202126(1도움), 개포동덕배_863212622(2도움), Gucci차붐_853272733(1도움), Gucci차붐_864176403(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:04:54</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>개포동덕배_856202126(1도움), 개포동덕배_863234396(1도움), 개포동덕배_856275298(1도움), 개포동덕배_848206113(1도움), Gucci차붐_864084333(1도움), Gucci차붐_864247686(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:20:02</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:08:25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(2도움), UNIT_848265695(1도움), 콩콩콩룔_851236496(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:56:21</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>7_1</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>오스트리아_864182152(2도움), 오스트리아_864140057(1도움), 오스트리아_851236636(4도움), ShangHaiPortFC_848031432(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:47:10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1도움), UNIT_863250723(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:45:30</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>오스트리아_851221671(1도움), 오스트리아_863223671(1도움), 오스트리아_863240709(1도움), 오스트리아_864140057(1도움), 오스트리아_851216275(1도움), ShangHaiPortFC_827143001(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:35:32</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1도움), 셀래스틴_848231866(2도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:18:25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>UNIT_839013383(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:24:43</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(1도움), 오스트리아_863240709(1도움), 셀래스틴_846001551(1도움), 셀래스틴_848194765(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:13:08</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>오스트리아_851221671(1도움), 셀래스틴_848231866(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:02:47</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(1도움), 오스트리아_864182152(1도움), 오스트리아_851236636(1도움), 셀래스틴_846001551(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-29 08:51:25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>0_2</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>셀래스틴_863200458(1도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>2026-09-29 04:33:11</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>여수가스</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>오스트리아</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>2_3</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>여수가스_852216393(1도움), 여수가스_861162895(1도움), 오스트리아_864140057(1도움), 오스트리아_851257075(1도움)</t>
         </is>

--- a/API데이터_경기_득점_및_도움_기록.xlsx
+++ b/API데이터_경기_득점_및_도움_기록.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:24:32</t>
+          <t>2026-10-03 17:55:25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,24 +467,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2골)</t>
+          <t>앙쿠_861049369(1골), UNIT_867166676(1골)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02 16:14:00</t>
+          <t>2026-10-03 17:38:01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -499,24 +499,24 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2골), UNIT_867166676(4골)</t>
+          <t>앙쿠_861049369(2골), 앙쿠_848176580(1골), 앙쿠_846193747(1골), 앙쿠_851194765(1골), UNIT_840192883(1골), UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02 15:54:37</t>
+          <t>2026-10-03 17:26:32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4_0</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_814226161(1골), 앙쿠_863246191(1골), 앙쿠_851194765(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_866266039(1골), UNIT_867166676(1골), UNIT_848180930(1골), UNIT_840192883(1골)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02 15:43:20</t>
+          <t>2026-10-03 17:14:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,24 +563,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0_6</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UNIT_840228251(2골), UNIT_840192883(1골), UNIT_867166676(3골)</t>
+          <t>앙쿠_866266039(2골), UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02 15:32:20</t>
+          <t>2026-10-03 16:54:05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -590,29 +590,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), UNIT_867166676(3골)</t>
+          <t>앙쿠_814226161(1골), 앙쿠_845246191(1골), 앙쿠_848176580(1골), 여수가스_861215732(2골), 여수가스_845020289(1골)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02 15:20:55</t>
+          <t>2026-10-03 16:42:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -622,40 +622,44 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>7_0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(1골), 앙쿠_848176580(4골), 앙쿠_845246191(2골)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-02 14:48:41</t>
+          <t>2026-10-03 15:45:24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -665,61 +669,61 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), UNIT_840192883(1골), UNIT_867166676(2골)</t>
+          <t>UNIT_848180930(1골), UNIT_867166676(4골), Voor_845009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-02 14:36:35</t>
+          <t>2026-10-03 15:32:25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_863246191(1골), UNIT_867166676(3골)</t>
+          <t>UNIT_848180930(3골), Voor_852233700(1골), Voor_848034079(1골)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-02 14:24:08</t>
+          <t>2026-10-03 15:20:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -729,61 +733,61 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>앙쿠_866266039(1골), 앙쿠_851194765(1골), UNIT_867166676(1골), UNIT_848180930(3골)</t>
+          <t>UNIT_851236403(1골), Voor_852233700(2골), Voor_861000027(1골)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-02 14:12:59</t>
+          <t>2026-10-03 15:09:15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_846193747(2골), 앙쿠_863246191(2골), UNIT_848180930(1골), UNIT_851236403(1골)</t>
+          <t>UNIT_840192883(2골), UNIT_867166676(1골), Voor_845009676(3골), Voor_852233700(3골)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-02 14:00:42</t>
+          <t>2026-10-03 14:56:34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -793,221 +797,221 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(2골), 앙쿠_866266039(1골), UNIT_867166676(3골), UNIT_848180930(1골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(2골), Voor_845009676(1골), Voor_845247090(1골), Voor_861000027(1골)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-02 13:50:00</t>
+          <t>2026-10-03 14:45:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 앙쿠_863246191(2골), 앙쿠_848176580(1골), UNIT_867166676(1골), UNIT_866247257(1골)</t>
+          <t>UNIT_848180930(1골), UNIT_867166676(1골), Voor_835183277(1골), Voor_845009676(2골)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-02 12:57:51</t>
+          <t>2026-10-03 14:30:09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_861005661(1골), 피파왕초보구단주_846208722(2골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(1골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(1골), Voor_845009676(1골), Voor_861000027(1골), Voor_835183277(1골), Voor_845247090(1골)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-02 12:45:28</t>
+          <t>2026-10-03 09:55:42</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_846208722(1골), 피파왕초보구단주_846045197(1골), 피파왕초보구단주_867000027(1골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(2골)</t>
+          <t>UNIT_867166676(2골), UNIT_848180930(2골), 셀래스틴_848230938(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-02 10:04:35</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 앙쿠_848176580(1골), UNIT_867166676(1골), UNIT_848180930(2골)</t>
+          <t>UNIT_848180930(1골), UNIT_840192883(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-01 15:50:18</t>
+          <t>2026-10-03 09:32:54</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>suma수마_861190046(1골), 피파왕초보구단주_861005661(3골)</t>
+          <t>UNIT_867166676(3골), UNIT_848180930(1골), UNIT_840228251(1골), 셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-01 15:38:48</t>
+          <t>2026-10-03 09:20:46</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>suma수마_861221162(1골), suma수마_861013383(1골), 피파왕초보구단주_846208722(1골), 피파왕초보구단주_856209331(1골)</t>
+          <t>UNIT_867166676(2골), UNIT_848180930(1골), 셀래스틴_848194765(1골)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-01 15:24:08</t>
+          <t>2026-10-03 09:08:53</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1017,61 +1021,61 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_846208722(2골), 피파왕초보구단주_867000027(2골), 피파왕초보구단주_861005661(1골), Gucci와퍼_852208128(1골)</t>
+          <t>UNIT_867166676(2골), UNIT_848180930(2골), 셀래스틴_861005680(1골), 셀래스틴_848194765(1골)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-01 15:12:09</t>
+          <t>2026-10-03 08:56:57</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_848209499(1골), 피파왕초보구단주_861005661(2골), Gucci와퍼_840208574(1골), Gucci와퍼_864200104(2골)</t>
+          <t>UNIT_848180930(1골), UNIT_867166676(2골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-01 14:56:12</t>
+          <t>2026-10-03 08:43:58</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1081,61 +1085,61 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0708ManUtd_848238794(1골), 호야국2인_848227236(1골), 호야국2인_848232293(1골)</t>
+          <t>UNIT_867166676(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-01 14:51:31</t>
+          <t>2026-10-02 16:24:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1_4</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>은안_852237692(1골), Gucci와퍼_852028765(1골), Gucci와퍼_852010264(1골), Gucci와퍼_864200104(2골)</t>
+          <t>앙쿠_848176580(2골)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-01 14:45:02</t>
+          <t>2026-10-02 16:14:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1145,29 +1149,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0708ManUtd_868037576(1골), 0708ManUtd_834239053(1골), 호야국2인_851216409(1골), 호야국2인_848232293(1골), 호야국2인_846192505(1골)</t>
+          <t>앙쿠_848176580(2골), UNIT_867166676(4골)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-01 14:39:52</t>
+          <t>2026-10-02 15:54:37</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1177,56 +1181,56 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>은안_877143001(3골), 은안_866241236(1골), Gucci와퍼_864200104(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_814226161(1골), 앙쿠_863246191(1골), 앙쿠_851194765(1골)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-01 14:31:32</t>
+          <t>2026-10-02 15:43:20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>0_6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(2골), 호야국2인_851216409(1골), Special블루_868001419(1골), Special블루_861047390(1골), Special블루_856246669(1골)</t>
+          <t>UNIT_840228251(2골), UNIT_840192883(1골), UNIT_867166676(3골)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-01 14:21:07</t>
+          <t>2026-10-02 15:32:20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1241,61 +1245,57 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(1골), Special블루_851251566(1골), Special블루_877001625(1골), Special블루_868001419(1골)</t>
+          <t>앙쿠_848176580(1골), UNIT_867166676(3골)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-01 14:08:57</t>
+          <t>2026-10-02 15:20:55</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>호야국2인_846192505(3골), 비주류중독_840052241(2골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-01 13:58:38</t>
+          <t>2026-10-02 14:48:41</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1305,29 +1305,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(1골), 비주류중독_829203376(1골), 비주류중독_839247699(3골), 비주류중독_840052241(1골)</t>
+          <t>앙쿠_848176580(1골), UNIT_840192883(1골), UNIT_867166676(2골)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-01 13:48:03</t>
+          <t>2026-10-02 14:36:35</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1335,27 +1335,31 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1골), 앙쿠_863246191(1골), UNIT_867166676(3골)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-01 13:34:35</t>
+          <t>2026-10-02 14:24:08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1365,46 +1369,46 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>아들러_861000570(1골), Special블루_877001625(1골), Special블루_848230666(1골)</t>
+          <t>앙쿠_866266039(1골), 앙쿠_851194765(1골), UNIT_867166676(1골), UNIT_848180930(3골)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-01 13:24:02</t>
+          <t>2026-10-02 14:12:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>아들러_855232639(2골), Special블루_868001419(1골), Special블루_877001625(2골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_846193747(2골), 앙쿠_863246191(2골), UNIT_848180930(1골), UNIT_851236403(1골)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-01 13:13:07</t>
+          <t>2026-10-02 14:00:42</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1414,29 +1418,29 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7_0</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(4골), 앙쿠_851194765(2골), 앙쿠_856247103(1골)</t>
+          <t>앙쿠_863246191(2골), 앙쿠_866266039(1골), UNIT_867166676(3골), UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-01 13:02:02</t>
+          <t>2026-10-02 13:50:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1446,40 +1450,44 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(1골), 앙쿠_863246191(2골), 앙쿠_848176580(1골), UNIT_867166676(1골), UNIT_866247257(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-01 13:01:02</t>
+          <t>2026-10-02 12:57:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1489,42 +1497,46 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), syma_867192629(1골)</t>
+          <t>피파왕초보구단주_861005661(1골), 피파왕초보구단주_846208722(2골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(1골)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-01 12:49:37</t>
+          <t>2026-10-02 12:45:28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>피파왕초보구단주_846208722(1골), 피파왕초보구단주_846045197(1골), 피파왕초보구단주_867000027(1골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(2골)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-01 11:22:46</t>
+          <t>2026-10-02 10:04:35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1534,29 +1546,29 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3_0</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 앙쿠_863246191(2골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_848176580(1골), UNIT_867166676(1골), UNIT_848180930(2골)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-01 11:15:46</t>
+          <t>2026-10-01 15:50:18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1566,76 +1578,76 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>suma수마_861190046(1골), suma수마_861221162(3골), suma수마_845192190(1골), 겐지간지_848170890(1골)</t>
+          <t>suma수마_861190046(1골), 피파왕초보구단주_861005661(3골)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-01 11:12:19</t>
+          <t>2026-10-01 15:38:48</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>앙쿠_814226161(1골), 앙쿠_848176580(2골), Gucci차붐_840191208(1골)</t>
+          <t>suma수마_861221162(1골), suma수마_861013383(1골), 피파왕초보구단주_846208722(1골), 피파왕초보구단주_856209331(1골)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-01 11:03:11</t>
+          <t>2026-10-01 15:24:08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1645,253 +1657,253 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>suma수마_861190046(2골), suma수마_861221162(1골), suma수마_840001114(2골), 겐지간지_814231747(1골), 겐지간지_852241461(1골), 겐지간지_856237679(1골)</t>
+          <t>피파왕초보구단주_846208722(2골), 피파왕초보구단주_867000027(2골), 피파왕초보구단주_861005661(1골), Gucci와퍼_852208128(1골)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-01 07:54:09</t>
+          <t>2026-10-01 15:12:09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>호야국2인_851261865(1골), 호야국2인_846192505(1골), 호야국2인_848232293(1골), 아들러_861000570(1골), 아들러_840191208(1골)</t>
+          <t>피파왕초보구단주_848209499(1골), 피파왕초보구단주_861005661(2골), Gucci와퍼_840208574(1골), Gucci와퍼_864200104(2골)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-01 07:42:04</t>
+          <t>2026-10-01 14:56:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>호야국2인</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>아들러</t>
-        </is>
-      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>호야국2인_848227236(2골), 호야국2인_848232293(1골), 호야국2인_848216435(1골), 호야국2인_851216409(1골), 아들러_291225126(1골), 아들러_866251377(1골)</t>
+          <t>0708ManUtd_848238794(1골), 호야국2인_848227236(1골), 호야국2인_848232293(1골)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-01 06:47:50</t>
+          <t>2026-10-01 14:51:31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>호야국2인_845198219(1골), 호야국2인_848232293(2골), 호야국2인_848216435(1골), suma수마_861190046(1골), suma수마_861221162(1골)</t>
+          <t>은안_852237692(1골), Gucci와퍼_852028765(1골), Gucci와퍼_852010264(1골), Gucci와퍼_864200104(2골)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-01 06:36:26</t>
+          <t>2026-10-01 14:45:02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>호야국2인</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>suma수마</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>호야국2인_851216409(1골), 호야국2인_845198219(1골), 호야국2인_846192505(1골), 호야국2인_848227236(1골), 호야국2인_848232293(1골), suma수마_861013383(1골), suma수마_861221162(1골)</t>
+          <t>0708ManUtd_868037576(1골), 0708ManUtd_834239053(1골), 호야국2인_851216409(1골), 호야국2인_848232293(1골), 호야국2인_846192505(1골)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-30 17:45:59</t>
+          <t>2026-10-01 14:39:52</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), Voor_845009676(1골), Voor_835183277(1골), Voor_852233700(3골)</t>
+          <t>은안_877143001(3골), 은안_866241236(1골), Gucci와퍼_864200104(1골)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-30 17:34:22</t>
+          <t>2026-10-01 14:31:32</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), UNIT_840192883(1골), Voor_845009676(1골), Voor_856256079(1골), Voor_852233700(2골)</t>
+          <t>호야국2인_848232293(2골), 호야국2인_851216409(1골), Special블루_868001419(1골), Special블루_861047390(1골), Special블루_856246669(1골)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-30 17:17:18</t>
+          <t>2026-10-01 14:21:07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), UNIT_848180930(2골), Voor_852233700(2골)</t>
+          <t>호야국2인_848232293(1골), Special블루_851251566(1골), Special블루_877001625(1골), Special블루_868001419(1골)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-30 17:03:54</t>
+          <t>2026-10-01 14:08:57</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1901,29 +1913,29 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UNIT_867166676(5골), Voor_845009676(1골)</t>
+          <t>호야국2인_846192505(3골), 비주류중독_840052241(2골)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-30 16:46:35</t>
+          <t>2026-10-01 13:58:38</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1933,29 +1945,29 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), Voor_845009676(1골), Voor_852233700(2골)</t>
+          <t>호야국2인_848232293(1골), 비주류중독_829203376(1골), 비주류중독_839247699(3골), 비주류중독_840052241(1골)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-30 14:01:02</t>
+          <t>2026-10-01 13:48:03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1963,63 +1975,59 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>UNIT_861221162(2골), 셀래스틴_861005680(4골), 셀래스틴_848231866(1골)</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-30 13:49:10</t>
+          <t>2026-10-01 13:34:35</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UNIT_867166676(3골), UNIT_861221162(2골), 셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
+          <t>아들러_861000570(1골), Special블루_877001625(1골), Special블루_848230666(1골)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-30 13:33:10</t>
+          <t>2026-10-01 13:24:02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2029,29 +2037,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(3골), 셀래스틴_852241461(1골)</t>
+          <t>아들러_855232639(2골), Special블루_868001419(1골), Special블루_877001625(2골)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:44</t>
+          <t>2026-10-01 13:13:07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>7_0</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2061,125 +2069,117 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gucci와퍼_864200104(4골), 비주류중독_840052241(1골), 비주류중독_825000240(1골), 비주류중독_839247699(1골)</t>
+          <t>앙쿠_863246191(4골), 앙쿠_851194765(2골), 앙쿠_856247103(1골)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-30 13:21:00</t>
+          <t>2026-10-01 13:02:02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>UNIT_848180930(1골), UNIT_867166676(1골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-30 13:12:24</t>
+          <t>2026-10-01 13:01:02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gucci와퍼_852028765(1골), Gucci와퍼_852168473(1골), 비주류중독_834239977(1골), 비주류중독_840052241(1골), 비주류중독_839247699(1골)</t>
+          <t>앙쿠_848176580(1골), syma_867192629(1골)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-30 13:10:05</t>
+          <t>2026-10-01 12:49:37</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>UNIT_867166676(3골), UNIT_840192883(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(2골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-30 12:57:48</t>
+          <t>2026-10-01 11:22:46</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>3_0</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2189,61 +2189,61 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), UNIT_848180930(1골), 셀래스틴_846001551(1골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_863246191(2골)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:39</t>
+          <t>2026-10-01 11:15:46</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 비주류중독_848006975(2골), 비주류중독_839247699(1골)</t>
+          <t>suma수마_861190046(1골), suma수마_861221162(3골), suma수마_845192190(1골), 겐지간지_848170890(1골)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-30 12:24:21</t>
+          <t>2026-10-01 11:12:19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2253,125 +2253,125 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
+          <t>앙쿠_814226161(1골), 앙쿠_848176580(2골), Gucci차붐_840191208(1골)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-30 12:00:21</t>
+          <t>2026-10-01 11:03:11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), 셀래스틴_861005680(2골), 셀래스틴_852241461(1골)</t>
+          <t>suma수마_861190046(2골), suma수마_861221162(1골), suma수마_840001114(2골), 겐지간지_814231747(1골), 겐지간지_852241461(1골), 겐지간지_856237679(1골)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-30 09:47:20</t>
+          <t>2026-10-01 07:54:09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>방덕_848007512(1골), 방덕_856228093(1골), 방덕_863184200(1골), Voor_845247090(2골), Voor_852233700(2골)</t>
+          <t>호야국2인_851261865(1골), 호야국2인_846192505(1골), 호야국2인_848232293(1골), 아들러_861000570(1골), 아들러_840191208(1골)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-30 09:35:39</t>
+          <t>2026-10-01 07:42:04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>방덕_101001419(1골), Voor_852233700(3골), Voor_845009676(2골), Voor_845247090(1골)</t>
+          <t>호야국2인_848227236(2골), 호야국2인_848232293(1골), 호야국2인_848216435(1골), 호야국2인_851216409(1골), 아들러_291225126(1골), 아들러_866251377(1골)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-30 08:27:58</t>
+          <t>2026-10-01 06:47:50</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2381,93 +2381,93 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Legend독수리_825190048(1골), Legend독수리_861081644(1골), Legend독수리_848188350(1골), syma_863228092(1골), syma_856233848(1골)</t>
+          <t>호야국2인_845198219(1골), 호야국2인_848232293(2골), 호야국2인_848216435(1골), suma수마_861190046(1골), suma수마_861221162(1골)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-30 08:16:55</t>
+          <t>2026-10-01 06:36:26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Legend독수리_825190048(1골), syma_866231913(1골), syma_863262863(1골), syma_846001845(3골), syma_852274967(1골)</t>
+          <t>호야국2인_851216409(1골), 호야국2인_845198219(1골), 호야국2인_846192505(1골), 호야국2인_848227236(1골), 호야국2인_848232293(1골), suma수마_861013383(1골), suma수마_861221162(1골)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-30 08:04:48</t>
+          <t>2026-09-30 17:45:59</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Legend독수리_861215732(1골), Legend독수리_852209658(1골), syma_866231913(1골), syma_863228092(1골)</t>
+          <t>UNIT_867166676(2골), Voor_845009676(1골), Voor_835183277(1골), Voor_852233700(3골)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-30 07:53:20</t>
+          <t>2026-09-30 17:34:22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2477,29 +2477,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Legend독수리_861215732(1골), syma_863222665(2골)</t>
+          <t>UNIT_848180930(2골), UNIT_840192883(1골), Voor_845009676(1골), Voor_856256079(1골), Voor_852233700(2골)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-29 14:16:03</t>
+          <t>2026-09-30 17:17:18</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2509,29 +2509,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>개포동덕배_848206113(1골), 개포동덕배_845208722(1골), 개포동덕배_856202126(1골), 개포동덕배_845190048(4골), Gucci차붐_864247686(1골), Gucci차붐_864176403(1골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(2골), Voor_852233700(2골)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-29 14:04:54</t>
+          <t>2026-09-30 17:03:54</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2541,14 +2541,14 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(3골), 개포동덕배_848206113(1골), Gucci차붐_853272733(1골), Gucci차붐_853242004(1골)</t>
+          <t>UNIT_867166676(5골), Voor_845009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-29 11:20:02</t>
+          <t>2026-09-30 16:46:35</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2573,14 +2573,14 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(2골)</t>
+          <t>UNIT_848180930(2골), Voor_845009676(1골), Voor_852233700(2골)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-29 11:08:25</t>
+          <t>2026-09-30 14:01:02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2590,44 +2590,44 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_848135455(1골), UNIT_867166676(1골), 콩콩콩룔_866223710(1골), 콩콩콩룔_867223848(1골)</t>
+          <t>UNIT_861221162(2골), 셀래스틴_861005680(4골), 셀래스틴_848231866(1골)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-29 10:56:21</t>
+          <t>2026-09-30 13:49:10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>7_1</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2637,14 +2637,14 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(3골), 오스트리아_851221671(1골), 오스트리아_864182152(1골), 오스트리아_864140057(1골), 오스트리아_851216275(1골), ShangHaiPortFC_864191910(1골)</t>
+          <t>UNIT_867166676(3골), UNIT_861221162(2골), 셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-29 10:47:10</t>
+          <t>2026-09-30 13:33:10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2659,39 +2659,39 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1골), UNIT_867166676(2골), 셀래스틴_848231866(1골), 셀래스틴_848230938(1골)</t>
+          <t>UNIT_848180930(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(3골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-29 10:45:30</t>
+          <t>2026-09-30 13:24:44</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(2골), 오스트리아_864182152(1골), 오스트리아_864199266(2골), ShangHaiPortFC_861051412(1골)</t>
+          <t>Gucci와퍼_864200104(4골), 비주류중독_840052241(1골), 비주류중독_825000240(1골), 비주류중독_839247699(1골)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-29 10:35:32</t>
+          <t>2026-09-30 13:21:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2723,61 +2723,61 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), 셀래스틴_846001551(1골), 셀래스틴_852241461(2골)</t>
+          <t>UNIT_848180930(1골), UNIT_867166676(1골)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-29 10:18:25</t>
+          <t>2026-09-30 13:12:24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), 셀래스틴_848194765(1골)</t>
+          <t>Gucci와퍼_852028765(1골), Gucci와퍼_852168473(1골), 비주류중독_834239977(1골), 비주류중독_840052241(1골), 비주류중독_839247699(1골)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-29 09:24:43</t>
+          <t>2026-09-30 13:10:05</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2787,29 +2787,29 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(1골), 오스트리아_851236636(1골), 셀래스틴_846001551(1골), 셀래스틴_861005680(1골), 셀래스틴_848230938(1골)</t>
+          <t>UNIT_867166676(3골), UNIT_840192883(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(2골)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-29 09:13:08</t>
+          <t>2026-09-30 12:57:48</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2819,111 +2819,751 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(1골), 셀래스틴_861005680(1골)</t>
+          <t>UNIT_867166676(2골), UNIT_848180930(1골), 셀래스틴_846001551(1골)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-29 09:02:47</t>
+          <t>2026-09-30 12:35:39</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(1골), 오스트리아_864199266(1골), 오스트리아_864182152(1골), 셀래스틴_861005680(1골)</t>
+          <t>셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 비주류중독_848006975(2골), 비주류중독_839247699(1골)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-29 08:51:25</t>
+          <t>2026-09-30 12:24:21</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0_2</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>셀래스틴_846001551(1골), 셀래스틴_861005680(1골)</t>
+          <t>셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>2026-09-30 12:00:21</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(2골), 셀래스틴_861005680(2골), 셀래스틴_852241461(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:47:20</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3_4</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>방덕_848007512(1골), 방덕_856228093(1골), 방덕_863184200(1골), Voor_845247090(2골), Voor_852233700(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:35:39</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1_6</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>방덕_101001419(1골), Voor_852233700(3골), Voor_845009676(2골), Voor_845247090(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:27:58</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Legend독수리_825190048(1골), Legend독수리_861081644(1골), Legend독수리_848188350(1골), syma_863228092(1골), syma_856233848(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:16:55</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1_6</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Legend독수리_825190048(1골), syma_866231913(1골), syma_863262863(1골), syma_846001845(3골), syma_852274967(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:04:48</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1골), Legend독수리_852209658(1골), syma_866231913(1골), syma_863228092(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-30 07:53:20</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1골), syma_863222665(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:16:03</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>7_2</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>개포동덕배_848206113(1골), 개포동덕배_845208722(1골), 개포동덕배_856202126(1골), 개포동덕배_845190048(4골), Gucci차붐_864247686(1골), Gucci차붐_864176403(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:04:54</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>개포동덕배_845190048(3골), 개포동덕배_848206113(1골), Gucci차붐_853272733(1골), Gucci차붐_853242004(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:20:02</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:08:25</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), UNIT_848135455(1골), UNIT_867166676(1골), 콩콩콩룔_866223710(1골), 콩콩콩룔_867223848(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:56:21</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>7_1</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(3골), 오스트리아_851221671(1골), 오스트리아_864182152(1골), 오스트리아_864140057(1골), 오스트리아_851216275(1골), ShangHaiPortFC_864191910(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:47:10</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>UNIT_840228251(1골), UNIT_867166676(2골), 셀래스틴_848231866(1골), 셀래스틴_848230938(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:45:30</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(2골), 오스트리아_864182152(1골), 오스트리아_864199266(2골), ShangHaiPortFC_861051412(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:35:32</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), 셀래스틴_846001551(1골), 셀래스틴_852241461(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:18:25</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), 셀래스틴_848194765(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:24:43</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(1골), 오스트리아_851236636(1골), 셀래스틴_846001551(1골), 셀래스틴_861005680(1골), 셀래스틴_848230938(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:13:08</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:02:47</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(1골), 오스트리아_864199266(1골), 오스트리아_864182152(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-29 08:51:25</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>0_2</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>셀래스틴_846001551(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
           <t>2026-09-29 04:33:11</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>여수가스</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>오스트리아</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>2_3</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>여수가스_828231747(1골), 여수가스_852274967(1골), 오스트리아_864191566(1골), 오스트리아_864199266(2골)</t>
         </is>
@@ -2940,7 +3580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2978,7 +3618,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:24:32</t>
+          <t>2026-10-03 17:55:25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2993,24 +3633,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>앙쿠_846193747(2도움)</t>
+          <t>앙쿠_851194765(1도움), UNIT_840210736(1도움)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02 16:14:00</t>
+          <t>2026-10-03 17:38:01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3025,24 +3665,24 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_814226161(1도움), UNIT_840228251(3도움), UNIT_845207439(1도움)</t>
+          <t>앙쿠_848176580(2도움), 앙쿠_851194765(2도움), UNIT_840228251(1도움), UNIT_840225782(1도움)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02 15:54:37</t>
+          <t>2026-10-03 17:26:32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3057,24 +3697,24 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4_0</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(3도움), 앙쿠_851194765(1도움)</t>
+          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), UNIT_867166676(2도움), UNIT_840228251(1도움)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02 15:43:20</t>
+          <t>2026-10-03 17:14:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3089,24 +3729,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0_6</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UNIT_840210736(1도움), UNIT_840228251(1도움), UNIT_840225782(1도움), UNIT_840192883(1도움), UNIT_863250723(1도움), UNIT_848135455(1도움)</t>
+          <t>앙쿠_856247103(1도움), 앙쿠_846186345(1도움), UNIT_840192883(1도움)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02 15:32:20</t>
+          <t>2026-10-03 16:54:05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3116,29 +3756,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>앙쿠_846193747(1도움), UNIT_840192883(1도움), UNIT_845207439(1도움)</t>
+          <t>앙쿠_845246191(1도움), 앙쿠_848176580(1도움), 앙쿠_846193747(1도움), 여수가스_846001551(1도움), 여수가스_861215732(1도움), 여수가스_828231747(1도움)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02 15:20:55</t>
+          <t>2026-10-03 16:42:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3148,40 +3788,44 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>7_0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(2도움), 앙쿠_845246191(3도움), 앙쿠_846193747(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-02 14:48:41</t>
+          <t>2026-10-03 15:45:24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3191,61 +3835,61 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(1도움), UNIT_840192883(2도움), UNIT_840228251(1도움)</t>
+          <t>UNIT_848180930(1도움), UNIT_840192883(1도움), UNIT_840225782(1도움), Voor_856256079(1도움)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-02 14:36:35</t>
+          <t>2026-10-03 15:32:25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(1도움), 앙쿠_851194765(1도움), UNIT_848265695(1도움), UNIT_840192883(2도움)</t>
+          <t>UNIT_867166676(1도움), UNIT_840228251(1도움), UNIT_848265695(1도움), Voor_856256079(1도움), Voor_845247090(1도움)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-02 14:24:08</t>
+          <t>2026-10-03 15:20:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3255,61 +3899,61 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_840228251(1도움), UNIT_840192883(2도움), UNIT_840225782(1도움)</t>
+          <t>UNIT_840192883(1도움), Voor_845009676(3도움)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-02 14:12:59</t>
+          <t>2026-10-03 15:09:15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2도움), 앙쿠_851194765(1도움), UNIT_840192883(2도움)</t>
+          <t>UNIT_867166676(1도움), UNIT_848180930(1도움), UNIT_863250723(1도움), Voor_861000027(2도움), Voor_845009676(2도움), Voor_835183277(2도움)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-02 14:00:42</t>
+          <t>2026-10-03 14:56:34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3319,221 +3963,221 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2도움), 앙쿠_856247103(1도움), UNIT_840228251(3도움), UNIT_840225782(1도움)</t>
+          <t>UNIT_867166676(1도움), UNIT_863250723(1도움), UNIT_840210736(1도움), Voor_856256079(1도움), Voor_835183277(1도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-02 13:50:00</t>
+          <t>2026-10-03 14:45:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(2도움), 앙쿠_863246191(2도움), UNIT_840228251(1도움)</t>
+          <t>UNIT_840210736(1도움), UNIT_840228251(1도움), Voor_835183277(2도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-02 12:57:51</t>
+          <t>2026-10-03 14:30:09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_846045197(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_867220502(1도움)</t>
+          <t>UNIT_840210736(1도움), UNIT_840225782(1도움), Voor_845239231(1도움), Voor_852233700(1도움), Voor_835183277(1도움), Voor_845247090(1도움)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-02 12:45:28</t>
+          <t>2026-10-03 09:55:42</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_846045197(1도움), 피파왕초보구단주_867000027(2도움), 콩콩콩룔_867220502(1도움)</t>
+          <t>UNIT_840225782(1도움), UNIT_867166676(1도움), UNIT_848265695(1도움), UNIT_840192883(1도움), 셀래스틴_861005680(1도움), 셀래스틴_848194765(1도움)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-02 10:04:35</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(1도움), UNIT_840210736(1도움), UNIT_840228251(2도움)</t>
+          <t>UNIT_848135455(1도움), 셀래스틴_861005680(1도움)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-01 15:50:18</t>
+          <t>2026-10-03 09:32:54</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>suma수마_861221162(1도움), 피파왕초보구단주_867000027(1도움), 피파왕초보구단주_851243057(2도움)</t>
+          <t>UNIT_848180930(1도움), UNIT_840228251(2도움), UNIT_840192883(2도움), 셀래스틴_848194765(1도움)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-01 15:38:48</t>
+          <t>2026-10-03 09:20:46</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>suma수마_845192190(1도움), suma수마_861190046(1도움), 피파왕초보구단주_867000027(1도움)</t>
+          <t>UNIT_840192883(2도움), UNIT_840210736(1도움), 셀래스틴_848230938(1도움)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-01 15:24:08</t>
+          <t>2026-10-03 09:08:53</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3543,61 +4187,61 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_846208722(1도움), 피파왕초보구단주_856209331(1도움), 피파왕초보구단주_851243057(1도움), 피파왕초보구단주_867000027(1도움), Gucci와퍼_864200104(1도움)</t>
+          <t>UNIT_867166676(2도움), UNIT_840210736(1도움), UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_848194765(1도움)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-01 15:12:09</t>
+          <t>2026-10-03 08:56:57</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_846208722(1도움), 피파왕초보구단주_867000027(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_864200104(1도움), Gucci와퍼_852168473(1도움)</t>
+          <t>UNIT_840225782(1도움), UNIT_848135455(1도움), 셀래스틴_863233419(1도움)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-01 14:56:12</t>
+          <t>2026-10-03 08:43:58</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3607,61 +4251,61 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(1도움), 호야국2인_846192505(1도움)</t>
+          <t>UNIT_840192883(1도움)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-01 14:51:31</t>
+          <t>2026-10-02 16:24:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1_4</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>은안_866241236(1도움), Gucci와퍼_851210697(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_840208574(1도움), Gucci와퍼_852010264(1도움)</t>
+          <t>앙쿠_846193747(2도움)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-01 14:45:02</t>
+          <t>2026-10-02 16:14:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3671,29 +4315,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0708ManUtd_834239053(1도움), 호야국2인_846192505(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_814226161(1도움), UNIT_840228251(3도움), UNIT_845207439(1도움)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-01 14:39:52</t>
+          <t>2026-10-02 15:54:37</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3703,56 +4347,56 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>은안_848231866(1도움), 은안_856251517(1도움), 은안_856246420(1도움), 은안_866241236(1도움), Gucci와퍼_861139720(1도움)</t>
+          <t>앙쿠_863246191(3도움), 앙쿠_851194765(1도움)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-01 14:31:32</t>
+          <t>2026-10-02 15:43:20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>0_6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>호야국2인_851216409(1도움), 호야국2인_845198219(1도움), Special블루_877001625(2도움), Special블루_861006975(1도움)</t>
+          <t>UNIT_840210736(1도움), UNIT_840228251(1도움), UNIT_840225782(1도움), UNIT_840192883(1도움), UNIT_863250723(1도움), UNIT_848135455(1도움)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-01 14:21:07</t>
+          <t>2026-10-02 15:32:20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3767,61 +4411,57 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>호야국2인_846192505(1도움), Special블루_861006975(1도움), Special블루_856246669(2도움)</t>
+          <t>앙쿠_846193747(1도움), UNIT_840192883(1도움), UNIT_845207439(1도움)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-01 14:08:57</t>
+          <t>2026-10-02 15:20:55</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>호야국2인_848216435(1도움), 호야국2인_845198219(1도움), 호야국2인_851261865(1도움), 비주류중독_839247699(1도움), 비주류중독_848006975(1도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-01 13:58:38</t>
+          <t>2026-10-02 14:48:41</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3831,29 +4471,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>비주류중독_848006975(3도움), 비주류중독_839247699(1도움), 비주류중독_840052241(1도움)</t>
+          <t>앙쿠_863246191(1도움), UNIT_840192883(2도움), UNIT_840228251(1도움)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-01 13:48:03</t>
+          <t>2026-10-02 14:36:35</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3861,27 +4501,31 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>앙쿠_863246191(1도움), 앙쿠_851194765(1도움), UNIT_848265695(1도움), UNIT_840192883(2도움)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-01 13:34:35</t>
+          <t>2026-10-02 14:24:08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3891,46 +4535,46 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>아들러_840191208(1도움), Special블루_877001625(1도움)</t>
+          <t>앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_840228251(1도움), UNIT_840192883(2도움), UNIT_840225782(1도움)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-01 13:24:02</t>
+          <t>2026-10-02 14:12:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>아들러_866251377(1도움), 아들러_861000570(1도움), Special블루_856246669(1도움), Special블루_848230666(1도움), Special블루_861006975(1도움)</t>
+          <t>앙쿠_848176580(2도움), 앙쿠_851194765(1도움), UNIT_840192883(2도움)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-01 13:13:07</t>
+          <t>2026-10-02 14:00:42</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3940,29 +4584,29 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7_0</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(5도움)</t>
+          <t>앙쿠_848176580(2도움), 앙쿠_856247103(1도움), UNIT_840228251(3도움), UNIT_840225782(1도움)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-01 13:02:02</t>
+          <t>2026-10-02 13:50:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3972,40 +4616,44 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(2도움), 앙쿠_863246191(2도움), UNIT_840228251(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-01 13:01:02</t>
+          <t>2026-10-02 12:57:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4015,42 +4663,46 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움), syma_851236295(1도움)</t>
+          <t>피파왕초보구단주_846045197(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_867220502(1도움)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-01 12:49:37</t>
+          <t>2026-10-02 12:45:28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>피파왕초보구단주_846045197(1도움), 피파왕초보구단주_867000027(2도움), 콩콩콩룔_867220502(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-01 11:22:46</t>
+          <t>2026-10-02 10:04:35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4060,29 +4712,29 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3_0</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_848176580(1도움)</t>
+          <t>앙쿠_863246191(1도움), UNIT_840210736(1도움), UNIT_840228251(2도움)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-01 11:15:46</t>
+          <t>2026-10-01 15:50:18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4092,76 +4744,76 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>suma수마_851234112(1도움), suma수마_840001114(1도움), suma수마_861190046(1도움), suma수마_848225439(1도움), 겐지간지_845183898(1도움)</t>
+          <t>suma수마_861221162(1도움), 피파왕초보구단주_867000027(1도움), 피파왕초보구단주_851243057(2도움)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-01 11:12:19</t>
+          <t>2026-10-01 15:38:48</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_848176580(1도움), 앙쿠_863246191(1도움), Gucci차붐_861182521(1도움)</t>
+          <t>suma수마_845192190(1도움), suma수마_861190046(1도움), 피파왕초보구단주_867000027(1도움)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-01 11:03:11</t>
+          <t>2026-10-01 15:24:08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4171,253 +4823,253 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>suma수마_861013383(2도움), suma수마_826223697(1도움), suma수마_861221162(1도움), suma수마_840001114(1도움), 겐지간지_852231443(1도움), 겐지간지_845158023(2도움)</t>
+          <t>피파왕초보구단주_846208722(1도움), 피파왕초보구단주_856209331(1도움), 피파왕초보구단주_851243057(1도움), 피파왕초보구단주_867000027(1도움), Gucci와퍼_864200104(1도움)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-01 07:54:09</t>
+          <t>2026-10-01 15:12:09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>호야국2인_848227236(2도움), 호야국2인_848232293(1도움), 아들러_866251377(1도움), 아들러_855232639(1도움)</t>
+          <t>피파왕초보구단주_846208722(1도움), 피파왕초보구단주_867000027(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_864200104(1도움), Gucci와퍼_852168473(1도움)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-01 07:42:04</t>
+          <t>2026-10-01 14:56:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>호야국2인</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>아들러</t>
-        </is>
-      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(2도움), 호야국2인_848217870(1도움), 호야국2인_851216409(1도움), 아들러_840191208(1도움)</t>
+          <t>호야국2인_848232293(1도움), 호야국2인_846192505(1도움)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-01 06:47:50</t>
+          <t>2026-10-01 14:51:31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>호야국2인_848217870(1도움), 호야국2인_848232293(1도움), 호야국2인_852001183(1도움), suma수마_861190046(1도움), suma수마_848225439(1도움)</t>
+          <t>은안_866241236(1도움), Gucci와퍼_851210697(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_840208574(1도움), Gucci와퍼_852010264(1도움)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-01 06:36:26</t>
+          <t>2026-10-01 14:45:02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>0708ManUtd</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>호야국2인</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>suma수마</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>호야국2인_851216409(1도움), 호야국2인_845198219(1도움), 호야국2인_846192505(1도움), 호야국2인_848216435(1도움), suma수마_826223697(1도움)</t>
+          <t>0708ManUtd_834239053(1도움), 호야국2인_846192505(1도움)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-30 17:45:59</t>
+          <t>2026-10-01 14:39:52</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움), Voor_856256079(1도움), Voor_861000027(4도움)</t>
+          <t>은안_848231866(1도움), 은안_856251517(1도움), 은안_856246420(1도움), 은안_866241236(1도움), Gucci와퍼_861139720(1도움)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-30 17:34:22</t>
+          <t>2026-10-01 14:31:32</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UNIT_861221162(1도움), UNIT_866247257(1도움), UNIT_840228251(1도움), Voor_845009676(1도움), Voor_858025420(1도움), Voor_835183277(1도움)</t>
+          <t>호야국2인_851216409(1도움), 호야국2인_845198219(1도움), Special블루_877001625(2도움), Special블루_861006975(1도움)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-30 17:17:18</t>
+          <t>2026-10-01 14:21:07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), UNIT_848135455(1도움), Voor_845239231(1도움), Voor_845009676(1도움)</t>
+          <t>호야국2인_846192505(1도움), Special블루_861006975(1도움), Special블루_856246669(2도움)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-30 17:03:54</t>
+          <t>2026-10-01 14:08:57</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4427,29 +5079,29 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_840192883(1도움), UNIT_848265695(3도움), Voor_852233700(1도움)</t>
+          <t>호야국2인_848216435(1도움), 호야국2인_845198219(1도움), 호야국2인_851261865(1도움), 비주류중독_839247699(1도움), 비주류중독_848006975(1도움)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-30 16:46:35</t>
+          <t>2026-10-01 13:58:38</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4459,29 +5111,29 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), Voor_845009676(1도움), Voor_846184943(1도움), Voor_852233700(1도움)</t>
+          <t>비주류중독_848006975(3도움), 비주류중독_839247699(1도움), 비주류중독_840052241(1도움)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-30 14:01:02</t>
+          <t>2026-10-01 13:48:03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4489,63 +5141,59 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>UNIT_867166676(2도움), 셀래스틴_848194765(1도움), 셀래스틴_848231866(1도움), 셀래스틴_852241461(1도움)</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-30 13:49:10</t>
+          <t>2026-10-01 13:34:35</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UNIT_840210736(2도움), UNIT_867166676(1도움), UNIT_848135455(1도움), UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852241461(2도움)</t>
+          <t>아들러_840191208(1도움), Special블루_877001625(1도움)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-30 13:33:10</t>
+          <t>2026-10-01 13:24:02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4555,29 +5203,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852259694(1도움), 셀래스틴_861005680(1도움)</t>
+          <t>아들러_866251377(1도움), 아들러_861000570(1도움), Special블루_856246669(1도움), Special블루_848230666(1도움), Special블루_861006975(1도움)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:44</t>
+          <t>2026-10-01 13:13:07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>7_0</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4587,125 +5235,117 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gucci와퍼_852168473(3도움), Gucci와퍼_852028765(1도움), 비주류중독_840052241(1도움), 비주류중독_862180283(1도움)</t>
+          <t>앙쿠_848176580(5도움)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-30 13:21:00</t>
+          <t>2026-10-01 13:02:02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>UNIT_840192883(1도움), UNIT_840228251(1도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-30 13:12:24</t>
+          <t>2026-10-01 13:01:02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gucci와퍼_852010264(1도움), 비주류중독_834239977(1도움), 비주류중독_848006975(1도움)</t>
+          <t>앙쿠_856247103(1도움), syma_851236295(1도움)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-30 13:10:05</t>
+          <t>2026-10-01 12:49:37</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>UNIT_867166676(1도움), UNIT_840192883(2도움), UNIT_840225782(1도움), 셀래스틴_848194765(1도움), 셀래스틴_863200458(1도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-30 12:57:48</t>
+          <t>2026-10-01 11:22:46</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>3_0</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4715,61 +5355,61 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UNIT_863250723(1도움), UNIT_840228251(2도움), 셀래스틴_852241461(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_848176580(1도움)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:39</t>
+          <t>2026-10-01 11:15:46</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>셀래스틴_848231866(1도움), 셀래스틴_852259694(1도움), 비주류중독_839247699(1도움), 비주류중독_834239977(2도움)</t>
+          <t>suma수마_851234112(1도움), suma수마_840001114(1도움), suma수마_861190046(1도움), suma수마_848225439(1도움), 겐지간지_845183898(1도움)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-30 12:24:21</t>
+          <t>2026-10-01 11:12:19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4779,125 +5419,125 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>셀래스틴_852259694(1도움), 셀래스틴_848194765(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_848176580(1도움), 앙쿠_863246191(1도움), Gucci차붐_861182521(1도움)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-30 12:00:21</t>
+          <t>2026-10-01 11:03:11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>UNIT_840225782(1도움), UNIT_867166676(1도움), 셀래스틴_848013038(1도움), 셀래스틴_852241461(2도움)</t>
+          <t>suma수마_861013383(2도움), suma수마_826223697(1도움), suma수마_861221162(1도움), suma수마_840001114(1도움), 겐지간지_852231443(1도움), 겐지간지_845158023(2도움)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-30 09:47:20</t>
+          <t>2026-10-01 07:54:09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>방덕_867001040(1도움), 방덕_848231478(2도움), Voor_845009676(1도움), Voor_845239231(1도움), Voor_835183277(1도움), Voor_848216150(1도움)</t>
+          <t>호야국2인_848227236(2도움), 호야국2인_848232293(1도움), 아들러_866251377(1도움), 아들러_855232639(1도움)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-30 09:35:39</t>
+          <t>2026-10-01 07:42:04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Voor_852233700(2도움), Voor_856256079(1도움), Voor_845009676(2도움), Voor_835183277(1도움)</t>
+          <t>호야국2인_848232293(2도움), 호야국2인_848217870(1도움), 호야국2인_851216409(1도움), 아들러_840191208(1도움)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-30 08:27:58</t>
+          <t>2026-10-01 06:47:50</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4907,93 +5547,93 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Legend독수리_861215732(1도움), Legend독수리_852209658(1도움), syma_852274967(1도움), syma_863228092(1도움)</t>
+          <t>호야국2인_848217870(1도움), 호야국2인_848232293(1도움), 호야국2인_852001183(1도움), suma수마_861190046(1도움), suma수마_848225439(1도움)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-30 08:16:55</t>
+          <t>2026-10-01 06:36:26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Legend독수리_861215732(1도움), syma_866231913(2도움), syma_863222665(4도움)</t>
+          <t>호야국2인_851216409(1도움), 호야국2인_845198219(1도움), 호야국2인_846192505(1도움), 호야국2인_848216435(1도움), suma수마_826223697(1도움)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-30 08:04:48</t>
+          <t>2026-09-30 17:45:59</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Legend독수리_848224425(1도움), Legend독수리_826236703(1도움), syma_856233848(1도움)</t>
+          <t>UNIT_840192883(1도움), Voor_856256079(1도움), Voor_861000027(4도움)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-30 07:53:20</t>
+          <t>2026-09-30 17:34:22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5003,29 +5643,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Legend독수리_861081644(1도움), syma_846001845(2도움)</t>
+          <t>UNIT_861221162(1도움), UNIT_866247257(1도움), UNIT_840228251(1도움), Voor_845009676(1도움), Voor_858025420(1도움), Voor_835183277(1도움)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-29 14:16:03</t>
+          <t>2026-09-30 17:17:18</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5035,29 +5675,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>개포동덕배_848206113(1도움), 개포동덕배_845208722(3도움), 개포동덕배_856202126(1도움), 개포동덕배_863212622(2도움), Gucci차붐_853272733(1도움), Gucci차붐_864176403(1도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), UNIT_848135455(1도움), Voor_845239231(1도움), Voor_845009676(1도움)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-29 14:04:54</t>
+          <t>2026-09-30 17:03:54</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5067,14 +5707,14 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>개포동덕배_856202126(1도움), 개포동덕배_863234396(1도움), 개포동덕배_856275298(1도움), 개포동덕배_848206113(1도움), Gucci차붐_864084333(1도움), Gucci차붐_864247686(1도움)</t>
+          <t>UNIT_848180930(1도움), UNIT_840192883(1도움), UNIT_848265695(3도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-29 11:20:02</t>
+          <t>2026-09-30 16:46:35</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5084,12 +5724,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5099,14 +5739,14 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(2도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), Voor_845009676(1도움), Voor_846184943(1도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-29 11:08:25</t>
+          <t>2026-09-30 14:01:02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5116,44 +5756,44 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UNIT_840192883(2도움), UNIT_848265695(1도움), 콩콩콩룔_851236496(1도움)</t>
+          <t>UNIT_867166676(2도움), 셀래스틴_848194765(1도움), 셀래스틴_848231866(1도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-29 10:56:21</t>
+          <t>2026-09-30 13:49:10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>7_1</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5163,14 +5803,14 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>오스트리아_864182152(2도움), 오스트리아_864140057(1도움), 오스트리아_851236636(4도움), ShangHaiPortFC_848031432(1도움)</t>
+          <t>UNIT_840210736(2도움), UNIT_867166676(1도움), UNIT_848135455(1도움), UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852241461(2도움)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-29 10:47:10</t>
+          <t>2026-09-30 13:33:10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5185,39 +5825,39 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_863250723(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+          <t>UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852259694(1도움), 셀래스틴_861005680(1도움)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-29 10:45:30</t>
+          <t>2026-09-30 13:24:44</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5227,14 +5867,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>오스트리아_851221671(1도움), 오스트리아_863223671(1도움), 오스트리아_863240709(1도움), 오스트리아_864140057(1도움), 오스트리아_851216275(1도움), ShangHaiPortFC_827143001(1도움)</t>
+          <t>Gucci와퍼_852168473(3도움), Gucci와퍼_852028765(1도움), 비주류중독_840052241(1도움), 비주류중독_862180283(1도움)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-29 10:35:32</t>
+          <t>2026-09-30 13:21:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5249,61 +5889,61 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1도움), 셀래스틴_848231866(2도움), 셀래스틴_852241461(1도움)</t>
+          <t>UNIT_840192883(1도움), UNIT_840228251(1도움)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-29 10:18:25</t>
+          <t>2026-09-30 13:12:24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>UNIT_839013383(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+          <t>Gucci와퍼_852010264(1도움), 비주류중독_834239977(1도움), 비주류중독_848006975(1도움)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-29 09:24:43</t>
+          <t>2026-09-30 13:10:05</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5313,29 +5953,29 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(1도움), 오스트리아_863240709(1도움), 셀래스틴_846001551(1도움), 셀래스틴_848194765(2도움)</t>
+          <t>UNIT_867166676(1도움), UNIT_840192883(2도움), UNIT_840225782(1도움), 셀래스틴_848194765(1도움), 셀래스틴_863200458(1도움)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-29 09:13:08</t>
+          <t>2026-09-30 12:57:48</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5345,111 +5985,751 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>오스트리아_851221671(1도움), 셀래스틴_848231866(1도움)</t>
+          <t>UNIT_863250723(1도움), UNIT_840228251(2도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-29 09:02:47</t>
+          <t>2026-09-30 12:35:39</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(1도움), 오스트리아_864182152(1도움), 오스트리아_851236636(1도움), 셀래스틴_846001551(1도움)</t>
+          <t>셀래스틴_848231866(1도움), 셀래스틴_852259694(1도움), 비주류중독_839247699(1도움), 비주류중독_834239977(2도움)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-29 08:51:25</t>
+          <t>2026-09-30 12:24:21</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0_2</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>셀래스틴_863200458(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>셀래스틴_852259694(1도움), 셀래스틴_848194765(1도움)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>2026-09-30 12:00:21</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>UNIT_840225782(1도움), UNIT_867166676(1도움), 셀래스틴_848013038(1도움), 셀래스틴_852241461(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:47:20</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3_4</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>방덕_867001040(1도움), 방덕_848231478(2도움), Voor_845009676(1도움), Voor_845239231(1도움), Voor_835183277(1도움), Voor_848216150(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:35:39</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1_6</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Voor_852233700(2도움), Voor_856256079(1도움), Voor_845009676(2도움), Voor_835183277(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:27:58</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1도움), Legend독수리_852209658(1도움), syma_852274967(1도움), syma_863228092(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:16:55</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1_6</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1도움), syma_866231913(2도움), syma_863222665(4도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:04:48</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Legend독수리_848224425(1도움), Legend독수리_826236703(1도움), syma_856233848(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-30 07:53:20</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Legend독수리_861081644(1도움), syma_846001845(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:16:03</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>7_2</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>개포동덕배_848206113(1도움), 개포동덕배_845208722(3도움), 개포동덕배_856202126(1도움), 개포동덕배_863212622(2도움), Gucci차붐_853272733(1도움), Gucci차붐_864176403(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:04:54</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>개포동덕배_856202126(1도움), 개포동덕배_863234396(1도움), 개포동덕배_856275298(1도움), 개포동덕배_848206113(1도움), Gucci차붐_864084333(1도움), Gucci차붐_864247686(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:20:02</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:08:25</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(2도움), UNIT_848265695(1도움), 콩콩콩룔_851236496(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:56:21</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>7_1</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>오스트리아_864182152(2도움), 오스트리아_864140057(1도움), 오스트리아_851236636(4도움), ShangHaiPortFC_848031432(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:47:10</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1도움), UNIT_863250723(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:45:30</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>오스트리아_851221671(1도움), 오스트리아_863223671(1도움), 오스트리아_863240709(1도움), 오스트리아_864140057(1도움), 오스트리아_851216275(1도움), ShangHaiPortFC_827143001(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:35:32</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1도움), 셀래스틴_848231866(2도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:18:25</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>UNIT_839013383(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:24:43</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(1도움), 오스트리아_863240709(1도움), 셀래스틴_846001551(1도움), 셀래스틴_848194765(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:13:08</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>오스트리아_851221671(1도움), 셀래스틴_848231866(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:02:47</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(1도움), 오스트리아_864182152(1도움), 오스트리아_851236636(1도움), 셀래스틴_846001551(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-29 08:51:25</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>0_2</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>셀래스틴_863200458(1도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
           <t>2026-09-29 04:33:11</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>여수가스</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>오스트리아</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>2_3</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>여수가스_852216393(1도움), 여수가스_861162895(1도움), 오스트리아_864140057(1도움), 오스트리아_851257075(1도움)</t>
         </is>

--- a/API데이터_경기_득점_및_도움_기록.xlsx
+++ b/API데이터_경기_득점_및_도움_기록.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,71 +452,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-03 17:55:25</t>
+          <t>2026-10-04 14:02:46</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>6_0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1골), UNIT_867166676(1골)</t>
+          <t>0708ManUtd_868037576(2골), 0708ManUtd_834239053(1골), 0708ManUtd_851226161(1골), 0708ManUtd_835183277(2골)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-03 17:38:01</t>
+          <t>2026-10-04 13:50:55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(2골), 앙쿠_848176580(1골), 앙쿠_846193747(1골), 앙쿠_851194765(1골), UNIT_840192883(1골), UNIT_848180930(1골)</t>
+          <t>0708ManUtd_851226161(1골), 0708ManUtd_861005661(1골), 0708ManUtd_834239053(1골), syma_845224574(2골), syma_867192629(1골)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-03 17:26:32</t>
+          <t>2026-10-04 13:24:32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -526,44 +526,44 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_866266039(1골), UNIT_867166676(1골), UNIT_848180930(1골), UNIT_840192883(1골)</t>
+          <t>앙쿠_861049369(1골), 앙쿠_848176580(4골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-03 17:14:22</t>
+          <t>2026-10-04 13:13:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>7_3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -573,46 +573,46 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>앙쿠_866266039(2골), UNIT_848180930(1골)</t>
+          <t>UNIT_840192883(1골), UNIT_848180930(3골), UNIT_867166676(3골), Legend독수리_846001845(2골), Legend독수리_848140601(1골)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-03 16:54:05</t>
+          <t>2026-10-04 13:02:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>앙쿠_814226161(1골), 앙쿠_845246191(1골), 앙쿠_848176580(1골), 여수가스_861215732(2골), 여수가스_845020289(1골)</t>
+          <t>UNIT_840228251(1골), UNIT_848180930(2골), UNIT_867166676(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-03 16:42:34</t>
+          <t>2026-10-04 12:51:38</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7_0</t>
+          <t>5_4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -637,29 +637,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 앙쿠_848176580(4골), 앙쿠_845246191(2골)</t>
+          <t>앙쿠_861049369(2골), 앙쿠_851194765(1골), 앙쿠_866266039(1골), 앙쿠_848176580(1골), Legend독수리_840192505(3골), Legend독수리_846001845(1골)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-03 15:45:24</t>
+          <t>2026-10-04 12:15:50</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -669,29 +669,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_867166676(4골), Voor_845009676(1골)</t>
+          <t>피파왕초보구단주_861005661(1골), 피파왕초보구단주_867000027(1골), 셀래스틴_861005680(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-03 15:32:25</t>
+          <t>2026-10-04 11:55:48</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>7_1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -701,189 +701,189 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UNIT_848180930(3골), Voor_852233700(1골), Voor_848034079(1골)</t>
+          <t>0708ManUtd_835183277(3골), 0708ManUtd_848238794(1골), 0708ManUtd_868001397(2골), 0708ManUtd_861005661(1골), ShangHaiPortFC_848031432(1골)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-03 15:20:36</t>
+          <t>2026-10-04 11:44:09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UNIT_851236403(1골), Voor_852233700(2골), Voor_861000027(1골)</t>
+          <t>0708ManUtd_848238794(1골), 0708ManUtd_868001397(2골), 0708ManUtd_861005661(1골), ShangHaiPortFC_864191910(1골)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-03 15:09:15</t>
+          <t>2026-10-04 11:41:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3_6</t>
+          <t>5_0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UNIT_840192883(2골), UNIT_867166676(1골), Voor_845009676(3골), Voor_852233700(3골)</t>
+          <t>검정소_868192181(2골), 검정소_861214098(1골), 검정소_100214100(2골)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-03 14:56:34</t>
+          <t>2026-10-04 11:31:42</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), UNIT_848180930(2골), Voor_845009676(1골), Voor_845247090(1골), Voor_861000027(1골)</t>
+          <t>검정소_868192181(1골), 검정소_861214098(1골), 검정소_100214100(2골), 용신_101173731(1골), 용신_272181458(1골)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-03 14:45:40</t>
+          <t>2026-10-04 11:28:25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_867166676(1골), Voor_835183277(1골), Voor_845009676(2골)</t>
+          <t>A지냐크_867166676(1골), A지냐크_877031432(3골), ShangHaiPortFC_827143001(1골), ShangHaiPortFC_864191910(1골), ShangHaiPortFC_848031432(1골)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-03 14:30:09</t>
+          <t>2026-10-04 11:20:27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), UNIT_848180930(1골), Voor_845009676(1골), Voor_861000027(1골), Voor_835183277(1골), Voor_845247090(1골)</t>
+          <t>용신_866200104(2골), Special블루_845001625(1골), Special블루_855241651(1골)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-03 09:55:42</t>
+          <t>2026-10-04 11:15:20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>7_1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -893,29 +893,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), UNIT_848180930(2골), 셀래스틴_848230938(1골), 셀래스틴_852241461(1골)</t>
+          <t>A지냐크_877031432(2골), A지냐크_863241496(1골), A지냐크_861167134(2골), A지냐크_867214101(2골), ShangHaiPortFC_861051412(1골)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-04 11:10:41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -925,93 +925,93 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_840192883(1골), 셀래스틴_852241461(1골)</t>
+          <t>용신_101173731(4골), 용신_866200104(1골), Special블루_845001625(1골), Special블루_855241651(1골)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-03 09:32:54</t>
+          <t>2026-10-04 10:58:01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UNIT_867166676(3골), UNIT_848180930(1골), UNIT_840228251(1골), 셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
+          <t>방덕_863184200(2골), 피파왕초보구단주_846208722(1골), 피파왕초보구단주_867000027(2골), 피파왕초보구단주_846045197(1골)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-03 09:20:46</t>
+          <t>2026-10-04 10:46:19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), UNIT_848180930(1골), 셀래스틴_848194765(1골)</t>
+          <t>방덕_868009676(1골), 방덕_856228093(1골), 피파왕초보구단주_846045197(1골), 피파왕초보구단주_867000027(2골)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-03 09:08:53</t>
+          <t>2026-10-04 10:45:44</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1021,61 +1021,61 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), UNIT_848180930(2골), 셀래스틴_861005680(1골), 셀래스틴_848194765(1골)</t>
+          <t>개포동덕배_856202126(4골), 용신_101173731(1골)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-03 08:56:57</t>
+          <t>2026-10-04 10:31:48</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>1_9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_867166676(2골), 셀래스틴_861005680(1골)</t>
+          <t>ShangHaiPortFC_848031432(1골), 용신_272181458(2골), 용신_866200104(1골), 용신_101173731(5골), 용신_826251421(1골)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-03 08:43:58</t>
+          <t>2026-10-04 10:20:09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>1_6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1085,61 +1085,61 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), 셀래스틴_852241461(1골)</t>
+          <t>ShangHaiPortFC_848031432(1골), 용신_101173731(2골), 용신_866200104(4골)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-02 16:24:32</t>
+          <t>2026-10-04 09:58:09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>2_6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2골)</t>
+          <t>은안_877143001(2골), 피파왕초보구단주_867000027(2골), 피파왕초보구단주_846208722(3골), 피파왕초보구단주_861005661(1골)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-02 16:14:00</t>
+          <t>2026-10-04 09:46:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1149,61 +1149,61 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2골), UNIT_867166676(4골)</t>
+          <t>은안_848231866(1골), 은안_856246420(1골), 피파왕초보구단주_846045197(1골), 피파왕초보구단주_846208722(1골), 피파왕초보구단주_867000027(1골)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-02 15:54:37</t>
+          <t>2026-10-04 09:43:49</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_814226161(1골), 앙쿠_863246191(1골), 앙쿠_851194765(1골)</t>
+          <t>ShangHaiPortFC_848031432(2골), ShangHaiPortFC_864191910(1골), Special블루_845001625(3골)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-02 15:43:20</t>
+          <t>2026-10-04 09:32:28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0_6</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1213,89 +1213,93 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UNIT_840228251(2골), UNIT_840192883(1골), UNIT_867166676(3골)</t>
+          <t>ShangHaiPortFC_827143001(1골), Special블루_845001625(1골), Special블루_856246669(1골), Special블루_861006975(2골), Special블루_856232580(1골)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-02 15:32:20</t>
+          <t>2026-10-04 08:02:54</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), UNIT_867166676(3골)</t>
+          <t>Gucci차붐_864176403(2골), Gucci차붐_851221671(1골), 셀래스틴_863233419(2골)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-02 15:20:55</t>
+          <t>2026-10-04 07:51:42</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gucci차붐_853272992(1골), Gucci차붐_864084333(1골), 셀래스틴_863200458(1골), 셀래스틴_863233419(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-02 14:48:41</t>
+          <t>2026-10-04 07:27:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>0_3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1305,88 +1309,88 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), UNIT_840192883(1골), UNIT_867166676(2골)</t>
+          <t>ShangHaiPortFC_864191910(2골), ShangHaiPortFC_284190813(1골)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-02 14:36:35</t>
+          <t>2026-10-04 07:17:33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_863246191(1골), UNIT_867166676(3골)</t>
+          <t>겐지간지_814231747(3골), ShangHaiPortFC_864191910(1골)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-02 14:24:08</t>
+          <t>2026-10-04 06:36:40</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>3_0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>앙쿠_866266039(1골), 앙쿠_851194765(1골), UNIT_867166676(1골), UNIT_848180930(3골)</t>
+          <t>호야국2인_851216409(1골), 호야국2인_848232293(1골), 호야국2인_848227236(1골)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-02 14:12:59</t>
+          <t>2026-10-04 06:15:10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1401,61 +1405,61 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_846193747(2골), 앙쿠_863246191(2골), UNIT_848180930(1골), UNIT_851236403(1골)</t>
+          <t>syma_867192629(1골), syma_851224415(2골), syma_845224574(2골), ShangHaiPortFC_848031432(1골), ShangHaiPortFC_827143001(1골)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-02 14:00:42</t>
+          <t>2026-10-04 06:04:11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(2골), 앙쿠_866266039(1골), UNIT_867166676(3골), UNIT_848180930(1골)</t>
+          <t>syma_851224415(1골), syma_845224574(1골), ShangHaiPortFC_861051412(1골), ShangHaiPortFC_864191910(1골)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-02 13:50:00</t>
+          <t>2026-10-04 05:51:46</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1465,189 +1469,185 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 앙쿠_863246191(2골), 앙쿠_848176580(1골), UNIT_867166676(1골), UNIT_866247257(1골)</t>
+          <t>셀래스틴_852241461(1골), 셀래스틴_861005680(2골), 셀래스틴_863200458(1골), 셀래스틴_863233419(1골), syma_866235522(1골), syma_851224415(1골)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-02 12:57:51</t>
+          <t>2026-10-04 05:50:55</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_861005661(1골), 피파왕초보구단주_846208722(2골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(1골)</t>
+          <t>호야국2인_848232293(1골), 호야국2인_846192505(1골), 호야국2인_851216409(1골), Gucci와퍼_864200104(2골), Gucci와퍼_852010264(2골)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-02 12:45:28</t>
+          <t>2026-10-04 05:40:38</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>피파왕초보구단주_846208722(1골), 피파왕초보구단주_846045197(1골), 피파왕초보구단주_867000027(1골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(2골)</t>
-        </is>
-      </c>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-02 10:04:35</t>
+          <t>2026-10-04 05:38:58</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 앙쿠_848176580(1골), UNIT_867166676(1골), UNIT_848180930(2골)</t>
+          <t>셀래스틴_861005680(3골), 셀래스틴_852241461(2골)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-01 15:50:18</t>
+          <t>2026-10-04 05:38:58</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>suma수마_861190046(1골), 피파왕초보구단주_861005661(3골)</t>
+          <t>호야국2인_848232293(1골), 호야국2인_846192505(1골), Gucci와퍼_864200104(1골)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-01 15:38:48</t>
+          <t>2026-10-04 05:27:25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>suma수마_861221162(1골), suma수마_861013383(1골), 피파왕초보구단주_846208722(1골), 피파왕초보구단주_856209331(1골)</t>
+          <t>호야국2인_848232293(1골), Gucci와퍼_864200104(1골), Gucci와퍼_852010264(1골)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-01 15:24:08</t>
+          <t>2026-10-04 05:21:46</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>8_0</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1657,19 +1657,19 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_846208722(2골), 피파왕초보구단주_867000027(2골), 피파왕초보구단주_861005661(1골), Gucci와퍼_852208128(1골)</t>
+          <t>셀래스틴_848231866(1골), 셀래스틴_861005680(2골), 셀래스틴_863233419(1골), 셀래스틴_852241461(4골)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-01 15:12:09</t>
+          <t>2026-10-04 05:16:16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1689,24 +1689,24 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_848209499(1골), 피파왕초보구단주_861005661(2골), Gucci와퍼_840208574(1골), Gucci와퍼_864200104(2골)</t>
+          <t>호야국2인_848232293(1골), Gucci와퍼_851210697(1골)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-01 14:56:12</t>
+          <t>2026-10-04 05:10:38</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1721,29 +1721,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0708ManUtd_848238794(1골), 호야국2인_848227236(1골), 호야국2인_848232293(1골)</t>
+          <t>셀래스틴_852241461(1골), ShangHaiPortFC_864191910(1골), ShangHaiPortFC_861051412(1골)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-01 14:51:31</t>
+          <t>2026-10-04 05:00:23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>호야국2인</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>은안</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Gucci와퍼</t>
-        </is>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1753,29 +1753,29 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>은안_852237692(1골), Gucci와퍼_852028765(1골), Gucci와퍼_852010264(1골), Gucci와퍼_864200104(2골)</t>
+          <t>호야국2인_852001183(1골), 호야국2인_826259399(1골), 은안_877143001(1골), 은안_866241236(2골)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-01 14:45:02</t>
+          <t>2026-10-04 04:48:36</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1785,249 +1785,253 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0708ManUtd_868037576(1골), 0708ManUtd_834239053(1골), 호야국2인_851216409(1골), 호야국2인_848232293(1골), 호야국2인_846192505(1골)</t>
+          <t>호야국2인_846192505(1골), 호야국2인_848232293(1골), 은안_877143001(2골)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-01 14:39:52</t>
+          <t>2026-10-03 18:10:10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>2_6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>은안_877143001(3골), 은안_866241236(1골), Gucci와퍼_864200104(1골)</t>
+          <t>앙쿠_861049369(1골), 앙쿠_851194765(1골), UNIT_867166676(2골), UNIT_848180930(2골), UNIT_840192883(2골)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-01 14:31:32</t>
+          <t>2026-10-03 17:55:25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(2골), 호야국2인_851216409(1골), Special블루_868001419(1골), Special블루_861047390(1골), Special블루_856246669(1골)</t>
+          <t>앙쿠_861049369(1골), UNIT_867166676(1골)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-01 14:21:07</t>
+          <t>2026-10-03 17:38:01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(1골), Special블루_851251566(1골), Special블루_877001625(1골), Special블루_868001419(1골)</t>
+          <t>앙쿠_846193747(1골), 앙쿠_851194765(1골), 앙쿠_861049369(2골), 앙쿠_848176580(1골), UNIT_840192883(1골), UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-01 14:08:57</t>
+          <t>2026-10-03 17:26:32</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>호야국2인_846192505(3골), 비주류중독_840052241(2골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_866266039(1골), UNIT_867166676(1골), UNIT_848180930(1골), UNIT_840192883(1골)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-01 13:58:38</t>
+          <t>2026-10-03 17:14:22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(1골), 비주류중독_829203376(1골), 비주류중독_839247699(3골), 비주류중독_840052241(1골)</t>
+          <t>앙쿠_866266039(2골), UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-01 13:48:03</t>
+          <t>2026-10-03 16:54:05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>앙쿠_814226161(1골), 앙쿠_845246191(1골), 앙쿠_848176580(1골), 여수가스_861215732(2골), 여수가스_845020289(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-01 13:34:35</t>
+          <t>2026-10-03 16:42:34</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>7_0</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>아들러_861000570(1골), Special블루_877001625(1골), Special블루_848230666(1골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_848176580(4골), 앙쿠_845246191(2골)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-01 13:24:02</t>
+          <t>2026-10-03 15:45:24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2037,29 +2041,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>아들러_855232639(2골), Special블루_868001419(1골), Special블루_877001625(2골)</t>
+          <t>UNIT_848180930(1골), UNIT_867166676(4골), Voor_845009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-01 13:13:07</t>
+          <t>2026-10-03 15:32:25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>7_0</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2069,29 +2073,29 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(4골), 앙쿠_851194765(2골), 앙쿠_856247103(1골)</t>
+          <t>UNIT_848180930(3골), Voor_852233700(1골), Voor_848034079(1골)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-01 13:02:02</t>
+          <t>2026-10-03 15:20:36</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2099,59 +2103,63 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>UNIT_851236403(1골), Voor_852233700(2골), Voor_861000027(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-01 13:01:02</t>
+          <t>2026-10-03 15:09:15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>3_6</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), syma_867192629(1골)</t>
+          <t>UNIT_840192883(2골), UNIT_867166676(1골), Voor_845009676(3골), Voor_852233700(3골)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-01 12:49:37</t>
+          <t>2026-10-03 14:56:34</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2159,91 +2167,95 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1골), UNIT_848180930(2골), Voor_845009676(1골), Voor_845247090(1골), Voor_861000027(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-01 11:22:46</t>
+          <t>2026-10-03 14:45:40</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3_0</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 앙쿠_863246191(2골)</t>
+          <t>UNIT_848180930(1골), UNIT_867166676(1골), Voor_835183277(1골), Voor_845009676(2골)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-01 11:15:46</t>
+          <t>2026-10-03 14:30:09</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>suma수마_861190046(1골), suma수마_861221162(3골), suma수마_845192190(1골), 겐지간지_848170890(1골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(1골), Voor_845009676(1골), Voor_861000027(1골), Voor_835183277(1골), Voor_845247090(1골)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-01 11:12:19</t>
+          <t>2026-10-03 09:55:42</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2253,29 +2265,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>앙쿠_814226161(1골), 앙쿠_848176580(2골), Gucci차붐_840191208(1골)</t>
+          <t>UNIT_867166676(2골), UNIT_848180930(2골), 셀래스틴_848230938(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-01 11:03:11</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2285,29 +2297,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>suma수마_861190046(2골), suma수마_861221162(1골), suma수마_840001114(2골), 겐지간지_814231747(1골), 겐지간지_852241461(1골), 겐지간지_856237679(1골)</t>
+          <t>UNIT_848180930(1골), UNIT_840192883(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-01 07:54:09</t>
+          <t>2026-10-03 09:32:54</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2317,29 +2329,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>호야국2인_851261865(1골), 호야국2인_846192505(1골), 호야국2인_848232293(1골), 아들러_861000570(1골), 아들러_840191208(1골)</t>
+          <t>UNIT_867166676(3골), UNIT_848180930(1골), UNIT_840228251(1골), 셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-01 07:42:04</t>
+          <t>2026-10-03 09:20:46</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2349,24 +2361,24 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>호야국2인_848227236(2골), 호야국2인_848232293(1골), 호야국2인_848216435(1골), 호야국2인_851216409(1골), 아들러_291225126(1골), 아들러_866251377(1골)</t>
+          <t>UNIT_867166676(2골), UNIT_848180930(1골), 셀래스틴_848194765(1골)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-01 06:47:50</t>
+          <t>2026-10-03 09:08:53</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2381,29 +2393,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>호야국2인_845198219(1골), 호야국2인_848232293(2골), 호야국2인_848216435(1골), suma수마_861190046(1골), suma수마_861221162(1골)</t>
+          <t>UNIT_867166676(2골), UNIT_848180930(2골), 셀래스틴_861005680(1골), 셀래스틴_848194765(1골)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-01 06:36:26</t>
+          <t>2026-10-03 08:56:57</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2413,14 +2425,14 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>호야국2인_851216409(1골), 호야국2인_845198219(1골), 호야국2인_846192505(1골), 호야국2인_848227236(1골), 호야국2인_848232293(1골), suma수마_861013383(1골), suma수마_861221162(1골)</t>
+          <t>UNIT_848180930(1골), UNIT_867166676(2골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-30 17:45:59</t>
+          <t>2026-10-03 08:43:58</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2430,12 +2442,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2445,93 +2457,93 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), Voor_845009676(1골), Voor_835183277(1골), Voor_852233700(3골)</t>
+          <t>UNIT_867166676(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-30 17:34:22</t>
+          <t>2026-10-02 16:24:32</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), UNIT_840192883(1골), Voor_845009676(1골), Voor_856256079(1골), Voor_852233700(2골)</t>
+          <t>앙쿠_848176580(2골)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-30 17:17:18</t>
+          <t>2026-10-02 16:14:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), UNIT_848180930(2골), Voor_852233700(2골)</t>
+          <t>앙쿠_848176580(2골), UNIT_867166676(4골)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-30 17:03:54</t>
+          <t>2026-10-02 15:54:37</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2541,29 +2553,29 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>UNIT_867166676(5골), Voor_845009676(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_814226161(1골), 앙쿠_863246191(1골), 앙쿠_851194765(1골)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-30 16:46:35</t>
+          <t>2026-10-02 15:43:20</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>0_6</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2573,29 +2585,29 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), Voor_845009676(1골), Voor_852233700(2골)</t>
+          <t>UNIT_840228251(2골), UNIT_840192883(1골), UNIT_867166676(3골)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-30 14:01:02</t>
+          <t>2026-10-02 15:32:20</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2605,61 +2617,57 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UNIT_861221162(2골), 셀래스틴_861005680(4골), 셀래스틴_848231866(1골)</t>
+          <t>앙쿠_848176580(1골), UNIT_867166676(3골)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-30 13:49:10</t>
+          <t>2026-10-02 15:20:55</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>UNIT_867166676(3골), UNIT_861221162(2골), 셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-30 13:33:10</t>
+          <t>2026-10-02 14:48:41</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2669,157 +2677,157 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(3골), 셀래스틴_852241461(1골)</t>
+          <t>앙쿠_848176580(1골), UNIT_840192883(1골), UNIT_867166676(2골)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:44</t>
+          <t>2026-10-02 14:36:35</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gucci와퍼_864200104(4골), 비주류중독_840052241(1골), 비주류중독_825000240(1골), 비주류중독_839247699(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_863246191(1골), UNIT_867166676(3골)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-30 13:21:00</t>
+          <t>2026-10-02 14:24:08</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_867166676(1골)</t>
+          <t>앙쿠_866266039(1골), 앙쿠_851194765(1골), UNIT_867166676(1골), UNIT_848180930(3골)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-30 13:12:24</t>
+          <t>2026-10-02 14:12:59</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gucci와퍼_852028765(1골), Gucci와퍼_852168473(1골), 비주류중독_834239977(1골), 비주류중독_840052241(1골), 비주류중독_839247699(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_846193747(2골), 앙쿠_863246191(2골), UNIT_848180930(1골), UNIT_851236403(1골)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-30 13:10:05</t>
+          <t>2026-10-02 14:00:42</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>UNIT_867166676(3골), UNIT_840192883(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(2골)</t>
+          <t>앙쿠_863246191(2골), 앙쿠_866266039(1골), UNIT_867166676(3골), UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-30 12:57:48</t>
+          <t>2026-10-02 13:50:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2829,88 +2837,88 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), UNIT_848180930(1골), 셀래스틴_846001551(1골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_863246191(2골), 앙쿠_848176580(1골), UNIT_867166676(1골), UNIT_866247257(1골)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:39</t>
+          <t>2026-10-02 12:57:51</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 비주류중독_848006975(2골), 비주류중독_839247699(1골)</t>
+          <t>피파왕초보구단주_861005661(1골), 피파왕초보구단주_846208722(2골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(1골)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-30 12:24:21</t>
+          <t>2026-10-02 12:45:28</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
+          <t>피파왕초보구단주_846208722(1골), 피파왕초보구단주_846045197(1골), 피파왕초보구단주_867000027(1골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(2골)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-30 12:00:21</t>
+          <t>2026-10-02 10:04:35</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2925,29 +2933,29 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), 셀래스틴_861005680(2골), 셀래스틴_852241461(1골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_848176580(1골), UNIT_867166676(1골), UNIT_848180930(2골)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-30 09:47:20</t>
+          <t>2026-10-01 15:50:18</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2957,61 +2965,61 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>방덕_848007512(1골), 방덕_856228093(1골), 방덕_863184200(1골), Voor_845247090(2골), Voor_852233700(2골)</t>
+          <t>suma수마_861190046(1골), 피파왕초보구단주_861005661(3골)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-30 09:35:39</t>
+          <t>2026-10-01 15:38:48</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>방덕_101001419(1골), Voor_852233700(3골), Voor_845009676(2골), Voor_845247090(1골)</t>
+          <t>suma수마_861221162(1골), suma수마_861013383(1골), 피파왕초보구단주_846208722(1골), 피파왕초보구단주_856209331(1골)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-30 08:27:58</t>
+          <t>2026-10-01 15:24:08</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3021,93 +3029,93 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Legend독수리_825190048(1골), Legend독수리_861081644(1골), Legend독수리_848188350(1골), syma_863228092(1골), syma_856233848(1골)</t>
+          <t>피파왕초보구단주_846208722(2골), 피파왕초보구단주_867000027(2골), 피파왕초보구단주_861005661(1골), Gucci와퍼_852208128(1골)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-30 08:16:55</t>
+          <t>2026-10-01 15:12:09</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Legend독수리_825190048(1골), syma_866231913(1골), syma_863262863(1골), syma_846001845(3골), syma_852274967(1골)</t>
+          <t>피파왕초보구단주_848209499(1골), 피파왕초보구단주_861005661(2골), Gucci와퍼_840208574(1골), Gucci와퍼_864200104(2골)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-30 08:04:48</t>
+          <t>2026-10-01 14:56:12</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Legend독수리_861215732(1골), Legend독수리_852209658(1골), syma_866231913(1골), syma_863228092(1골)</t>
+          <t>0708ManUtd_848238794(1골), 호야국2인_848227236(1골), 호야국2인_848232293(1골)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-30 07:53:20</t>
+          <t>2026-10-01 14:51:31</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3117,61 +3125,61 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Legend독수리_861215732(1골), syma_863222665(2골)</t>
+          <t>은안_852237692(1골), Gucci와퍼_852028765(1골), Gucci와퍼_852010264(1골), Gucci와퍼_864200104(2골)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-29 14:16:03</t>
+          <t>2026-10-01 14:45:02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>개포동덕배_848206113(1골), 개포동덕배_845208722(1골), 개포동덕배_856202126(1골), 개포동덕배_845190048(4골), Gucci차붐_864247686(1골), Gucci차붐_864176403(1골)</t>
+          <t>0708ManUtd_868037576(1골), 0708ManUtd_834239053(1골), 호야국2인_851216409(1골), 호야국2인_848232293(1골), 호야국2인_846192505(1골)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-29 14:04:54</t>
+          <t>2026-10-01 14:39:52</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3181,93 +3189,93 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(3골), 개포동덕배_848206113(1골), Gucci차붐_853272733(1골), Gucci차붐_853242004(1골)</t>
+          <t>은안_877143001(3골), 은안_866241236(1골), Gucci와퍼_864200104(1골)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-29 11:20:02</t>
+          <t>2026-10-01 14:31:32</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(2골)</t>
+          <t>호야국2인_848232293(2골), 호야국2인_851216409(1골), Special블루_868001419(1골), Special블루_861047390(1골), Special블루_856246669(1골)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-29 11:08:25</t>
+          <t>2026-10-01 14:21:07</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), UNIT_848135455(1골), UNIT_867166676(1골), 콩콩콩룔_866223710(1골), 콩콩콩룔_867223848(1골)</t>
+          <t>호야국2인_848232293(1골), Special블루_851251566(1골), Special블루_877001625(1골), Special블루_868001419(1골)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-29 10:56:21</t>
+          <t>2026-10-01 14:08:57</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>7_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3277,93 +3285,89 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(3골), 오스트리아_851221671(1골), 오스트리아_864182152(1골), 오스트리아_864140057(1골), 오스트리아_851216275(1골), ShangHaiPortFC_864191910(1골)</t>
+          <t>호야국2인_846192505(3골), 비주류중독_840052241(2골)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-29 10:47:10</t>
+          <t>2026-10-01 13:58:38</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1골), UNIT_867166676(2골), 셀래스틴_848231866(1골), 셀래스틴_848230938(1골)</t>
+          <t>호야국2인_848232293(1골), 비주류중독_829203376(1골), 비주류중독_839247699(3골), 비주류중독_840052241(1골)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-29 10:45:30</t>
+          <t>2026-10-01 13:48:03</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>오스트리아_864140057(2골), 오스트리아_864182152(1골), 오스트리아_864199266(2골), ShangHaiPortFC_861051412(1골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-29 10:35:32</t>
+          <t>2026-10-01 13:34:35</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3373,125 +3377,121 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1골), 셀래스틴_846001551(1골), 셀래스틴_852241461(2골)</t>
+          <t>아들러_861000570(1골), Special블루_877001625(1골), Special블루_848230666(1골)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-29 10:18:25</t>
+          <t>2026-10-01 13:24:02</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), 셀래스틴_848194765(1골)</t>
+          <t>아들러_855232639(2골), Special블루_868001419(1골), Special블루_877001625(2골)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-29 09:24:43</t>
+          <t>2026-10-01 13:13:07</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>7_0</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(1골), 오스트리아_851236636(1골), 셀래스틴_846001551(1골), 셀래스틴_861005680(1골), 셀래스틴_848230938(1골)</t>
+          <t>앙쿠_863246191(4골), 앙쿠_851194765(2골), 앙쿠_856247103(1골)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-29 09:13:08</t>
+          <t>2026-10-01 13:02:02</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>오스트리아_864199266(1골), 셀래스틴_861005680(1골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-29 09:02:47</t>
+          <t>2026-10-01 13:01:02</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3501,29 +3501,29 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(1골), 오스트리아_864199266(1골), 오스트리아_864182152(1골), 셀래스틴_861005680(1골)</t>
+          <t>앙쿠_848176580(1골), syma_867192629(1골)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-29 08:51:25</t>
+          <t>2026-10-01 12:49:37</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0_2</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3531,39 +3531,1411 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>셀래스틴_846001551(1골), 셀래스틴_861005680(1골)</t>
-        </is>
-      </c>
+      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>2026-10-01 11:22:46</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3_0</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(1골), 앙쿠_863246191(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:46</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>suma수마_861190046(1골), suma수마_861221162(3골), suma수마_845192190(1골), 겐지간지_848170890(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:12:19</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>앙쿠_814226161(1골), 앙쿠_848176580(2골), Gucci차붐_840191208(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:03:11</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>5_3</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>suma수마_861190046(2골), suma수마_861221162(1골), suma수마_840001114(2골), 겐지간지_814231747(1골), 겐지간지_852241461(1골), 겐지간지_856237679(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-01 07:54:09</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>호야국2인</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>호야국2인_851261865(1골), 호야국2인_846192505(1골), 호야국2인_848232293(1골), 아들러_861000570(1골), 아들러_840191208(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-01 07:42:04</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>호야국2인</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>호야국2인_848227236(2골), 호야국2인_848232293(1골), 호야국2인_848216435(1골), 호야국2인_851216409(1골), 아들러_291225126(1골), 아들러_866251377(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:47:50</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>호야국2인</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>호야국2인_845198219(1골), 호야국2인_848232293(2골), 호야국2인_848216435(1골), suma수마_861190046(1골), suma수마_861221162(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:36:26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>호야국2인</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>호야국2인_851216409(1골), 호야국2인_845198219(1골), 호야국2인_846192505(1골), 호야국2인_848227236(1골), 호야국2인_848232293(1골), suma수마_861013383(1골), suma수마_861221162(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:45:59</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2_5</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), Voor_845009676(1골), Voor_835183277(1골), Voor_852233700(3골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:34:22</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3_4</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(2골), UNIT_840192883(1골), Voor_845009676(1골), Voor_856256079(1골), Voor_852233700(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:17:18</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1골), UNIT_848180930(2골), Voor_852233700(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:03:54</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(5골), Voor_845009676(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:46:35</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(2골), Voor_845009676(1골), Voor_852233700(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-30 14:01:02</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2_5</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>UNIT_861221162(2골), 셀래스틴_861005680(4골), 셀래스틴_848231866(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:49:10</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>5_3</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(3골), UNIT_861221162(2골), 셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:33:10</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>1_5</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(3골), 셀래스틴_852241461(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:24:44</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Gucci와퍼_864200104(4골), 비주류중독_840052241(1골), 비주류중독_825000240(1골), 비주류중독_839247699(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:21:00</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), UNIT_867166676(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:12:24</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Gucci와퍼_852028765(1골), Gucci와퍼_852168473(1골), 비주류중독_834239977(1골), 비주류중독_840052241(1골), 비주류중독_839247699(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:10:05</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(3골), UNIT_840192883(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:57:48</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), UNIT_848180930(1골), 셀래스틴_846001551(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:35:39</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>셀래스틴_846001551(1골), 셀래스틴_852241461(1골), 비주류중독_848006975(2골), 비주류중독_839247699(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:24:21</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:00:21</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(2골), 셀래스틴_861005680(2골), 셀래스틴_852241461(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:47:20</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>3_4</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>방덕_848007512(1골), 방덕_856228093(1골), 방덕_863184200(1골), Voor_845247090(2골), Voor_852233700(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:35:39</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>1_6</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>방덕_101001419(1골), Voor_852233700(3골), Voor_845009676(2골), Voor_845247090(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:27:58</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Legend독수리_825190048(1골), Legend독수리_861081644(1골), Legend독수리_848188350(1골), syma_863228092(1골), syma_856233848(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:16:55</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>1_6</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Legend독수리_825190048(1골), syma_866231913(1골), syma_863262863(1골), syma_846001845(3골), syma_852274967(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:04:48</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1골), Legend독수리_852209658(1골), syma_866231913(1골), syma_863228092(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-30 07:53:20</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1골), syma_863222665(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:16:03</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>7_2</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>개포동덕배_848206113(1골), 개포동덕배_845208722(1골), 개포동덕배_856202126(1골), 개포동덕배_845190048(4골), Gucci차붐_864247686(1골), Gucci차붐_864176403(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:04:54</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>개포동덕배_845190048(3골), 개포동덕배_848206113(1골), Gucci차붐_853272733(1골), Gucci차붐_853242004(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:20:02</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), 콩콩콩룔_867223848(1골), 콩콩콩룔_866223710(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:08:25</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), UNIT_848135455(1골), UNIT_867166676(1골), 콩콩콩룔_866223710(1골), 콩콩콩룔_867223848(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:56:21</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>7_1</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(3골), 오스트리아_851221671(1골), 오스트리아_864182152(1골), 오스트리아_864140057(1골), 오스트리아_851216275(1골), ShangHaiPortFC_864191910(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:47:10</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>UNIT_840228251(1골), UNIT_867166676(2골), 셀래스틴_848231866(1골), 셀래스틴_848230938(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:45:30</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(2골), 오스트리아_864182152(1골), 오스트리아_864199266(2골), ShangHaiPortFC_861051412(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:35:32</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1골), 셀래스틴_846001551(1골), 셀래스틴_852241461(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:18:25</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), 셀래스틴_848194765(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:24:43</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(1골), 오스트리아_851236636(1골), 셀래스틴_846001551(1골), 셀래스틴_861005680(1골), 셀래스틴_848230938(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:13:08</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:02:47</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(1골), 오스트리아_864199266(1골), 오스트리아_864182152(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-29 08:51:25</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>0_2</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>셀래스틴_846001551(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>2026-09-29 04:33:11</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>여수가스</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>오스트리아</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>2_3</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>여수가스_828231747(1골), 여수가스_852274967(1골), 오스트리아_864191566(1골), 오스트리아_864199266(2골)</t>
         </is>
@@ -3580,7 +4952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3618,71 +4990,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-03 17:55:25</t>
+          <t>2026-10-04 14:02:46</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>6_0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), UNIT_840210736(1도움)</t>
+          <t>0708ManUtd_868001397(3도움), 0708ManUtd_834239053(3도움)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-03 17:38:01</t>
+          <t>2026-10-04 13:50:55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2도움), 앙쿠_851194765(2도움), UNIT_840228251(1도움), UNIT_840225782(1도움)</t>
+          <t>0708ManUtd_851226161(1도움), 0708ManUtd_861005661(1도움), 0708ManUtd_834239053(1도움), syma_867192629(1도움), syma_866235522(2도움)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-03 17:26:32</t>
+          <t>2026-10-04 13:24:32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3692,44 +5064,44 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움), 앙쿠_814226161(1도움), UNIT_867166676(2도움), UNIT_840228251(1도움)</t>
+          <t>앙쿠_861049369(2도움), 앙쿠_851194765(1도움), 앙쿠_848176580(1도움), 앙쿠_846186345(1도움), 셀래스틴_852259694(1도움)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-03 17:14:22</t>
+          <t>2026-10-04 13:13:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>7_3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3739,46 +5111,46 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움), 앙쿠_846186345(1도움), UNIT_840192883(1도움)</t>
+          <t>UNIT_840225782(1도움), UNIT_840228251(2도움), UNIT_840192883(3도움), Legend독수리_852229880(1도움), Legend독수리_821143001(1도움)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-03 16:54:05</t>
+          <t>2026-10-04 13:02:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>앙쿠_845246191(1도움), 앙쿠_848176580(1도움), 앙쿠_846193747(1도움), 여수가스_846001551(1도움), 여수가스_861215732(1도움), 여수가스_828231747(1도움)</t>
+          <t>UNIT_840225782(1도움), UNIT_840192883(3도움), 셀래스틴_861005680(1도움)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-03 16:42:34</t>
+          <t>2026-10-04 12:51:38</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3788,12 +5160,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>Legend독수리</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7_0</t>
+          <t>5_4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3803,29 +5175,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(2도움), 앙쿠_845246191(3도움), 앙쿠_846193747(1도움)</t>
+          <t>앙쿠_846186345(1도움), 앙쿠_851194765(1도움), 앙쿠_848176580(1도움), Legend독수리_829200145(1도움), Legend독수리_840205988(1도움), Legend독수리_821143001(2도움)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-03 15:45:24</t>
+          <t>2026-10-04 12:15:50</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3835,29 +5207,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_840192883(1도움), UNIT_840225782(1도움), Voor_856256079(1도움)</t>
+          <t>피파왕초보구단주_867000027(1도움), 피파왕초보구단주_846208722(1도움), 셀래스틴_861005680(1도움), 셀래스틴_863200458(1도움)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-03 15:32:25</t>
+          <t>2026-10-04 11:55:48</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>7_1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3867,189 +5239,189 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1도움), UNIT_840228251(1도움), UNIT_848265695(1도움), Voor_856256079(1도움), Voor_845247090(1도움)</t>
+          <t>0708ManUtd_835183277(3도움), 0708ManUtd_848238794(1도움), 0708ManUtd_863239231(1도움), 0708ManUtd_861005661(1도움), ShangHaiPortFC_827143001(1도움)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-03 15:20:36</t>
+          <t>2026-10-04 11:44:09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움), Voor_845009676(3도움)</t>
+          <t>0708ManUtd_848238794(1도움), 0708ManUtd_868001397(1도움), 0708ManUtd_861005661(1도움), 0708ManUtd_834231281(1도움), ShangHaiPortFC_861051412(1도움)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-03 15:09:15</t>
+          <t>2026-10-04 11:41:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3_6</t>
+          <t>5_0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1도움), UNIT_848180930(1도움), UNIT_863250723(1도움), Voor_861000027(2도움), Voor_845009676(2도움), Voor_835183277(2도움)</t>
+          <t>검정소_861005003(1도움), 검정소_868192181(2도움), 검정소_861214098(1도움), 검정소_100214100(1도움)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-03 14:56:34</t>
+          <t>2026-10-04 11:31:42</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1도움), UNIT_863250723(1도움), UNIT_840210736(1도움), Voor_856256079(1도움), Voor_835183277(1도움), Voor_852233700(1도움)</t>
+          <t>검정소_861005003(1도움), 검정소_867241096(1도움), 검정소_100214100(1도움), 용신_272181458(1도움), 용신_866200104(1도움)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-03 14:45:40</t>
+          <t>2026-10-04 11:28:25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UNIT_840210736(1도움), UNIT_840228251(1도움), Voor_835183277(2도움), Voor_852233700(1도움)</t>
+          <t>A지냐크_867214101(1도움), A지냐크_863241496(1도움), A지냐크_861167134(1도움), A지냐크_877031432(1도움), ShangHaiPortFC_284190813(1도움), ShangHaiPortFC_256164959(1도움), ShangHaiPortFC_845231138(1도움)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-03 14:30:09</t>
+          <t>2026-10-04 11:20:27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UNIT_840210736(1도움), UNIT_840225782(1도움), Voor_845239231(1도움), Voor_852233700(1도움), Voor_835183277(1도움), Voor_845247090(1도움)</t>
+          <t>용신_101173731(2도움), Special블루_845001625(1도움), Special블루_855241651(1도움)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-03 09:55:42</t>
+          <t>2026-10-04 11:15:20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>7_1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4059,29 +5431,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UNIT_840225782(1도움), UNIT_867166676(1도움), UNIT_848265695(1도움), UNIT_840192883(1도움), 셀래스틴_861005680(1도움), 셀래스틴_848194765(1도움)</t>
+          <t>A지냐크_877031432(2도움), A지냐크_863241496(1도움), A지냐크_861167134(3도움), ShangHaiPortFC_827143001(1도움)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-04 11:10:41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4091,93 +5463,93 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UNIT_848135455(1도움), 셀래스틴_861005680(1도움)</t>
+          <t>용신_826251421(1도움), 용신_272181458(1도움), 용신_866200104(3도움), Special블루_861047390(1도움), Special블루_845001625(1도움)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-03 09:32:54</t>
+          <t>2026-10-04 10:58:01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_840228251(2도움), UNIT_840192883(2도움), 셀래스틴_848194765(1도움)</t>
+          <t>방덕_867001040(2도움), 피파왕초보구단주_861005661(1도움), 피파왕초보구단주_851243057(1도움)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-03 09:20:46</t>
+          <t>2026-10-04 10:46:19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UNIT_840192883(2도움), UNIT_840210736(1도움), 셀래스틴_848230938(1도움)</t>
+          <t>방덕_848231478(1도움), 피파왕초보구단주_846045197(1도움), 피파왕초보구단주_856209331(2도움)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-03 09:08:53</t>
+          <t>2026-10-04 10:45:44</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4187,61 +5559,61 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2도움), UNIT_840210736(1도움), UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_848194765(1도움)</t>
+          <t>개포동덕배_845190048(1도움), 개포동덕배_845208722(1도움), 개포동덕배_848206113(2도움), 용신_866200104(1도움)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-03 08:56:57</t>
+          <t>2026-10-04 10:31:48</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>1_9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UNIT_840225782(1도움), UNIT_848135455(1도움), 셀래스틴_863233419(1도움)</t>
+          <t>ShangHaiPortFC_284190813(1도움), 용신_272181458(3도움), 용신_877177003(1도움), 용신_866200104(3도움), 용신_826251421(1도움)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-03 08:43:58</t>
+          <t>2026-10-04 10:20:09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>1_6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4251,61 +5623,61 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움)</t>
+          <t>ShangHaiPortFC_827143001(1도움), 용신_101173731(2도움), 용신_866200104(1도움), 용신_272181458(3도움)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-02 16:24:32</t>
+          <t>2026-10-04 09:58:09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>2_6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>앙쿠_846193747(2도움)</t>
+          <t>은안_848231866(1도움), 은안_866241236(1도움), 피파왕초보구단주_856209331(1도움), 피파왕초보구단주_846045197(1도움), 피파왕초보구단주_851243057(1도움), 피파왕초보구단주_846216267(1도움), 피파왕초보구단주_846231281(2도움)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-02 16:14:00</t>
+          <t>2026-10-04 09:46:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4315,61 +5687,61 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_814226161(1도움), UNIT_840228251(3도움), UNIT_845207439(1도움)</t>
+          <t>은안_856251517(1도움), 피파왕초보구단주_856209331(1도움), 피파왕초보구단주_861005661(1도움)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-02 15:54:37</t>
+          <t>2026-10-04 09:43:49</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(3도움), 앙쿠_851194765(1도움)</t>
+          <t>ShangHaiPortFC_252175589(2도움), ShangHaiPortFC_827143001(1도움), Special블루_856246669(1도움), Special블루_868001419(1도움)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-02 15:43:20</t>
+          <t>2026-10-04 09:32:28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0_6</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4379,89 +5751,93 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UNIT_840210736(1도움), UNIT_840228251(1도움), UNIT_840225782(1도움), UNIT_840192883(1도움), UNIT_863250723(1도움), UNIT_848135455(1도움)</t>
+          <t>Special블루_856246669(1도움), Special블루_861006975(2도움), Special블루_855241651(2도움)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-02 15:32:20</t>
+          <t>2026-10-04 08:02:54</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>앙쿠_846193747(1도움), UNIT_840192883(1도움), UNIT_845207439(1도움)</t>
+          <t>Gucci차붐_853272733(2도움), 셀래스틴_848231866(1도움), 셀래스틴_848230938(1도움)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-02 15:20:55</t>
+          <t>2026-10-04 07:51:42</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gucci차붐_851221671(1도움), Gucci차붐_864247686(1도움), 셀래스틴_861005680(1도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-02 14:48:41</t>
+          <t>2026-10-04 07:27:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>0_3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4471,88 +5847,88 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(1도움), UNIT_840192883(2도움), UNIT_840228251(1도움)</t>
+          <t>ShangHaiPortFC_827143001(1도움), ShangHaiPortFC_861051412(1도움)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-02 14:36:35</t>
+          <t>2026-10-04 07:17:33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>겐지간지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(1도움), 앙쿠_851194765(1도움), UNIT_848265695(1도움), UNIT_840192883(2도움)</t>
+          <t>겐지간지_861001668(2도움), 겐지간지_848170890(1도움), ShangHaiPortFC_861051412(1도움)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-02 14:24:08</t>
+          <t>2026-10-04 06:36:40</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>3_0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_840228251(1도움), UNIT_840192883(2도움), UNIT_840225782(1도움)</t>
+          <t>호야국2인_848232293(1도움), 호야국2인_848227236(1도움)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-02 14:12:59</t>
+          <t>2026-10-04 06:15:10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4567,61 +5943,61 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2도움), 앙쿠_851194765(1도움), UNIT_840192883(2도움)</t>
+          <t>syma_866235522(2도움), syma_867192629(2도움), syma_845224574(1도움), ShangHaiPortFC_864191910(1도움), ShangHaiPortFC_256164959(1도움)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-02 14:00:42</t>
+          <t>2026-10-04 06:04:11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2도움), 앙쿠_856247103(1도움), UNIT_840228251(3도움), UNIT_840225782(1도움)</t>
+          <t>syma_858008348(1도움), syma_867192629(1도움), ShangHaiPortFC_848031432(1도움), ShangHaiPortFC_827143001(1도움)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-02 13:50:00</t>
+          <t>2026-10-04 05:51:46</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4631,189 +6007,185 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(2도움), 앙쿠_863246191(2도움), UNIT_840228251(1도움)</t>
+          <t>셀래스틴_848230938(1도움), 셀래스틴_852241461(1도움), 셀래스틴_848194765(1도움), 셀래스틴_863233419(2도움), syma_867192629(1도움), syma_845224574(1도움)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-02 12:57:51</t>
+          <t>2026-10-04 05:50:55</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_846045197(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_867220502(1도움)</t>
+          <t>호야국2인_848216435(1도움), 호야국2인_845198219(1도움), 호야국2인_851261865(1도움), Gucci와퍼_852028765(1도움), Gucci와퍼_852168473(1도움), Gucci와퍼_852208128(1도움)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-02 12:45:28</t>
+          <t>2026-10-04 05:40:38</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>피파왕초보구단주_846045197(1도움), 피파왕초보구단주_867000027(2도움), 콩콩콩룔_867220502(1도움)</t>
-        </is>
-      </c>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-02 10:04:35</t>
+          <t>2026-10-04 05:38:58</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>앙쿠_863246191(1도움), UNIT_840210736(1도움), UNIT_840228251(2도움)</t>
+          <t>셀래스틴_852259694(1도움), 셀래스틴_861005680(1도움), 셀래스틴_852241461(3도움)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-01 15:50:18</t>
+          <t>2026-10-04 05:38:58</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>suma수마_861221162(1도움), 피파왕초보구단주_867000027(1도움), 피파왕초보구단주_851243057(2도움)</t>
+          <t>호야국2인_848232293(1도움), 호야국2인_845198219(1도움)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-01 15:38:48</t>
+          <t>2026-10-04 05:27:25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>suma수마_845192190(1도움), suma수마_861190046(1도움), 피파왕초보구단주_867000027(1도움)</t>
+          <t>호야국2인_846192505(1도움), Gucci와퍼_864200104(1도움), Gucci와퍼_852010264(1도움)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-01 15:24:08</t>
+          <t>2026-10-04 05:21:46</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>8_0</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4823,19 +6195,19 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_846208722(1도움), 피파왕초보구단주_856209331(1도움), 피파왕초보구단주_851243057(1도움), 피파왕초보구단주_867000027(1도움), Gucci와퍼_864200104(1도움)</t>
+          <t>셀래스틴_848231866(1도움), 셀래스틴_861005680(1도움), 셀래스틴_863233419(4도움), 셀래스틴_848194765(2도움)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-01 15:12:09</t>
+          <t>2026-10-04 05:16:16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>피파왕초보구단주</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4845,7 +6217,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4855,24 +6227,24 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>피파왕초보구단주_846208722(1도움), 피파왕초보구단주_867000027(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_864200104(1도움), Gucci와퍼_852168473(1도움)</t>
+          <t>호야국2인_846192505(1도움), Gucci와퍼_840208574(1도움)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-01 14:56:12</t>
+          <t>2026-10-04 05:10:38</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4887,29 +6259,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(1도움), 호야국2인_846192505(1도움)</t>
+          <t>셀래스틴_852259694(1도움), ShangHaiPortFC_848031432(2도움)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-01 14:51:31</t>
+          <t>2026-10-04 05:00:23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>호야국2인</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>은안</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Gucci와퍼</t>
-        </is>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4919,29 +6291,29 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>은안_866241236(1도움), Gucci와퍼_851210697(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_840208574(1도움), Gucci와퍼_852010264(1도움)</t>
+          <t>호야국2인_848232293(1도움), 호야국2인_848241390(1도움), 은안_852237692(1도움), 은안_856246420(2도움)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-01 14:45:02</t>
+          <t>2026-10-04 04:48:36</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0708ManUtd</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4951,249 +6323,253 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0708ManUtd_834239053(1도움), 호야국2인_846192505(1도움)</t>
+          <t>호야국2인_848217870(1도움), 호야국2인_848227236(1도움), 은안_848231866(1도움), 은안_856246420(1도움)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-01 14:39:52</t>
+          <t>2026-10-03 18:10:10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4_1</t>
+          <t>2_6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>은안_848231866(1도움), 은안_856251517(1도움), 은안_856246420(1도움), 은안_866241236(1도움), Gucci와퍼_861139720(1도움)</t>
+          <t>앙쿠_848176580(1도움), 앙쿠_846193747(1도움), UNIT_867166676(1도움), UNIT_840228251(1도움), UNIT_863250723(2도움), UNIT_848180930(1도움)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-01 14:31:32</t>
+          <t>2026-10-03 17:55:25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>호야국2인_851216409(1도움), 호야국2인_845198219(1도움), Special블루_877001625(2도움), Special블루_861006975(1도움)</t>
+          <t>앙쿠_851194765(1도움), UNIT_840210736(1도움)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-01 14:21:07</t>
+          <t>2026-10-03 17:38:01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>호야국2인_846192505(1도움), Special블루_861006975(1도움), Special블루_856246669(2도움)</t>
+          <t>앙쿠_851194765(2도움), 앙쿠_848176580(2도움), UNIT_840225782(1도움), UNIT_840228251(1도움)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-01 14:08:57</t>
+          <t>2026-10-03 17:26:32</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>호야국2인_848216435(1도움), 호야국2인_845198219(1도움), 호야국2인_851261865(1도움), 비주류중독_839247699(1도움), 비주류중독_848006975(1도움)</t>
+          <t>앙쿠_814226161(1도움), 앙쿠_856247103(1도움), UNIT_840228251(1도움), UNIT_867166676(2도움)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-01 13:58:38</t>
+          <t>2026-10-03 17:14:22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>비주류중독_848006975(3도움), 비주류중독_839247699(1도움), 비주류중독_840052241(1도움)</t>
+          <t>앙쿠_846186345(1도움), 앙쿠_856247103(1도움), UNIT_840192883(1도움)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-01 13:48:03</t>
+          <t>2026-10-03 16:54:05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>앙쿠_845246191(1도움), 앙쿠_848176580(1도움), 앙쿠_846193747(1도움), 여수가스_828231747(1도움), 여수가스_846001551(1도움), 여수가스_861215732(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-01 13:34:35</t>
+          <t>2026-10-03 16:42:34</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>7_0</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>아들러_840191208(1도움), Special블루_877001625(1도움)</t>
+          <t>앙쿠_851194765(2도움), 앙쿠_845246191(3도움), 앙쿠_846193747(1도움)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-01 13:24:02</t>
+          <t>2026-10-03 15:45:24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Special블루</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5203,29 +6579,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>아들러_866251377(1도움), 아들러_861000570(1도움), Special블루_856246669(1도움), Special블루_848230666(1도움), Special블루_861006975(1도움)</t>
+          <t>UNIT_848180930(1도움), UNIT_840192883(1도움), UNIT_840225782(1도움), Voor_856256079(1도움)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-01 13:13:07</t>
+          <t>2026-10-03 15:32:25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>7_0</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5235,29 +6611,29 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(5도움)</t>
+          <t>UNIT_867166676(1도움), UNIT_840228251(1도움), UNIT_848265695(1도움), Voor_856256079(1도움), Voor_845247090(1도움)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-01 13:02:02</t>
+          <t>2026-10-03 15:20:36</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5265,59 +6641,63 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(1도움), Voor_845009676(3도움)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-01 13:01:02</t>
+          <t>2026-10-03 15:09:15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>3_6</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>앙쿠_856247103(1도움), syma_851236295(1도움)</t>
+          <t>UNIT_867166676(1도움), UNIT_848180930(1도움), UNIT_863250723(1도움), Voor_861000027(2도움), Voor_845009676(2도움), Voor_835183277(2도움)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-01 12:49:37</t>
+          <t>2026-10-03 14:56:34</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5325,91 +6705,95 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1도움), UNIT_863250723(1도움), UNIT_840210736(1도움), Voor_856256079(1도움), Voor_835183277(1도움), Voor_852233700(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-01 11:22:46</t>
+          <t>2026-10-03 14:45:40</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3_0</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_848176580(1도움)</t>
+          <t>UNIT_840210736(1도움), UNIT_840228251(1도움), Voor_835183277(2도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-01 11:15:46</t>
+          <t>2026-10-03 14:30:09</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>suma수마_851234112(1도움), suma수마_840001114(1도움), suma수마_861190046(1도움), suma수마_848225439(1도움), 겐지간지_845183898(1도움)</t>
+          <t>UNIT_840210736(1도움), UNIT_840225782(1도움), Voor_845239231(1도움), Voor_852233700(1도움), Voor_835183277(1도움), Voor_845247090(1도움)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-01 11:12:19</t>
+          <t>2026-10-03 09:55:42</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5419,29 +6803,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_848176580(1도움), 앙쿠_863246191(1도움), Gucci차붐_861182521(1도움)</t>
+          <t>UNIT_840225782(1도움), UNIT_867166676(1도움), UNIT_848265695(1도움), UNIT_840192883(1도움), 셀래스틴_861005680(1도움), 셀래스틴_848194765(1도움)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-01 11:03:11</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5451,29 +6835,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>suma수마_861013383(2도움), suma수마_826223697(1도움), suma수마_861221162(1도움), suma수마_840001114(1도움), 겐지간지_852231443(1도움), 겐지간지_845158023(2도움)</t>
+          <t>UNIT_848135455(1도움), 셀래스틴_861005680(1도움)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-01 07:54:09</t>
+          <t>2026-10-03 09:32:54</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5483,29 +6867,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>호야국2인_848227236(2도움), 호야국2인_848232293(1도움), 아들러_866251377(1도움), 아들러_855232639(1도움)</t>
+          <t>UNIT_848180930(1도움), UNIT_840228251(2도움), UNIT_840192883(2도움), 셀래스틴_848194765(1도움)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-01 07:42:04</t>
+          <t>2026-10-03 09:20:46</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>아들러</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5515,24 +6899,24 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(2도움), 호야국2인_848217870(1도움), 호야국2인_851216409(1도움), 아들러_840191208(1도움)</t>
+          <t>UNIT_840192883(2도움), UNIT_840210736(1도움), 셀래스틴_848230938(1도움)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-01 06:47:50</t>
+          <t>2026-10-03 09:08:53</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5547,29 +6931,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>호야국2인_848217870(1도움), 호야국2인_848232293(1도움), 호야국2인_852001183(1도움), suma수마_861190046(1도움), suma수마_848225439(1도움)</t>
+          <t>UNIT_867166676(2도움), UNIT_840210736(1도움), UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_848194765(1도움)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-01 06:36:26</t>
+          <t>2026-10-03 08:56:57</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>suma수마</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5579,14 +6963,14 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>호야국2인_851216409(1도움), 호야국2인_845198219(1도움), 호야국2인_846192505(1도움), 호야국2인_848216435(1도움), suma수마_826223697(1도움)</t>
+          <t>UNIT_840225782(1도움), UNIT_848135455(1도움), 셀래스틴_863233419(1도움)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-30 17:45:59</t>
+          <t>2026-10-03 08:43:58</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5596,12 +6980,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5611,93 +6995,93 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움), Voor_856256079(1도움), Voor_861000027(4도움)</t>
+          <t>UNIT_840192883(1도움)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-30 17:34:22</t>
+          <t>2026-10-02 16:24:32</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>UNIT_861221162(1도움), UNIT_866247257(1도움), UNIT_840228251(1도움), Voor_845009676(1도움), Voor_858025420(1도움), Voor_835183277(1도움)</t>
+          <t>앙쿠_846193747(2도움)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-30 17:17:18</t>
+          <t>2026-10-02 16:14:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), UNIT_848135455(1도움), Voor_845239231(1도움), Voor_845009676(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_814226161(1도움), UNIT_840228251(3도움), UNIT_845207439(1도움)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-30 17:03:54</t>
+          <t>2026-10-02 15:54:37</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5707,29 +7091,29 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_840192883(1도움), UNIT_848265695(3도움), Voor_852233700(1도움)</t>
+          <t>앙쿠_863246191(3도움), 앙쿠_851194765(1도움)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-30 16:46:35</t>
+          <t>2026-10-02 15:43:20</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>0_6</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5739,29 +7123,29 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), Voor_845009676(1도움), Voor_846184943(1도움), Voor_852233700(1도움)</t>
+          <t>UNIT_840210736(1도움), UNIT_840228251(1도움), UNIT_840225782(1도움), UNIT_840192883(1도움), UNIT_863250723(1도움), UNIT_848135455(1도움)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-30 14:01:02</t>
+          <t>2026-10-02 15:32:20</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5771,61 +7155,57 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2도움), 셀래스틴_848194765(1도움), 셀래스틴_848231866(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>앙쿠_846193747(1도움), UNIT_840192883(1도움), UNIT_845207439(1도움)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-30 13:49:10</t>
+          <t>2026-10-02 15:20:55</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>UNIT_840210736(2도움), UNIT_867166676(1도움), UNIT_848135455(1도움), UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852241461(2도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-30 13:33:10</t>
+          <t>2026-10-02 14:48:41</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5835,157 +7215,157 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852259694(1도움), 셀래스틴_861005680(1도움)</t>
+          <t>앙쿠_863246191(1도움), UNIT_840192883(2도움), UNIT_840228251(1도움)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:44</t>
+          <t>2026-10-02 14:36:35</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gucci와퍼_852168473(3도움), Gucci와퍼_852028765(1도움), 비주류중독_840052241(1도움), 비주류중독_862180283(1도움)</t>
+          <t>앙쿠_863246191(1도움), 앙쿠_851194765(1도움), UNIT_848265695(1도움), UNIT_840192883(2도움)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-30 13:21:00</t>
+          <t>2026-10-02 14:24:08</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움), UNIT_840228251(1도움)</t>
+          <t>앙쿠_863246191(1도움), 앙쿠_856247103(1도움), UNIT_840228251(1도움), UNIT_840192883(2도움), UNIT_840225782(1도움)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-30 13:12:24</t>
+          <t>2026-10-02 14:12:59</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Gucci와퍼</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>5_2</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gucci와퍼_852010264(1도움), 비주류중독_834239977(1도움), 비주류중독_848006975(1도움)</t>
+          <t>앙쿠_848176580(2도움), 앙쿠_851194765(1도움), UNIT_840192883(2도움)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-30 13:10:05</t>
+          <t>2026-10-02 14:00:42</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1도움), UNIT_840192883(2도움), UNIT_840225782(1도움), 셀래스틴_848194765(1도움), 셀래스틴_863200458(1도움)</t>
+          <t>앙쿠_848176580(2도움), 앙쿠_856247103(1도움), UNIT_840228251(3도움), UNIT_840225782(1도움)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-30 12:57:48</t>
+          <t>2026-10-02 13:50:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5995,88 +7375,88 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>UNIT_863250723(1도움), UNIT_840228251(2도움), 셀래스틴_852241461(1도움)</t>
+          <t>앙쿠_851194765(2도움), 앙쿠_863246191(2도움), UNIT_840228251(1도움)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:39</t>
+          <t>2026-10-02 12:57:51</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>셀래스틴_848231866(1도움), 셀래스틴_852259694(1도움), 비주류중독_839247699(1도움), 비주류중독_834239977(2도움)</t>
+          <t>피파왕초보구단주_846045197(1도움), 콩콩콩룔_867223848(1도움), 콩콩콩룔_867220502(1도움)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-30 12:24:21</t>
+          <t>2026-10-02 12:45:28</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>비주류중독</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>셀래스틴_852259694(1도움), 셀래스틴_848194765(1도움)</t>
+          <t>피파왕초보구단주_846045197(1도움), 피파왕초보구단주_867000027(2도움), 콩콩콩룔_867220502(1도움)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-30 12:00:21</t>
+          <t>2026-10-02 10:04:35</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6091,29 +7471,29 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>UNIT_840225782(1도움), UNIT_867166676(1도움), 셀래스틴_848013038(1도움), 셀래스틴_852241461(2도움)</t>
+          <t>앙쿠_863246191(1도움), UNIT_840210736(1도움), UNIT_840228251(2도움)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-30 09:47:20</t>
+          <t>2026-10-01 15:50:18</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6123,61 +7503,61 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>방덕_867001040(1도움), 방덕_848231478(2도움), Voor_845009676(1도움), Voor_845239231(1도움), Voor_835183277(1도움), Voor_848216150(1도움)</t>
+          <t>suma수마_861221162(1도움), 피파왕초보구단주_867000027(1도움), 피파왕초보구단주_851243057(2도움)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-30 09:35:39</t>
+          <t>2026-10-01 15:38:48</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>suma수마</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Voor_852233700(2도움), Voor_856256079(1도움), Voor_845009676(2도움), Voor_835183277(1도움)</t>
+          <t>suma수마_845192190(1도움), suma수마_861190046(1도움), 피파왕초보구단주_867000027(1도움)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-30 08:27:58</t>
+          <t>2026-10-01 15:24:08</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -6187,93 +7567,93 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Legend독수리_861215732(1도움), Legend독수리_852209658(1도움), syma_852274967(1도움), syma_863228092(1도움)</t>
+          <t>피파왕초보구단주_846208722(1도움), 피파왕초보구단주_856209331(1도움), 피파왕초보구단주_851243057(1도움), 피파왕초보구단주_867000027(1도움), Gucci와퍼_864200104(1도움)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-30 08:16:55</t>
+          <t>2026-10-01 15:12:09</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>피파왕초보구단주</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1_6</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Legend독수리_861215732(1도움), syma_866231913(2도움), syma_863222665(4도움)</t>
+          <t>피파왕초보구단주_846208722(1도움), 피파왕초보구단주_867000027(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_864200104(1도움), Gucci와퍼_852168473(1도움)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-30 08:04:48</t>
+          <t>2026-10-01 14:56:12</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Legend독수리_848224425(1도움), Legend독수리_826236703(1도움), syma_856233848(1도움)</t>
+          <t>호야국2인_848232293(1도움), 호야국2인_846192505(1도움)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-30 07:53:20</t>
+          <t>2026-10-01 14:51:31</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Legend독수리</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6283,61 +7663,61 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Legend독수리_861081644(1도움), syma_846001845(2도움)</t>
+          <t>은안_866241236(1도움), Gucci와퍼_851210697(1도움), Gucci와퍼_852208128(1도움), Gucci와퍼_840208574(1도움), Gucci와퍼_852010264(1도움)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-29 14:16:03</t>
+          <t>2026-10-01 14:45:02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>0708ManUtd</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>7_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>개포동덕배_848206113(1도움), 개포동덕배_845208722(3도움), 개포동덕배_856202126(1도움), 개포동덕배_863212622(2도움), Gucci차붐_853272733(1도움), Gucci차붐_864176403(1도움)</t>
+          <t>0708ManUtd_834239053(1도움), 호야국2인_846192505(1도움)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-29 14:04:54</t>
+          <t>2026-10-01 14:39:52</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>Gucci와퍼</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6347,93 +7727,93 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>개포동덕배_856202126(1도움), 개포동덕배_863234396(1도움), 개포동덕배_856275298(1도움), 개포동덕배_848206113(1도움), Gucci차붐_864084333(1도움), Gucci차붐_864247686(1도움)</t>
+          <t>은안_848231866(1도움), 은안_856251517(1도움), 은안_856246420(1도움), 은안_866241236(1도움), Gucci와퍼_861139720(1도움)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-29 11:20:02</t>
+          <t>2026-10-01 14:31:32</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(2도움)</t>
+          <t>호야국2인_851216409(1도움), 호야국2인_845198219(1도움), Special블루_877001625(2도움), Special블루_861006975(1도움)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-29 11:08:25</t>
+          <t>2026-10-01 14:21:07</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>UNIT_840192883(2도움), UNIT_848265695(1도움), 콩콩콩룔_851236496(1도움)</t>
+          <t>호야국2인_846192505(1도움), Special블루_861006975(1도움), Special블루_856246669(2도움)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-29 10:56:21</t>
+          <t>2026-10-01 14:08:57</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>7_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6443,93 +7823,89 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>오스트리아_864182152(2도움), 오스트리아_864140057(1도움), 오스트리아_851236636(4도움), ShangHaiPortFC_848031432(1도움)</t>
+          <t>호야국2인_848216435(1도움), 호야국2인_845198219(1도움), 호야국2인_851261865(1도움), 비주류중독_839247699(1도움), 비주류중독_848006975(1도움)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-29 10:47:10</t>
+          <t>2026-10-01 13:58:38</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UNIT_848180930(1도움), UNIT_863250723(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+          <t>비주류중독_848006975(3도움), 비주류중독_839247699(1도움), 비주류중독_840052241(1도움)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-29 10:45:30</t>
+          <t>2026-10-01 13:48:03</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ShangHaiPortFC</t>
+          <t>비주류중독</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>오스트리아_851221671(1도움), 오스트리아_863223671(1도움), 오스트리아_863240709(1도움), 오스트리아_864140057(1도움), 오스트리아_851216275(1도움), ShangHaiPortFC_827143001(1도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-29 10:35:32</t>
+          <t>2026-10-01 13:34:35</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6539,125 +7915,121 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1도움), 셀래스틴_848231866(2도움), 셀래스틴_852241461(1도움)</t>
+          <t>아들러_840191208(1도움), Special블루_877001625(1도움)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-29 10:18:25</t>
+          <t>2026-10-01 13:24:02</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>아들러</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Special블루</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UNIT_839013383(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+          <t>아들러_866251377(1도움), 아들러_861000570(1도움), Special블루_856246669(1도움), Special블루_848230666(1도움), Special블루_861006975(1도움)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-29 09:24:43</t>
+          <t>2026-10-01 13:13:07</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>7_0</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>오스트리아_864199266(1도움), 오스트리아_863240709(1도움), 셀래스틴_846001551(1도움), 셀래스틴_848194765(2도움)</t>
+          <t>앙쿠_848176580(5도움)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-29 09:13:08</t>
+          <t>2026-10-01 13:02:02</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>오스트리아_851221671(1도움), 셀래스틴_848231866(1도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-29 09:02:47</t>
+          <t>2026-10-01 13:01:02</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6667,29 +8039,29 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>오스트리아_864140057(1도움), 오스트리아_864182152(1도움), 오스트리아_851236636(1도움), 셀래스틴_846001551(1도움)</t>
+          <t>앙쿠_856247103(1도움), syma_851236295(1도움)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-29 08:51:25</t>
+          <t>2026-10-01 12:49:37</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>오스트리아</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0_2</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6697,39 +8069,1411 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>셀래스틴_863200458(1도움), 셀래스틴_852241461(1도움)</t>
-        </is>
-      </c>
+      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>2026-10-01 11:22:46</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3_0</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(1도움), 앙쿠_848176580(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:46</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>suma수마_851234112(1도움), suma수마_840001114(1도움), suma수마_861190046(1도움), suma수마_848225439(1도움), 겐지간지_845183898(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:12:19</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(1도움), 앙쿠_848176580(1도움), 앙쿠_863246191(1도움), Gucci차붐_861182521(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:03:11</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>5_3</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>suma수마_861013383(2도움), suma수마_826223697(1도움), suma수마_861221162(1도움), suma수마_840001114(1도움), 겐지간지_852231443(1도움), 겐지간지_845158023(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-01 07:54:09</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>호야국2인</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>호야국2인_848227236(2도움), 호야국2인_848232293(1도움), 아들러_866251377(1도움), 아들러_855232639(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-01 07:42:04</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>호야국2인</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>아들러</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>호야국2인_848232293(2도움), 호야국2인_848217870(1도움), 호야국2인_851216409(1도움), 아들러_840191208(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:47:50</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>호야국2인</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>호야국2인_848217870(1도움), 호야국2인_848232293(1도움), 호야국2인_852001183(1도움), suma수마_861190046(1도움), suma수마_848225439(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:36:26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>호야국2인</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>suma수마</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>호야국2인_851216409(1도움), 호야국2인_845198219(1도움), 호야국2인_846192505(1도움), 호야국2인_848216435(1도움), suma수마_826223697(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:45:59</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2_5</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(1도움), Voor_856256079(1도움), Voor_861000027(4도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:34:22</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3_4</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>UNIT_861221162(1도움), UNIT_866247257(1도움), UNIT_840228251(1도움), Voor_845009676(1도움), Voor_858025420(1도움), Voor_835183277(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:17:18</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), UNIT_848135455(1도움), Voor_845239231(1도움), Voor_845009676(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:03:54</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1도움), UNIT_840192883(1도움), UNIT_848265695(3도움), Voor_852233700(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:46:35</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>UNIT_840228251(1도움), UNIT_840192883(1도움), Voor_845009676(1도움), Voor_846184943(1도움), Voor_852233700(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-30 14:01:02</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2_5</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2도움), 셀래스틴_848194765(1도움), 셀래스틴_848231866(1도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:49:10</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>5_3</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>UNIT_840210736(2도움), UNIT_867166676(1도움), UNIT_848135455(1도움), UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852241461(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:33:10</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>1_5</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852259694(1도움), 셀래스틴_861005680(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:24:44</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Gucci와퍼_852168473(3도움), Gucci와퍼_852028765(1도움), 비주류중독_840052241(1도움), 비주류중독_862180283(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:21:00</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(1도움), UNIT_840228251(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:12:24</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Gucci와퍼</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Gucci와퍼_852010264(1도움), 비주류중독_834239977(1도움), 비주류중독_848006975(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:10:05</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>4_3</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1도움), UNIT_840192883(2도움), UNIT_840225782(1도움), 셀래스틴_848194765(1도움), 셀래스틴_863200458(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:57:48</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>UNIT_863250723(1도움), UNIT_840228251(2도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:35:39</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>셀래스틴_848231866(1도움), 셀래스틴_852259694(1도움), 비주류중독_839247699(1도움), 비주류중독_834239977(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:24:21</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>비주류중독</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>셀래스틴_852259694(1도움), 셀래스틴_848194765(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:00:21</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>UNIT_840225782(1도움), UNIT_867166676(1도움), 셀래스틴_848013038(1도움), 셀래스틴_852241461(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:47:20</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>3_4</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>방덕_867001040(1도움), 방덕_848231478(2도움), Voor_845009676(1도움), Voor_845239231(1도움), Voor_835183277(1도움), Voor_848216150(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:35:39</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>방덕</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>1_6</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Voor_852233700(2도움), Voor_856256079(1도움), Voor_845009676(2도움), Voor_835183277(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:27:58</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1도움), Legend독수리_852209658(1도움), syma_852274967(1도움), syma_863228092(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:16:55</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>1_6</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Legend독수리_861215732(1도움), syma_866231913(2도움), syma_863222665(4도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:04:48</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Legend독수리_848224425(1도움), Legend독수리_826236703(1도움), syma_856233848(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-30 07:53:20</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Legend독수리</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Legend독수리_861081644(1도움), syma_846001845(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:16:03</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>7_2</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>개포동덕배_848206113(1도움), 개포동덕배_845208722(3도움), 개포동덕배_856202126(1도움), 개포동덕배_863212622(2도움), Gucci차붐_853272733(1도움), Gucci차붐_864176403(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:04:54</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>개포동덕배_856202126(1도움), 개포동덕배_863234396(1도움), 개포동덕배_856275298(1도움), 개포동덕배_848206113(1도움), Gucci차붐_864084333(1도움), Gucci차붐_864247686(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:20:02</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_848189505(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:08:25</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>콩콩콩룔</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(2도움), UNIT_848265695(1도움), 콩콩콩룔_851236496(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:56:21</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>7_1</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>오스트리아_864182152(2도움), 오스트리아_864140057(1도움), 오스트리아_851236636(4도움), ShangHaiPortFC_848031432(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:47:10</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(1도움), UNIT_863250723(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:45:30</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ShangHaiPortFC</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>오스트리아_851221671(1도움), 오스트리아_863223671(1도움), 오스트리아_863240709(1도움), 오스트리아_864140057(1도움), 오스트리아_851216275(1도움), ShangHaiPortFC_827143001(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:35:32</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1도움), 셀래스틴_848231866(2도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:18:25</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>UNIT_839013383(1도움), UNIT_840192883(1도움), 셀래스틴_846001551(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:24:43</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>오스트리아_864199266(1도움), 오스트리아_863240709(1도움), 셀래스틴_846001551(1도움), 셀래스틴_848194765(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:13:08</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>오스트리아_851221671(1도움), 셀래스틴_848231866(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:02:47</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>오스트리아_864140057(1도움), 오스트리아_864182152(1도움), 오스트리아_851236636(1도움), 셀래스틴_846001551(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-29 08:51:25</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>오스트리아</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>0_2</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>셀래스틴_863200458(1도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>2026-09-29 04:33:11</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>여수가스</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>오스트리아</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>2_3</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>여수가스_852216393(1도움), 여수가스_861162895(1도움), 오스트리아_864140057(1도움), 오스트리아_851257075(1도움)</t>
         </is>

--- a/API데이터_경기_득점_및_도움_기록.xlsx
+++ b/API데이터_경기_득점_및_도움_기록.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,54 +452,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:51:44</t>
+          <t>2026-10-09 13:36:17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6_2</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_861049369(3골), 앙쿠_851194765(2골), 셀래스틴_848194765(1골), 셀래스틴_861005680(1골)</t>
+          <t>검정소_868192181(3골), 콩콩콩룔_866223710(3골)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:39:26</t>
+          <t>2026-10-09 13:33:58</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -509,29 +509,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UNIT_867166676(3골), UNIT_848180930(1골), 셀래스틴_863233419(1골), 셀래스틴_861005680(1골)</t>
+          <t>셀래스틴_852241461(2골)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:28:13</t>
+          <t>2026-10-09 13:25:18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>10_4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -541,51 +541,51 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>앙쿠_866266039(1골), 앙쿠_861049369(1골), UNIT_863250723(1골)</t>
+          <t>검정소_868192181(5골), 검정소_100214100(5골), 콩콩콩룔_866223710(1골), 콩콩콩룔_867223848(2골), 콩콩콩룔_848189505(1골)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:16:19</t>
+          <t>2026-10-09 13:23:55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1골), 앙쿠_848176580(1골), 셀래스틴_861005680(2골), 셀래스틴_848231866(1골)</t>
+          <t>셀래스틴_863233419(2골), 셀래스틴_848194765(1골), syma_861000041(1골), syma_839191695(1골)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:05:29</t>
+          <t>2026-10-09 05:08:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -595,39 +595,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), 셀래스틴_861005680(2골), 셀래스틴_852241461(1골)</t>
+          <t>ZD장인지참치_840191208(2골), ZD장인지참치_848199503(1골), ZD장인지참치_839200104(2골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-07 12:50:50</t>
+          <t>2026-10-09 04:53:33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>3_6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -637,29 +637,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 앙쿠_861049369(1골), UNIT_848180930(3골), UNIT_867166676(2골)</t>
+          <t>ZD장인지참치_848199503(1골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골), 셀래스틴_861005680(1골), 셀래스틴_848230938(1골), 셀래스틴_863233419(1골), 셀래스틴_852241461(3골)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-07 12:30:57</t>
+          <t>2026-10-09 04:42:24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -669,19 +669,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), ZD장인지참치_840191208(1골)</t>
+          <t>ZD장인지참치_839200104(2골), ZD장인지참치_840256630(2골), 셀래스틴_861005680(2골)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-07 12:14:34</t>
+          <t>2026-10-09 04:31:15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -691,29 +691,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3_0</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1골), 앙쿠_848176580(1골), 앙쿠_866266039(1골)</t>
+          <t>ZD장인지참치_851240740(1골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골), 셀래스틴_852241461(2골), 셀래스틴_863233419(1골), 셀래스틴_863200458(1골)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-07 12:04:29</t>
+          <t>2026-10-09 04:19:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -733,29 +733,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(2골), 앙쿠_866266039(1골), 셀래스틴_852241461(1골)</t>
+          <t>ZD장인지참치_840191208(1골), ZD장인지참치_839200104(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-07 11:33:41</t>
+          <t>2026-10-09 04:04:37</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -763,39 +763,1439 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>용신_825212188(3골)</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>2026-10-09 03:48:59</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1_0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>UNIT_863250723(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-09 02:36:22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>syma_867192629(1골), 용신_866200104(1골), 용신_804264453(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-09 02:26:03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>syma_848192638(1골), syma_845224574(1골), 용신_101173731(2골), 용신_866200104(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-08 17:16:26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5_4</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(3골), UNIT_840192883(2골), Voor_858025420(1골), Voor_852233700(2골), Voor_845009676(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-08 17:00:32</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1골), UNIT_848180930(1골), Voor_845009676(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:48:25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0_2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Voor_845009676(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:33:10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>검정소</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>5_3</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>검정소_868192181(4골), 검정소_100214100(1골), Voor_858025420(1골), Voor_861000027(1골), Voor_845009676(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:21:30</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>검정소</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>검정소_868192181(2골), Voor_845009676(2골), Voor_852233700(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:05:27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>검정소</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3_4</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), UNIT_848180930(1골), 검정소_861214098(1골), 검정소_868192181(1골), 검정소_100214100(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:53:08</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>검정소</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1골), UNIT_848180930(2골), 검정소_868192181(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:41:21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>검정소</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(2골), 검정소_868192181(1골), 검정소_867241096(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:34:46</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>호야국2인</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>호야국2인_846192505(1골), UNIT_848180930(1골), UNIT_867166676(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:19:20</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3_3</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(2골), UNIT_867166676(1골), 셀래스틴_861005680(2골), 셀래스틴_848231866(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:05:46</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>호야국2인</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1_0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>호야국2인_848232293(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:50:45</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3_3</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gucci차붐_840191208(3골), ZD장인지참치_861182521(1골), ZD장인지참치_840191208(1골), ZD장인지참치_839200104(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:27:59</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3_6</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gucci차붐_853227659(1골), Gucci차붐_864084333(1골), Gucci차붐_864176403(1골), 셀래스틴_861005680(2골), 셀래스틴_848194765(2골), 셀래스틴_852241461(1골), 셀래스틴_863233419(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:15:09</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>4_5</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gucci차붐_864247686(1골), Gucci차붐_853272992(2골), Gucci차붐_853227659(1골), 셀래스틴_861005680(2골), 셀래스틴_845167680(1골), 셀래스틴_852241461(2골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:47:28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>개포동덕배_845190048(2골), 개포동덕배_856202126(1골), 개포동덕배_845208722(2골), Voor_861000027(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:46:17</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0_5</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>용신_877177003(1골), 용신_826251421(1골), 용신_866200104(3골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:33:33</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>셀래스틴_861005680(1골), 용신_826251421(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:27:12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>은안</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>6_1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>개포동덕배_845208722(2골), 개포동덕배_845190048(3골), 개포동덕배_848206113(1골), 은안_856246420(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:25:05</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_225238224(1골), syma_867192629(1골), syma_845224574(1골), syma_866235522(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:16:35</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>은안</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>7_1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>개포동덕배_856202126(4골), 개포동덕배_848206113(1골), 개포동덕배_845190048(2골), 은안_866241236(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:13:50</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_277205156(1골), syma_867192629(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:11:09</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(2골), ZD장인지참치_840191208(1골), ZD장인지참치_851240740(1골), ZD장인지참치_848199503(1골), ZD장인지참치_839200104(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:59:25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0_0</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:58:38</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1골), 앙쿠_845246191(1골), ZD장인지참치_839200104(4골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:26:36</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2_6</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_225238224(1골), 경남FC가즈아_805267825(1골), 셀래스틴_861005680(5골), 셀래스틴_848230938(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:13:33</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3_3</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_805267825(3골), 셀래스틴_863233419(1골), 셀래스틴_852241461(1골), 셀래스틴_848230938(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:00:38</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_839200104(4골), ZD장인지참치_840191208(1골), 용신_101173731(1골), 용신_863245367(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:49:29</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(1골), ZD장인지참치_840247263(1골), 용신_863245367(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:25:42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1_0</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:14:55</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1_4</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(1골), UNIT_863250723(1골), UNIT_848180930(1골), UNIT_840228251(1골), UNIT_867166676(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:03:01</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(1골), 앙쿠_848176580(1골), 앙쿠_863232488(1골), 셀래스틴_863233419(1골), 셀래스틴_848231866(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:51:44</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6_2</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(3골), 앙쿠_851194765(2골), 앙쿠_848176580(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:39:26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(3골), UNIT_848180930(1골), 셀래스틴_863233419(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:28:13</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>앙쿠_866266039(1골), 앙쿠_861049369(1골), UNIT_863250723(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:16:19</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(1골), 앙쿠_848176580(1골), 셀래스틴_861005680(2골), 셀래스틴_848231866(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:05:29</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1골), 셀래스틴_861005680(2골), 셀래스틴_852241461(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:50:50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2_5</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(1골), 앙쿠_851194765(1골), UNIT_867166676(2골), UNIT_848180930(3골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:30:57</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), ZD장인지참치_840191208(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:14:34</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3_0</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1골), 앙쿠_866266039(1골), 앙쿠_861049369(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:04:29</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(2골), 앙쿠_866266039(1골), 셀래스틴_852241461(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:33:41</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0_3</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>용신_825212188(3골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>2026-10-07 11:21:15</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>겐지간지</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>용신</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>1_4</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>겐지간지_845158023(1골), 용신_866200104(1골), 용신_825212188(3골)</t>
         </is>
@@ -812,7 +2212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -850,54 +2250,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:51:44</t>
+          <t>2026-10-09 13:36:17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6_2</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1도움), 앙쿠_861049369(1도움), 앙쿠_851194765(3도움), 셀래스틴_852241461(1도움)</t>
+          <t>검정소_100214100(1도움), 검정소_861005003(2도움), 콩콩콩룔_848189505(1도움), 콩콩콩룔_867220502(2도움)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:39:26</t>
+          <t>2026-10-09 13:33:58</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -907,29 +2307,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UNIT_840192883(2도움), UNIT_840210736(1도움), UNIT_840228251(1도움)</t>
+          <t>셀래스틴_861005680(1도움), 셀래스틴_848231866(1도움)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:28:13</t>
+          <t>2026-10-09 13:25:18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>10_4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,51 +2339,51 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>앙쿠_846193747(1도움)</t>
+          <t>검정소_861005003(3도움), 검정소_868192181(2도움), 검정소_861214098(2도움), 검정소_851241721(1도움), 검정소_100214100(1도움), 콩콩콩룔_861006235(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_867223848(1도움)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:16:19</t>
+          <t>2026-10-09 13:23:55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1도움), 앙쿠_851194765(1도움), 셀래스틴_852241461(2도움), 셀래스틴_863233419(1도움)</t>
+          <t>셀래스틴_848194765(1도움), 셀래스틴_852241461(1도움), 셀래스틴_848230938(1도움), syma_863251854(1도움), syma_866264388(1도움)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:05:29</t>
+          <t>2026-10-09 05:08:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -993,39 +2393,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UNIT_840210736(1도움), 셀래스틴_852259694(1도움), 셀래스틴_848230938(1도움)</t>
+          <t>ZD장인지참치_840256630(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_851240740(2도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-07 12:50:50</t>
+          <t>2026-10-09 04:53:33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>3_6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1035,29 +2435,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1도움), UNIT_863250723(1도움), UNIT_840228251(1도움), UNIT_840210736(2도움), UNIT_840192883(1도움)</t>
+          <t>ZD장인지참치_861182521(1도움), ZD장인지참치_840191208(1도움), ZD장인지참치_851240740(1도움), 셀래스틴_861005680(2도움), 셀래스틴_848231866(1도움), 셀래스틴_848194765(2도움), 셀래스틴_863200458(1도움)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-07 12:30:57</t>
+          <t>2026-10-09 04:42:24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1067,19 +2467,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UNIT_840210736(1도움), ZD장인지참치_840256630(1도움)</t>
+          <t>ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_851240740(1도움), 셀래스틴_848013038(1도움), 셀래스틴_852259694(1도움)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-07 12:14:34</t>
+          <t>2026-10-09 04:31:15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1089,29 +2489,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3_0</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(2도움), 앙쿠_846186345(1도움)</t>
+          <t>ZD장인지참치_848199503(1도움), ZD장인지참치_840191208(2도움), 셀래스틴_852241461(1도움), 셀래스틴_863233419(1도움), 셀래스틴_861005680(1도움), 셀래스틴_863200458(1도움)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-07 12:04:29</t>
+          <t>2026-10-09 04:19:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1121,7 +2521,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1131,29 +2531,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_846186345(1도움), 앙쿠_848176580(1도움), 셀래스틴_863200458(1도움)</t>
+          <t>ZD장인지참치_840191208(1도움), ZD장인지참치_861182521(1도움), 셀래스틴_848231866(1도움)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-07 11:33:41</t>
+          <t>2026-10-09 04:04:37</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1161,39 +2561,1439 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>용신_101173731(1도움), 용신_866200104(1도움)</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>2026-10-09 03:48:59</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1_0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-09 02:36:22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1_2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>syma_845224574(1도움), 용신_826251421(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-09 02:26:03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>syma_867192629(1도움), syma_851224415(1도움), 용신_877177003(1도움), 용신_101173731(1도움), 용신_826251421(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-08 17:16:26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5_4</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>UNIT_840225782(1도움), UNIT_848265695(1도움), UNIT_863250723(1도움), UNIT_840228251(1도움), Voor_856256079(1도움), Voor_861045674(1도움), Voor_852233700(1도움), Voor_845009676(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-08 17:00:32</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>UNIT_863250723(1도움), UNIT_840228251(1도움), Voor_852233700(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:48:25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0_2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Voor_852233700(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:33:10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>검정소</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>5_3</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>검정소_861005003(2도움), 검정소_851241721(1도움), 검정소_100214100(1도움), Voor_852233700(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:21:30</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>검정소</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>검정소_861005003(2도움), Voor_861000027(1도움), Voor_845247090(1도움), Voor_852233700(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:05:27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>검정소</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3_4</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(3도움), 검정소_867241096(1도움), 검정소_851247229(1도움), 검정소_861005003(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:53:08</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>검정소</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>UNIT_848265695(1도움), UNIT_867166676(1도움), 검정소_861214098(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:41:21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>검정소</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2_2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(1도움), UNIT_840228251(1도움), 검정소_861214098(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:34:46</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>호야국2인</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>호야국2인_848216435(1도움), UNIT_840225782(1도움), UNIT_840210736(1도움), UNIT_840192883(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:19:20</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3_3</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>UNIT_840228251(1도움), UNIT_840210736(1도움), UNIT_840192883(1도움), 셀래스틴_852259694(1도움), 셀래스틴_852241461(1도움), 셀래스틴_863200458(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:05:46</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>호야국2인</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1_0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>호야국2인_848216435(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:50:45</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3_3</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gucci차붐_867208128(2도움), Gucci차붐_877256630(1도움), ZD장인지참치_840191208(1도움), ZD장인지참치_851240740(1도움), ZD장인지참치_839200104(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:27:59</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3_6</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gucci차붐_853227659(1도움), Gucci차붐_864247686(1도움), 셀래스틴_848230938(2도움), 셀래스틴_861005680(1도움), 셀래스틴_852241461(1도움), 셀래스틴_863233419(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:15:09</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Gucci차붐</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>4_5</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gucci차붐_864176403(1도움), Gucci차붐_851221671(2도움), 셀래스틴_863200458(1도움), 셀래스틴_852259694(1도움), 셀래스틴_848194765(2도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:47:28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Voor</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>5_1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>개포동덕배_848206113(1도움), 개포동덕배_856202126(1도움), 개포동덕배_856212622(1도움), 개포동덕배_852225375(1도움), 개포동덕배_863234396(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:46:17</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0_5</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>용신_877177003(1도움), 용신_101173731(2도움), 용신_863245367(1도움), 용신_856243576(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:33:33</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>셀래스틴_863233419(1도움), 용신_101173731(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:27:12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>은안</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>6_1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>개포동덕배_845208722(2도움), 개포동덕배_856202126(4도움), 은안_866241236(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:25:05</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_518251161(1도움), syma_861001668(1도움), syma_867192629(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:16:35</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>은안</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>7_1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>개포동덕배_845208722(3도움), 개포동덕배_856202126(1도움), 개포동덕배_845190048(1도움), 개포동덕배_856275298(2도움), 은안_877143001(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:13:50</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_805267825(1도움), syma_861001668(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:11:09</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(1도움), 앙쿠_845246191(1도움), ZD장인지참치_852213331(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_839200104(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:59:25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0_0</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:58:38</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1도움), 앙쿠_851194765(1도움), ZD장인지참치_840191208(2도움), ZD장인지참치_861182521(1도움), ZD장인지참치_848199503(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:26:36</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2_6</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_805207730(1도움), 경남FC가즈아_853221467(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852241461(3도움), 셀래스틴_852259694(1도움), 셀래스틴_848194765(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:13:33</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3_3</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_225238224(1도움), 경남FC가즈아_853221467(2도움), 셀래스틴_861005680(1도움), 셀래스틴_848230938(1도움), 셀래스틴_848194765(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:00:38</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_861182521(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_840191208(1도움), 용신_101173731(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:49:29</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_861182521(1도움), 용신_101173731(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:25:42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1_0</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>UNIT_840228251(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:14:55</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1_4</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1도움), UNIT_840228251(1도움), UNIT_867166676(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:03:01</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(2도움), 앙쿠_846186345(1도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:51:44</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6_2</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(1도움), 앙쿠_851194765(3도움), 앙쿠_848176580(1도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:39:26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(2도움), UNIT_840228251(1도움), UNIT_840210736(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:28:13</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>앙쿠_846193747(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:16:19</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(1도움), 앙쿠_861049369(1도움), 셀래스틴_852241461(2도움), 셀래스틴_863233419(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:05:29</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>UNIT_840210736(1도움), 셀래스틴_852259694(1도움), 셀래스틴_848230938(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:50:50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2_5</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1도움), UNIT_840210736(2도움), UNIT_840192883(1도움), UNIT_863250723(1도움), UNIT_840228251(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:30:57</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>UNIT_840210736(1도움), ZD장인지참치_840256630(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:14:34</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3_0</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>앙쿠_846186345(1도움), 앙쿠_851194765(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:04:29</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>앙쿠_846186345(1도움), 앙쿠_851194765(1도움), 앙쿠_848176580(1도움), 셀래스틴_863200458(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:33:41</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0_3</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>용신_101173731(1도움), 용신_866200104(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>2026-10-07 11:21:15</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>겐지간지</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>용신</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>1_4</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>겐지간지_852231443(1도움), 용신_866200104(1도움), 용신_291213648(2도움)</t>
         </is>

--- a/API데이터_경기_득점_및_도움_기록.xlsx
+++ b/API데이터_경기_득점_및_도움_기록.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,54 +452,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:36:17</t>
+          <t>2026-10-10 15:15:02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>검정소_868192181(3골), 콩콩콩룔_866223710(3골)</t>
+          <t>앙쿠_861049369(1골), 앙쿠_848176580(1골), Voor_835183277(1골), Voor_852001201(1골), Voor_845009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09 13:33:58</t>
+          <t>2026-10-10 15:00:33</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -509,29 +509,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>셀래스틴_852241461(2골)</t>
+          <t>앙쿠_866266039(1골), 앙쿠_848176580(2골), Voor_852233700(1골), Voor_856256079(1골)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-09 13:25:18</t>
+          <t>2026-10-10 14:50:04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10_4</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>검정소_868192181(5골), 검정소_100214100(5골), 콩콩콩룔_866223710(1골), 콩콩콩룔_867223848(2골), 콩콩콩룔_848189505(1골)</t>
+          <t>앙쿠_861049369(1골), 앙쿠_851194765(1골), Voor_852233700(1골)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-09 13:23:55</t>
+          <t>2026-10-10 13:38:29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -573,19 +573,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>셀래스틴_863233419(2골), 셀래스틴_848194765(1골), syma_861000041(1골), syma_839191695(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_851194765(2골), 셀래스틴_848194765(1골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09 05:08:26</t>
+          <t>2026-10-10 13:28:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -595,29 +595,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2골), ZD장인지참치_848199503(1골), ZD장인지참치_839200104(2골), 셀래스틴_861005680(1골)</t>
+          <t>앙쿠_861049369(1골), 앙쿠_848176580(1골), 앙쿠_851194765(1골), 셀래스틴_861005680(2골), 셀래스틴_852259694(1골), 셀래스틴_848231866(1골)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-09 04:53:33</t>
+          <t>2026-10-10 13:17:07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -627,29 +627,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3_6</t>
+          <t>6_2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ZD장인지참치_848199503(1골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골), 셀래스틴_861005680(1골), 셀래스틴_848230938(1골), 셀래스틴_863233419(1골), 셀래스틴_852241461(3골)</t>
+          <t>앙쿠_848176580(3골), 앙쿠_851194765(1골), 앙쿠_861049369(2골), 셀래스틴_861005680(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-09 04:42:24</t>
+          <t>2026-10-10 13:05:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -669,19 +669,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ZD장인지참치_839200104(2골), ZD장인지참치_840256630(2골), 셀래스틴_861005680(2골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_866266039(1골), 앙쿠_846193747(1골), 셀래스틴_861005680(2골)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09 04:31:15</t>
+          <t>2026-10-10 12:53:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -701,19 +701,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ZD장인지참치_851240740(1골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골), 셀래스틴_852241461(2골), 셀래스틴_863233419(1골), 셀래스틴_863200458(1골)</t>
+          <t>앙쿠_851194765(1골), 셀래스틴_863233419(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-09 04:19:11</t>
+          <t>2026-10-10 12:42:29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -723,99 +723,103 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(1골), ZD장인지참치_839200104(1골), 셀래스틴_852241461(1골)</t>
+          <t>앙쿠_814226161(1골), 앙쿠_851194765(1골), 셀래스틴_863233419(1골), 셀래스틴_848194765(1골)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-09 04:04:37</t>
+          <t>2026-10-10 11:51:07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>여수가스_861162895(1골), 여수가스_861215732(1골), 경남FC가즈아_225238224(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-09 03:48:59</t>
+          <t>2026-10-10 11:39:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1_0</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UNIT_863250723(1골)</t>
+          <t>여수가스_828231747(1골), 여수가스_861215732(1골), 경남FC가즈아_225238224(3골)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-09 02:36:22</t>
+          <t>2026-10-10 10:22:50</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>0_4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -825,61 +829,61 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>syma_867192629(1골), 용신_866200104(1골), 용신_804264453(1골)</t>
+          <t>셀래스틴_861005680(2골), 셀래스틴_863200458(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-09 02:26:03</t>
+          <t>2026-10-10 10:11:12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>syma_848192638(1골), syma_845224574(1골), 용신_101173731(2골), 용신_866200104(1골)</t>
+          <t>앙쿠_851194765(2골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-08 17:16:26</t>
+          <t>2026-10-10 10:00:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -889,93 +893,93 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UNIT_848180930(3골), UNIT_840192883(2골), Voor_858025420(1골), Voor_852233700(2골), Voor_845009676(1골)</t>
+          <t>앙쿠_861049369(1골), 앙쿠_851194765(1골), 셀래스틴_863233419(1골)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-08 17:00:32</t>
+          <t>2026-10-09 18:49:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Voor</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), UNIT_848180930(1골), Voor_845009676(1골)</t>
+          <t>앙쿠_861049369(1골), UNIT_848180930(4골), UNIT_867166676(1골)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-08 16:48:25</t>
+          <t>2026-10-09 18:38:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Voor</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0_2</t>
+          <t>6_4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Voor_845009676(2골)</t>
+          <t>앙쿠_861049369(2골), 앙쿠_848176580(3골), 앙쿠_866266039(1골), UNIT_848180930(1골), UNIT_867166676(3골)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-08 16:33:10</t>
+          <t>2026-10-09 18:28:19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -985,14 +989,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>검정소_868192181(4골), 검정소_100214100(1골), Voor_858025420(1골), Voor_861000027(1골), Voor_845009676(1골)</t>
+          <t>앙쿠_861049369(2골), 앙쿠_851194765(1골), 앙쿠_848176580(1골), UNIT_848180930(1골), UNIT_867166676(2골)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-08 16:21:30</t>
+          <t>2026-10-09 13:36:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1002,76 +1006,76 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>검정소_868192181(2골), Voor_845009676(2골), Voor_852233700(1골)</t>
+          <t>검정소_868192181(3골), 콩콩콩룔_866223710(3골)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-08 16:05:27</t>
+          <t>2026-10-09 13:33:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), UNIT_848180930(1골), 검정소_861214098(1골), 검정소_868192181(1골), 검정소_100214100(2골)</t>
+          <t>셀래스틴_852241461(2골)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-08 15:53:08</t>
+          <t>2026-10-09 13:25:18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>10_4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1081,83 +1085,83 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), UNIT_848180930(2골), 검정소_868192181(1골)</t>
+          <t>검정소_868192181(5골), 검정소_100214100(5골), 콩콩콩룔_866223710(1골), 콩콩콩룔_867223848(2골), 콩콩콩룔_848189505(1골)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-08 15:41:21</t>
+          <t>2026-10-09 13:23:55</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), 검정소_868192181(1골), 검정소_867241096(1골)</t>
+          <t>셀래스틴_863233419(2골), 셀래스틴_848194765(1골), syma_861000041(1골), syma_839191695(1골)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-08 14:34:46</t>
+          <t>2026-10-09 05:08:26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>호야국2인_846192505(1골), UNIT_848180930(1골), UNIT_867166676(2골)</t>
+          <t>ZD장인지참치_840191208(2골), ZD장인지참치_848199503(1골), ZD장인지참치_839200104(2골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-08 14:19:20</t>
+          <t>2026-10-09 04:53:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1167,29 +1171,29 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>3_6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), UNIT_867166676(1골), 셀래스틴_861005680(2골), 셀래스틴_848231866(1골)</t>
+          <t>ZD장인지참치_848199503(1골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골), 셀래스틴_861005680(1골), 셀래스틴_848230938(1골), 셀래스틴_863233419(1골), 셀래스틴_852241461(3골)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-08 14:05:46</t>
+          <t>2026-10-09 04:42:24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1199,7 +1203,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1_0</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1209,51 +1213,51 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(1골)</t>
+          <t>ZD장인지참치_839200104(2골), ZD장인지참치_840256630(2골), 셀래스틴_861005680(2골)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-08 13:50:45</t>
+          <t>2026-10-09 04:31:15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gucci차붐_840191208(3골), ZD장인지참치_861182521(1골), ZD장인지참치_840191208(1골), ZD장인지참치_839200104(1골)</t>
+          <t>ZD장인지참치_851240740(1골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골), 셀래스틴_852241461(2골), 셀래스틴_863233419(1골), 셀래스틴_863200458(1골)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-08 13:27:59</t>
+          <t>2026-10-09 04:19:11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1263,29 +1267,29 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3_6</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gucci차붐_853227659(1골), Gucci차붐_864084333(1골), Gucci차붐_864176403(1골), 셀래스틴_861005680(2골), 셀래스틴_848194765(2골), 셀래스틴_852241461(1골), 셀래스틴_863233419(1골)</t>
+          <t>ZD장인지참치_840191208(1골), ZD장인지참치_839200104(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-08 13:15:09</t>
+          <t>2026-10-09 04:04:37</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1295,7 +1299,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4_5</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1303,31 +1307,27 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Gucci차붐_864247686(1골), Gucci차붐_853272992(2골), Gucci차붐_853227659(1골), 셀래스틴_861005680(2골), 셀래스틴_845167680(1골), 셀래스틴_852241461(2골)</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-08 12:47:28</t>
+          <t>2026-10-09 03:48:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>1_0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1337,19 +1337,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(2골), 개포동덕배_856202126(1골), 개포동덕배_845208722(2골), Voor_861000027(1골)</t>
+          <t>UNIT_863250723(1골)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-08 12:46:17</t>
+          <t>2026-10-09 02:36:22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0_5</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1369,19 +1369,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>용신_877177003(1골), 용신_826251421(1골), 용신_866200104(3골)</t>
+          <t>syma_867192629(1골), 용신_866200104(1골), 용신_804264453(1골)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-08 12:33:33</t>
+          <t>2026-10-09 02:26:03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1391,39 +1391,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>셀래스틴_861005680(1골), 용신_826251421(1골)</t>
+          <t>syma_848192638(1골), syma_845224574(1골), 용신_101173731(2골), 용신_866200104(1골)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-08 12:27:12</t>
+          <t>2026-10-08 17:16:26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6_1</t>
+          <t>5_4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1433,125 +1433,125 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>개포동덕배_845208722(2골), 개포동덕배_845190048(3골), 개포동덕배_848206113(1골), 은안_856246420(1골)</t>
+          <t>UNIT_848180930(3골), UNIT_840192883(2골), Voor_858025420(1골), Voor_852233700(2골), Voor_845009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-08 12:25:05</t>
+          <t>2026-10-08 17:00:32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>경남FC가즈아_225238224(1골), syma_867192629(1골), syma_845224574(1골), syma_866235522(1골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(1골), Voor_845009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-08 12:16:35</t>
+          <t>2026-10-08 16:48:25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7_1</t>
+          <t>0_2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>개포동덕배_856202126(4골), 개포동덕배_848206113(1골), 개포동덕배_845190048(2골), 은안_866241236(1골)</t>
+          <t>Voor_845009676(2골)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-08 12:13:50</t>
+          <t>2026-10-08 16:33:10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>경남FC가즈아_277205156(1골), syma_867192629(1골)</t>
+          <t>검정소_868192181(4골), 검정소_100214100(1골), Voor_858025420(1골), Voor_861000027(1골), Voor_845009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-08 12:11:09</t>
+          <t>2026-10-08 16:21:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1561,29 +1561,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2골), ZD장인지참치_840191208(1골), ZD장인지참치_851240740(1골), ZD장인지참치_848199503(1골), ZD장인지참치_839200104(1골)</t>
+          <t>검정소_868192181(2골), Voor_845009676(2골), Voor_852233700(1골)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-08 11:59:25</t>
+          <t>2026-10-08 16:05:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1591,59 +1591,63 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), UNIT_848180930(1골), 검정소_861214098(1골), 검정소_868192181(1골), 검정소_100214100(2골)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-08 11:58:38</t>
+          <t>2026-10-08 15:53:08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_845246191(1골), ZD장인지참치_839200104(4골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(2골), 검정소_868192181(1골)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-08 11:26:36</t>
+          <t>2026-10-08 15:41:21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2_6</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1653,93 +1657,93 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>경남FC가즈아_225238224(1골), 경남FC가즈아_805267825(1골), 셀래스틴_861005680(5골), 셀래스틴_848230938(1골)</t>
+          <t>UNIT_848180930(2골), 검정소_868192181(1골), 검정소_867241096(1골)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-08 11:13:33</t>
+          <t>2026-10-08 14:34:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>경남FC가즈아_805267825(3골), 셀래스틴_863233419(1골), 셀래스틴_852241461(1골), 셀래스틴_848230938(1골)</t>
+          <t>호야국2인_846192505(1골), UNIT_848180930(1골), UNIT_867166676(2골)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-08 11:00:38</t>
+          <t>2026-10-08 14:19:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ZD장인지참치_839200104(4골), ZD장인지참치_840191208(1골), 용신_101173731(1골), 용신_863245367(1골)</t>
+          <t>UNIT_848180930(2골), UNIT_867166676(1골), 셀래스틴_861005680(2골), 셀래스틴_848231866(1골)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-08 10:49:29</t>
+          <t>2026-10-08 14:05:46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>1_0</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1749,61 +1753,61 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(1골), ZD장인지참치_840247263(1골), 용신_863245367(1골)</t>
+          <t>호야국2인_848232293(1골)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-07 14:25:42</t>
+          <t>2026-10-08 13:50:45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1골)</t>
+          <t>Gucci차붐_840191208(3골), ZD장인지참치_861182521(1골), ZD장인지참치_840191208(1골), ZD장인지참치_839200104(1골)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-07 14:14:55</t>
+          <t>2026-10-08 13:27:59</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1_4</t>
+          <t>3_6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1813,19 +1817,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1골), UNIT_863250723(1골), UNIT_848180930(1골), UNIT_840228251(1골), UNIT_867166676(1골)</t>
+          <t>Gucci차붐_853227659(1골), Gucci차붐_864084333(1골), Gucci차붐_864176403(1골), 셀래스틴_861005680(2골), 셀래스틴_848194765(2골), 셀래스틴_852241461(1골), 셀래스틴_863233419(1골)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-07 14:03:01</t>
+          <t>2026-10-08 13:15:09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1835,39 +1839,39 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1골), 앙쿠_848176580(1골), 앙쿠_863232488(1골), 셀래스틴_863233419(1골), 셀래스틴_848231866(1골)</t>
+          <t>Gucci차붐_864247686(1골), Gucci차붐_853272992(2골), Gucci차붐_853227659(1골), 셀래스틴_861005680(2골), 셀래스틴_845167680(1골), 셀래스틴_852241461(2골)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-07 13:51:44</t>
+          <t>2026-10-08 12:47:28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>6_2</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1877,120 +1881,120 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(3골), 앙쿠_851194765(2골), 앙쿠_848176580(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(1골)</t>
+          <t>개포동덕배_845190048(2골), 개포동덕배_856202126(1골), 개포동덕배_845208722(2골), Voor_861000027(1골)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-07 13:39:26</t>
+          <t>2026-10-08 12:46:17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>0_5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UNIT_867166676(3골), UNIT_848180930(1골), 셀래스틴_863233419(1골), 셀래스틴_861005680(1골)</t>
+          <t>용신_877177003(1골), 용신_826251421(1골), 용신_866200104(3골)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-07 13:28:13</t>
+          <t>2026-10-08 12:33:33</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>앙쿠_866266039(1골), 앙쿠_861049369(1골), UNIT_863250723(1골)</t>
+          <t>셀래스틴_861005680(1골), 용신_826251421(1골)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-07 13:16:19</t>
+          <t>2026-10-08 12:27:12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1골), 앙쿠_848176580(1골), 셀래스틴_861005680(2골), 셀래스틴_848231866(1골)</t>
+          <t>개포동덕배_845208722(2골), 개포동덕배_845190048(3골), 개포동덕배_848206113(1골), 은안_856246420(1골)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-07 13:05:29</t>
+          <t>2026-10-08 12:25:05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2005,78 +2009,78 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), 셀래스틴_861005680(2골), 셀래스틴_852241461(1골)</t>
+          <t>경남FC가즈아_225238224(1골), syma_867192629(1골), syma_845224574(1골), syma_866235522(1골)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-07 12:50:50</t>
+          <t>2026-10-08 12:16:35</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>7_1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1골), 앙쿠_851194765(1골), UNIT_867166676(2골), UNIT_848180930(3골)</t>
+          <t>개포동덕배_856202126(4골), 개포동덕배_848206113(1골), 개포동덕배_845190048(2골), 은안_866241236(1골)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-07 12:30:57</t>
+          <t>2026-10-08 12:13:50</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), ZD장인지참치_840191208(1골)</t>
+          <t>경남FC가즈아_277205156(1골), syma_867192629(1골)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-07 12:14:34</t>
+          <t>2026-10-08 12:11:09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2086,29 +2090,29 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3_0</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_866266039(1골), 앙쿠_861049369(1골)</t>
+          <t>앙쿠_848176580(2골), ZD장인지참치_840191208(1골), ZD장인지참치_851240740(1골), ZD장인지참치_848199503(1골), ZD장인지참치_839200104(1골)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-07 12:04:29</t>
+          <t>2026-10-08 11:59:25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2118,44 +2122,40 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>앙쿠_861049369(2골), 앙쿠_866266039(1골), 셀래스틴_852241461(1골)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-07 11:33:41</t>
+          <t>2026-10-08 11:58:38</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0_3</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2165,37 +2165,581 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>용신_825212188(3골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_845246191(1골), ZD장인지참치_839200104(4골)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>2026-10-08 11:26:36</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2_6</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_225238224(1골), 경남FC가즈아_805267825(1골), 셀래스틴_861005680(5골), 셀래스틴_848230938(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:13:33</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3_3</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_805267825(3골), 셀래스틴_863233419(1골), 셀래스틴_852241461(1골), 셀래스틴_848230938(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:00:38</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_839200104(4골), ZD장인지참치_840191208(1골), 용신_101173731(1골), 용신_863245367(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:49:29</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(1골), ZD장인지참치_840247263(1골), 용신_863245367(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:25:42</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1_0</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:14:55</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1_4</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(1골), UNIT_863250723(1골), UNIT_848180930(1골), UNIT_840228251(1골), UNIT_867166676(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:03:01</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(1골), 앙쿠_848176580(1골), 앙쿠_863232488(1골), 셀래스틴_863233419(1골), 셀래스틴_848231866(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:51:44</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>6_2</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(3골), 앙쿠_851194765(2골), 앙쿠_848176580(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:39:26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(3골), UNIT_848180930(1골), 셀래스틴_863233419(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:28:13</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>앙쿠_866266039(1골), 앙쿠_861049369(1골), UNIT_863250723(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:16:19</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(1골), 앙쿠_848176580(1골), 셀래스틴_861005680(2골), 셀래스틴_848231866(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:05:29</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(1골), 셀래스틴_861005680(2골), 셀래스틴_852241461(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:50:50</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2_5</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(1골), 앙쿠_851194765(1골), UNIT_867166676(2골), UNIT_848180930(3골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:30:57</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>UNIT_867166676(2골), ZD장인지참치_840191208(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:14:34</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3_0</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1골), 앙쿠_866266039(1골), 앙쿠_861049369(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:04:29</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(2골), 앙쿠_866266039(1골), 셀래스틴_852241461(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:33:41</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>0_3</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>용신_825212188(3골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>2026-10-07 11:21:15</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>겐지간지</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>용신</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>1_4</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>겐지간지_845158023(1골), 용신_866200104(1골), 용신_825212188(3골)</t>
         </is>
@@ -2212,7 +2756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2250,54 +2794,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:36:17</t>
+          <t>2026-10-10 15:15:02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>검정소_100214100(1도움), 검정소_861005003(2도움), 콩콩콩룔_848189505(1도움), 콩콩콩룔_867220502(2도움)</t>
+          <t>앙쿠_851194765(2도움), Voor_858020775(1도움), Voor_861000027(1도움)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09 13:33:58</t>
+          <t>2026-10-10 15:00:33</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2307,29 +2851,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>셀래스틴_861005680(1도움), 셀래스틴_848231866(1도움)</t>
+          <t>앙쿠_846193747(1도움), 앙쿠_861049369(2도움), Voor_835183277(1도움), Voor_845247090(1도움)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-09 13:25:18</t>
+          <t>2026-10-10 14:50:04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10_4</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2339,24 +2883,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>검정소_861005003(3도움), 검정소_868192181(2도움), 검정소_861214098(2도움), 검정소_851241721(1도움), 검정소_100214100(1도움), 콩콩콩룔_861006235(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_867223848(1도움)</t>
+          <t>앙쿠_848176580(1도움), 앙쿠_861049369(1도움), Voor_845009676(1도움)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-09 13:23:55</t>
+          <t>2026-10-10 13:38:29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2371,19 +2915,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>셀래스틴_848194765(1도움), 셀래스틴_852241461(1도움), 셀래스틴_848230938(1도움), syma_863251854(1도움), syma_866264388(1도움)</t>
+          <t>앙쿠_848176580(1도움), 앙쿠_851194765(1도움), 셀래스틴_848194765(1도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09 05:08:26</t>
+          <t>2026-10-10 13:28:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2393,29 +2937,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840256630(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_851240740(2도움), 셀래스틴_852241461(1도움)</t>
+          <t>앙쿠_861049369(2도움), 앙쿠_848176580(1도움), 셀래스틴_861005680(1도움), 셀래스틴_848194765(1도움), 셀래스틴_863200458(1도움)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-09 04:53:33</t>
+          <t>2026-10-10 13:17:07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2425,29 +2969,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3_6</t>
+          <t>6_2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ZD장인지참치_861182521(1도움), ZD장인지참치_840191208(1도움), ZD장인지참치_851240740(1도움), 셀래스틴_861005680(2도움), 셀래스틴_848231866(1도움), 셀래스틴_848194765(2도움), 셀래스틴_863200458(1도움)</t>
+          <t>앙쿠_851194765(4도움), 앙쿠_852232119(1도움), 앙쿠_814226161(1도움), 셀래스틴_863233419(1도움), 셀래스틴_863200458(1도움)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-09 04:42:24</t>
+          <t>2026-10-10 13:05:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2457,7 +3001,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2467,19 +3011,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_851240740(1도움), 셀래스틴_848013038(1도움), 셀래스틴_852259694(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_861049369(1도움), 앙쿠_846193747(1도움), 셀래스틴_848231866(1도움), 셀래스틴_863200458(1도움)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09 04:31:15</t>
+          <t>2026-10-10 12:53:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2489,7 +3033,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2499,19 +3043,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ZD장인지참치_848199503(1도움), ZD장인지참치_840191208(2도움), 셀래스틴_852241461(1도움), 셀래스틴_863233419(1도움), 셀래스틴_861005680(1도움), 셀래스틴_863200458(1도움)</t>
+          <t>앙쿠_861049369(1도움), 셀래스틴_863200458(1도움), 셀래스틴_848194765(1도움)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-09 04:19:11</t>
+          <t>2026-10-10 12:42:29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2521,99 +3065,103 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(1도움), ZD장인지참치_861182521(1도움), 셀래스틴_848231866(1도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_848176580(1도움), 셀래스틴_861005680(1도움), 셀래스틴_852259694(1도움)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-09 04:04:37</t>
+          <t>2026-10-10 11:51:07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>여수가스_861215732(1도움), 여수가스_828231747(1도움), 경남FC가즈아_805207730(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-09 03:48:59</t>
+          <t>2026-10-10 11:39:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1_0</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움)</t>
+          <t>여수가스_861162895(1도움), 경남FC가즈아_277205156(1도움), 경남FC가즈아_805207730(1도움)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-09 02:36:22</t>
+          <t>2026-10-10 10:22:50</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>0_4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2623,61 +3171,61 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>syma_845224574(1도움), 용신_826251421(2도움)</t>
+          <t>셀래스틴_861005680(1도움), 셀래스틴_848013038(1도움), 셀래스틴_863233419(1도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-09 02:26:03</t>
+          <t>2026-10-10 10:11:12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>syma_867192629(1도움), syma_851224415(1도움), 용신_877177003(1도움), 용신_101173731(1도움), 용신_826251421(1도움)</t>
+          <t>앙쿠_861049369(1도움), 셀래스틴_863200458(1도움)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-08 17:16:26</t>
+          <t>2026-10-10 10:00:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2687,93 +3235,93 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UNIT_840225782(1도움), UNIT_848265695(1도움), UNIT_863250723(1도움), UNIT_840228251(1도움), Voor_856256079(1도움), Voor_861045674(1도움), Voor_852233700(1도움), Voor_845009676(1도움)</t>
+          <t>앙쿠_861049369(1도움), 앙쿠_851194765(1도움)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-08 17:00:32</t>
+          <t>2026-10-09 18:49:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Voor</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UNIT_863250723(1도움), UNIT_840228251(1도움), Voor_852233700(1도움)</t>
+          <t>앙쿠_851194765(1도움), UNIT_840228251(1도움), UNIT_840192883(2도움), UNIT_840210736(1도움), UNIT_867166676(1도움)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-08 16:48:25</t>
+          <t>2026-10-09 18:38:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Voor</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0_2</t>
+          <t>6_4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Voor_852233700(1도움)</t>
+          <t>앙쿠_861049369(1도움), 앙쿠_846193747(1도움), 앙쿠_851194765(2도움), 앙쿠_848176580(1도움), UNIT_840192883(1도움), UNIT_840225782(1도움), UNIT_852053302(2도움)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-08 16:33:10</t>
+          <t>2026-10-09 18:28:19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2783,14 +3331,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>검정소_861005003(2도움), 검정소_851241721(1도움), 검정소_100214100(1도움), Voor_852233700(2도움)</t>
+          <t>앙쿠_861049369(1도움), 앙쿠_851194765(3도움), UNIT_840228251(2도움), UNIT_840210736(1도움)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-08 16:21:30</t>
+          <t>2026-10-09 13:36:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2800,76 +3348,76 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>검정소_861005003(2도움), Voor_861000027(1도움), Voor_845247090(1도움), Voor_852233700(1도움)</t>
+          <t>검정소_100214100(1도움), 검정소_861005003(2도움), 콩콩콩룔_848189505(1도움), 콩콩콩룔_867220502(2도움)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-08 16:05:27</t>
+          <t>2026-10-09 13:33:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UNIT_840192883(3도움), 검정소_867241096(1도움), 검정소_851247229(1도움), 검정소_861005003(1도움)</t>
+          <t>셀래스틴_861005680(1도움), 셀래스틴_848231866(1도움)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-08 15:53:08</t>
+          <t>2026-10-09 13:25:18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>10_4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2879,83 +3427,83 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UNIT_848265695(1도움), UNIT_867166676(1도움), 검정소_861214098(1도움)</t>
+          <t>검정소_861005003(3도움), 검정소_868192181(2도움), 검정소_861214098(2도움), 검정소_851241721(1도움), 검정소_100214100(1도움), 콩콩콩룔_861006235(1도움), 콩콩콩룔_867220502(1도움), 콩콩콩룔_867223848(1도움)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-08 15:41:21</t>
+          <t>2026-10-09 13:23:55</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1도움), UNIT_840228251(1도움), 검정소_861214098(1도움)</t>
+          <t>셀래스틴_848194765(1도움), 셀래스틴_852241461(1도움), 셀래스틴_848230938(1도움), syma_863251854(1도움), syma_866264388(1도움)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-08 14:34:46</t>
+          <t>2026-10-09 05:08:26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>호야국2인_848216435(1도움), UNIT_840225782(1도움), UNIT_840210736(1도움), UNIT_840192883(1도움)</t>
+          <t>ZD장인지참치_840256630(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_839200104(1도움), ZD장인지참치_851240740(2도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-08 14:19:20</t>
+          <t>2026-10-09 04:53:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2965,29 +3513,29 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>3_6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움), UNIT_840210736(1도움), UNIT_840192883(1도움), 셀래스틴_852259694(1도움), 셀래스틴_852241461(1도움), 셀래스틴_863200458(1도움)</t>
+          <t>ZD장인지참치_861182521(1도움), ZD장인지참치_840191208(1도움), ZD장인지참치_851240740(1도움), 셀래스틴_861005680(2도움), 셀래스틴_848231866(1도움), 셀래스틴_848194765(2도움), 셀래스틴_863200458(1도움)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-08 14:05:46</t>
+          <t>2026-10-09 04:42:24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2997,7 +3545,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1_0</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3007,51 +3555,51 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>호야국2인_848216435(1도움)</t>
+          <t>ZD장인지참치_839200104(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_851240740(1도움), 셀래스틴_848013038(1도움), 셀래스틴_852259694(1도움)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-08 13:50:45</t>
+          <t>2026-10-09 04:31:15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gucci차붐_867208128(2도움), Gucci차붐_877256630(1도움), ZD장인지참치_840191208(1도움), ZD장인지참치_851240740(1도움), ZD장인지참치_839200104(1도움)</t>
+          <t>ZD장인지참치_848199503(1도움), ZD장인지참치_840191208(2도움), 셀래스틴_852241461(1도움), 셀래스틴_863233419(1도움), 셀래스틴_861005680(1도움), 셀래스틴_863200458(1도움)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-08 13:27:59</t>
+          <t>2026-10-09 04:19:11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3061,29 +3609,29 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3_6</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gucci차붐_853227659(1도움), Gucci차붐_864247686(1도움), 셀래스틴_848230938(2도움), 셀래스틴_861005680(1도움), 셀래스틴_852241461(1도움), 셀래스틴_863233419(2도움)</t>
+          <t>ZD장인지참치_840191208(1도움), ZD장인지참치_861182521(1도움), 셀래스틴_848231866(1도움)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-08 13:15:09</t>
+          <t>2026-10-09 04:04:37</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3093,7 +3641,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4_5</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3101,31 +3649,27 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Gucci차붐_864176403(1도움), Gucci차붐_851221671(2도움), 셀래스틴_863200458(1도움), 셀래스틴_852259694(1도움), 셀래스틴_848194765(2도움), 셀래스틴_852241461(1도움)</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-08 12:47:28</t>
+          <t>2026-10-09 03:48:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>1_0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3135,19 +3679,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>개포동덕배_848206113(1도움), 개포동덕배_856202126(1도움), 개포동덕배_856212622(1도움), 개포동덕배_852225375(1도움), 개포동덕배_863234396(1도움)</t>
+          <t>UNIT_840192883(1도움)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-08 12:46:17</t>
+          <t>2026-10-09 02:36:22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3157,7 +3701,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0_5</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3167,19 +3711,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>용신_877177003(1도움), 용신_101173731(2도움), 용신_863245367(1도움), 용신_856243576(1도움)</t>
+          <t>syma_845224574(1도움), 용신_826251421(2도움)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-08 12:33:33</t>
+          <t>2026-10-09 02:26:03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3189,39 +3733,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>셀래스틴_863233419(1도움), 용신_101173731(1도움)</t>
+          <t>syma_867192629(1도움), syma_851224415(1도움), 용신_877177003(1도움), 용신_101173731(1도움), 용신_826251421(1도움)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-08 12:27:12</t>
+          <t>2026-10-08 17:16:26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6_1</t>
+          <t>5_4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3231,125 +3775,125 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>개포동덕배_845208722(2도움), 개포동덕배_856202126(4도움), 은안_866241236(1도움)</t>
+          <t>UNIT_840225782(1도움), UNIT_848265695(1도움), UNIT_863250723(1도움), UNIT_840228251(1도움), Voor_856256079(1도움), Voor_861045674(1도움), Voor_852233700(1도움), Voor_845009676(1도움)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-08 12:25:05</t>
+          <t>2026-10-08 17:00:32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>경남FC가즈아_518251161(1도움), syma_861001668(1도움), syma_867192629(1도움)</t>
+          <t>UNIT_863250723(1도움), UNIT_840228251(1도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-08 12:16:35</t>
+          <t>2026-10-08 16:48:25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7_1</t>
+          <t>0_2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>개포동덕배_845208722(3도움), 개포동덕배_856202126(1도움), 개포동덕배_845190048(1도움), 개포동덕배_856275298(2도움), 은안_877143001(1도움)</t>
+          <t>Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-08 12:13:50</t>
+          <t>2026-10-08 16:33:10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>경남FC가즈아_805267825(1도움), syma_861001668(1도움)</t>
+          <t>검정소_861005003(2도움), 검정소_851241721(1도움), 검정소_100214100(1도움), Voor_852233700(2도움)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-08 12:11:09</t>
+          <t>2026-10-08 16:21:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3359,29 +3903,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_845246191(1도움), ZD장인지참치_852213331(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_839200104(1도움)</t>
+          <t>검정소_861005003(2도움), Voor_861000027(1도움), Voor_845247090(1도움), Voor_852233700(1도움)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-08 11:59:25</t>
+          <t>2026-10-08 16:05:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3389,59 +3933,63 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(3도움), 검정소_867241096(1도움), 검정소_851247229(1도움), 검정소_861005003(1도움)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-08 11:58:38</t>
+          <t>2026-10-08 15:53:08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1도움), 앙쿠_851194765(1도움), ZD장인지참치_840191208(2도움), ZD장인지참치_861182521(1도움), ZD장인지참치_848199503(1도움)</t>
+          <t>UNIT_848265695(1도움), UNIT_867166676(1도움), 검정소_861214098(1도움)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-08 11:26:36</t>
+          <t>2026-10-08 15:41:21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2_6</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3451,93 +3999,93 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>경남FC가즈아_805207730(1도움), 경남FC가즈아_853221467(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852241461(3도움), 셀래스틴_852259694(1도움), 셀래스틴_848194765(1도움)</t>
+          <t>UNIT_840192883(1도움), UNIT_840228251(1도움), 검정소_861214098(1도움)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-08 11:13:33</t>
+          <t>2026-10-08 14:34:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>경남FC가즈아_225238224(1도움), 경남FC가즈아_853221467(2도움), 셀래스틴_861005680(1도움), 셀래스틴_848230938(1도움), 셀래스틴_848194765(1도움)</t>
+          <t>호야국2인_848216435(1도움), UNIT_840225782(1도움), UNIT_840210736(1도움), UNIT_840192883(1도움)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-08 11:00:38</t>
+          <t>2026-10-08 14:19:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ZD장인지참치_861182521(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_840191208(1도움), 용신_101173731(1도움)</t>
+          <t>UNIT_840228251(1도움), UNIT_840210736(1도움), UNIT_840192883(1도움), 셀래스틴_852259694(1도움), 셀래스틴_852241461(1도움), 셀래스틴_863200458(1도움)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-08 10:49:29</t>
+          <t>2026-10-08 14:05:46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>1_0</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3547,61 +4095,61 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ZD장인지참치_861182521(1도움), 용신_101173731(1도움)</t>
+          <t>호야국2인_848216435(1도움)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-07 14:25:42</t>
+          <t>2026-10-08 13:50:45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1_0</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UNIT_840228251(1도움)</t>
+          <t>Gucci차붐_867208128(2도움), Gucci차붐_877256630(1도움), ZD장인지참치_840191208(1도움), ZD장인지참치_851240740(1도움), ZD장인지참치_839200104(1도움)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-07 14:14:55</t>
+          <t>2026-10-08 13:27:59</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1_4</t>
+          <t>3_6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3611,19 +4159,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1도움), UNIT_840228251(1도움), UNIT_867166676(1도움)</t>
+          <t>Gucci차붐_853227659(1도움), Gucci차붐_864247686(1도움), 셀래스틴_848230938(2도움), 셀래스틴_861005680(1도움), 셀래스틴_852241461(1도움), 셀래스틴_863233419(2도움)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-07 14:03:01</t>
+          <t>2026-10-08 13:15:09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3633,39 +4181,39 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(2도움), 앙쿠_846186345(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>Gucci차붐_864176403(1도움), Gucci차붐_851221671(2도움), 셀래스틴_863200458(1도움), 셀래스틴_852259694(1도움), 셀래스틴_848194765(2도움), 셀래스틴_852241461(1도움)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-07 13:51:44</t>
+          <t>2026-10-08 12:47:28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>6_2</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3675,120 +4223,120 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1도움), 앙쿠_851194765(3도움), 앙쿠_848176580(1도움), 셀래스틴_852241461(1도움)</t>
+          <t>개포동덕배_848206113(1도움), 개포동덕배_856202126(1도움), 개포동덕배_856212622(1도움), 개포동덕배_852225375(1도움), 개포동덕배_863234396(1도움)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-07 13:39:26</t>
+          <t>2026-10-08 12:46:17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>0_5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UNIT_840192883(2도움), UNIT_840228251(1도움), UNIT_840210736(1도움)</t>
+          <t>용신_877177003(1도움), 용신_101173731(2도움), 용신_863245367(1도움), 용신_856243576(1도움)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-07 13:28:13</t>
+          <t>2026-10-08 12:33:33</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>앙쿠_846193747(1도움)</t>
+          <t>셀래스틴_863233419(1도움), 용신_101173731(1도움)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-07 13:16:19</t>
+          <t>2026-10-08 12:27:12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1도움), 앙쿠_861049369(1도움), 셀래스틴_852241461(2도움), 셀래스틴_863233419(1도움)</t>
+          <t>개포동덕배_845208722(2도움), 개포동덕배_856202126(4도움), 은안_866241236(1도움)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-07 13:05:29</t>
+          <t>2026-10-08 12:25:05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3803,78 +4351,78 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UNIT_840210736(1도움), 셀래스틴_852259694(1도움), 셀래스틴_848230938(1도움)</t>
+          <t>경남FC가즈아_518251161(1도움), syma_861001668(1도움), syma_867192629(1도움)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-07 12:50:50</t>
+          <t>2026-10-08 12:16:35</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>7_1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1도움), UNIT_840210736(2도움), UNIT_840192883(1도움), UNIT_863250723(1도움), UNIT_840228251(1도움)</t>
+          <t>개포동덕배_845208722(3도움), 개포동덕배_856202126(1도움), 개포동덕배_845190048(1도움), 개포동덕배_856275298(2도움), 은안_877143001(1도움)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-07 12:30:57</t>
+          <t>2026-10-08 12:13:50</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UNIT_840210736(1도움), ZD장인지참치_840256630(1도움)</t>
+          <t>경남FC가즈아_805267825(1도움), syma_861001668(1도움)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-07 12:14:34</t>
+          <t>2026-10-08 12:11:09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3884,29 +4432,29 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3_0</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>앙쿠_846186345(1도움), 앙쿠_851194765(2도움)</t>
+          <t>앙쿠_851194765(1도움), 앙쿠_845246191(1도움), ZD장인지참치_852213331(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_848199503(1도움), ZD장인지참치_839200104(1도움)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-07 12:04:29</t>
+          <t>2026-10-08 11:59:25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3916,44 +4464,40 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>승</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>앙쿠_846186345(1도움), 앙쿠_851194765(1도움), 앙쿠_848176580(1도움), 셀래스틴_863200458(1도움)</t>
-        </is>
-      </c>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-07 11:33:41</t>
+          <t>2026-10-08 11:58:38</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0_3</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3963,37 +4507,581 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>용신_101173731(1도움), 용신_866200104(1도움)</t>
+          <t>앙쿠_848176580(1도움), 앙쿠_851194765(1도움), ZD장인지참치_840191208(2도움), ZD장인지참치_861182521(1도움), ZD장인지참치_848199503(1도움)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>2026-10-08 11:26:36</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2_6</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_805207730(1도움), 경남FC가즈아_853221467(1도움), 셀래스틴_863200458(1도움), 셀래스틴_852241461(3도움), 셀래스틴_852259694(1도움), 셀래스틴_848194765(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:13:33</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3_3</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_225238224(1도움), 경남FC가즈아_853221467(2도움), 셀래스틴_861005680(1도움), 셀래스틴_848230938(1도움), 셀래스틴_848194765(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:00:38</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_861182521(2도움), ZD장인지참치_839200104(1도움), ZD장인지참치_840256630(1도움), ZD장인지참치_840191208(1도움), 용신_101173731(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:49:29</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_861182521(1도움), 용신_101173731(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:25:42</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1_0</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>UNIT_840228251(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:14:55</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1_4</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1도움), UNIT_840228251(1도움), UNIT_867166676(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:03:01</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(2도움), 앙쿠_846186345(1도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:51:44</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>6_2</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(1도움), 앙쿠_851194765(3도움), 앙쿠_848176580(1도움), 셀래스틴_852241461(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:39:26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(2도움), UNIT_840228251(1도움), UNIT_840210736(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:28:13</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>앙쿠_846193747(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:16:19</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>앙쿠_851194765(1도움), 앙쿠_861049369(1도움), 셀래스틴_852241461(2도움), 셀래스틴_863233419(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:05:29</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1_3</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>UNIT_840210736(1도움), 셀래스틴_852259694(1도움), 셀래스틴_848230938(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:50:50</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2_5</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1도움), UNIT_840210736(2도움), UNIT_840192883(1도움), UNIT_863250723(1도움), UNIT_840228251(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:30:57</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>UNIT_840210736(1도움), ZD장인지참치_840256630(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:14:34</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3_0</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>앙쿠_846186345(1도움), 앙쿠_851194765(2도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:04:29</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>3_1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>앙쿠_846186345(1도움), 앙쿠_851194765(1도움), 앙쿠_848176580(1도움), 셀래스틴_863200458(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:33:41</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>겐지간지</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>0_3</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>용신_101173731(1도움), 용신_866200104(1도움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>2026-10-07 11:21:15</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>겐지간지</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>용신</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>1_4</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>겐지간지_852231443(1도움), 용신_866200104(1도움), 용신_291213648(2도움)</t>
         </is>

--- a/API데이터_경기_득점_및_도움_기록.xlsx
+++ b/API데이터_경기_득점_및_도움_기록.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-10 15:15:02</t>
+          <t>2026-10-11 12:25:49</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -462,29 +462,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1골), 앙쿠_848176580(1골), Voor_835183277(1골), Voor_852001201(1골), Voor_845009676(1골)</t>
+          <t>앙쿠_861049369(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-10 15:00:33</t>
+          <t>2026-10-11 12:16:11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -494,29 +494,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>0_2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>앙쿠_866266039(1골), 앙쿠_848176580(2골), Voor_852233700(1골), Voor_856256079(1골)</t>
+          <t>셀래스틴_852241461(1골), 셀래스틴_863233419(1골)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-10 14:50:04</t>
+          <t>2026-10-11 12:05:40</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -526,34 +526,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1골), 앙쿠_851194765(1골), Voor_852233700(1골)</t>
+          <t>앙쿠_848176580(1골), 셀래스틴_861005680(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-10 13:38:29</t>
+          <t>2026-10-11 11:23:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -573,19 +573,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_851194765(2골), 셀래스틴_848194765(1골), 셀래스틴_861005680(1골)</t>
+          <t>여수가스_861215732(1골), 여수가스_846001551(1골), 셀래스틴_863233419(1골)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-10 13:28:04</t>
+          <t>2026-10-11 11:11:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>4_6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -605,29 +605,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1골), 앙쿠_848176580(1골), 앙쿠_851194765(1골), 셀래스틴_861005680(2골), 셀래스틴_852259694(1골), 셀래스틴_848231866(1골)</t>
+          <t>여수가스_846001551(1골), 여수가스_861215732(3골), 셀래스틴_852241461(3골), 셀래스틴_863233419(1골), 셀래스틴_861005680(2골)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-10 13:17:07</t>
+          <t>2026-10-11 10:48:32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -637,61 +637,61 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(3골), 앙쿠_851194765(1골), 앙쿠_861049369(2골), 셀래스틴_861005680(1골), 셀래스틴_852241461(1골)</t>
+          <t>ShangHaiPortFC_861051412(1골), ShangHaiPortFC_845231138(1골), ShangHaiPortFC_256164959(1골), 용신_866200104(2골)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-10 13:05:40</t>
+          <t>2026-10-11 10:08:39</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>2_6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 앙쿠_866266039(1골), 앙쿠_846193747(1골), 셀래스틴_861005680(2골)</t>
+          <t>ShangHaiPortFC_848031432(2골), 용신_863245367(1골), 용신_866200104(1골), 용신_826251421(2골), 용신_101173731(2골)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-10 12:53:40</t>
+          <t>2026-10-11 08:45:05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -701,93 +701,93 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(1골), 셀래스틴_863233419(1골), 셀래스틴_852241461(1골)</t>
+          <t>A지냐크_863241496(1골), ShangHaiPortFC_848031432(3골), ShangHaiPortFC_864191910(2골)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-10 12:42:29</t>
+          <t>2026-10-11 08:33:57</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ShangHaiPortFC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>앙쿠_814226161(1골), 앙쿠_851194765(1골), 셀래스틴_863233419(1골), 셀래스틴_848194765(1골)</t>
+          <t>A지냐크_834271400(3골), A지냐크_877031432(3골), A지냐크_863241496(1골), ShangHaiPortFC_848031432(2골)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-10 11:51:07</t>
+          <t>2026-10-11 07:59:52</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>여수가스_861162895(1골), 여수가스_861215732(1골), 경남FC가즈아_225238224(1골)</t>
+          <t>A지냐크_861167134(2골), 셀래스틴_861005680(1골), 셀래스틴_863233419(2골)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-10 11:39:57</t>
+          <t>2026-10-11 07:47:05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>여수가스</t>
+          <t>A지냐크</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -797,19 +797,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>여수가스_828231747(1골), 여수가스_861215732(1골), 경남FC가즈아_225238224(3골)</t>
+          <t>A지냐크_877031432(1골), A지냐크_861167134(1골), 셀래스틴_863233419(1골), 셀래스틴_861005680(2골), 셀래스틴_852241461(2골)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-10 10:22:50</t>
+          <t>2026-10-11 07:11:18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -819,29 +819,29 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0_4</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>셀래스틴_861005680(2골), 셀래스틴_863200458(1골), 셀래스틴_852241461(1골)</t>
+          <t>UNIT_848180930(1골), UNIT_840192883(1골), 셀래스틴_863233419(1골)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-10 10:11:12</t>
+          <t>2026-10-11 06:57:48</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -861,19 +861,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>앙쿠_851194765(2골), 셀래스틴_852241461(1골)</t>
+          <t>UNIT_848180930(1골), UNIT_867166676(2골), UNIT_840192883(1골), 셀래스틴_861005680(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-10 10:00:32</t>
+          <t>2026-10-11 06:46:50</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -883,39 +883,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1골), 앙쿠_851194765(1골), 셀래스틴_863233419(1골)</t>
+          <t>UNIT_867166676(3골), 셀래스틴_863233419(1골), 셀래스틴_852241461(1골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-09 18:49:33</t>
+          <t>2026-10-11 06:09:42</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1_5</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -925,29 +925,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1골), UNIT_848180930(4골), UNIT_867166676(1골)</t>
+          <t>은안_877143001(1골), 검정소_868013128(1골), 검정소_868192181(3골)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-09 18:38:57</t>
+          <t>2026-10-11 05:58:09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6_4</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -957,29 +957,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(2골), 앙쿠_848176580(3골), 앙쿠_866266039(1골), UNIT_848180930(1골), UNIT_867166676(3골)</t>
+          <t>은안_866241236(2골), 은안_877143001(2골), 검정소_868192181(2골)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-09 18:28:19</t>
+          <t>2026-10-11 05:44:51</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4_3</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -989,61 +989,61 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(2골), 앙쿠_851194765(1골), 앙쿠_848176580(1골), UNIT_848180930(1골), UNIT_867166676(2골)</t>
+          <t>UNIT_867166676(1골), 셀래스틴_863233419(1골)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-09 13:36:17</t>
+          <t>2026-10-11 05:30:27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>검정소_868192181(3골), 콩콩콩룔_866223710(3골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(1골), 셀래스틴_848231866(1골), 셀래스틴_861005680(2골)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-09 13:33:58</t>
+          <t>2026-10-11 04:22:54</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2_0</t>
+          <t>2_None</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1053,61 +1053,61 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>셀래스틴_852241461(2골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(1골)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-09 13:25:18</t>
+          <t>2026-10-11 04:11:42</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>콩콩콩룔</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>검정소_868192181(5골), 검정소_100214100(5골), 콩콩콩룔_866223710(1골), 콩콩콩룔_867223848(2골), 콩콩콩룔_848189505(1골)</t>
+          <t>UNIT_848180930(1골), UNIT_867166676(1골), 셀래스틴_861005680(2골), 셀래스틴_848194765(1골)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-09 13:23:55</t>
+          <t>2026-10-11 04:01:22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>4_0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1117,19 +1117,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>셀래스틴_863233419(2골), 셀래스틴_848194765(1골), syma_861000041(1골), syma_839191695(1골)</t>
+          <t>UNIT_867166676(2골), UNIT_848180930(2골)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-09 05:08:26</t>
+          <t>2026-10-11 03:49:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>4_1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1149,29 +1149,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(2골), ZD장인지참치_848199503(1골), ZD장인지참치_839200104(2골), 셀래스틴_861005680(1골)</t>
+          <t>UNIT_840228251(1골), UNIT_852053302(1골), UNIT_867166676(2골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-09 04:53:33</t>
+          <t>2026-10-10 15:15:02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3_6</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1181,29 +1181,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ZD장인지참치_848199503(1골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골), 셀래스틴_861005680(1골), 셀래스틴_848230938(1골), 셀래스틴_863233419(1골), 셀래스틴_852241461(3골)</t>
+          <t>앙쿠_861049369(1골), 앙쿠_848176580(1골), Voor_852001201(1골), Voor_835183277(1골), Voor_845009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-09 04:42:24</t>
+          <t>2026-10-10 15:00:33</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1213,51 +1213,51 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ZD장인지참치_839200104(2골), ZD장인지참치_840256630(2골), 셀래스틴_861005680(2골)</t>
+          <t>앙쿠_866266039(1골), 앙쿠_848176580(2골), Voor_856256079(1골), Voor_852233700(1골)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-09 04:31:15</t>
+          <t>2026-10-10 14:50:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ZD장인지참치_851240740(1골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골), 셀래스틴_852241461(2골), 셀래스틴_863233419(1골), 셀래스틴_863200458(1골)</t>
+          <t>앙쿠_861049369(1골), 앙쿠_851194765(1골), Voor_852233700(1골)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-09 04:19:11</t>
+          <t>2026-10-10 13:38:29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1277,19 +1277,19 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(1골), ZD장인지참치_839200104(1골), 셀래스틴_852241461(1골)</t>
+          <t>앙쿠_848176580(1골), 앙쿠_851194765(2골), 셀래스틴_848194765(1골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-09 04:04:37</t>
+          <t>2026-10-10 13:28:04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1307,17 +1307,21 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(1골), 앙쿠_848176580(1골), 앙쿠_851194765(1골), 셀래스틴_861005680(2골), 셀래스틴_852259694(1골), 셀래스틴_848231866(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-09 03:48:59</t>
+          <t>2026-10-10 13:17:07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1327,7 +1331,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1_0</t>
+          <t>6_2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1337,61 +1341,61 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UNIT_863250723(1골)</t>
+          <t>앙쿠_848176580(3골), 앙쿠_851194765(1골), 앙쿠_861049369(2골), 셀래스틴_861005680(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-09 02:36:22</t>
+          <t>2026-10-10 13:05:40</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1_2</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>syma_867192629(1골), 용신_866200104(1골), 용신_804264453(1골)</t>
+          <t>앙쿠_851194765(1골), 앙쿠_866266039(1골), 앙쿠_846193747(1골), 셀래스틴_861005680(2골)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-09 02:26:03</t>
+          <t>2026-10-10 12:53:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1401,56 +1405,56 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>syma_848192638(1골), syma_845224574(1골), 용신_101173731(2골), 용신_866200104(1골)</t>
+          <t>앙쿠_851194765(1골), 셀래스틴_863233419(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-08 17:16:26</t>
+          <t>2026-10-10 12:42:29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5_4</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UNIT_848180930(3골), UNIT_840192883(2골), Voor_858025420(1골), Voor_852233700(2골), Voor_845009676(1골)</t>
+          <t>앙쿠_814226161(1골), 앙쿠_851194765(1골), 셀래스틴_863233419(1골), 셀래스틴_848194765(1골)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-08 17:00:32</t>
+          <t>2026-10-10 11:51:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1465,29 +1469,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), UNIT_848180930(1골), Voor_845009676(1골)</t>
+          <t>여수가스_861162895(1골), 여수가스_861215732(1골), 경남FC가즈아_225238224(1골)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-08 16:48:25</t>
+          <t>2026-10-10 11:39:57</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>여수가스</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1497,179 +1501,179 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Voor_845009676(2골)</t>
+          <t>여수가스_828231747(1골), 여수가스_861215732(1골), 경남FC가즈아_225238224(3골)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-08 16:33:10</t>
+          <t>2026-10-10 10:22:50</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5_3</t>
+          <t>0_4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>검정소_868192181(4골), 검정소_100214100(1골), Voor_858025420(1골), Voor_861000027(1골), Voor_845009676(1골)</t>
+          <t>셀래스틴_861005680(2골), 셀래스틴_863200458(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-08 16:21:30</t>
+          <t>2026-10-10 10:11:12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>검정소_868192181(2골), Voor_845009676(2골), Voor_852233700(1골)</t>
+          <t>앙쿠_851194765(2골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-08 16:05:27</t>
+          <t>2026-10-10 10:00:32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>검정소</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3_4</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), UNIT_848180930(1골), 검정소_861214098(1골), 검정소_868192181(1골), 검정소_100214100(2골)</t>
+          <t>앙쿠_861049369(1골), 앙쿠_851194765(1골), 셀래스틴_863233419(1골)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-08 15:53:08</t>
+          <t>2026-10-09 18:49:33</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>검정소</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>1_5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), UNIT_848180930(2골), 검정소_868192181(1골)</t>
+          <t>앙쿠_861049369(1골), UNIT_848180930(4골), UNIT_867166676(1골)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-08 15:41:21</t>
+          <t>2026-10-09 18:38:57</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>검정소</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2_2</t>
+          <t>6_4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), 검정소_868192181(1골), 검정소_867241096(1골)</t>
+          <t>앙쿠_861049369(2골), 앙쿠_848176580(3골), 앙쿠_866266039(1골), UNIT_848180930(1골), UNIT_867166676(3골)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-08 14:34:46</t>
+          <t>2026-10-09 18:28:19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>앙쿠</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1679,34 +1683,34 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>호야국2인_846192505(1골), UNIT_848180930(1골), UNIT_867166676(2골)</t>
+          <t>앙쿠_861049369(2골), 앙쿠_851194765(1골), 앙쿠_848176580(1골), UNIT_848180930(1골), UNIT_867166676(2골)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-08 14:19:20</t>
+          <t>2026-10-09 13:36:17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1721,29 +1725,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UNIT_848180930(2골), UNIT_867166676(1골), 셀래스틴_861005680(2골), 셀래스틴_848231866(1골)</t>
+          <t>검정소_868192181(3골), 콩콩콩룔_866223710(3골)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-08 14:05:46</t>
+          <t>2026-10-09 13:33:58</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>호야국2인</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1_0</t>
+          <t>2_0</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1753,83 +1757,83 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>호야국2인_848232293(1골)</t>
+          <t>셀래스틴_852241461(2골)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-08 13:50:45</t>
+          <t>2026-10-09 13:25:18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>콩콩콩룔</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>10_4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gucci차붐_840191208(3골), ZD장인지참치_861182521(1골), ZD장인지참치_840191208(1골), ZD장인지참치_839200104(1골)</t>
+          <t>검정소_868192181(5골), 검정소_100214100(5골), 콩콩콩룔_866223710(1골), 콩콩콩룔_867223848(2골), 콩콩콩룔_848189505(1골)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-08 13:27:59</t>
+          <t>2026-10-09 13:23:55</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3_6</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gucci차붐_853227659(1골), Gucci차붐_864084333(1골), Gucci차붐_864176403(1골), 셀래스틴_861005680(2골), 셀래스틴_848194765(2골), 셀래스틴_852241461(1골), 셀래스틴_863233419(1골)</t>
+          <t>셀래스틴_863233419(2골), 셀래스틴_848194765(1골), syma_861000041(1골), syma_839191695(1골)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-08 13:15:09</t>
+          <t>2026-10-09 05:08:26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gucci차붐</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1839,135 +1843,135 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4_5</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gucci차붐_864247686(1골), Gucci차붐_853272992(2골), Gucci차붐_853227659(1골), 셀래스틴_861005680(2골), 셀래스틴_845167680(1골), 셀래스틴_852241461(2골)</t>
+          <t>ZD장인지참치_840191208(2골), ZD장인지참치_848199503(1골), ZD장인지참치_839200104(2골), 셀래스틴_861005680(1골)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-08 12:47:28</t>
+          <t>2026-10-09 04:53:33</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Voor</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5_1</t>
+          <t>3_6</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>개포동덕배_845190048(2골), 개포동덕배_856202126(1골), 개포동덕배_845208722(2골), Voor_861000027(1골)</t>
+          <t>ZD장인지참치_848199503(1골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골), 셀래스틴_861005680(1골), 셀래스틴_848230938(1골), 셀래스틴_863233419(1골), 셀래스틴_852241461(3골)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-08 12:46:17</t>
+          <t>2026-10-09 04:42:24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0_5</t>
+          <t>4_2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>용신_877177003(1골), 용신_826251421(1골), 용신_866200104(3골)</t>
+          <t>ZD장인지참치_839200104(2골), ZD장인지참치_840256630(2골), 셀래스틴_861005680(2골)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-08 12:33:33</t>
+          <t>2026-10-09 04:31:15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>셀래스틴_861005680(1골), 용신_826251421(1골)</t>
+          <t>ZD장인지참치_851240740(1골), ZD장인지참치_839200104(1골), ZD장인지참치_840191208(1골), 셀래스틴_852241461(2골), 셀래스틴_863233419(1골), 셀래스틴_863200458(1골)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-08 12:27:12</t>
+          <t>2026-10-09 04:19:11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>6_1</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1977,29 +1981,29 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>개포동덕배_845208722(2골), 개포동덕배_845190048(3골), 개포동덕배_848206113(1골), 은안_856246420(1골)</t>
+          <t>ZD장인지참치_840191208(1골), ZD장인지참치_839200104(1골), 셀래스틴_852241461(1골)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-08 12:25:05</t>
+          <t>2026-10-09 04:04:37</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>0_0</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2007,31 +2011,27 @@
           <t>패</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>경남FC가즈아_225238224(1골), syma_867192629(1골), syma_845224574(1골), syma_866235522(1골)</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-08 12:16:35</t>
+          <t>2026-10-09 03:48:59</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>개포동덕배</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>은안</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7_1</t>
+          <t>1_0</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2041,61 +2041,61 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>개포동덕배_856202126(4골), 개포동덕배_848206113(1골), 개포동덕배_845190048(2골), 은안_866241236(1골)</t>
+          <t>UNIT_863250723(1골)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-08 12:13:50</t>
+          <t>2026-10-09 02:36:22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>syma</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1_1</t>
+          <t>1_2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>경남FC가즈아_277205156(1골), syma_867192629(1골)</t>
+          <t>syma_867192629(1골), 용신_866200104(1골), 용신_804264453(1골)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-08 12:11:09</t>
+          <t>2026-10-09 02:26:03</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2105,89 +2105,93 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(2골), ZD장인지참치_840191208(1골), ZD장인지참치_851240740(1골), ZD장인지참치_848199503(1골), ZD장인지참치_839200104(1골)</t>
+          <t>syma_848192638(1골), syma_845224574(1골), 용신_101173731(2골), 용신_866200104(1골)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-08 11:59:25</t>
+          <t>2026-10-08 17:16:26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0_0</t>
+          <t>5_4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>패</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>UNIT_848180930(3골), UNIT_840192883(2골), Voor_858025420(1골), Voor_852233700(2골), Voor_845009676(1골)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-08 11:58:38</t>
+          <t>2026-10-08 17:00:32</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2_4</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_845246191(1골), ZD장인지참치_839200104(4골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(1골), Voor_845009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-08 11:26:36</t>
+          <t>2026-10-08 16:48:25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2_6</t>
+          <t>0_2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2197,110 +2201,110 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>경남FC가즈아_225238224(1골), 경남FC가즈아_805267825(1골), 셀래스틴_861005680(5골), 셀래스틴_848230938(1골)</t>
+          <t>Voor_845009676(2골)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-08 11:13:33</t>
+          <t>2026-10-08 16:33:10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>경남FC가즈아</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3_3</t>
+          <t>5_3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>경남FC가즈아_805267825(3골), 셀래스틴_863233419(1골), 셀래스틴_852241461(1골), 셀래스틴_848230938(1골)</t>
+          <t>검정소_868192181(4골), 검정소_100214100(1골), Voor_858025420(1골), Voor_861000027(1골), Voor_845009676(1골)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-08 11:00:38</t>
+          <t>2026-10-08 16:21:30</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5_2</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ZD장인지참치_839200104(4골), ZD장인지참치_840191208(1골), 용신_101173731(1골), 용신_863245367(1골)</t>
+          <t>검정소_868192181(2골), Voor_845009676(2골), Voor_852233700(1골)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-08 10:49:29</t>
+          <t>2026-10-08 16:05:27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>3_4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ZD장인지참치_840191208(1골), ZD장인지참치_840247263(1골), 용신_863245367(1골)</t>
+          <t>UNIT_867166676(2골), UNIT_848180930(1골), 검정소_861214098(1골), 검정소_868192181(1골), 검정소_100214100(2골)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-07 14:25:42</t>
+          <t>2026-10-08 15:53:08</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2310,12 +2314,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1_0</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2325,29 +2329,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>UNIT_840192883(1골)</t>
+          <t>UNIT_867166676(1골), UNIT_848180930(2골), 검정소_868192181(1골)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-07 14:14:55</t>
+          <t>2026-10-08 15:41:21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>검정소</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1_4</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2357,51 +2361,51 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1골), UNIT_863250723(1골), UNIT_848180930(1골), UNIT_840228251(1골), UNIT_867166676(1골)</t>
+          <t>UNIT_848180930(2골), 검정소_868192181(1골), 검정소_867241096(1골)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-07 14:03:01</t>
+          <t>2026-10-08 14:34:46</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3_2</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1골), 앙쿠_848176580(1골), 앙쿠_863232488(1골), 셀래스틴_863233419(1골), 셀래스틴_848231866(1골)</t>
+          <t>호야국2인_846192505(1골), UNIT_848180930(1골), UNIT_867166676(2골)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-07 13:51:44</t>
+          <t>2026-10-08 14:19:20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2411,29 +2415,29 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>6_2</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(3골), 앙쿠_851194765(2골), 앙쿠_848176580(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(1골)</t>
+          <t>UNIT_848180930(2골), UNIT_867166676(1골), 셀래스틴_861005680(2골), 셀래스틴_848231866(1골)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-07 13:39:26</t>
+          <t>2026-10-08 14:05:46</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>호야국2인</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2443,7 +2447,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>4_2</t>
+          <t>1_0</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2453,51 +2457,51 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>UNIT_867166676(3골), UNIT_848180930(1골), 셀래스틴_863233419(1골), 셀래스틴_861005680(1골)</t>
+          <t>호야국2인_848232293(1골)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-07 13:28:13</t>
+          <t>2026-10-08 13:50:45</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>ZD장인지참치</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>3_3</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>앙쿠_866266039(1골), 앙쿠_861049369(1골), UNIT_863250723(1골)</t>
+          <t>Gucci차붐_840191208(3골), ZD장인지참치_861182521(1골), ZD장인지참치_840191208(1골), ZD장인지참치_839200104(1골)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-07 13:16:19</t>
+          <t>2026-10-08 13:27:59</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2507,7 +2511,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2_3</t>
+          <t>3_6</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2517,19 +2521,19 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1골), 앙쿠_848176580(1골), 셀래스틴_861005680(2골), 셀래스틴_848231866(1골)</t>
+          <t>Gucci차붐_853227659(1골), Gucci차붐_864084333(1골), Gucci차붐_864176403(1골), 셀래스틴_861005680(2골), 셀래스틴_848194765(2골), 셀래스틴_852241461(1골), 셀래스틴_863233419(1골)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-07 13:05:29</t>
+          <t>2026-10-08 13:15:09</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Gucci차붐</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2539,7 +2543,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1_3</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2549,125 +2553,125 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>UNIT_867166676(1골), 셀래스틴_861005680(2골), 셀래스틴_852241461(1골)</t>
+          <t>Gucci차붐_864247686(1골), Gucci차붐_853272992(2골), Gucci차붐_853227659(1골), 셀래스틴_861005680(2골), 셀래스틴_845167680(1골), 셀래스틴_852241461(2골)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-07 12:50:50</t>
+          <t>2026-10-08 12:47:28</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>Voor</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2_5</t>
+          <t>5_1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>패</t>
+          <t>승</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(1골), 앙쿠_851194765(1골), UNIT_867166676(2골), UNIT_848180930(3골)</t>
+          <t>개포동덕배_845190048(2골), 개포동덕배_856202126(1골), 개포동덕배_845208722(2골), Voor_861000027(1골)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-07 12:30:57</t>
+          <t>2026-10-08 12:46:17</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ZD장인지참치</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2_1</t>
+          <t>0_5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>패</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UNIT_867166676(2골), ZD장인지참치_840191208(1골)</t>
+          <t>용신_877177003(1골), 용신_826251421(1골), 용신_866200104(3골)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-07 12:14:34</t>
+          <t>2026-10-08 12:33:33</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>셀래스틴</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>용신</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3_0</t>
+          <t>1_1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>승</t>
+          <t>무</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>앙쿠_848176580(1골), 앙쿠_866266039(1골), 앙쿠_861049369(1골)</t>
+          <t>셀래스틴_861005680(1골), 용신_826251421(1골)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-07 12:04:29</t>
+          <t>2026-10-08 12:27:12</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>앙쿠</t>
+          <t>개포동덕배</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>셀래스틴</t>
+          <t>은안</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3_1</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2677,29 +2681,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>앙쿠_861049369(2골), 앙쿠_866266039(1골), 셀래스틴_852241461(1골)</t>
+          <t>개포동덕배_845208722(2골), 개포동덕배_845190048(3골), 개포동덕배_848206113(1골), 은안_856246420(1골)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-07 11:33:41</t>
+          <t>2026-10-08 12:25:05</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>겐지간지</t>
+          <t>경남FC가즈아</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>용신</t>
+          <t>syma</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0_3</t>
+          <t>1_3</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2709,37 +2713,737 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>용신_825212188(3골)</t>
+          <t>경남FC가즈아_225238224(1골), syma_867192629(1골), syma_845224574(1골), syma_866235522(1골)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>2026-10-08 12:16:35</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>개포동덕배</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>은안</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>7_1</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>개포동덕배_856202126(4골), 개포동덕배_848206113(1골), 개포동덕배_845190048(2골), 은안_866241236(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:13:50</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>syma</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1_1</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_277205156(1골), syma_867192629(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:11:09</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(2골), ZD장인지참치_840191208(1골), ZD장인지참치_851240740(1골), ZD장인지참치_848199503(1골), ZD장인지참치_839200104(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:59:25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>0_0</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:58:38</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>앙쿠_848176580(1골), 앙쿠_845246191(1골), ZD장인지참치_839200104(4골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:26:36</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2_6</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_225238224(1골), 경남FC가즈아_805267825(1골), 셀래스틴_861005680(5골), 셀래스틴_848230938(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:13:33</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>경남FC가즈아</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>3_3</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>경남FC가즈아_805267825(3골), 셀래스틴_863233419(1골), 셀래스틴_852241461(1골), 셀래스틴_848230938(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:00:38</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_839200104(4골), ZD장인지참치_840191208(1골), 용신_101173731(1골), 용신_863245367(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:49:29</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ZD장인지참치</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>용신</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2_1</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>ZD장인지참치_840191208(1골), ZD장인지참치_840247263(1골), 용신_863245367(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:25:42</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1_0</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>UNIT_840192883(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:14:55</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1_4</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>패</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(1골), UNIT_863250723(1골), UNIT_848180930(1골), UNIT_840228251(1골), UNIT_867166676(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:03:01</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(1골), 앙쿠_848176580(1골), 앙쿠_863232488(1골), 셀래스틴_863233419(1골), 셀래스틴_848231866(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:51:44</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>앙쿠</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>셀래스틴</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>6_2</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>승</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>앙쿠_861049369(3골), 앙쿠_851194765(2골), 앙쿠_848176580(1골), 셀래스틴_848194765(1골), 셀래스틴_861005680(1골)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:39:26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"